--- a/Birthday Data Master.xlsx
+++ b/Birthday Data Master.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F594"/>
+  <dimension ref="A1:F616"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.6" customWidth="1" min="1" max="1"/>
@@ -19432,6 +19432,710 @@
         </is>
       </c>
     </row>
+    <row r="595">
+      <c r="A595" t="inlineStr">
+        <is>
+          <t>02,Feb</t>
+        </is>
+      </c>
+      <c r="B595" t="inlineStr">
+        <is>
+          <t>VAISHNAVI KUMARI</t>
+        </is>
+      </c>
+      <c r="C595" t="inlineStr">
+        <is>
+          <t>RAJESH KUMAR</t>
+        </is>
+      </c>
+      <c r="D595" t="inlineStr">
+        <is>
+          <t>KAVITA KUMARI</t>
+        </is>
+      </c>
+      <c r="E595" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F595" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" t="inlineStr">
+        <is>
+          <t>02,Feb</t>
+        </is>
+      </c>
+      <c r="B596" t="inlineStr">
+        <is>
+          <t>ARADHYA KUMARI</t>
+        </is>
+      </c>
+      <c r="C596" t="inlineStr">
+        <is>
+          <t>ABHAY KUMAR</t>
+        </is>
+      </c>
+      <c r="D596" t="inlineStr">
+        <is>
+          <t>Kumari SONAM</t>
+        </is>
+      </c>
+      <c r="E596" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="F596" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" t="inlineStr">
+        <is>
+          <t>02,Feb</t>
+        </is>
+      </c>
+      <c r="B597" t="inlineStr">
+        <is>
+          <t>SHIVAM RAJ</t>
+        </is>
+      </c>
+      <c r="C597" t="inlineStr">
+        <is>
+          <t>VINAY SINGH</t>
+        </is>
+      </c>
+      <c r="D597" t="inlineStr">
+        <is>
+          <t>SUBI DEVI</t>
+        </is>
+      </c>
+      <c r="E597" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="F597" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" t="inlineStr">
+        <is>
+          <t>02,Feb</t>
+        </is>
+      </c>
+      <c r="B598" t="inlineStr">
+        <is>
+          <t>SAKSHI  KUMARI</t>
+        </is>
+      </c>
+      <c r="C598" t="inlineStr">
+        <is>
+          <t>KUMAR SAURABH SINGH</t>
+        </is>
+      </c>
+      <c r="D598" t="inlineStr">
+        <is>
+          <t>JYOTI SINGH</t>
+        </is>
+      </c>
+      <c r="E598" t="inlineStr">
+        <is>
+          <t>VIII</t>
+        </is>
+      </c>
+      <c r="F598" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" t="inlineStr">
+        <is>
+          <t>02,Feb</t>
+        </is>
+      </c>
+      <c r="B599" t="inlineStr">
+        <is>
+          <t>SHREYA KUMARI</t>
+        </is>
+      </c>
+      <c r="C599" t="inlineStr">
+        <is>
+          <t>BABLU KUMAR SHARMA</t>
+        </is>
+      </c>
+      <c r="D599" t="inlineStr">
+        <is>
+          <t>RAULI DEVI</t>
+        </is>
+      </c>
+      <c r="E599" t="inlineStr">
+        <is>
+          <t>XI</t>
+        </is>
+      </c>
+      <c r="F599" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" t="inlineStr">
+        <is>
+          <t>02,Feb</t>
+        </is>
+      </c>
+      <c r="B600" t="inlineStr">
+        <is>
+          <t>Ayush  Narayan</t>
+        </is>
+      </c>
+      <c r="C600" t="inlineStr">
+        <is>
+          <t>Abhiram Pankaj</t>
+        </is>
+      </c>
+      <c r="D600" t="inlineStr">
+        <is>
+          <t>Kumari Sweety</t>
+        </is>
+      </c>
+      <c r="E600" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F600" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" t="inlineStr">
+        <is>
+          <t>02,Feb</t>
+        </is>
+      </c>
+      <c r="B601" t="inlineStr">
+        <is>
+          <t>VIRAJ  BHARDWAJ</t>
+        </is>
+      </c>
+      <c r="C601" t="inlineStr">
+        <is>
+          <t>MITHILESH MISHRA</t>
+        </is>
+      </c>
+      <c r="D601" t="inlineStr">
+        <is>
+          <t>JAYA BHARTI</t>
+        </is>
+      </c>
+      <c r="E601" t="inlineStr">
+        <is>
+          <t>IV</t>
+        </is>
+      </c>
+      <c r="F601" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" t="inlineStr">
+        <is>
+          <t>02,Feb</t>
+        </is>
+      </c>
+      <c r="B602" t="inlineStr">
+        <is>
+          <t>Aarohi Kumari</t>
+        </is>
+      </c>
+      <c r="C602" t="inlineStr">
+        <is>
+          <t>Rajan Kumar</t>
+        </is>
+      </c>
+      <c r="D602" t="inlineStr">
+        <is>
+          <t>Sapna Kumari</t>
+        </is>
+      </c>
+      <c r="E602" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="F602" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" t="inlineStr">
+        <is>
+          <t>02,Feb</t>
+        </is>
+      </c>
+      <c r="B603" t="inlineStr">
+        <is>
+          <t>AANAND  SHANKAR</t>
+        </is>
+      </c>
+      <c r="C603" t="inlineStr">
+        <is>
+          <t>YOGENDRA KUMAR</t>
+        </is>
+      </c>
+      <c r="D603" t="inlineStr">
+        <is>
+          <t>NIKKI KUMARI</t>
+        </is>
+      </c>
+      <c r="E603" t="inlineStr">
+        <is>
+          <t>VII</t>
+        </is>
+      </c>
+      <c r="F603" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" t="inlineStr">
+        <is>
+          <t>02,Feb</t>
+        </is>
+      </c>
+      <c r="B604" t="inlineStr">
+        <is>
+          <t>AYANSH RAJ</t>
+        </is>
+      </c>
+      <c r="C604" t="inlineStr">
+        <is>
+          <t>ANIL KUMAR</t>
+        </is>
+      </c>
+      <c r="D604" t="inlineStr">
+        <is>
+          <t>RUBI KUMARI</t>
+        </is>
+      </c>
+      <c r="E604" t="inlineStr">
+        <is>
+          <t>UKG</t>
+        </is>
+      </c>
+      <c r="F604" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" t="inlineStr">
+        <is>
+          <t>02,Feb</t>
+        </is>
+      </c>
+      <c r="B605" t="inlineStr">
+        <is>
+          <t>Laxmi kumari</t>
+        </is>
+      </c>
+      <c r="C605" t="inlineStr">
+        <is>
+          <t>Manoj Kumar</t>
+        </is>
+      </c>
+      <c r="D605" t="inlineStr">
+        <is>
+          <t>Sandhya Devi</t>
+        </is>
+      </c>
+      <c r="E605" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F605" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" t="inlineStr">
+        <is>
+          <t>02,Feb</t>
+        </is>
+      </c>
+      <c r="B606" t="inlineStr">
+        <is>
+          <t>PIYUSH BHASKAR</t>
+        </is>
+      </c>
+      <c r="C606" t="inlineStr">
+        <is>
+          <t>RAM KUMAR VERMA</t>
+        </is>
+      </c>
+      <c r="D606" t="inlineStr">
+        <is>
+          <t>VIBHA KUMARI</t>
+        </is>
+      </c>
+      <c r="E606" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="F606" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" t="inlineStr">
+        <is>
+          <t>02,Feb</t>
+        </is>
+      </c>
+      <c r="B607" t="inlineStr">
+        <is>
+          <t>VENKATESH SWAMI</t>
+        </is>
+      </c>
+      <c r="C607" t="inlineStr">
+        <is>
+          <t>RAJNISH KUMAR</t>
+        </is>
+      </c>
+      <c r="D607" t="inlineStr">
+        <is>
+          <t>SANGITA DEVI</t>
+        </is>
+      </c>
+      <c r="E607" t="inlineStr">
+        <is>
+          <t>IV</t>
+        </is>
+      </c>
+      <c r="F607" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" t="inlineStr">
+        <is>
+          <t>02,Feb</t>
+        </is>
+      </c>
+      <c r="B608" t="inlineStr">
+        <is>
+          <t>DIVYANSH KUMAR</t>
+        </is>
+      </c>
+      <c r="C608" t="inlineStr">
+        <is>
+          <t>KUMAR SAURABH SINGH</t>
+        </is>
+      </c>
+      <c r="D608" t="inlineStr">
+        <is>
+          <t>JYOTI SINGH</t>
+        </is>
+      </c>
+      <c r="E608" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="F608" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" t="inlineStr">
+        <is>
+          <t>02,Feb</t>
+        </is>
+      </c>
+      <c r="B609" t="inlineStr">
+        <is>
+          <t>DITYA SINGH</t>
+        </is>
+      </c>
+      <c r="C609" t="inlineStr">
+        <is>
+          <t>RAJESH KUMAR</t>
+        </is>
+      </c>
+      <c r="D609" t="inlineStr">
+        <is>
+          <t>MANISHA</t>
+        </is>
+      </c>
+      <c r="E609" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="F609" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" t="inlineStr">
+        <is>
+          <t>02,Feb</t>
+        </is>
+      </c>
+      <c r="B610" t="inlineStr">
+        <is>
+          <t>MOHAMMAD ASHAZ AMJAD</t>
+        </is>
+      </c>
+      <c r="C610" t="inlineStr">
+        <is>
+          <t>MD. AMJAD</t>
+        </is>
+      </c>
+      <c r="D610" t="inlineStr">
+        <is>
+          <t>ANAM NAAZ</t>
+        </is>
+      </c>
+      <c r="E610" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="F610" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" t="inlineStr">
+        <is>
+          <t>02,Feb</t>
+        </is>
+      </c>
+      <c r="B611" t="inlineStr">
+        <is>
+          <t>SARTHAK SINGH</t>
+        </is>
+      </c>
+      <c r="C611" t="inlineStr">
+        <is>
+          <t>BIMLESH KUMAR</t>
+        </is>
+      </c>
+      <c r="D611" t="inlineStr">
+        <is>
+          <t>SWATI KUMARI</t>
+        </is>
+      </c>
+      <c r="E611" t="inlineStr">
+        <is>
+          <t>IV</t>
+        </is>
+      </c>
+      <c r="F611" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" t="inlineStr">
+        <is>
+          <t>02,Feb</t>
+        </is>
+      </c>
+      <c r="B612" t="inlineStr">
+        <is>
+          <t>RUMI KUMARI</t>
+        </is>
+      </c>
+      <c r="C612" t="inlineStr">
+        <is>
+          <t>SUDHIR KUMAR</t>
+        </is>
+      </c>
+      <c r="D612" t="inlineStr">
+        <is>
+          <t>GUDIYA DEVI</t>
+        </is>
+      </c>
+      <c r="E612" t="inlineStr">
+        <is>
+          <t>VII</t>
+        </is>
+      </c>
+      <c r="F612" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" t="inlineStr">
+        <is>
+          <t>02,Feb</t>
+        </is>
+      </c>
+      <c r="B613" t="inlineStr">
+        <is>
+          <t>HARSHIT RAJ</t>
+        </is>
+      </c>
+      <c r="C613" t="inlineStr">
+        <is>
+          <t>SAHENDRA KUMAR</t>
+        </is>
+      </c>
+      <c r="D613" t="inlineStr">
+        <is>
+          <t>RUPA KUMARI</t>
+        </is>
+      </c>
+      <c r="E613" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="F613" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" t="inlineStr">
+        <is>
+          <t>02,Feb</t>
+        </is>
+      </c>
+      <c r="B614" t="inlineStr">
+        <is>
+          <t>Deepanjali</t>
+        </is>
+      </c>
+      <c r="C614" t="inlineStr">
+        <is>
+          <t>Rajeev Ranjan</t>
+        </is>
+      </c>
+      <c r="D614" t="inlineStr">
+        <is>
+          <t>Pinki Kumari</t>
+        </is>
+      </c>
+      <c r="E614" t="inlineStr">
+        <is>
+          <t>VIII</t>
+        </is>
+      </c>
+      <c r="F614" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" t="inlineStr">
+        <is>
+          <t>02,Feb</t>
+        </is>
+      </c>
+      <c r="B615" t="inlineStr">
+        <is>
+          <t>AASHISH RAJ</t>
+        </is>
+      </c>
+      <c r="C615" t="inlineStr">
+        <is>
+          <t>PURUSHOTAM KUMAR</t>
+        </is>
+      </c>
+      <c r="D615" t="inlineStr">
+        <is>
+          <t>REENA KUMARI</t>
+        </is>
+      </c>
+      <c r="E615" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="F615" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" t="inlineStr">
+        <is>
+          <t>02,Feb</t>
+        </is>
+      </c>
+      <c r="B616" t="inlineStr">
+        <is>
+          <t>Priya Rani</t>
+        </is>
+      </c>
+      <c r="C616" t="inlineStr">
+        <is>
+          <t>Jitendra Kumar</t>
+        </is>
+      </c>
+      <c r="D616" t="inlineStr">
+        <is>
+          <t>Pinki Kumari</t>
+        </is>
+      </c>
+      <c r="E616" t="inlineStr">
+        <is>
+          <t>VIII</t>
+        </is>
+      </c>
+      <c r="F616" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Birthday Data Master.xlsx
+++ b/Birthday Data Master.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F616"/>
+  <dimension ref="A1:F623"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.6" customWidth="1" min="1" max="1"/>
@@ -20136,6 +20136,230 @@
         </is>
       </c>
     </row>
+    <row r="617">
+      <c r="A617" t="inlineStr">
+        <is>
+          <t>03,Feb</t>
+        </is>
+      </c>
+      <c r="B617" t="inlineStr">
+        <is>
+          <t>VAIBHAV CHANDRA</t>
+        </is>
+      </c>
+      <c r="C617" t="inlineStr">
+        <is>
+          <t>VIKASH CHANDRA PANDEY</t>
+        </is>
+      </c>
+      <c r="D617" t="inlineStr">
+        <is>
+          <t>PRIYANKA KUMARI</t>
+        </is>
+      </c>
+      <c r="E617" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="F617" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" t="inlineStr">
+        <is>
+          <t>03,Feb</t>
+        </is>
+      </c>
+      <c r="B618" t="inlineStr">
+        <is>
+          <t>SHIVANSH SINGH</t>
+        </is>
+      </c>
+      <c r="C618" t="inlineStr">
+        <is>
+          <t>GAUTAM KUMAR</t>
+        </is>
+      </c>
+      <c r="D618" t="inlineStr">
+        <is>
+          <t>RANI KUMARI</t>
+        </is>
+      </c>
+      <c r="E618" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F618" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" t="inlineStr">
+        <is>
+          <t>03,Feb</t>
+        </is>
+      </c>
+      <c r="B619" t="inlineStr">
+        <is>
+          <t>RAUNAK RAJ</t>
+        </is>
+      </c>
+      <c r="C619" t="inlineStr">
+        <is>
+          <t>GUDDU KUMAR</t>
+        </is>
+      </c>
+      <c r="D619" t="inlineStr">
+        <is>
+          <t>REENA KUMARI</t>
+        </is>
+      </c>
+      <c r="E619" t="inlineStr">
+        <is>
+          <t>VII</t>
+        </is>
+      </c>
+      <c r="F619" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" t="inlineStr">
+        <is>
+          <t>03,Feb</t>
+        </is>
+      </c>
+      <c r="B620" t="inlineStr">
+        <is>
+          <t>PIHU  KUMARI</t>
+        </is>
+      </c>
+      <c r="C620" t="inlineStr">
+        <is>
+          <t>SANJAY KUMAR</t>
+        </is>
+      </c>
+      <c r="D620" t="inlineStr">
+        <is>
+          <t>RUPA DEVI</t>
+        </is>
+      </c>
+      <c r="E620" t="inlineStr">
+        <is>
+          <t>VII</t>
+        </is>
+      </c>
+      <c r="F620" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" t="inlineStr">
+        <is>
+          <t>03,Feb</t>
+        </is>
+      </c>
+      <c r="B621" t="inlineStr">
+        <is>
+          <t>Rani  Sunidhi</t>
+        </is>
+      </c>
+      <c r="C621" t="inlineStr">
+        <is>
+          <t>Sunil Kumar</t>
+        </is>
+      </c>
+      <c r="D621" t="inlineStr">
+        <is>
+          <t>Pinki Kumari</t>
+        </is>
+      </c>
+      <c r="E621" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F621" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" t="inlineStr">
+        <is>
+          <t>03,Feb</t>
+        </is>
+      </c>
+      <c r="B622" t="inlineStr">
+        <is>
+          <t>NAVYA KUMARI</t>
+        </is>
+      </c>
+      <c r="C622" t="inlineStr">
+        <is>
+          <t>AKSHAY KUMAR</t>
+        </is>
+      </c>
+      <c r="D622" t="inlineStr">
+        <is>
+          <t>URWIJA KUMARI</t>
+        </is>
+      </c>
+      <c r="E622" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="F622" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" t="inlineStr">
+        <is>
+          <t>03,Feb</t>
+        </is>
+      </c>
+      <c r="B623" t="inlineStr">
+        <is>
+          <t>MD HUZAIF ALAM</t>
+        </is>
+      </c>
+      <c r="C623" t="inlineStr">
+        <is>
+          <t>MOHAMMAD MANNU</t>
+        </is>
+      </c>
+      <c r="D623" t="inlineStr">
+        <is>
+          <t>ZOHRA NASAR</t>
+        </is>
+      </c>
+      <c r="E623" t="inlineStr">
+        <is>
+          <t>LKG</t>
+        </is>
+      </c>
+      <c r="F623" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Birthday Data Master.xlsx
+++ b/Birthday Data Master.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F623"/>
+  <dimension ref="A1:F628"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.6" customWidth="1" min="1" max="1"/>
@@ -20360,6 +20360,166 @@
         </is>
       </c>
     </row>
+    <row r="624">
+      <c r="A624" t="inlineStr">
+        <is>
+          <t>04,Feb</t>
+        </is>
+      </c>
+      <c r="B624" t="inlineStr">
+        <is>
+          <t>ALIJA SINHA</t>
+        </is>
+      </c>
+      <c r="C624" t="inlineStr">
+        <is>
+          <t>ARVIND KUMAR SINHA</t>
+        </is>
+      </c>
+      <c r="D624" t="inlineStr">
+        <is>
+          <t>PUJA SINHA</t>
+        </is>
+      </c>
+      <c r="E624" t="inlineStr">
+        <is>
+          <t>IX</t>
+        </is>
+      </c>
+      <c r="F624" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" t="inlineStr">
+        <is>
+          <t>04,Feb</t>
+        </is>
+      </c>
+      <c r="B625" t="inlineStr">
+        <is>
+          <t>PAWAN KUMAR</t>
+        </is>
+      </c>
+      <c r="C625" t="inlineStr">
+        <is>
+          <t>PUSHPENDRA KUMAR</t>
+        </is>
+      </c>
+      <c r="D625" t="inlineStr">
+        <is>
+          <t>SUSHMITA KUMARI</t>
+        </is>
+      </c>
+      <c r="E625" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="F625" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" t="inlineStr">
+        <is>
+          <t>04,Feb</t>
+        </is>
+      </c>
+      <c r="B626" t="inlineStr">
+        <is>
+          <t>NISHA KUMARI</t>
+        </is>
+      </c>
+      <c r="C626" t="inlineStr">
+        <is>
+          <t>NIPPU KUMAR</t>
+        </is>
+      </c>
+      <c r="D626" t="inlineStr">
+        <is>
+          <t>NITU DEVI</t>
+        </is>
+      </c>
+      <c r="E626" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="F626" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" t="inlineStr">
+        <is>
+          <t>04,Feb</t>
+        </is>
+      </c>
+      <c r="B627" t="inlineStr">
+        <is>
+          <t>Akshat Ranjan</t>
+        </is>
+      </c>
+      <c r="C627" t="inlineStr">
+        <is>
+          <t>Rakesh Ranjan</t>
+        </is>
+      </c>
+      <c r="D627" t="inlineStr">
+        <is>
+          <t>Sanju Sinha</t>
+        </is>
+      </c>
+      <c r="E627" t="inlineStr">
+        <is>
+          <t>VIII</t>
+        </is>
+      </c>
+      <c r="F627" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" t="inlineStr">
+        <is>
+          <t>04,Feb</t>
+        </is>
+      </c>
+      <c r="B628" t="inlineStr">
+        <is>
+          <t>Yash Vardhan Kumar</t>
+        </is>
+      </c>
+      <c r="C628" t="inlineStr">
+        <is>
+          <t>Prince Kumar</t>
+        </is>
+      </c>
+      <c r="D628" t="inlineStr">
+        <is>
+          <t>Seema Devi</t>
+        </is>
+      </c>
+      <c r="E628" t="inlineStr">
+        <is>
+          <t>IX</t>
+        </is>
+      </c>
+      <c r="F628" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Birthday Data Master.xlsx
+++ b/Birthday Data Master.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F628"/>
+  <dimension ref="A1:F640"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.6" customWidth="1" min="1" max="1"/>
@@ -20520,6 +20520,390 @@
         </is>
       </c>
     </row>
+    <row r="629">
+      <c r="A629" t="inlineStr">
+        <is>
+          <t>05,Feb</t>
+        </is>
+      </c>
+      <c r="B629" t="inlineStr">
+        <is>
+          <t>LAXMI PRIYA</t>
+        </is>
+      </c>
+      <c r="C629" t="inlineStr">
+        <is>
+          <t>RAVIKANT KUMAR KASHYAP</t>
+        </is>
+      </c>
+      <c r="D629" t="inlineStr">
+        <is>
+          <t>SEEMA KUMARI</t>
+        </is>
+      </c>
+      <c r="E629" t="inlineStr">
+        <is>
+          <t>VII</t>
+        </is>
+      </c>
+      <c r="F629" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" t="inlineStr">
+        <is>
+          <t>05,Feb</t>
+        </is>
+      </c>
+      <c r="B630" t="inlineStr">
+        <is>
+          <t>MANIKANT BHUSHAN</t>
+        </is>
+      </c>
+      <c r="C630" t="inlineStr">
+        <is>
+          <t>SHASHIKANT BHUSHAN</t>
+        </is>
+      </c>
+      <c r="D630" t="inlineStr">
+        <is>
+          <t>ARTI GUPTA</t>
+        </is>
+      </c>
+      <c r="E630" t="inlineStr">
+        <is>
+          <t>IV</t>
+        </is>
+      </c>
+      <c r="F630" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" t="inlineStr">
+        <is>
+          <t>05,Feb</t>
+        </is>
+      </c>
+      <c r="B631" t="inlineStr">
+        <is>
+          <t>Akarsh Kumar</t>
+        </is>
+      </c>
+      <c r="C631" t="inlineStr">
+        <is>
+          <t>Gyanendra Kumar</t>
+        </is>
+      </c>
+      <c r="D631" t="inlineStr">
+        <is>
+          <t>Sangita Kumari</t>
+        </is>
+      </c>
+      <c r="E631" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F631" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" t="inlineStr">
+        <is>
+          <t>05,Feb</t>
+        </is>
+      </c>
+      <c r="B632" t="inlineStr">
+        <is>
+          <t>SABHYATA  KUMARI</t>
+        </is>
+      </c>
+      <c r="C632" t="inlineStr">
+        <is>
+          <t>RAJNI KANT</t>
+        </is>
+      </c>
+      <c r="D632" t="inlineStr">
+        <is>
+          <t>SARITA KUMARI</t>
+        </is>
+      </c>
+      <c r="E632" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="F632" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" t="inlineStr">
+        <is>
+          <t>05,Feb</t>
+        </is>
+      </c>
+      <c r="B633" t="inlineStr">
+        <is>
+          <t>Harshit Kumar</t>
+        </is>
+      </c>
+      <c r="C633" t="inlineStr">
+        <is>
+          <t>Naresh Kumar</t>
+        </is>
+      </c>
+      <c r="D633" t="inlineStr">
+        <is>
+          <t>Renu Kumari</t>
+        </is>
+      </c>
+      <c r="E633" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F633" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" t="inlineStr">
+        <is>
+          <t>05,Feb</t>
+        </is>
+      </c>
+      <c r="B634" t="inlineStr">
+        <is>
+          <t>ANISHA BHARTI</t>
+        </is>
+      </c>
+      <c r="C634" t="inlineStr">
+        <is>
+          <t>GAJENDRA CHAUDHARY</t>
+        </is>
+      </c>
+      <c r="D634" t="inlineStr">
+        <is>
+          <t>ANITA DEVI</t>
+        </is>
+      </c>
+      <c r="E634" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="F634" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" t="inlineStr">
+        <is>
+          <t>05,Feb</t>
+        </is>
+      </c>
+      <c r="B635" t="inlineStr">
+        <is>
+          <t>NILEENA KUMARI</t>
+        </is>
+      </c>
+      <c r="C635" t="inlineStr">
+        <is>
+          <t>FUNNY BHUSHAN</t>
+        </is>
+      </c>
+      <c r="D635" t="inlineStr">
+        <is>
+          <t>SANGEETA SHARMA</t>
+        </is>
+      </c>
+      <c r="E635" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="F635" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" t="inlineStr">
+        <is>
+          <t>05,Feb</t>
+        </is>
+      </c>
+      <c r="B636" t="inlineStr">
+        <is>
+          <t>ARYA RAJ</t>
+        </is>
+      </c>
+      <c r="C636" t="inlineStr">
+        <is>
+          <t>AMARJEET KUMAR</t>
+        </is>
+      </c>
+      <c r="D636" t="inlineStr">
+        <is>
+          <t>PINKI KUMARI</t>
+        </is>
+      </c>
+      <c r="E636" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="F636" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" t="inlineStr">
+        <is>
+          <t>05,Feb</t>
+        </is>
+      </c>
+      <c r="B637" t="inlineStr">
+        <is>
+          <t>GAURAV SINGH</t>
+        </is>
+      </c>
+      <c r="C637" t="inlineStr">
+        <is>
+          <t>CHANDAN KUMAR</t>
+        </is>
+      </c>
+      <c r="D637" t="inlineStr">
+        <is>
+          <t>MIKU KUMARI</t>
+        </is>
+      </c>
+      <c r="E637" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F637" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" t="inlineStr">
+        <is>
+          <t>05,Feb</t>
+        </is>
+      </c>
+      <c r="B638" t="inlineStr">
+        <is>
+          <t>AYUSH RAJ</t>
+        </is>
+      </c>
+      <c r="C638" t="inlineStr">
+        <is>
+          <t>RANJIT PRASAD</t>
+        </is>
+      </c>
+      <c r="D638" t="inlineStr">
+        <is>
+          <t>SHEELA DEVI</t>
+        </is>
+      </c>
+      <c r="E638" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="F638" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" t="inlineStr">
+        <is>
+          <t>05,Feb</t>
+        </is>
+      </c>
+      <c r="B639" t="inlineStr">
+        <is>
+          <t>AYUSHMAN SHARMA</t>
+        </is>
+      </c>
+      <c r="C639" t="inlineStr">
+        <is>
+          <t>NISHANT SAURABH</t>
+        </is>
+      </c>
+      <c r="D639" t="inlineStr">
+        <is>
+          <t>SMITA KUMARI</t>
+        </is>
+      </c>
+      <c r="E639" t="inlineStr">
+        <is>
+          <t>LKG</t>
+        </is>
+      </c>
+      <c r="F639" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" t="inlineStr">
+        <is>
+          <t>05,Feb</t>
+        </is>
+      </c>
+      <c r="B640" t="inlineStr">
+        <is>
+          <t>ADITI RAJ</t>
+        </is>
+      </c>
+      <c r="C640" t="inlineStr">
+        <is>
+          <t>DHANANJAY KUMAR DIWAKAR</t>
+        </is>
+      </c>
+      <c r="D640" t="inlineStr">
+        <is>
+          <t>SONI KUMARI</t>
+        </is>
+      </c>
+      <c r="E640" t="inlineStr">
+        <is>
+          <t>IV</t>
+        </is>
+      </c>
+      <c r="F640" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Birthday Data Master.xlsx
+++ b/Birthday Data Master.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F640"/>
+  <dimension ref="A1:F653"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.6" customWidth="1" min="1" max="1"/>
@@ -20904,6 +20904,422 @@
         </is>
       </c>
     </row>
+    <row r="641">
+      <c r="A641" t="inlineStr">
+        <is>
+          <t>06,Feb</t>
+        </is>
+      </c>
+      <c r="B641" t="inlineStr">
+        <is>
+          <t>Ritika Kumari</t>
+        </is>
+      </c>
+      <c r="C641" t="inlineStr">
+        <is>
+          <t>Triveni Kumar</t>
+        </is>
+      </c>
+      <c r="D641" t="inlineStr">
+        <is>
+          <t>Shubh Lakshmi Kumari</t>
+        </is>
+      </c>
+      <c r="E641" t="inlineStr">
+        <is>
+          <t>VIII</t>
+        </is>
+      </c>
+      <c r="F641" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" t="inlineStr">
+        <is>
+          <t>06,Feb</t>
+        </is>
+      </c>
+      <c r="B642" t="inlineStr">
+        <is>
+          <t>Ritika  kumari</t>
+        </is>
+      </c>
+      <c r="C642" t="inlineStr">
+        <is>
+          <t>RANDHIR KUMAR DHIRAJ</t>
+        </is>
+      </c>
+      <c r="D642" t="inlineStr">
+        <is>
+          <t>sweta kumari</t>
+        </is>
+      </c>
+      <c r="E642" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="F642" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" t="inlineStr">
+        <is>
+          <t>06,Feb</t>
+        </is>
+      </c>
+      <c r="B643" t="inlineStr">
+        <is>
+          <t>SATYAM KUMAR</t>
+        </is>
+      </c>
+      <c r="C643" t="inlineStr">
+        <is>
+          <t>SANTOSH KUMAR</t>
+        </is>
+      </c>
+      <c r="D643" t="inlineStr">
+        <is>
+          <t>NITU KUMARI</t>
+        </is>
+      </c>
+      <c r="E643" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="F643" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" t="inlineStr">
+        <is>
+          <t>06,Feb</t>
+        </is>
+      </c>
+      <c r="B644" t="inlineStr">
+        <is>
+          <t>SHRUTI  KUMARI</t>
+        </is>
+      </c>
+      <c r="C644" t="inlineStr">
+        <is>
+          <t>SHRIRAM PRASAD</t>
+        </is>
+      </c>
+      <c r="D644" t="inlineStr">
+        <is>
+          <t>SONI KUMARI</t>
+        </is>
+      </c>
+      <c r="E644" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F644" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" t="inlineStr">
+        <is>
+          <t>06,Feb</t>
+        </is>
+      </c>
+      <c r="B645" t="inlineStr">
+        <is>
+          <t>ADITI KUMARI</t>
+        </is>
+      </c>
+      <c r="C645" t="inlineStr">
+        <is>
+          <t>ADITYA KUMAR</t>
+        </is>
+      </c>
+      <c r="D645" t="inlineStr">
+        <is>
+          <t>NISHA KUMARI</t>
+        </is>
+      </c>
+      <c r="E645" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="F645" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" t="inlineStr">
+        <is>
+          <t>06,Feb</t>
+        </is>
+      </c>
+      <c r="B646" t="inlineStr">
+        <is>
+          <t>Raj Anand</t>
+        </is>
+      </c>
+      <c r="C646" t="inlineStr">
+        <is>
+          <t>Purnanand Kumar</t>
+        </is>
+      </c>
+      <c r="D646" t="inlineStr">
+        <is>
+          <t>Prem Lata Sinha</t>
+        </is>
+      </c>
+      <c r="E646" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F646" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" t="inlineStr">
+        <is>
+          <t>06,Feb</t>
+        </is>
+      </c>
+      <c r="B647" t="inlineStr">
+        <is>
+          <t>Shaumik Sinha</t>
+        </is>
+      </c>
+      <c r="C647" t="inlineStr">
+        <is>
+          <t>Sanjay Kumar</t>
+        </is>
+      </c>
+      <c r="D647" t="inlineStr">
+        <is>
+          <t>Jyoti Sinha</t>
+        </is>
+      </c>
+      <c r="E647" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F647" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" t="inlineStr">
+        <is>
+          <t>06,Feb</t>
+        </is>
+      </c>
+      <c r="B648" t="inlineStr">
+        <is>
+          <t>PUSKAR KUMAR</t>
+        </is>
+      </c>
+      <c r="C648" t="inlineStr">
+        <is>
+          <t>PRAMOD KUMAR</t>
+        </is>
+      </c>
+      <c r="D648" t="inlineStr">
+        <is>
+          <t>LALITA DEVI</t>
+        </is>
+      </c>
+      <c r="E648" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="F648" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" t="inlineStr">
+        <is>
+          <t>06,Feb</t>
+        </is>
+      </c>
+      <c r="B649" t="inlineStr">
+        <is>
+          <t>HARDIK SHARMA</t>
+        </is>
+      </c>
+      <c r="C649" t="inlineStr">
+        <is>
+          <t>PRAMENDRA KUMAR</t>
+        </is>
+      </c>
+      <c r="D649" t="inlineStr">
+        <is>
+          <t>CHUMCHUM DEVI</t>
+        </is>
+      </c>
+      <c r="E649" t="inlineStr">
+        <is>
+          <t>VII</t>
+        </is>
+      </c>
+      <c r="F649" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" t="inlineStr">
+        <is>
+          <t>06,Feb</t>
+        </is>
+      </c>
+      <c r="B650" t="inlineStr">
+        <is>
+          <t>NIKHIL  RAJ</t>
+        </is>
+      </c>
+      <c r="C650" t="inlineStr">
+        <is>
+          <t>SANJEEV KUMAR</t>
+        </is>
+      </c>
+      <c r="D650" t="inlineStr">
+        <is>
+          <t>ANJANI KUMARI</t>
+        </is>
+      </c>
+      <c r="E650" t="inlineStr">
+        <is>
+          <t>VII</t>
+        </is>
+      </c>
+      <c r="F650" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" t="inlineStr">
+        <is>
+          <t>06,Feb</t>
+        </is>
+      </c>
+      <c r="B651" t="inlineStr">
+        <is>
+          <t>SANU KUMAR</t>
+        </is>
+      </c>
+      <c r="C651" t="inlineStr">
+        <is>
+          <t>SRIRAM KUMAR</t>
+        </is>
+      </c>
+      <c r="D651" t="inlineStr">
+        <is>
+          <t>SUNITA KUMARI</t>
+        </is>
+      </c>
+      <c r="E651" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="F651" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" t="inlineStr">
+        <is>
+          <t>06,Feb</t>
+        </is>
+      </c>
+      <c r="B652" t="inlineStr">
+        <is>
+          <t>GAURAV KUMAR</t>
+        </is>
+      </c>
+      <c r="C652" t="inlineStr">
+        <is>
+          <t>SANTOSH KUMAR</t>
+        </is>
+      </c>
+      <c r="D652" t="inlineStr">
+        <is>
+          <t>BABY DEVI</t>
+        </is>
+      </c>
+      <c r="E652" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="F652" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" t="inlineStr">
+        <is>
+          <t>06,Feb</t>
+        </is>
+      </c>
+      <c r="B653" t="inlineStr">
+        <is>
+          <t>Aayushi Kumari</t>
+        </is>
+      </c>
+      <c r="C653" t="inlineStr">
+        <is>
+          <t>Arvind Kumar</t>
+        </is>
+      </c>
+      <c r="D653" t="inlineStr">
+        <is>
+          <t>Chumchum Kumari</t>
+        </is>
+      </c>
+      <c r="E653" t="inlineStr">
+        <is>
+          <t>IX</t>
+        </is>
+      </c>
+      <c r="F653" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Birthday Data Master.xlsx
+++ b/Birthday Data Master.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F653"/>
+  <dimension ref="A1:F662"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.6" customWidth="1" min="1" max="1"/>
@@ -21320,6 +21320,294 @@
         </is>
       </c>
     </row>
+    <row r="654">
+      <c r="A654" t="inlineStr">
+        <is>
+          <t>07,Feb</t>
+        </is>
+      </c>
+      <c r="B654" t="inlineStr">
+        <is>
+          <t>ADITI KUMARI</t>
+        </is>
+      </c>
+      <c r="C654" t="inlineStr">
+        <is>
+          <t>DINESH KUMAR</t>
+        </is>
+      </c>
+      <c r="D654" t="inlineStr">
+        <is>
+          <t>SONAM KUMARI</t>
+        </is>
+      </c>
+      <c r="E654" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="F654" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" t="inlineStr">
+        <is>
+          <t>07,Feb</t>
+        </is>
+      </c>
+      <c r="B655" t="inlineStr">
+        <is>
+          <t>ANSH RAJ</t>
+        </is>
+      </c>
+      <c r="C655" t="inlineStr">
+        <is>
+          <t>SUSHANT KUMAR PATHAK</t>
+        </is>
+      </c>
+      <c r="D655" t="inlineStr">
+        <is>
+          <t>MALA KUMARI</t>
+        </is>
+      </c>
+      <c r="E655" t="inlineStr">
+        <is>
+          <t>IV</t>
+        </is>
+      </c>
+      <c r="F655" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" t="inlineStr">
+        <is>
+          <t>07,Feb</t>
+        </is>
+      </c>
+      <c r="B656" t="inlineStr">
+        <is>
+          <t>RAGIB  MOSHARAF</t>
+        </is>
+      </c>
+      <c r="C656" t="inlineStr">
+        <is>
+          <t>MOSHARAF ALAM</t>
+        </is>
+      </c>
+      <c r="D656" t="inlineStr">
+        <is>
+          <t>ARZU BANO</t>
+        </is>
+      </c>
+      <c r="E656" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="F656" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" t="inlineStr">
+        <is>
+          <t>07,Feb</t>
+        </is>
+      </c>
+      <c r="B657" t="inlineStr">
+        <is>
+          <t>AASTHA SINGH</t>
+        </is>
+      </c>
+      <c r="C657" t="inlineStr">
+        <is>
+          <t>TRIVENI KUMAR SINGH</t>
+        </is>
+      </c>
+      <c r="D657" t="inlineStr">
+        <is>
+          <t>MADHVI SINGH</t>
+        </is>
+      </c>
+      <c r="E657" t="inlineStr">
+        <is>
+          <t>XI</t>
+        </is>
+      </c>
+      <c r="F657" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" t="inlineStr">
+        <is>
+          <t>07,Feb</t>
+        </is>
+      </c>
+      <c r="B658" t="inlineStr">
+        <is>
+          <t>ASAD KAMAL</t>
+        </is>
+      </c>
+      <c r="C658" t="inlineStr">
+        <is>
+          <t>SHAHID KAMAL</t>
+        </is>
+      </c>
+      <c r="D658" t="inlineStr">
+        <is>
+          <t>NAHEED MALLICK</t>
+        </is>
+      </c>
+      <c r="E658" t="inlineStr">
+        <is>
+          <t>XI</t>
+        </is>
+      </c>
+      <c r="F658" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" t="inlineStr">
+        <is>
+          <t>07,Feb</t>
+        </is>
+      </c>
+      <c r="B659" t="inlineStr">
+        <is>
+          <t>Shifa Jawed</t>
+        </is>
+      </c>
+      <c r="C659" t="inlineStr">
+        <is>
+          <t>MD Rashid Jawed</t>
+        </is>
+      </c>
+      <c r="D659" t="inlineStr">
+        <is>
+          <t>Zeba Tabassum</t>
+        </is>
+      </c>
+      <c r="E659" t="inlineStr">
+        <is>
+          <t>IX</t>
+        </is>
+      </c>
+      <c r="F659" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" t="inlineStr">
+        <is>
+          <t>07,Feb</t>
+        </is>
+      </c>
+      <c r="B660" t="inlineStr">
+        <is>
+          <t>Radhika Sharma</t>
+        </is>
+      </c>
+      <c r="C660" t="inlineStr">
+        <is>
+          <t>Ranjeet Kumar</t>
+        </is>
+      </c>
+      <c r="D660" t="inlineStr">
+        <is>
+          <t>Puja Kumari</t>
+        </is>
+      </c>
+      <c r="E660" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="F660" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" t="inlineStr">
+        <is>
+          <t>07,Feb</t>
+        </is>
+      </c>
+      <c r="B661" t="inlineStr">
+        <is>
+          <t>NANDANI KUMARI</t>
+        </is>
+      </c>
+      <c r="C661" t="inlineStr">
+        <is>
+          <t>SUNIL KUMAR</t>
+        </is>
+      </c>
+      <c r="D661" t="inlineStr">
+        <is>
+          <t>PRATIMA DEVI</t>
+        </is>
+      </c>
+      <c r="E661" t="inlineStr">
+        <is>
+          <t>VII</t>
+        </is>
+      </c>
+      <c r="F661" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" t="inlineStr">
+        <is>
+          <t>07,Feb</t>
+        </is>
+      </c>
+      <c r="B662" t="inlineStr">
+        <is>
+          <t>SANVI KUMARI</t>
+        </is>
+      </c>
+      <c r="C662" t="inlineStr">
+        <is>
+          <t>RAJEEV KUMAR</t>
+        </is>
+      </c>
+      <c r="D662" t="inlineStr">
+        <is>
+          <t>PUSHPA KUMARI</t>
+        </is>
+      </c>
+      <c r="E662" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="F662" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Birthday Data Master.xlsx
+++ b/Birthday Data Master.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F662"/>
+  <dimension ref="A1:F668"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.6" customWidth="1" min="1" max="1"/>
@@ -21608,6 +21608,198 @@
         </is>
       </c>
     </row>
+    <row r="663">
+      <c r="A663" t="inlineStr">
+        <is>
+          <t>08,Feb</t>
+        </is>
+      </c>
+      <c r="B663" t="inlineStr">
+        <is>
+          <t>Krishna  Kumar</t>
+        </is>
+      </c>
+      <c r="C663" t="inlineStr">
+        <is>
+          <t>Sidharth Kumar</t>
+        </is>
+      </c>
+      <c r="D663" t="inlineStr">
+        <is>
+          <t>Sudha Kumari</t>
+        </is>
+      </c>
+      <c r="E663" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F663" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" t="inlineStr">
+        <is>
+          <t>08,Feb</t>
+        </is>
+      </c>
+      <c r="B664" t="inlineStr">
+        <is>
+          <t>Kumar Ansh Raj</t>
+        </is>
+      </c>
+      <c r="C664" t="inlineStr">
+        <is>
+          <t>Vinod Kumar</t>
+        </is>
+      </c>
+      <c r="D664" t="inlineStr">
+        <is>
+          <t>Rimpi Kumari</t>
+        </is>
+      </c>
+      <c r="E664" t="inlineStr">
+        <is>
+          <t>VIII</t>
+        </is>
+      </c>
+      <c r="F664" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" t="inlineStr">
+        <is>
+          <t>08,Feb</t>
+        </is>
+      </c>
+      <c r="B665" t="inlineStr">
+        <is>
+          <t>MANSI KUMARI</t>
+        </is>
+      </c>
+      <c r="C665" t="inlineStr">
+        <is>
+          <t>PAWAN KUMAR</t>
+        </is>
+      </c>
+      <c r="D665" t="inlineStr">
+        <is>
+          <t>BABITA KUMARI</t>
+        </is>
+      </c>
+      <c r="E665" t="inlineStr">
+        <is>
+          <t>UKG</t>
+        </is>
+      </c>
+      <c r="F665" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" t="inlineStr">
+        <is>
+          <t>08,Feb</t>
+        </is>
+      </c>
+      <c r="B666" t="inlineStr">
+        <is>
+          <t>ADITYA DUBEY</t>
+        </is>
+      </c>
+      <c r="C666" t="inlineStr">
+        <is>
+          <t>SHIVANAND DUBEY</t>
+        </is>
+      </c>
+      <c r="D666" t="inlineStr">
+        <is>
+          <t>SANJU DUBEY</t>
+        </is>
+      </c>
+      <c r="E666" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="F666" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" t="inlineStr">
+        <is>
+          <t>08,Feb</t>
+        </is>
+      </c>
+      <c r="B667" t="inlineStr">
+        <is>
+          <t>Shahil Raj</t>
+        </is>
+      </c>
+      <c r="C667" t="inlineStr">
+        <is>
+          <t>Santosh Kumar</t>
+        </is>
+      </c>
+      <c r="D667" t="inlineStr">
+        <is>
+          <t>Rina Devi</t>
+        </is>
+      </c>
+      <c r="E667" t="inlineStr">
+        <is>
+          <t>VIII</t>
+        </is>
+      </c>
+      <c r="F667" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" t="inlineStr">
+        <is>
+          <t>08,Feb</t>
+        </is>
+      </c>
+      <c r="B668" t="inlineStr">
+        <is>
+          <t>Diwakar Kumar</t>
+        </is>
+      </c>
+      <c r="C668" t="inlineStr">
+        <is>
+          <t>Niranjan Kumar</t>
+        </is>
+      </c>
+      <c r="D668" t="inlineStr">
+        <is>
+          <t>Juli Kumari</t>
+        </is>
+      </c>
+      <c r="E668" t="inlineStr">
+        <is>
+          <t>IX</t>
+        </is>
+      </c>
+      <c r="F668" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Birthday Data Master.xlsx
+++ b/Birthday Data Master.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F668"/>
+  <dimension ref="A1:F671"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.6" customWidth="1" min="1" max="1"/>
@@ -21800,6 +21800,102 @@
         </is>
       </c>
     </row>
+    <row r="669">
+      <c r="A669" t="inlineStr">
+        <is>
+          <t>09,Feb</t>
+        </is>
+      </c>
+      <c r="B669" t="inlineStr">
+        <is>
+          <t>HARSH  RAJ</t>
+        </is>
+      </c>
+      <c r="C669" t="inlineStr">
+        <is>
+          <t>PRAMOD KUMAR</t>
+        </is>
+      </c>
+      <c r="D669" t="inlineStr">
+        <is>
+          <t>AMRITA KUMARI</t>
+        </is>
+      </c>
+      <c r="E669" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="F669" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" t="inlineStr">
+        <is>
+          <t>09,Feb</t>
+        </is>
+      </c>
+      <c r="B670" t="inlineStr">
+        <is>
+          <t>Shivam</t>
+        </is>
+      </c>
+      <c r="C670" t="inlineStr">
+        <is>
+          <t>Sanjeev Kumar Manav</t>
+        </is>
+      </c>
+      <c r="D670" t="inlineStr">
+        <is>
+          <t>Pinki Kumari</t>
+        </is>
+      </c>
+      <c r="E670" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F670" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" t="inlineStr">
+        <is>
+          <t>09,Feb</t>
+        </is>
+      </c>
+      <c r="B671" t="inlineStr">
+        <is>
+          <t>PRATIK  KUMAR</t>
+        </is>
+      </c>
+      <c r="C671" t="inlineStr">
+        <is>
+          <t>DEEPAK KUMAR</t>
+        </is>
+      </c>
+      <c r="D671" t="inlineStr">
+        <is>
+          <t>AARTI DEVI</t>
+        </is>
+      </c>
+      <c r="E671" t="inlineStr">
+        <is>
+          <t>VII</t>
+        </is>
+      </c>
+      <c r="F671" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Birthday Data Master.xlsx
+++ b/Birthday Data Master.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F671"/>
+  <dimension ref="A1:F682"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.6" customWidth="1" min="1" max="1"/>
@@ -21896,6 +21896,358 @@
         </is>
       </c>
     </row>
+    <row r="672">
+      <c r="A672" t="inlineStr">
+        <is>
+          <t>10,Feb</t>
+        </is>
+      </c>
+      <c r="B672" t="inlineStr">
+        <is>
+          <t>ARYAN KUMAR MISHRA</t>
+        </is>
+      </c>
+      <c r="C672" t="inlineStr">
+        <is>
+          <t>Abhishek KUMAR MISHRA</t>
+        </is>
+      </c>
+      <c r="D672" t="inlineStr">
+        <is>
+          <t>NIKITA KUMARI</t>
+        </is>
+      </c>
+      <c r="E672" t="inlineStr">
+        <is>
+          <t>IV</t>
+        </is>
+      </c>
+      <c r="F672" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" t="inlineStr">
+        <is>
+          <t>10,Feb</t>
+        </is>
+      </c>
+      <c r="B673" t="inlineStr">
+        <is>
+          <t>Rishika Ranjan</t>
+        </is>
+      </c>
+      <c r="C673" t="inlineStr">
+        <is>
+          <t>Ranjan Kumar</t>
+        </is>
+      </c>
+      <c r="D673" t="inlineStr">
+        <is>
+          <t>Minu Devi</t>
+        </is>
+      </c>
+      <c r="E673" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F673" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" t="inlineStr">
+        <is>
+          <t>10,Feb</t>
+        </is>
+      </c>
+      <c r="B674" t="inlineStr">
+        <is>
+          <t>SHREYA BHARTI</t>
+        </is>
+      </c>
+      <c r="C674" t="inlineStr">
+        <is>
+          <t>RAJEEV KUMAR SINGH</t>
+        </is>
+      </c>
+      <c r="D674" t="inlineStr">
+        <is>
+          <t>ANJU KUMARI</t>
+        </is>
+      </c>
+      <c r="E674" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="F674" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" t="inlineStr">
+        <is>
+          <t>10,Feb</t>
+        </is>
+      </c>
+      <c r="B675" t="inlineStr">
+        <is>
+          <t>ADITYA RAJ</t>
+        </is>
+      </c>
+      <c r="C675" t="inlineStr">
+        <is>
+          <t>MANTOSH KUMAR</t>
+        </is>
+      </c>
+      <c r="D675" t="inlineStr">
+        <is>
+          <t>RAMA KUMARI</t>
+        </is>
+      </c>
+      <c r="E675" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="F675" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" t="inlineStr">
+        <is>
+          <t>10,Feb</t>
+        </is>
+      </c>
+      <c r="B676" t="inlineStr">
+        <is>
+          <t>Harsh Raj Kumar</t>
+        </is>
+      </c>
+      <c r="C676" t="inlineStr">
+        <is>
+          <t>Sanjeet Kumar</t>
+        </is>
+      </c>
+      <c r="D676" t="inlineStr">
+        <is>
+          <t>Nigam Kumari</t>
+        </is>
+      </c>
+      <c r="E676" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F676" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" t="inlineStr">
+        <is>
+          <t>10,Feb</t>
+        </is>
+      </c>
+      <c r="B677" t="inlineStr">
+        <is>
+          <t>Harsh Kumar</t>
+        </is>
+      </c>
+      <c r="C677" t="inlineStr">
+        <is>
+          <t>Satish Kumar</t>
+        </is>
+      </c>
+      <c r="D677" t="inlineStr">
+        <is>
+          <t>Arti Kumari</t>
+        </is>
+      </c>
+      <c r="E677" t="inlineStr">
+        <is>
+          <t>VIII</t>
+        </is>
+      </c>
+      <c r="F677" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" t="inlineStr">
+        <is>
+          <t>10,Feb</t>
+        </is>
+      </c>
+      <c r="B678" t="inlineStr">
+        <is>
+          <t>Prit Raj</t>
+        </is>
+      </c>
+      <c r="C678" t="inlineStr">
+        <is>
+          <t>Pankaj Kumar</t>
+        </is>
+      </c>
+      <c r="D678" t="inlineStr">
+        <is>
+          <t>Anshu Devi</t>
+        </is>
+      </c>
+      <c r="E678" t="inlineStr">
+        <is>
+          <t>VIII</t>
+        </is>
+      </c>
+      <c r="F678" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" t="inlineStr">
+        <is>
+          <t>10,Feb</t>
+        </is>
+      </c>
+      <c r="B679" t="inlineStr">
+        <is>
+          <t>Satyam Kumar</t>
+        </is>
+      </c>
+      <c r="C679" t="inlineStr">
+        <is>
+          <t>Shashi Ranjan Kumar</t>
+        </is>
+      </c>
+      <c r="D679" t="inlineStr">
+        <is>
+          <t>Guriya Kumari</t>
+        </is>
+      </c>
+      <c r="E679" t="inlineStr">
+        <is>
+          <t>IX</t>
+        </is>
+      </c>
+      <c r="F679" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" t="inlineStr">
+        <is>
+          <t>10,Feb</t>
+        </is>
+      </c>
+      <c r="B680" t="inlineStr">
+        <is>
+          <t>AARAV RAJ</t>
+        </is>
+      </c>
+      <c r="C680" t="inlineStr">
+        <is>
+          <t>SUBODH KUMAR</t>
+        </is>
+      </c>
+      <c r="D680" t="inlineStr">
+        <is>
+          <t>SONI KUMARI</t>
+        </is>
+      </c>
+      <c r="E680" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="F680" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" t="inlineStr">
+        <is>
+          <t>10,Feb</t>
+        </is>
+      </c>
+      <c r="B681" t="inlineStr">
+        <is>
+          <t>PRACHI  SEN</t>
+        </is>
+      </c>
+      <c r="C681" t="inlineStr">
+        <is>
+          <t>BISHWAK SEN KUMAR</t>
+        </is>
+      </c>
+      <c r="D681" t="inlineStr">
+        <is>
+          <t>KANCHAN KUMARI</t>
+        </is>
+      </c>
+      <c r="E681" t="inlineStr">
+        <is>
+          <t>IX</t>
+        </is>
+      </c>
+      <c r="F681" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" t="inlineStr">
+        <is>
+          <t>10,Feb</t>
+        </is>
+      </c>
+      <c r="B682" t="inlineStr">
+        <is>
+          <t>KISHU RAJ</t>
+        </is>
+      </c>
+      <c r="C682" t="inlineStr">
+        <is>
+          <t>GAUTAM SHARMA</t>
+        </is>
+      </c>
+      <c r="D682" t="inlineStr">
+        <is>
+          <t>PRATIMA DEVI</t>
+        </is>
+      </c>
+      <c r="E682" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="F682" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Birthday Data Master.xlsx
+++ b/Birthday Data Master.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F682"/>
+  <dimension ref="A1:F688"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.6" customWidth="1" min="1" max="1"/>
@@ -22248,6 +22248,198 @@
         </is>
       </c>
     </row>
+    <row r="683">
+      <c r="A683" t="inlineStr">
+        <is>
+          <t>11,Feb</t>
+        </is>
+      </c>
+      <c r="B683" t="inlineStr">
+        <is>
+          <t>AYANSH KUMAR</t>
+        </is>
+      </c>
+      <c r="C683" t="inlineStr">
+        <is>
+          <t>PRINCE KUMAR</t>
+        </is>
+      </c>
+      <c r="D683" t="inlineStr">
+        <is>
+          <t>PUSHPA KUMARI</t>
+        </is>
+      </c>
+      <c r="E683" t="inlineStr">
+        <is>
+          <t>LKG</t>
+        </is>
+      </c>
+      <c r="F683" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" t="inlineStr">
+        <is>
+          <t>11,Feb</t>
+        </is>
+      </c>
+      <c r="B684" t="inlineStr">
+        <is>
+          <t>NUTAN KUMARI</t>
+        </is>
+      </c>
+      <c r="C684" t="inlineStr">
+        <is>
+          <t>RAHUL KUMAR</t>
+        </is>
+      </c>
+      <c r="D684" t="inlineStr">
+        <is>
+          <t>PINKI KUMARI</t>
+        </is>
+      </c>
+      <c r="E684" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="F684" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" t="inlineStr">
+        <is>
+          <t>11,Feb</t>
+        </is>
+      </c>
+      <c r="B685" t="inlineStr">
+        <is>
+          <t>SIYA  KUMARI</t>
+        </is>
+      </c>
+      <c r="C685" t="inlineStr">
+        <is>
+          <t>JAY PRAKASH KUMAR</t>
+        </is>
+      </c>
+      <c r="D685" t="inlineStr">
+        <is>
+          <t>KANTI DEVI</t>
+        </is>
+      </c>
+      <c r="E685" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="F685" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" t="inlineStr">
+        <is>
+          <t>11,Feb</t>
+        </is>
+      </c>
+      <c r="B686" t="inlineStr">
+        <is>
+          <t>ADARSH ANAND</t>
+        </is>
+      </c>
+      <c r="C686" t="inlineStr">
+        <is>
+          <t>DHIRAJ KUMAR SINHA</t>
+        </is>
+      </c>
+      <c r="D686" t="inlineStr">
+        <is>
+          <t>RASHMI SRIVASTAVA</t>
+        </is>
+      </c>
+      <c r="E686" t="inlineStr">
+        <is>
+          <t>VII</t>
+        </is>
+      </c>
+      <c r="F686" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" t="inlineStr">
+        <is>
+          <t>11,Feb</t>
+        </is>
+      </c>
+      <c r="B687" t="inlineStr">
+        <is>
+          <t>Vaishnav KUMAR</t>
+        </is>
+      </c>
+      <c r="C687" t="inlineStr">
+        <is>
+          <t>Rakesh Kumar</t>
+        </is>
+      </c>
+      <c r="D687" t="inlineStr">
+        <is>
+          <t>Chummi Kumari</t>
+        </is>
+      </c>
+      <c r="E687" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F687" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" t="inlineStr">
+        <is>
+          <t>11,Feb</t>
+        </is>
+      </c>
+      <c r="B688" t="inlineStr">
+        <is>
+          <t>VIJETA KUMARI</t>
+        </is>
+      </c>
+      <c r="C688" t="inlineStr">
+        <is>
+          <t>RAKESH KUMAR</t>
+        </is>
+      </c>
+      <c r="D688" t="inlineStr">
+        <is>
+          <t>SUNITA KUMARI</t>
+        </is>
+      </c>
+      <c r="E688" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="F688" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Birthday Data Master.xlsx
+++ b/Birthday Data Master.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F688"/>
+  <dimension ref="A1:F703"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.6" customWidth="1" min="1" max="1"/>
@@ -22440,6 +22440,486 @@
         </is>
       </c>
     </row>
+    <row r="689">
+      <c r="A689" t="inlineStr">
+        <is>
+          <t>12,Feb</t>
+        </is>
+      </c>
+      <c r="B689" t="inlineStr">
+        <is>
+          <t>AALYA</t>
+        </is>
+      </c>
+      <c r="C689" t="inlineStr">
+        <is>
+          <t>ANIL KUMAR SAXENA</t>
+        </is>
+      </c>
+      <c r="D689" t="inlineStr">
+        <is>
+          <t>NISHU KUMARI</t>
+        </is>
+      </c>
+      <c r="E689" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="F689" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" t="inlineStr">
+        <is>
+          <t>12,Feb</t>
+        </is>
+      </c>
+      <c r="B690" t="inlineStr">
+        <is>
+          <t>Dhanlaxmi Kumari</t>
+        </is>
+      </c>
+      <c r="C690" t="inlineStr">
+        <is>
+          <t>Indra Kumar Singh</t>
+        </is>
+      </c>
+      <c r="D690" t="inlineStr">
+        <is>
+          <t>Parwati Devi</t>
+        </is>
+      </c>
+      <c r="E690" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F690" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" t="inlineStr">
+        <is>
+          <t>12,Feb</t>
+        </is>
+      </c>
+      <c r="B691" t="inlineStr">
+        <is>
+          <t>Muskan Kumari</t>
+        </is>
+      </c>
+      <c r="C691" t="inlineStr">
+        <is>
+          <t>Ratnesh Chandra Pandey</t>
+        </is>
+      </c>
+      <c r="D691" t="inlineStr">
+        <is>
+          <t>Santoshi Kumari</t>
+        </is>
+      </c>
+      <c r="E691" t="inlineStr">
+        <is>
+          <t>IX</t>
+        </is>
+      </c>
+      <c r="F691" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" t="inlineStr">
+        <is>
+          <t>12,Feb</t>
+        </is>
+      </c>
+      <c r="B692" t="inlineStr">
+        <is>
+          <t>SHYAM KISHOR SHARMA</t>
+        </is>
+      </c>
+      <c r="C692" t="inlineStr">
+        <is>
+          <t>RANVIJAY KUMAR</t>
+        </is>
+      </c>
+      <c r="D692" t="inlineStr">
+        <is>
+          <t>MALA</t>
+        </is>
+      </c>
+      <c r="E692" t="inlineStr">
+        <is>
+          <t>IV</t>
+        </is>
+      </c>
+      <c r="F692" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" t="inlineStr">
+        <is>
+          <t>12,Feb</t>
+        </is>
+      </c>
+      <c r="B693" t="inlineStr">
+        <is>
+          <t>SHIVAM PRAKASH</t>
+        </is>
+      </c>
+      <c r="C693" t="inlineStr">
+        <is>
+          <t>DR AJEET KUMAR</t>
+        </is>
+      </c>
+      <c r="D693" t="inlineStr">
+        <is>
+          <t>RASHMI RANI</t>
+        </is>
+      </c>
+      <c r="E693" t="inlineStr">
+        <is>
+          <t>VIII</t>
+        </is>
+      </c>
+      <c r="F693" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" t="inlineStr">
+        <is>
+          <t>12,Feb</t>
+        </is>
+      </c>
+      <c r="B694" t="inlineStr">
+        <is>
+          <t>SRISHTI RAJ</t>
+        </is>
+      </c>
+      <c r="C694" t="inlineStr">
+        <is>
+          <t>GIRISH KUMAR</t>
+        </is>
+      </c>
+      <c r="D694" t="inlineStr">
+        <is>
+          <t>ARPANA KUMARI</t>
+        </is>
+      </c>
+      <c r="E694" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="F694" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" t="inlineStr">
+        <is>
+          <t>12,Feb</t>
+        </is>
+      </c>
+      <c r="B695" t="inlineStr">
+        <is>
+          <t>AKANKSHA KUMARI</t>
+        </is>
+      </c>
+      <c r="C695" t="inlineStr">
+        <is>
+          <t>KRISHNA KUMAR</t>
+        </is>
+      </c>
+      <c r="D695" t="inlineStr">
+        <is>
+          <t>NEERA KUMARI</t>
+        </is>
+      </c>
+      <c r="E695" t="inlineStr">
+        <is>
+          <t>VII</t>
+        </is>
+      </c>
+      <c r="F695" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" t="inlineStr">
+        <is>
+          <t>12,Feb</t>
+        </is>
+      </c>
+      <c r="B696" t="inlineStr">
+        <is>
+          <t>ARNAV ANAND</t>
+        </is>
+      </c>
+      <c r="C696" t="inlineStr">
+        <is>
+          <t>SHREE KANT KUMAR</t>
+        </is>
+      </c>
+      <c r="D696" t="inlineStr">
+        <is>
+          <t>RANI ARPANA</t>
+        </is>
+      </c>
+      <c r="E696" t="inlineStr">
+        <is>
+          <t>VII</t>
+        </is>
+      </c>
+      <c r="F696" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" t="inlineStr">
+        <is>
+          <t>12,Feb</t>
+        </is>
+      </c>
+      <c r="B697" t="inlineStr">
+        <is>
+          <t>ANKIT  KUMAR</t>
+        </is>
+      </c>
+      <c r="C697" t="inlineStr">
+        <is>
+          <t>ANIL KUMAR</t>
+        </is>
+      </c>
+      <c r="D697" t="inlineStr">
+        <is>
+          <t>RUPA KUMARI</t>
+        </is>
+      </c>
+      <c r="E697" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="F697" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" t="inlineStr">
+        <is>
+          <t>12,Feb</t>
+        </is>
+      </c>
+      <c r="B698" t="inlineStr">
+        <is>
+          <t>Shahil Raj  Tripathi</t>
+        </is>
+      </c>
+      <c r="C698" t="inlineStr">
+        <is>
+          <t>Sanjeev Kumar</t>
+        </is>
+      </c>
+      <c r="D698" t="inlineStr">
+        <is>
+          <t>Sarita Pandey</t>
+        </is>
+      </c>
+      <c r="E698" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F698" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" t="inlineStr">
+        <is>
+          <t>12,Feb</t>
+        </is>
+      </c>
+      <c r="B699" t="inlineStr">
+        <is>
+          <t>Amrit Raj</t>
+        </is>
+      </c>
+      <c r="C699" t="inlineStr">
+        <is>
+          <t>Sunil Kr.Singh</t>
+        </is>
+      </c>
+      <c r="D699" t="inlineStr">
+        <is>
+          <t>Pratima Kumari</t>
+        </is>
+      </c>
+      <c r="E699" t="inlineStr">
+        <is>
+          <t>IX</t>
+        </is>
+      </c>
+      <c r="F699" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" t="inlineStr">
+        <is>
+          <t>12,Feb</t>
+        </is>
+      </c>
+      <c r="B700" t="inlineStr">
+        <is>
+          <t>SHREYA KUMARI</t>
+        </is>
+      </c>
+      <c r="C700" t="inlineStr">
+        <is>
+          <t>AVINASH KUMAR</t>
+        </is>
+      </c>
+      <c r="D700" t="inlineStr">
+        <is>
+          <t>ANITA KUMARI</t>
+        </is>
+      </c>
+      <c r="E700" t="inlineStr">
+        <is>
+          <t>IV</t>
+        </is>
+      </c>
+      <c r="F700" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" t="inlineStr">
+        <is>
+          <t>12,Feb</t>
+        </is>
+      </c>
+      <c r="B701" t="inlineStr">
+        <is>
+          <t>Tejaswi Kumari vats</t>
+        </is>
+      </c>
+      <c r="C701" t="inlineStr">
+        <is>
+          <t>Dharmendra Kumar</t>
+        </is>
+      </c>
+      <c r="D701" t="inlineStr">
+        <is>
+          <t>Mamta Kumari</t>
+        </is>
+      </c>
+      <c r="E701" t="inlineStr">
+        <is>
+          <t>VIII</t>
+        </is>
+      </c>
+      <c r="F701" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" t="inlineStr">
+        <is>
+          <t>12,Feb</t>
+        </is>
+      </c>
+      <c r="B702" t="inlineStr">
+        <is>
+          <t>Ansh Raj</t>
+        </is>
+      </c>
+      <c r="C702" t="inlineStr">
+        <is>
+          <t>Santosh Kumar</t>
+        </is>
+      </c>
+      <c r="D702" t="inlineStr">
+        <is>
+          <t>Poonam</t>
+        </is>
+      </c>
+      <c r="E702" t="inlineStr">
+        <is>
+          <t>VIII</t>
+        </is>
+      </c>
+      <c r="F702" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" t="inlineStr">
+        <is>
+          <t>12,Feb</t>
+        </is>
+      </c>
+      <c r="B703" t="inlineStr">
+        <is>
+          <t>SHUBH KUMAR</t>
+        </is>
+      </c>
+      <c r="C703" t="inlineStr">
+        <is>
+          <t>NEERAJ KUMAR</t>
+        </is>
+      </c>
+      <c r="D703" t="inlineStr">
+        <is>
+          <t>JYOTI KUMARI</t>
+        </is>
+      </c>
+      <c r="E703" t="inlineStr">
+        <is>
+          <t>LKG</t>
+        </is>
+      </c>
+      <c r="F703" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Birthday Data Master.xlsx
+++ b/Birthday Data Master.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F703"/>
+  <dimension ref="A1:F710"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.6" customWidth="1" min="1" max="1"/>
@@ -22920,6 +22920,230 @@
         </is>
       </c>
     </row>
+    <row r="704">
+      <c r="A704" t="inlineStr">
+        <is>
+          <t>13,Feb</t>
+        </is>
+      </c>
+      <c r="B704" t="inlineStr">
+        <is>
+          <t>ANSHIKA RAJ</t>
+        </is>
+      </c>
+      <c r="C704" t="inlineStr">
+        <is>
+          <t>VINAY KUMAR</t>
+        </is>
+      </c>
+      <c r="D704" t="inlineStr">
+        <is>
+          <t>PUSHPA KUMARI</t>
+        </is>
+      </c>
+      <c r="E704" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F704" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" t="inlineStr">
+        <is>
+          <t>13,Feb</t>
+        </is>
+      </c>
+      <c r="B705" t="inlineStr">
+        <is>
+          <t>Ayush RAJ</t>
+        </is>
+      </c>
+      <c r="C705" t="inlineStr">
+        <is>
+          <t>Rajesh Kumar</t>
+        </is>
+      </c>
+      <c r="D705" t="inlineStr">
+        <is>
+          <t>Poonam Kumari</t>
+        </is>
+      </c>
+      <c r="E705" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F705" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" t="inlineStr">
+        <is>
+          <t>13,Feb</t>
+        </is>
+      </c>
+      <c r="B706" t="inlineStr">
+        <is>
+          <t>PRIYA  KUMARI</t>
+        </is>
+      </c>
+      <c r="C706" t="inlineStr">
+        <is>
+          <t>SURENDRA KUMAR</t>
+        </is>
+      </c>
+      <c r="D706" t="inlineStr">
+        <is>
+          <t>BIBHA KUMARI</t>
+        </is>
+      </c>
+      <c r="E706" t="inlineStr">
+        <is>
+          <t>VII</t>
+        </is>
+      </c>
+      <c r="F706" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" t="inlineStr">
+        <is>
+          <t>13,Feb</t>
+        </is>
+      </c>
+      <c r="B707" t="inlineStr">
+        <is>
+          <t>VARSHA SINGH</t>
+        </is>
+      </c>
+      <c r="C707" t="inlineStr">
+        <is>
+          <t>PAWAN KUMAR</t>
+        </is>
+      </c>
+      <c r="D707" t="inlineStr">
+        <is>
+          <t>SUMAN KUMARI</t>
+        </is>
+      </c>
+      <c r="E707" t="inlineStr">
+        <is>
+          <t>VII</t>
+        </is>
+      </c>
+      <c r="F707" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" t="inlineStr">
+        <is>
+          <t>13,Feb</t>
+        </is>
+      </c>
+      <c r="B708" t="inlineStr">
+        <is>
+          <t>SIVANGI KUMARI</t>
+        </is>
+      </c>
+      <c r="C708" t="inlineStr">
+        <is>
+          <t>MANISH KUMAR</t>
+        </is>
+      </c>
+      <c r="D708" t="inlineStr">
+        <is>
+          <t>AMRITA KUMARI</t>
+        </is>
+      </c>
+      <c r="E708" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="F708" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" t="inlineStr">
+        <is>
+          <t>13,Feb</t>
+        </is>
+      </c>
+      <c r="B709" t="inlineStr">
+        <is>
+          <t>SWETA KUMARI</t>
+        </is>
+      </c>
+      <c r="C709" t="inlineStr">
+        <is>
+          <t>SURENDRA KUMAR</t>
+        </is>
+      </c>
+      <c r="D709" t="inlineStr">
+        <is>
+          <t>BIBHA DEVI</t>
+        </is>
+      </c>
+      <c r="E709" t="inlineStr">
+        <is>
+          <t>VII</t>
+        </is>
+      </c>
+      <c r="F709" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" t="inlineStr">
+        <is>
+          <t>13,Feb</t>
+        </is>
+      </c>
+      <c r="B710" t="inlineStr">
+        <is>
+          <t>GYANENDRA KUMAR</t>
+        </is>
+      </c>
+      <c r="C710" t="inlineStr">
+        <is>
+          <t>NAVAL KISHOR SHASTRI</t>
+        </is>
+      </c>
+      <c r="D710" t="inlineStr">
+        <is>
+          <t>JULI DEVI</t>
+        </is>
+      </c>
+      <c r="E710" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="F710" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Birthday Data Master.xlsx
+++ b/Birthday Data Master.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F710"/>
+  <dimension ref="A1:F727"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.6" customWidth="1" min="1" max="1"/>
@@ -23144,6 +23144,550 @@
         </is>
       </c>
     </row>
+    <row r="711">
+      <c r="A711" t="inlineStr">
+        <is>
+          <t>14,Feb</t>
+        </is>
+      </c>
+      <c r="B711" t="inlineStr">
+        <is>
+          <t>Ankit Kumar</t>
+        </is>
+      </c>
+      <c r="C711" t="inlineStr">
+        <is>
+          <t>Akshay Kumar</t>
+        </is>
+      </c>
+      <c r="D711" t="inlineStr">
+        <is>
+          <t>Guddi Devi</t>
+        </is>
+      </c>
+      <c r="E711" t="inlineStr">
+        <is>
+          <t>IX</t>
+        </is>
+      </c>
+      <c r="F711" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" t="inlineStr">
+        <is>
+          <t>14,Feb</t>
+        </is>
+      </c>
+      <c r="B712" t="inlineStr">
+        <is>
+          <t>TRISHA</t>
+        </is>
+      </c>
+      <c r="C712" t="inlineStr">
+        <is>
+          <t>BRAJESH KUMAR PANDEY</t>
+        </is>
+      </c>
+      <c r="D712" t="inlineStr">
+        <is>
+          <t>DIMPI KUMARI</t>
+        </is>
+      </c>
+      <c r="E712" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="F712" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" t="inlineStr">
+        <is>
+          <t>14,Feb</t>
+        </is>
+      </c>
+      <c r="B713" t="inlineStr">
+        <is>
+          <t>Manav  Ranjan</t>
+        </is>
+      </c>
+      <c r="C713" t="inlineStr">
+        <is>
+          <t>Manjay Lal</t>
+        </is>
+      </c>
+      <c r="D713" t="inlineStr">
+        <is>
+          <t>Renuka KUMARI</t>
+        </is>
+      </c>
+      <c r="E713" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F713" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" t="inlineStr">
+        <is>
+          <t>14,Feb</t>
+        </is>
+      </c>
+      <c r="B714" t="inlineStr">
+        <is>
+          <t>Ishani Anand</t>
+        </is>
+      </c>
+      <c r="C714" t="inlineStr">
+        <is>
+          <t>Pankaj Burman</t>
+        </is>
+      </c>
+      <c r="D714" t="inlineStr">
+        <is>
+          <t>Punam</t>
+        </is>
+      </c>
+      <c r="E714" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="F714" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="715">
+      <c r="A715" t="inlineStr">
+        <is>
+          <t>14,Feb</t>
+        </is>
+      </c>
+      <c r="B715" t="inlineStr">
+        <is>
+          <t>MANIKANT KUMAR</t>
+        </is>
+      </c>
+      <c r="C715" t="inlineStr">
+        <is>
+          <t>NITISH KUMAR</t>
+        </is>
+      </c>
+      <c r="D715" t="inlineStr">
+        <is>
+          <t>SANJU DEVI</t>
+        </is>
+      </c>
+      <c r="E715" t="inlineStr">
+        <is>
+          <t>IV</t>
+        </is>
+      </c>
+      <c r="F715" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" t="inlineStr">
+        <is>
+          <t>14,Feb</t>
+        </is>
+      </c>
+      <c r="B716" t="inlineStr">
+        <is>
+          <t>ADITYA KUMAR</t>
+        </is>
+      </c>
+      <c r="C716" t="inlineStr">
+        <is>
+          <t>BINOD KUMAR</t>
+        </is>
+      </c>
+      <c r="D716" t="inlineStr">
+        <is>
+          <t>MAMTA KUMARI</t>
+        </is>
+      </c>
+      <c r="E716" t="inlineStr">
+        <is>
+          <t>XI</t>
+        </is>
+      </c>
+      <c r="F716" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" t="inlineStr">
+        <is>
+          <t>14,Feb</t>
+        </is>
+      </c>
+      <c r="B717" t="inlineStr">
+        <is>
+          <t>NISHANT KUMAR</t>
+        </is>
+      </c>
+      <c r="C717" t="inlineStr">
+        <is>
+          <t>NIRAJ KUMAR</t>
+        </is>
+      </c>
+      <c r="D717" t="inlineStr">
+        <is>
+          <t>RINKU DEVI</t>
+        </is>
+      </c>
+      <c r="E717" t="inlineStr">
+        <is>
+          <t>IV</t>
+        </is>
+      </c>
+      <c r="F717" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="718">
+      <c r="A718" t="inlineStr">
+        <is>
+          <t>14,Feb</t>
+        </is>
+      </c>
+      <c r="B718" t="inlineStr">
+        <is>
+          <t>RISHAN KUMAR</t>
+        </is>
+      </c>
+      <c r="C718" t="inlineStr">
+        <is>
+          <t>RANJEET KUMAR</t>
+        </is>
+      </c>
+      <c r="D718" t="inlineStr">
+        <is>
+          <t>PUJA KUMARI</t>
+        </is>
+      </c>
+      <c r="E718" t="inlineStr">
+        <is>
+          <t>LKG</t>
+        </is>
+      </c>
+      <c r="F718" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" t="inlineStr">
+        <is>
+          <t>14,Feb</t>
+        </is>
+      </c>
+      <c r="B719" t="inlineStr">
+        <is>
+          <t>Rishabh Raj</t>
+        </is>
+      </c>
+      <c r="C719" t="inlineStr">
+        <is>
+          <t>Krishna Kisore Jha</t>
+        </is>
+      </c>
+      <c r="D719" t="inlineStr">
+        <is>
+          <t>Kajal Devi</t>
+        </is>
+      </c>
+      <c r="E719" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F719" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" t="inlineStr">
+        <is>
+          <t>14,Feb</t>
+        </is>
+      </c>
+      <c r="B720" t="inlineStr">
+        <is>
+          <t>Shivansh Raj</t>
+        </is>
+      </c>
+      <c r="C720" t="inlineStr">
+        <is>
+          <t>Upendra Kumar</t>
+        </is>
+      </c>
+      <c r="D720" t="inlineStr">
+        <is>
+          <t>Pinki Kumari</t>
+        </is>
+      </c>
+      <c r="E720" t="inlineStr">
+        <is>
+          <t>IX</t>
+        </is>
+      </c>
+      <c r="F720" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="721">
+      <c r="A721" t="inlineStr">
+        <is>
+          <t>14,Feb</t>
+        </is>
+      </c>
+      <c r="B721" t="inlineStr">
+        <is>
+          <t>TEJASHVI BARDHAN</t>
+        </is>
+      </c>
+      <c r="C721" t="inlineStr">
+        <is>
+          <t>GYAN BARDHAN</t>
+        </is>
+      </c>
+      <c r="D721" t="inlineStr">
+        <is>
+          <t>MUNI BARDHAN</t>
+        </is>
+      </c>
+      <c r="E721" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="F721" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722" t="inlineStr">
+        <is>
+          <t>14,Feb</t>
+        </is>
+      </c>
+      <c r="B722" t="inlineStr">
+        <is>
+          <t>JAY NARAYAN</t>
+        </is>
+      </c>
+      <c r="C722" t="inlineStr">
+        <is>
+          <t>LAXMI KANT KUMAR</t>
+        </is>
+      </c>
+      <c r="D722" t="inlineStr">
+        <is>
+          <t>NEHA KUMARI</t>
+        </is>
+      </c>
+      <c r="E722" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="F722" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" t="inlineStr">
+        <is>
+          <t>14,Feb</t>
+        </is>
+      </c>
+      <c r="B723" t="inlineStr">
+        <is>
+          <t>ANABIA FATIMA</t>
+        </is>
+      </c>
+      <c r="C723" t="inlineStr">
+        <is>
+          <t>MD AKHTAR HUSSAIN</t>
+        </is>
+      </c>
+      <c r="D723" t="inlineStr">
+        <is>
+          <t>SULTANA DARAKHSHAN</t>
+        </is>
+      </c>
+      <c r="E723" t="inlineStr">
+        <is>
+          <t>UKG</t>
+        </is>
+      </c>
+      <c r="F723" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" t="inlineStr">
+        <is>
+          <t>14,Feb</t>
+        </is>
+      </c>
+      <c r="B724" t="inlineStr">
+        <is>
+          <t>DEEP SHIKHA KUMARI</t>
+        </is>
+      </c>
+      <c r="C724" t="inlineStr">
+        <is>
+          <t>ABHAY KUMAR</t>
+        </is>
+      </c>
+      <c r="D724" t="inlineStr">
+        <is>
+          <t>KIRAN KUMARI</t>
+        </is>
+      </c>
+      <c r="E724" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="F724" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" t="inlineStr">
+        <is>
+          <t>14,Feb</t>
+        </is>
+      </c>
+      <c r="B725" t="inlineStr">
+        <is>
+          <t>AYUSHI KUMARI</t>
+        </is>
+      </c>
+      <c r="C725" t="inlineStr">
+        <is>
+          <t>NEERAJ KUMAR</t>
+        </is>
+      </c>
+      <c r="D725" t="inlineStr">
+        <is>
+          <t>RENU KUMARI</t>
+        </is>
+      </c>
+      <c r="E725" t="inlineStr">
+        <is>
+          <t>VII</t>
+        </is>
+      </c>
+      <c r="F725" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="726">
+      <c r="A726" t="inlineStr">
+        <is>
+          <t>14,Feb</t>
+        </is>
+      </c>
+      <c r="B726" t="inlineStr">
+        <is>
+          <t>Priyam Raj</t>
+        </is>
+      </c>
+      <c r="C726" t="inlineStr">
+        <is>
+          <t>Pankaj Kumar Sharma</t>
+        </is>
+      </c>
+      <c r="D726" t="inlineStr">
+        <is>
+          <t>Sadhana Kumari</t>
+        </is>
+      </c>
+      <c r="E726" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F726" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" t="inlineStr">
+        <is>
+          <t>14,Feb</t>
+        </is>
+      </c>
+      <c r="B727" t="inlineStr">
+        <is>
+          <t>Ravish Kumar</t>
+        </is>
+      </c>
+      <c r="C727" t="inlineStr">
+        <is>
+          <t>Dhananjay Kumar</t>
+        </is>
+      </c>
+      <c r="D727" t="inlineStr">
+        <is>
+          <t>Vandana Devi</t>
+        </is>
+      </c>
+      <c r="E727" t="inlineStr">
+        <is>
+          <t>VIII</t>
+        </is>
+      </c>
+      <c r="F727" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Birthday Data Master.xlsx
+++ b/Birthday Data Master.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F727"/>
+  <dimension ref="A1:F740"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.6" customWidth="1" min="1" max="1"/>
@@ -23688,6 +23688,422 @@
         </is>
       </c>
     </row>
+    <row r="728">
+      <c r="A728" t="inlineStr">
+        <is>
+          <t>15,Feb</t>
+        </is>
+      </c>
+      <c r="B728" t="inlineStr">
+        <is>
+          <t>RISHU RAJ</t>
+        </is>
+      </c>
+      <c r="C728" t="inlineStr">
+        <is>
+          <t>RAJESH KUMAR</t>
+        </is>
+      </c>
+      <c r="D728" t="inlineStr">
+        <is>
+          <t>ARTI</t>
+        </is>
+      </c>
+      <c r="E728" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="F728" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" t="inlineStr">
+        <is>
+          <t>15,Feb</t>
+        </is>
+      </c>
+      <c r="B729" t="inlineStr">
+        <is>
+          <t>Suman Kumar</t>
+        </is>
+      </c>
+      <c r="C729" t="inlineStr">
+        <is>
+          <t>Pushpendra Kumar</t>
+        </is>
+      </c>
+      <c r="D729" t="inlineStr">
+        <is>
+          <t>Sushmita Kumari</t>
+        </is>
+      </c>
+      <c r="E729" t="inlineStr">
+        <is>
+          <t>IX</t>
+        </is>
+      </c>
+      <c r="F729" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" t="inlineStr">
+        <is>
+          <t>15,Feb</t>
+        </is>
+      </c>
+      <c r="B730" t="inlineStr">
+        <is>
+          <t>SHREYANSH RAJ</t>
+        </is>
+      </c>
+      <c r="C730" t="inlineStr">
+        <is>
+          <t>PANCHAM KUMAR</t>
+        </is>
+      </c>
+      <c r="D730" t="inlineStr">
+        <is>
+          <t>PRIYANKA KUMARI</t>
+        </is>
+      </c>
+      <c r="E730" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F730" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" t="inlineStr">
+        <is>
+          <t>15,Feb</t>
+        </is>
+      </c>
+      <c r="B731" t="inlineStr">
+        <is>
+          <t>PRANSHU SHARMA</t>
+        </is>
+      </c>
+      <c r="C731" t="inlineStr">
+        <is>
+          <t>ABHIJIT BHARDWAJ</t>
+        </is>
+      </c>
+      <c r="D731" t="inlineStr">
+        <is>
+          <t>ANU KUMARI</t>
+        </is>
+      </c>
+      <c r="E731" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="F731" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" t="inlineStr">
+        <is>
+          <t>15,Feb</t>
+        </is>
+      </c>
+      <c r="B732" t="inlineStr">
+        <is>
+          <t>DEVANSH RAJ</t>
+        </is>
+      </c>
+      <c r="C732" t="inlineStr">
+        <is>
+          <t>MANISH KUMAR</t>
+        </is>
+      </c>
+      <c r="D732" t="inlineStr">
+        <is>
+          <t>NIKI KUMARI</t>
+        </is>
+      </c>
+      <c r="E732" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F732" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" t="inlineStr">
+        <is>
+          <t>15,Feb</t>
+        </is>
+      </c>
+      <c r="B733" t="inlineStr">
+        <is>
+          <t>Anshu  Kumar</t>
+        </is>
+      </c>
+      <c r="C733" t="inlineStr">
+        <is>
+          <t>Sunil Kumar</t>
+        </is>
+      </c>
+      <c r="D733" t="inlineStr">
+        <is>
+          <t>Anju Devi</t>
+        </is>
+      </c>
+      <c r="E733" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F733" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="734">
+      <c r="A734" t="inlineStr">
+        <is>
+          <t>15,Feb</t>
+        </is>
+      </c>
+      <c r="B734" t="inlineStr">
+        <is>
+          <t>AASHISH RAJ</t>
+        </is>
+      </c>
+      <c r="C734" t="inlineStr">
+        <is>
+          <t>DHANANJAY KUMAR DIWAKAR</t>
+        </is>
+      </c>
+      <c r="D734" t="inlineStr">
+        <is>
+          <t>SONI KUMARI</t>
+        </is>
+      </c>
+      <c r="E734" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="F734" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735" t="inlineStr">
+        <is>
+          <t>15,Feb</t>
+        </is>
+      </c>
+      <c r="B735" t="inlineStr">
+        <is>
+          <t>ADITYA RAJ</t>
+        </is>
+      </c>
+      <c r="C735" t="inlineStr">
+        <is>
+          <t>RAJESH KUMAR</t>
+        </is>
+      </c>
+      <c r="D735" t="inlineStr">
+        <is>
+          <t>ARTI</t>
+        </is>
+      </c>
+      <c r="E735" t="inlineStr">
+        <is>
+          <t>IV</t>
+        </is>
+      </c>
+      <c r="F735" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" t="inlineStr">
+        <is>
+          <t>15,Feb</t>
+        </is>
+      </c>
+      <c r="B736" t="inlineStr">
+        <is>
+          <t>RISHABH RANJAN</t>
+        </is>
+      </c>
+      <c r="C736" t="inlineStr">
+        <is>
+          <t>Mukesh KUMAR</t>
+        </is>
+      </c>
+      <c r="D736" t="inlineStr">
+        <is>
+          <t>PUNAM KUMARI</t>
+        </is>
+      </c>
+      <c r="E736" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="F736" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="737">
+      <c r="A737" t="inlineStr">
+        <is>
+          <t>15,Feb</t>
+        </is>
+      </c>
+      <c r="B737" t="inlineStr">
+        <is>
+          <t>PRIYANSHU KUMAR</t>
+        </is>
+      </c>
+      <c r="C737" t="inlineStr">
+        <is>
+          <t>SANOJ KUMAR</t>
+        </is>
+      </c>
+      <c r="D737" t="inlineStr">
+        <is>
+          <t>RINKU DEVI</t>
+        </is>
+      </c>
+      <c r="E737" t="inlineStr">
+        <is>
+          <t>VII</t>
+        </is>
+      </c>
+      <c r="F737" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="738">
+      <c r="A738" t="inlineStr">
+        <is>
+          <t>15,Feb</t>
+        </is>
+      </c>
+      <c r="B738" t="inlineStr">
+        <is>
+          <t>ANANYA KUMARI</t>
+        </is>
+      </c>
+      <c r="C738" t="inlineStr">
+        <is>
+          <t>AMIT KUMAR</t>
+        </is>
+      </c>
+      <c r="D738" t="inlineStr">
+        <is>
+          <t>CHANDRASHILA KUMARI</t>
+        </is>
+      </c>
+      <c r="E738" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="F738" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="739">
+      <c r="A739" t="inlineStr">
+        <is>
+          <t>15,Feb</t>
+        </is>
+      </c>
+      <c r="B739" t="inlineStr">
+        <is>
+          <t>Mayank Kumar</t>
+        </is>
+      </c>
+      <c r="C739" t="inlineStr">
+        <is>
+          <t>Mritunjay Kumar</t>
+        </is>
+      </c>
+      <c r="D739" t="inlineStr">
+        <is>
+          <t>Sunita Devi</t>
+        </is>
+      </c>
+      <c r="E739" t="inlineStr">
+        <is>
+          <t>IX</t>
+        </is>
+      </c>
+      <c r="F739" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="740">
+      <c r="A740" t="inlineStr">
+        <is>
+          <t>15,Feb</t>
+        </is>
+      </c>
+      <c r="B740" t="inlineStr">
+        <is>
+          <t>Arhaan Ahmad</t>
+        </is>
+      </c>
+      <c r="C740" t="inlineStr">
+        <is>
+          <t>Qaisher Shamim</t>
+        </is>
+      </c>
+      <c r="D740" t="inlineStr">
+        <is>
+          <t>Arshadi Khatoon</t>
+        </is>
+      </c>
+      <c r="E740" t="inlineStr">
+        <is>
+          <t>VIII</t>
+        </is>
+      </c>
+      <c r="F740" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Birthday Data Master.xlsx
+++ b/Birthday Data Master.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F740"/>
+  <dimension ref="A1:F746"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.6" customWidth="1" min="1" max="1"/>
@@ -24104,6 +24104,198 @@
         </is>
       </c>
     </row>
+    <row r="741">
+      <c r="A741" t="inlineStr">
+        <is>
+          <t>16,Feb</t>
+        </is>
+      </c>
+      <c r="B741" t="inlineStr">
+        <is>
+          <t>Satyam Kishan   Kumar</t>
+        </is>
+      </c>
+      <c r="C741" t="inlineStr">
+        <is>
+          <t>Sudhir Kumar</t>
+        </is>
+      </c>
+      <c r="D741" t="inlineStr">
+        <is>
+          <t>Asha Kumari</t>
+        </is>
+      </c>
+      <c r="E741" t="inlineStr">
+        <is>
+          <t>IX</t>
+        </is>
+      </c>
+      <c r="F741" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742" t="inlineStr">
+        <is>
+          <t>16,Feb</t>
+        </is>
+      </c>
+      <c r="B742" t="inlineStr">
+        <is>
+          <t>Saurav Kumar</t>
+        </is>
+      </c>
+      <c r="C742" t="inlineStr">
+        <is>
+          <t>Omprakash Kumar</t>
+        </is>
+      </c>
+      <c r="D742" t="inlineStr">
+        <is>
+          <t>Suryamani Devi</t>
+        </is>
+      </c>
+      <c r="E742" t="inlineStr">
+        <is>
+          <t>IX</t>
+        </is>
+      </c>
+      <c r="F742" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" t="inlineStr">
+        <is>
+          <t>16,Feb</t>
+        </is>
+      </c>
+      <c r="B743" t="inlineStr">
+        <is>
+          <t>Anand  Kumar</t>
+        </is>
+      </c>
+      <c r="C743" t="inlineStr">
+        <is>
+          <t>Binay Kumar</t>
+        </is>
+      </c>
+      <c r="D743" t="inlineStr">
+        <is>
+          <t>Chandrakala Kumari</t>
+        </is>
+      </c>
+      <c r="E743" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F743" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="744">
+      <c r="A744" t="inlineStr">
+        <is>
+          <t>16,Feb</t>
+        </is>
+      </c>
+      <c r="B744" t="inlineStr">
+        <is>
+          <t>PRACHI SHARMA</t>
+        </is>
+      </c>
+      <c r="C744" t="inlineStr">
+        <is>
+          <t>NIKANDAN KUMNAR</t>
+        </is>
+      </c>
+      <c r="D744" t="inlineStr">
+        <is>
+          <t>JYOTI KUMARI</t>
+        </is>
+      </c>
+      <c r="E744" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F744" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" t="inlineStr">
+        <is>
+          <t>16,Feb</t>
+        </is>
+      </c>
+      <c r="B745" t="inlineStr">
+        <is>
+          <t>PIYUSH KUMAR</t>
+        </is>
+      </c>
+      <c r="C745" t="inlineStr">
+        <is>
+          <t>VIKASH KUMAR</t>
+        </is>
+      </c>
+      <c r="D745" t="inlineStr">
+        <is>
+          <t>ARCHANA KUMARI</t>
+        </is>
+      </c>
+      <c r="E745" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="F745" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746" t="inlineStr">
+        <is>
+          <t>16,Feb</t>
+        </is>
+      </c>
+      <c r="B746" t="inlineStr">
+        <is>
+          <t>PUNIT KUMAR</t>
+        </is>
+      </c>
+      <c r="C746" t="inlineStr">
+        <is>
+          <t>VIKASH KUMAR</t>
+        </is>
+      </c>
+      <c r="D746" t="inlineStr">
+        <is>
+          <t>ARCHANA KUMARI</t>
+        </is>
+      </c>
+      <c r="E746" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="F746" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Birthday Data Master.xlsx
+++ b/Birthday Data Master.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F746"/>
+  <dimension ref="A1:F756"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.6" customWidth="1" min="1" max="1"/>
@@ -24296,6 +24296,326 @@
         </is>
       </c>
     </row>
+    <row r="747">
+      <c r="A747" t="inlineStr">
+        <is>
+          <t>17,Feb</t>
+        </is>
+      </c>
+      <c r="B747" t="inlineStr">
+        <is>
+          <t>SAKSHI PRIYA</t>
+        </is>
+      </c>
+      <c r="C747" t="inlineStr">
+        <is>
+          <t>SURESH KUMAR</t>
+        </is>
+      </c>
+      <c r="D747" t="inlineStr">
+        <is>
+          <t>MAMTA KUMARI</t>
+        </is>
+      </c>
+      <c r="E747" t="inlineStr">
+        <is>
+          <t>VIII</t>
+        </is>
+      </c>
+      <c r="F747" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="748">
+      <c r="A748" t="inlineStr">
+        <is>
+          <t>17,Feb</t>
+        </is>
+      </c>
+      <c r="B748" t="inlineStr">
+        <is>
+          <t>Aditya Kumar</t>
+        </is>
+      </c>
+      <c r="C748" t="inlineStr">
+        <is>
+          <t>Amrendra Kumar</t>
+        </is>
+      </c>
+      <c r="D748" t="inlineStr">
+        <is>
+          <t>Dauli Kumari</t>
+        </is>
+      </c>
+      <c r="E748" t="inlineStr">
+        <is>
+          <t>VIII</t>
+        </is>
+      </c>
+      <c r="F748" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="749">
+      <c r="A749" t="inlineStr">
+        <is>
+          <t>17,Feb</t>
+        </is>
+      </c>
+      <c r="B749" t="inlineStr">
+        <is>
+          <t>Shivam</t>
+        </is>
+      </c>
+      <c r="C749" t="inlineStr">
+        <is>
+          <t>Vijendra Kumar</t>
+        </is>
+      </c>
+      <c r="D749" t="inlineStr">
+        <is>
+          <t>Abha Rani</t>
+        </is>
+      </c>
+      <c r="E749" t="inlineStr">
+        <is>
+          <t>IV</t>
+        </is>
+      </c>
+      <c r="F749" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750" t="inlineStr">
+        <is>
+          <t>17,Feb</t>
+        </is>
+      </c>
+      <c r="B750" t="inlineStr">
+        <is>
+          <t>Atul Raj</t>
+        </is>
+      </c>
+      <c r="C750" t="inlineStr">
+        <is>
+          <t>Pawan Kumar</t>
+        </is>
+      </c>
+      <c r="D750" t="inlineStr">
+        <is>
+          <t>Chanchala Kumari</t>
+        </is>
+      </c>
+      <c r="E750" t="inlineStr">
+        <is>
+          <t>IX</t>
+        </is>
+      </c>
+      <c r="F750" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+    </row>
+    <row r="751">
+      <c r="A751" t="inlineStr">
+        <is>
+          <t>17,Feb</t>
+        </is>
+      </c>
+      <c r="B751" t="inlineStr">
+        <is>
+          <t>RISHABH KUMAR</t>
+        </is>
+      </c>
+      <c r="C751" t="inlineStr">
+        <is>
+          <t>NEERAJ KUMAR</t>
+        </is>
+      </c>
+      <c r="D751" t="inlineStr">
+        <is>
+          <t>JYOTI KUMARI</t>
+        </is>
+      </c>
+      <c r="E751" t="inlineStr">
+        <is>
+          <t>UKG</t>
+        </is>
+      </c>
+      <c r="F751" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="752">
+      <c r="A752" t="inlineStr">
+        <is>
+          <t>17,Feb</t>
+        </is>
+      </c>
+      <c r="B752" t="inlineStr">
+        <is>
+          <t>ARYAN RAJ</t>
+        </is>
+      </c>
+      <c r="C752" t="inlineStr">
+        <is>
+          <t>BIGAN THAKUR</t>
+        </is>
+      </c>
+      <c r="D752" t="inlineStr">
+        <is>
+          <t>SARITA KUMARI</t>
+        </is>
+      </c>
+      <c r="E752" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="F752" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="753">
+      <c r="A753" t="inlineStr">
+        <is>
+          <t>17,Feb</t>
+        </is>
+      </c>
+      <c r="B753" t="inlineStr">
+        <is>
+          <t>GOVIND KRISHAN</t>
+        </is>
+      </c>
+      <c r="C753" t="inlineStr">
+        <is>
+          <t>PURUSOTAM</t>
+        </is>
+      </c>
+      <c r="D753" t="inlineStr">
+        <is>
+          <t>NILAM DEVI</t>
+        </is>
+      </c>
+      <c r="E753" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="F753" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="754">
+      <c r="A754" t="inlineStr">
+        <is>
+          <t>17,Feb</t>
+        </is>
+      </c>
+      <c r="B754" t="inlineStr">
+        <is>
+          <t>KAVYA SINGH</t>
+        </is>
+      </c>
+      <c r="C754" t="inlineStr">
+        <is>
+          <t>SHARAD KUMAR</t>
+        </is>
+      </c>
+      <c r="D754" t="inlineStr">
+        <is>
+          <t>Asha Kumari</t>
+        </is>
+      </c>
+      <c r="E754" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="F754" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="755">
+      <c r="A755" t="inlineStr">
+        <is>
+          <t>17,Feb</t>
+        </is>
+      </c>
+      <c r="B755" t="inlineStr">
+        <is>
+          <t>MANGESH TANAY</t>
+        </is>
+      </c>
+      <c r="C755" t="inlineStr">
+        <is>
+          <t>PANKAJ KUMAR</t>
+        </is>
+      </c>
+      <c r="D755" t="inlineStr">
+        <is>
+          <t>VINITA KUMARI</t>
+        </is>
+      </c>
+      <c r="E755" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="F755" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="756">
+      <c r="A756" t="inlineStr">
+        <is>
+          <t>17,Feb</t>
+        </is>
+      </c>
+      <c r="B756" t="inlineStr">
+        <is>
+          <t>Shruti Suman</t>
+        </is>
+      </c>
+      <c r="C756" t="inlineStr">
+        <is>
+          <t>Ravindra Kumar</t>
+        </is>
+      </c>
+      <c r="D756" t="inlineStr">
+        <is>
+          <t>Radha Kumari</t>
+        </is>
+      </c>
+      <c r="E756" t="inlineStr">
+        <is>
+          <t>IX</t>
+        </is>
+      </c>
+      <c r="F756" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Birthday Data Master.xlsx
+++ b/Birthday Data Master.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F756"/>
+  <dimension ref="A1:F765"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.6" customWidth="1" min="1" max="1"/>
@@ -24616,6 +24616,294 @@
         </is>
       </c>
     </row>
+    <row r="757">
+      <c r="A757" t="inlineStr">
+        <is>
+          <t>18,Feb</t>
+        </is>
+      </c>
+      <c r="B757" t="inlineStr">
+        <is>
+          <t>SAKSHAM KUMAR</t>
+        </is>
+      </c>
+      <c r="C757" t="inlineStr">
+        <is>
+          <t>SARVENDRA KUMAR</t>
+        </is>
+      </c>
+      <c r="D757" t="inlineStr">
+        <is>
+          <t>MONI KUMARI</t>
+        </is>
+      </c>
+      <c r="E757" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="F757" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="758">
+      <c r="A758" t="inlineStr">
+        <is>
+          <t>18,Feb</t>
+        </is>
+      </c>
+      <c r="B758" t="inlineStr">
+        <is>
+          <t>KHUSHI KUMARI</t>
+        </is>
+      </c>
+      <c r="C758" t="inlineStr">
+        <is>
+          <t>ASHUTOSH KUMAR</t>
+        </is>
+      </c>
+      <c r="D758" t="inlineStr">
+        <is>
+          <t>RIMPI KUMARI</t>
+        </is>
+      </c>
+      <c r="E758" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="F758" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="759">
+      <c r="A759" t="inlineStr">
+        <is>
+          <t>18,Feb</t>
+        </is>
+      </c>
+      <c r="B759" t="inlineStr">
+        <is>
+          <t>RAJ ARYAN</t>
+        </is>
+      </c>
+      <c r="C759" t="inlineStr">
+        <is>
+          <t>GIRDHARI KUMAR</t>
+        </is>
+      </c>
+      <c r="D759" t="inlineStr">
+        <is>
+          <t>ANITA KUMARI</t>
+        </is>
+      </c>
+      <c r="E759" t="inlineStr">
+        <is>
+          <t>VIII</t>
+        </is>
+      </c>
+      <c r="F759" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="760">
+      <c r="A760" t="inlineStr">
+        <is>
+          <t>18,Feb</t>
+        </is>
+      </c>
+      <c r="B760" t="inlineStr">
+        <is>
+          <t>RUDRA PRATAP KUMAR</t>
+        </is>
+      </c>
+      <c r="C760" t="inlineStr">
+        <is>
+          <t>DHIRENDRA KUMAR</t>
+        </is>
+      </c>
+      <c r="D760" t="inlineStr">
+        <is>
+          <t>MANORANJAN DEVI</t>
+        </is>
+      </c>
+      <c r="E760" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="F760" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="761">
+      <c r="A761" t="inlineStr">
+        <is>
+          <t>18,Feb</t>
+        </is>
+      </c>
+      <c r="B761" t="inlineStr">
+        <is>
+          <t>Akarsh Kumar</t>
+        </is>
+      </c>
+      <c r="C761" t="inlineStr">
+        <is>
+          <t>Dileep Kumar</t>
+        </is>
+      </c>
+      <c r="D761" t="inlineStr">
+        <is>
+          <t>Priyanka Keshri</t>
+        </is>
+      </c>
+      <c r="E761" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F761" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="762">
+      <c r="A762" t="inlineStr">
+        <is>
+          <t>18,Feb</t>
+        </is>
+      </c>
+      <c r="B762" t="inlineStr">
+        <is>
+          <t>PRIYAL KUMARI</t>
+        </is>
+      </c>
+      <c r="C762" t="inlineStr">
+        <is>
+          <t>ROHIT KUMAR</t>
+        </is>
+      </c>
+      <c r="D762" t="inlineStr">
+        <is>
+          <t>PUJA KUMARI</t>
+        </is>
+      </c>
+      <c r="E762" t="inlineStr">
+        <is>
+          <t>UKG</t>
+        </is>
+      </c>
+      <c r="F762" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="763">
+      <c r="A763" t="inlineStr">
+        <is>
+          <t>18,Feb</t>
+        </is>
+      </c>
+      <c r="B763" t="inlineStr">
+        <is>
+          <t>AYAAN VERMA</t>
+        </is>
+      </c>
+      <c r="C763" t="inlineStr">
+        <is>
+          <t>MANISH KUMAR VERMA</t>
+        </is>
+      </c>
+      <c r="D763" t="inlineStr">
+        <is>
+          <t>PUSHPA DEVI</t>
+        </is>
+      </c>
+      <c r="E763" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="F763" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="764">
+      <c r="A764" t="inlineStr">
+        <is>
+          <t>18,Feb</t>
+        </is>
+      </c>
+      <c r="B764" t="inlineStr">
+        <is>
+          <t>JAHNVI KASHYAP</t>
+        </is>
+      </c>
+      <c r="C764" t="inlineStr">
+        <is>
+          <t>NRIPESH KUMAR</t>
+        </is>
+      </c>
+      <c r="D764" t="inlineStr">
+        <is>
+          <t>ANURADHA KUMARI</t>
+        </is>
+      </c>
+      <c r="E764" t="inlineStr">
+        <is>
+          <t>VIII</t>
+        </is>
+      </c>
+      <c r="F764" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="765">
+      <c r="A765" t="inlineStr">
+        <is>
+          <t>18,Feb</t>
+        </is>
+      </c>
+      <c r="B765" t="inlineStr">
+        <is>
+          <t>PRABHAKAR KUMAR</t>
+        </is>
+      </c>
+      <c r="C765" t="inlineStr">
+        <is>
+          <t>PRAMOD KUMAR</t>
+        </is>
+      </c>
+      <c r="D765" t="inlineStr">
+        <is>
+          <t>MAMTA KUMARI</t>
+        </is>
+      </c>
+      <c r="E765" t="inlineStr">
+        <is>
+          <t>VII</t>
+        </is>
+      </c>
+      <c r="F765" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Birthday Data Master.xlsx
+++ b/Birthday Data Master.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F765"/>
+  <dimension ref="A1:F772"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.6" customWidth="1" min="1" max="1"/>
@@ -24904,6 +24904,230 @@
         </is>
       </c>
     </row>
+    <row r="766">
+      <c r="A766" t="inlineStr">
+        <is>
+          <t>19,Feb</t>
+        </is>
+      </c>
+      <c r="B766" t="inlineStr">
+        <is>
+          <t>SAPNA KUMARI</t>
+        </is>
+      </c>
+      <c r="C766" t="inlineStr">
+        <is>
+          <t>VIJAY KUMAR</t>
+        </is>
+      </c>
+      <c r="D766" t="inlineStr">
+        <is>
+          <t>REKHA DEVI</t>
+        </is>
+      </c>
+      <c r="E766" t="inlineStr">
+        <is>
+          <t>VII</t>
+        </is>
+      </c>
+      <c r="F766" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="767">
+      <c r="A767" t="inlineStr">
+        <is>
+          <t>19,Feb</t>
+        </is>
+      </c>
+      <c r="B767" t="inlineStr">
+        <is>
+          <t>ISHIKA RAJ</t>
+        </is>
+      </c>
+      <c r="C767" t="inlineStr">
+        <is>
+          <t>CHANDAN KUMAR</t>
+        </is>
+      </c>
+      <c r="D767" t="inlineStr">
+        <is>
+          <t>GEETA RAJ</t>
+        </is>
+      </c>
+      <c r="E767" t="inlineStr">
+        <is>
+          <t>IV</t>
+        </is>
+      </c>
+      <c r="F767" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="768">
+      <c r="A768" t="inlineStr">
+        <is>
+          <t>19,Feb</t>
+        </is>
+      </c>
+      <c r="B768" t="inlineStr">
+        <is>
+          <t>RIYA KUMARI</t>
+        </is>
+      </c>
+      <c r="C768" t="inlineStr">
+        <is>
+          <t>ARJUN KUMAR</t>
+        </is>
+      </c>
+      <c r="D768" t="inlineStr">
+        <is>
+          <t>NIRAJA KUMARI</t>
+        </is>
+      </c>
+      <c r="E768" t="inlineStr">
+        <is>
+          <t>VIII</t>
+        </is>
+      </c>
+      <c r="F768" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="769">
+      <c r="A769" t="inlineStr">
+        <is>
+          <t>19,Feb</t>
+        </is>
+      </c>
+      <c r="B769" t="inlineStr">
+        <is>
+          <t>Md Ali Imam</t>
+        </is>
+      </c>
+      <c r="C769" t="inlineStr">
+        <is>
+          <t>Md Qusar Imam</t>
+        </is>
+      </c>
+      <c r="D769" t="inlineStr">
+        <is>
+          <t>Shahiva Perveen</t>
+        </is>
+      </c>
+      <c r="E769" t="inlineStr">
+        <is>
+          <t>IX</t>
+        </is>
+      </c>
+      <c r="F769" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="770">
+      <c r="A770" t="inlineStr">
+        <is>
+          <t>19,Feb</t>
+        </is>
+      </c>
+      <c r="B770" t="inlineStr">
+        <is>
+          <t>AYUSH RAJ HANS</t>
+        </is>
+      </c>
+      <c r="C770" t="inlineStr">
+        <is>
+          <t>GANIT KUMAR</t>
+        </is>
+      </c>
+      <c r="D770" t="inlineStr">
+        <is>
+          <t>SUNAINA KUMARI</t>
+        </is>
+      </c>
+      <c r="E770" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F770" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="771">
+      <c r="A771" t="inlineStr">
+        <is>
+          <t>19,Feb</t>
+        </is>
+      </c>
+      <c r="B771" t="inlineStr">
+        <is>
+          <t>MANISH KUMAR</t>
+        </is>
+      </c>
+      <c r="C771" t="inlineStr">
+        <is>
+          <t>BHUSHAN KUMAR</t>
+        </is>
+      </c>
+      <c r="D771" t="inlineStr">
+        <is>
+          <t>MINTA DEVI</t>
+        </is>
+      </c>
+      <c r="E771" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="F771" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="772">
+      <c r="A772" t="inlineStr">
+        <is>
+          <t>19,Feb</t>
+        </is>
+      </c>
+      <c r="B772" t="inlineStr">
+        <is>
+          <t>Shreya Bhardwaj</t>
+        </is>
+      </c>
+      <c r="C772" t="inlineStr">
+        <is>
+          <t>Shyam Kishore</t>
+        </is>
+      </c>
+      <c r="D772" t="inlineStr">
+        <is>
+          <t>Arpana Kumari</t>
+        </is>
+      </c>
+      <c r="E772" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F772" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Birthday Data Master.xlsx
+++ b/Birthday Data Master.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F772"/>
+  <dimension ref="A1:F783"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.6" customWidth="1" min="1" max="1"/>
@@ -25128,6 +25128,358 @@
         </is>
       </c>
     </row>
+    <row r="773">
+      <c r="A773" t="inlineStr">
+        <is>
+          <t>20,Feb</t>
+        </is>
+      </c>
+      <c r="B773" t="inlineStr">
+        <is>
+          <t>SAANVIKA RAMAN</t>
+        </is>
+      </c>
+      <c r="C773" t="inlineStr">
+        <is>
+          <t>ROHIT RAMAN</t>
+        </is>
+      </c>
+      <c r="D773" t="inlineStr">
+        <is>
+          <t>SONY RAMAN</t>
+        </is>
+      </c>
+      <c r="E773" t="inlineStr">
+        <is>
+          <t>IV</t>
+        </is>
+      </c>
+      <c r="F773" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="774">
+      <c r="A774" t="inlineStr">
+        <is>
+          <t>20,Feb</t>
+        </is>
+      </c>
+      <c r="B774" t="inlineStr">
+        <is>
+          <t>AARADHYA GOSWAMI</t>
+        </is>
+      </c>
+      <c r="C774" t="inlineStr">
+        <is>
+          <t>PARMESHWAR GOSWAMI</t>
+        </is>
+      </c>
+      <c r="D774" t="inlineStr">
+        <is>
+          <t>RENUKA GOSWAMI</t>
+        </is>
+      </c>
+      <c r="E774" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="F774" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="775">
+      <c r="A775" t="inlineStr">
+        <is>
+          <t>20,Feb</t>
+        </is>
+      </c>
+      <c r="B775" t="inlineStr">
+        <is>
+          <t>SACHIN KUMAR</t>
+        </is>
+      </c>
+      <c r="C775" t="inlineStr">
+        <is>
+          <t>JITENDRA KUMAR</t>
+        </is>
+      </c>
+      <c r="D775" t="inlineStr">
+        <is>
+          <t>SANGEETA KUMARI</t>
+        </is>
+      </c>
+      <c r="E775" t="inlineStr">
+        <is>
+          <t>IX</t>
+        </is>
+      </c>
+      <c r="F775" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="776">
+      <c r="A776" t="inlineStr">
+        <is>
+          <t>20,Feb</t>
+        </is>
+      </c>
+      <c r="B776" t="inlineStr">
+        <is>
+          <t>Shashank Kumar</t>
+        </is>
+      </c>
+      <c r="C776" t="inlineStr">
+        <is>
+          <t>Rajnish Kumar</t>
+        </is>
+      </c>
+      <c r="D776" t="inlineStr">
+        <is>
+          <t>Poonam Devi</t>
+        </is>
+      </c>
+      <c r="E776" t="inlineStr">
+        <is>
+          <t>IX</t>
+        </is>
+      </c>
+      <c r="F776" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="777">
+      <c r="A777" t="inlineStr">
+        <is>
+          <t>20,Feb</t>
+        </is>
+      </c>
+      <c r="B777" t="inlineStr">
+        <is>
+          <t>RAHUL KUMAR</t>
+        </is>
+      </c>
+      <c r="C777" t="inlineStr">
+        <is>
+          <t>RAVI KUMAR</t>
+        </is>
+      </c>
+      <c r="D777" t="inlineStr">
+        <is>
+          <t>SHASHI KUMARI</t>
+        </is>
+      </c>
+      <c r="E777" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="F777" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="778">
+      <c r="A778" t="inlineStr">
+        <is>
+          <t>20,Feb</t>
+        </is>
+      </c>
+      <c r="B778" t="inlineStr">
+        <is>
+          <t>SHRISTI SINGH</t>
+        </is>
+      </c>
+      <c r="C778" t="inlineStr">
+        <is>
+          <t>AMARJEET SINGH</t>
+        </is>
+      </c>
+      <c r="D778" t="inlineStr">
+        <is>
+          <t>RITA SINGH</t>
+        </is>
+      </c>
+      <c r="E778" t="inlineStr">
+        <is>
+          <t>VII</t>
+        </is>
+      </c>
+      <c r="F778" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="779">
+      <c r="A779" t="inlineStr">
+        <is>
+          <t>20,Feb</t>
+        </is>
+      </c>
+      <c r="B779" t="inlineStr">
+        <is>
+          <t>SARAV SINGH</t>
+        </is>
+      </c>
+      <c r="C779" t="inlineStr">
+        <is>
+          <t>GYANI JAIL SINGH</t>
+        </is>
+      </c>
+      <c r="D779" t="inlineStr">
+        <is>
+          <t>AAKANKSHA KUMARI</t>
+        </is>
+      </c>
+      <c r="E779" t="inlineStr">
+        <is>
+          <t>LKG</t>
+        </is>
+      </c>
+      <c r="F779" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="780">
+      <c r="A780" t="inlineStr">
+        <is>
+          <t>20,Feb</t>
+        </is>
+      </c>
+      <c r="B780" t="inlineStr">
+        <is>
+          <t>ARYAN SINHA</t>
+        </is>
+      </c>
+      <c r="C780" t="inlineStr">
+        <is>
+          <t>RAKESH SINHA</t>
+        </is>
+      </c>
+      <c r="D780" t="inlineStr">
+        <is>
+          <t>BABLI SINHA</t>
+        </is>
+      </c>
+      <c r="E780" t="inlineStr">
+        <is>
+          <t>VII</t>
+        </is>
+      </c>
+      <c r="F780" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="781">
+      <c r="A781" t="inlineStr">
+        <is>
+          <t>20,Feb</t>
+        </is>
+      </c>
+      <c r="B781" t="inlineStr">
+        <is>
+          <t>VEENA KUMARI</t>
+        </is>
+      </c>
+      <c r="C781" t="inlineStr">
+        <is>
+          <t>YOGENDRA KUMAR</t>
+        </is>
+      </c>
+      <c r="D781" t="inlineStr">
+        <is>
+          <t>ANITA DEVI</t>
+        </is>
+      </c>
+      <c r="E781" t="inlineStr">
+        <is>
+          <t>VII</t>
+        </is>
+      </c>
+      <c r="F781" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+    </row>
+    <row r="782">
+      <c r="A782" t="inlineStr">
+        <is>
+          <t>20,Feb</t>
+        </is>
+      </c>
+      <c r="B782" t="inlineStr">
+        <is>
+          <t>Pakhi Kumari</t>
+        </is>
+      </c>
+      <c r="C782" t="inlineStr">
+        <is>
+          <t>Saryu Singh</t>
+        </is>
+      </c>
+      <c r="D782" t="inlineStr">
+        <is>
+          <t>Kiran Devi</t>
+        </is>
+      </c>
+      <c r="E782" t="inlineStr">
+        <is>
+          <t>VIII</t>
+        </is>
+      </c>
+      <c r="F782" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="783">
+      <c r="A783" t="inlineStr">
+        <is>
+          <t>20,Feb</t>
+        </is>
+      </c>
+      <c r="B783" t="inlineStr">
+        <is>
+          <t>PARTH VIBHAV</t>
+        </is>
+      </c>
+      <c r="C783" t="inlineStr">
+        <is>
+          <t>MANIBHUSHAN PRASAD SINHA</t>
+        </is>
+      </c>
+      <c r="D783" t="inlineStr">
+        <is>
+          <t>ANITA SINHA</t>
+        </is>
+      </c>
+      <c r="E783" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="F783" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Birthday Data Master.xlsx
+++ b/Birthday Data Master.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F783"/>
+  <dimension ref="A1:F794"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.6" customWidth="1" min="1" max="1"/>
@@ -25480,6 +25480,358 @@
         </is>
       </c>
     </row>
+    <row r="784">
+      <c r="A784" t="inlineStr">
+        <is>
+          <t>21,Feb</t>
+        </is>
+      </c>
+      <c r="B784" t="inlineStr">
+        <is>
+          <t>SATYAM KUMAR</t>
+        </is>
+      </c>
+      <c r="C784" t="inlineStr">
+        <is>
+          <t>NIRAJ KUMAR</t>
+        </is>
+      </c>
+      <c r="D784" t="inlineStr">
+        <is>
+          <t>CHANDANI KUMARI</t>
+        </is>
+      </c>
+      <c r="E784" t="inlineStr">
+        <is>
+          <t>VII</t>
+        </is>
+      </c>
+      <c r="F784" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+    </row>
+    <row r="785">
+      <c r="A785" t="inlineStr">
+        <is>
+          <t>21,Feb</t>
+        </is>
+      </c>
+      <c r="B785" t="inlineStr">
+        <is>
+          <t>Roshni Kumari</t>
+        </is>
+      </c>
+      <c r="C785" t="inlineStr">
+        <is>
+          <t>Rakesh Kumar</t>
+        </is>
+      </c>
+      <c r="D785" t="inlineStr">
+        <is>
+          <t>Banti DEVI Sharma</t>
+        </is>
+      </c>
+      <c r="E785" t="inlineStr">
+        <is>
+          <t>VIII</t>
+        </is>
+      </c>
+      <c r="F785" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+    </row>
+    <row r="786">
+      <c r="A786" t="inlineStr">
+        <is>
+          <t>21,Feb</t>
+        </is>
+      </c>
+      <c r="B786" t="inlineStr">
+        <is>
+          <t>Aman  Kumar</t>
+        </is>
+      </c>
+      <c r="C786" t="inlineStr">
+        <is>
+          <t>Akshay Kumar</t>
+        </is>
+      </c>
+      <c r="D786" t="inlineStr">
+        <is>
+          <t>Guddi Devi</t>
+        </is>
+      </c>
+      <c r="E786" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F786" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="787">
+      <c r="A787" t="inlineStr">
+        <is>
+          <t>21,Feb</t>
+        </is>
+      </c>
+      <c r="B787" t="inlineStr">
+        <is>
+          <t>VAIBHAV KUMAR</t>
+        </is>
+      </c>
+      <c r="C787" t="inlineStr">
+        <is>
+          <t>RAVI RANJAN KUMAR</t>
+        </is>
+      </c>
+      <c r="D787" t="inlineStr">
+        <is>
+          <t>GURIYA KUMARI</t>
+        </is>
+      </c>
+      <c r="E787" t="inlineStr">
+        <is>
+          <t>IV</t>
+        </is>
+      </c>
+      <c r="F787" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="788">
+      <c r="A788" t="inlineStr">
+        <is>
+          <t>21,Feb</t>
+        </is>
+      </c>
+      <c r="B788" t="inlineStr">
+        <is>
+          <t>ANUBHAV  SHARMA</t>
+        </is>
+      </c>
+      <c r="C788" t="inlineStr">
+        <is>
+          <t>DARVESH KUMAR</t>
+        </is>
+      </c>
+      <c r="D788" t="inlineStr">
+        <is>
+          <t>SUPRIYA KUMARi</t>
+        </is>
+      </c>
+      <c r="E788" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="F788" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="789">
+      <c r="A789" t="inlineStr">
+        <is>
+          <t>21,Feb</t>
+        </is>
+      </c>
+      <c r="B789" t="inlineStr">
+        <is>
+          <t>CHHAVI  KUMARI</t>
+        </is>
+      </c>
+      <c r="C789" t="inlineStr">
+        <is>
+          <t>KAMAKHYA KUMAR</t>
+        </is>
+      </c>
+      <c r="D789" t="inlineStr">
+        <is>
+          <t>ARTI SINHA</t>
+        </is>
+      </c>
+      <c r="E789" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="F789" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="790">
+      <c r="A790" t="inlineStr">
+        <is>
+          <t>21,Feb</t>
+        </is>
+      </c>
+      <c r="B790" t="inlineStr">
+        <is>
+          <t>PIYUSH  KUMAR</t>
+        </is>
+      </c>
+      <c r="C790" t="inlineStr">
+        <is>
+          <t>SANJAY PASWAN</t>
+        </is>
+      </c>
+      <c r="D790" t="inlineStr">
+        <is>
+          <t>POONAM KUMARI</t>
+        </is>
+      </c>
+      <c r="E790" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="F790" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+    </row>
+    <row r="791">
+      <c r="A791" t="inlineStr">
+        <is>
+          <t>21,Feb</t>
+        </is>
+      </c>
+      <c r="B791" t="inlineStr">
+        <is>
+          <t>IRA SHREE</t>
+        </is>
+      </c>
+      <c r="C791" t="inlineStr">
+        <is>
+          <t>BINOD KUMAR PASWAN</t>
+        </is>
+      </c>
+      <c r="D791" t="inlineStr">
+        <is>
+          <t>TARA KUMARI</t>
+        </is>
+      </c>
+      <c r="E791" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="F791" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="792">
+      <c r="A792" t="inlineStr">
+        <is>
+          <t>21,Feb</t>
+        </is>
+      </c>
+      <c r="B792" t="inlineStr">
+        <is>
+          <t>ADITYA KUMAR JAYSAWAL</t>
+        </is>
+      </c>
+      <c r="C792" t="inlineStr">
+        <is>
+          <t>RAVI KUMAR</t>
+        </is>
+      </c>
+      <c r="D792" t="inlineStr">
+        <is>
+          <t>SUNITA KUMARI</t>
+        </is>
+      </c>
+      <c r="E792" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F792" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="793">
+      <c r="A793" t="inlineStr">
+        <is>
+          <t>21,Feb</t>
+        </is>
+      </c>
+      <c r="B793" t="inlineStr">
+        <is>
+          <t>Anushka Gupta</t>
+        </is>
+      </c>
+      <c r="C793" t="inlineStr">
+        <is>
+          <t>Sintu Kumar</t>
+        </is>
+      </c>
+      <c r="D793" t="inlineStr">
+        <is>
+          <t>Renu Devi</t>
+        </is>
+      </c>
+      <c r="E793" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F793" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="794">
+      <c r="A794" t="inlineStr">
+        <is>
+          <t>21,Feb</t>
+        </is>
+      </c>
+      <c r="B794" t="inlineStr">
+        <is>
+          <t>Saurabh Raj</t>
+        </is>
+      </c>
+      <c r="C794" t="inlineStr">
+        <is>
+          <t>RAJ KUMAR</t>
+        </is>
+      </c>
+      <c r="D794" t="inlineStr">
+        <is>
+          <t>Surekha Azad</t>
+        </is>
+      </c>
+      <c r="E794" t="inlineStr">
+        <is>
+          <t>IX</t>
+        </is>
+      </c>
+      <c r="F794" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Birthday Data Master.xlsx
+++ b/Birthday Data Master.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F794"/>
+  <dimension ref="A1:F800"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.6" customWidth="1" min="1" max="1"/>
@@ -25832,6 +25832,198 @@
         </is>
       </c>
     </row>
+    <row r="795">
+      <c r="A795" t="inlineStr">
+        <is>
+          <t>22,Feb</t>
+        </is>
+      </c>
+      <c r="B795" t="inlineStr">
+        <is>
+          <t>NYSA  Singh</t>
+        </is>
+      </c>
+      <c r="C795" t="inlineStr">
+        <is>
+          <t>RAJESH KUMAR</t>
+        </is>
+      </c>
+      <c r="D795" t="inlineStr">
+        <is>
+          <t>REENA SINGH</t>
+        </is>
+      </c>
+      <c r="E795" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F795" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="796">
+      <c r="A796" t="inlineStr">
+        <is>
+          <t>22,Feb</t>
+        </is>
+      </c>
+      <c r="B796" t="inlineStr">
+        <is>
+          <t>SAKSHI PRIYA</t>
+        </is>
+      </c>
+      <c r="C796" t="inlineStr">
+        <is>
+          <t>SHAMBHU KUMAR</t>
+        </is>
+      </c>
+      <c r="D796" t="inlineStr">
+        <is>
+          <t>SUNITA KUMARI</t>
+        </is>
+      </c>
+      <c r="E796" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="F796" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="797">
+      <c r="A797" t="inlineStr">
+        <is>
+          <t>22,Feb</t>
+        </is>
+      </c>
+      <c r="B797" t="inlineStr">
+        <is>
+          <t>RANVEER SINGH</t>
+        </is>
+      </c>
+      <c r="C797" t="inlineStr">
+        <is>
+          <t>GUDDU KUMAR</t>
+        </is>
+      </c>
+      <c r="D797" t="inlineStr">
+        <is>
+          <t>RAJNI KUMARI</t>
+        </is>
+      </c>
+      <c r="E797" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="F797" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="798">
+      <c r="A798" t="inlineStr">
+        <is>
+          <t>22,Feb</t>
+        </is>
+      </c>
+      <c r="B798" t="inlineStr">
+        <is>
+          <t>SUHARSH BHARTI</t>
+        </is>
+      </c>
+      <c r="C798" t="inlineStr">
+        <is>
+          <t>SUDHIR KUMAR</t>
+        </is>
+      </c>
+      <c r="D798" t="inlineStr">
+        <is>
+          <t>SARITA KUMARI</t>
+        </is>
+      </c>
+      <c r="E798" t="inlineStr">
+        <is>
+          <t>IX</t>
+        </is>
+      </c>
+      <c r="F798" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="799">
+      <c r="A799" t="inlineStr">
+        <is>
+          <t>22,Feb</t>
+        </is>
+      </c>
+      <c r="B799" t="inlineStr">
+        <is>
+          <t>Vaishnavi Kumari</t>
+        </is>
+      </c>
+      <c r="C799" t="inlineStr">
+        <is>
+          <t>Krishnkant Kumar</t>
+        </is>
+      </c>
+      <c r="D799" t="inlineStr">
+        <is>
+          <t>Ansu Kumari</t>
+        </is>
+      </c>
+      <c r="E799" t="inlineStr">
+        <is>
+          <t>IX</t>
+        </is>
+      </c>
+      <c r="F799" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="800">
+      <c r="A800" t="inlineStr">
+        <is>
+          <t>22,Feb</t>
+        </is>
+      </c>
+      <c r="B800" t="inlineStr">
+        <is>
+          <t>Hansika Kumari</t>
+        </is>
+      </c>
+      <c r="C800" t="inlineStr">
+        <is>
+          <t>Pawan Kumar</t>
+        </is>
+      </c>
+      <c r="D800" t="inlineStr">
+        <is>
+          <t>Babita Devi</t>
+        </is>
+      </c>
+      <c r="E800" t="inlineStr">
+        <is>
+          <t>VIII</t>
+        </is>
+      </c>
+      <c r="F800" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Birthday Data Master.xlsx
+++ b/Birthday Data Master.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F800"/>
+  <dimension ref="A1:F810"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.6" customWidth="1" min="1" max="1"/>
@@ -26024,6 +26024,326 @@
         </is>
       </c>
     </row>
+    <row r="801">
+      <c r="A801" t="inlineStr">
+        <is>
+          <t>23,Feb</t>
+        </is>
+      </c>
+      <c r="B801" t="inlineStr">
+        <is>
+          <t>KUMARI SWETA SUMAN</t>
+        </is>
+      </c>
+      <c r="C801" t="inlineStr">
+        <is>
+          <t>ANIL CHAUDHARY</t>
+        </is>
+      </c>
+      <c r="D801" t="inlineStr">
+        <is>
+          <t>KIRAN DEVI</t>
+        </is>
+      </c>
+      <c r="E801" t="inlineStr">
+        <is>
+          <t>VII</t>
+        </is>
+      </c>
+      <c r="F801" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="802">
+      <c r="A802" t="inlineStr">
+        <is>
+          <t>23,Feb</t>
+        </is>
+      </c>
+      <c r="B802" t="inlineStr">
+        <is>
+          <t>SONAKSHI SHARMA</t>
+        </is>
+      </c>
+      <c r="C802" t="inlineStr">
+        <is>
+          <t>NAVIN KUMAR</t>
+        </is>
+      </c>
+      <c r="D802" t="inlineStr">
+        <is>
+          <t>RANJANA KUMARI</t>
+        </is>
+      </c>
+      <c r="E802" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="F802" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="803">
+      <c r="A803" t="inlineStr">
+        <is>
+          <t>23,Feb</t>
+        </is>
+      </c>
+      <c r="B803" t="inlineStr">
+        <is>
+          <t>SHOBHIT SINHA</t>
+        </is>
+      </c>
+      <c r="C803" t="inlineStr">
+        <is>
+          <t>AMRENDRA KUMAR</t>
+        </is>
+      </c>
+      <c r="D803" t="inlineStr">
+        <is>
+          <t>PINKI KUMARI</t>
+        </is>
+      </c>
+      <c r="E803" t="inlineStr">
+        <is>
+          <t>IV</t>
+        </is>
+      </c>
+      <c r="F803" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="804">
+      <c r="A804" t="inlineStr">
+        <is>
+          <t>23,Feb</t>
+        </is>
+      </c>
+      <c r="B804" t="inlineStr">
+        <is>
+          <t>TEJ PRATAP</t>
+        </is>
+      </c>
+      <c r="C804" t="inlineStr">
+        <is>
+          <t>SUDHIR KUMAR</t>
+        </is>
+      </c>
+      <c r="D804" t="inlineStr">
+        <is>
+          <t>PINKY KUMARI</t>
+        </is>
+      </c>
+      <c r="E804" t="inlineStr">
+        <is>
+          <t>VII</t>
+        </is>
+      </c>
+      <c r="F804" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="805">
+      <c r="A805" t="inlineStr">
+        <is>
+          <t>23,Feb</t>
+        </is>
+      </c>
+      <c r="B805" t="inlineStr">
+        <is>
+          <t>Muhammad Altamash</t>
+        </is>
+      </c>
+      <c r="C805" t="inlineStr">
+        <is>
+          <t>Jahangeer Alam ANSARI</t>
+        </is>
+      </c>
+      <c r="D805" t="inlineStr">
+        <is>
+          <t>Farhat Anjum</t>
+        </is>
+      </c>
+      <c r="E805" t="inlineStr">
+        <is>
+          <t>IX</t>
+        </is>
+      </c>
+      <c r="F805" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="806">
+      <c r="A806" t="inlineStr">
+        <is>
+          <t>23,Feb</t>
+        </is>
+      </c>
+      <c r="B806" t="inlineStr">
+        <is>
+          <t>Aditya Kumar Sah</t>
+        </is>
+      </c>
+      <c r="C806" t="inlineStr">
+        <is>
+          <t>Sachin Kumar</t>
+        </is>
+      </c>
+      <c r="D806" t="inlineStr">
+        <is>
+          <t>Sunita Kumari</t>
+        </is>
+      </c>
+      <c r="E806" t="inlineStr">
+        <is>
+          <t>VIII</t>
+        </is>
+      </c>
+      <c r="F806" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="807">
+      <c r="A807" t="inlineStr">
+        <is>
+          <t>23,Feb</t>
+        </is>
+      </c>
+      <c r="B807" t="inlineStr">
+        <is>
+          <t>HANSHIT</t>
+        </is>
+      </c>
+      <c r="C807" t="inlineStr">
+        <is>
+          <t>BRAHMARSHI AMBRISH ADITYA</t>
+        </is>
+      </c>
+      <c r="D807" t="inlineStr">
+        <is>
+          <t>RASHMI KUMARI</t>
+        </is>
+      </c>
+      <c r="E807" t="inlineStr">
+        <is>
+          <t>IV</t>
+        </is>
+      </c>
+      <c r="F807" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="808">
+      <c r="A808" t="inlineStr">
+        <is>
+          <t>23,Feb</t>
+        </is>
+      </c>
+      <c r="B808" t="inlineStr">
+        <is>
+          <t>NAINVI KUMARI</t>
+        </is>
+      </c>
+      <c r="C808" t="inlineStr">
+        <is>
+          <t>DHARAMVEER KUMAR</t>
+        </is>
+      </c>
+      <c r="D808" t="inlineStr">
+        <is>
+          <t>VANDANA DEVI</t>
+        </is>
+      </c>
+      <c r="E808" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="F808" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="809">
+      <c r="A809" t="inlineStr">
+        <is>
+          <t>23,Feb</t>
+        </is>
+      </c>
+      <c r="B809" t="inlineStr">
+        <is>
+          <t>AMARJEET KUMAR</t>
+        </is>
+      </c>
+      <c r="C809" t="inlineStr">
+        <is>
+          <t>Ajit Kumar</t>
+        </is>
+      </c>
+      <c r="D809" t="inlineStr">
+        <is>
+          <t>Supriya Kumari</t>
+        </is>
+      </c>
+      <c r="E809" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="F809" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="810">
+      <c r="A810" t="inlineStr">
+        <is>
+          <t>23,Feb</t>
+        </is>
+      </c>
+      <c r="B810" t="inlineStr">
+        <is>
+          <t>Saurav Kumar</t>
+        </is>
+      </c>
+      <c r="C810" t="inlineStr">
+        <is>
+          <t>Munna Kumar</t>
+        </is>
+      </c>
+      <c r="D810" t="inlineStr">
+        <is>
+          <t>Rinku Kumari</t>
+        </is>
+      </c>
+      <c r="E810" t="inlineStr">
+        <is>
+          <t>VIII</t>
+        </is>
+      </c>
+      <c r="F810" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Birthday Data Master.xlsx
+++ b/Birthday Data Master.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F810"/>
+  <dimension ref="A1:F818"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.6" customWidth="1" min="1" max="1"/>
@@ -26344,6 +26344,262 @@
         </is>
       </c>
     </row>
+    <row r="811">
+      <c r="A811" t="inlineStr">
+        <is>
+          <t>24,Feb</t>
+        </is>
+      </c>
+      <c r="B811" t="inlineStr">
+        <is>
+          <t>Yuvraj Singh</t>
+        </is>
+      </c>
+      <c r="C811" t="inlineStr">
+        <is>
+          <t>Gorav Kumar</t>
+        </is>
+      </c>
+      <c r="D811" t="inlineStr">
+        <is>
+          <t>Juli Kumari</t>
+        </is>
+      </c>
+      <c r="E811" t="inlineStr">
+        <is>
+          <t>IX</t>
+        </is>
+      </c>
+      <c r="F811" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="812">
+      <c r="A812" t="inlineStr">
+        <is>
+          <t>24,Feb</t>
+        </is>
+      </c>
+      <c r="B812" t="inlineStr">
+        <is>
+          <t>NAVISHA SHARMA</t>
+        </is>
+      </c>
+      <c r="C812" t="inlineStr">
+        <is>
+          <t>NAVIN KUMAR</t>
+        </is>
+      </c>
+      <c r="D812" t="inlineStr">
+        <is>
+          <t>RANJANA KUMARI</t>
+        </is>
+      </c>
+      <c r="E812" t="inlineStr">
+        <is>
+          <t>IV</t>
+        </is>
+      </c>
+      <c r="F812" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="813">
+      <c r="A813" t="inlineStr">
+        <is>
+          <t>24,Feb</t>
+        </is>
+      </c>
+      <c r="B813" t="inlineStr">
+        <is>
+          <t>KRISHNA KUMAR</t>
+        </is>
+      </c>
+      <c r="C813" t="inlineStr">
+        <is>
+          <t>ANUJ KUMAR</t>
+        </is>
+      </c>
+      <c r="D813" t="inlineStr">
+        <is>
+          <t>JYOTI SHARMA</t>
+        </is>
+      </c>
+      <c r="E813" t="inlineStr">
+        <is>
+          <t>VII</t>
+        </is>
+      </c>
+      <c r="F813" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="814">
+      <c r="A814" t="inlineStr">
+        <is>
+          <t>24,Feb</t>
+        </is>
+      </c>
+      <c r="B814" t="inlineStr">
+        <is>
+          <t>RAJVIR RANJAN</t>
+        </is>
+      </c>
+      <c r="C814" t="inlineStr">
+        <is>
+          <t>AMIT RANJAN</t>
+        </is>
+      </c>
+      <c r="D814" t="inlineStr">
+        <is>
+          <t>JULY RANJAN</t>
+        </is>
+      </c>
+      <c r="E814" t="inlineStr">
+        <is>
+          <t>LKG</t>
+        </is>
+      </c>
+      <c r="F814" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="815">
+      <c r="A815" t="inlineStr">
+        <is>
+          <t>24,Feb</t>
+        </is>
+      </c>
+      <c r="B815" t="inlineStr">
+        <is>
+          <t>SUKRITI AISHWARYA</t>
+        </is>
+      </c>
+      <c r="C815" t="inlineStr">
+        <is>
+          <t>RAJIV KUMAR SINHA</t>
+        </is>
+      </c>
+      <c r="D815" t="inlineStr">
+        <is>
+          <t>NEETA SINHA</t>
+        </is>
+      </c>
+      <c r="E815" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="F815" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="816">
+      <c r="A816" t="inlineStr">
+        <is>
+          <t>24,Feb</t>
+        </is>
+      </c>
+      <c r="B816" t="inlineStr">
+        <is>
+          <t>SONA KUMARI</t>
+        </is>
+      </c>
+      <c r="C816" t="inlineStr">
+        <is>
+          <t>BIKI PRAKASH</t>
+        </is>
+      </c>
+      <c r="D816" t="inlineStr">
+        <is>
+          <t>RINKU KUMARI</t>
+        </is>
+      </c>
+      <c r="E816" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F816" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="817">
+      <c r="A817" t="inlineStr">
+        <is>
+          <t>24,Feb</t>
+        </is>
+      </c>
+      <c r="B817" t="inlineStr">
+        <is>
+          <t>Amrit Raj</t>
+        </is>
+      </c>
+      <c r="C817" t="inlineStr">
+        <is>
+          <t>Shambhu Kumar</t>
+        </is>
+      </c>
+      <c r="D817" t="inlineStr">
+        <is>
+          <t>Sunita Kumari</t>
+        </is>
+      </c>
+      <c r="E817" t="inlineStr">
+        <is>
+          <t>VIII</t>
+        </is>
+      </c>
+      <c r="F817" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="818">
+      <c r="A818" t="inlineStr">
+        <is>
+          <t>24,Feb</t>
+        </is>
+      </c>
+      <c r="B818" t="inlineStr">
+        <is>
+          <t>DAMINI  SINGH</t>
+        </is>
+      </c>
+      <c r="C818" t="inlineStr">
+        <is>
+          <t>SANTOSH KUMAR</t>
+        </is>
+      </c>
+      <c r="D818" t="inlineStr">
+        <is>
+          <t>PINKY KUMARI</t>
+        </is>
+      </c>
+      <c r="E818" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="F818" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Birthday Data Master.xlsx
+++ b/Birthday Data Master.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F818"/>
+  <dimension ref="A1:F834"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.6" customWidth="1" min="1" max="1"/>
@@ -26600,6 +26600,518 @@
         </is>
       </c>
     </row>
+    <row r="819">
+      <c r="A819" t="inlineStr">
+        <is>
+          <t>25,Feb</t>
+        </is>
+      </c>
+      <c r="B819" t="inlineStr">
+        <is>
+          <t>Kritika Raj</t>
+        </is>
+      </c>
+      <c r="C819" t="inlineStr">
+        <is>
+          <t>Binod Kumar</t>
+        </is>
+      </c>
+      <c r="D819" t="inlineStr">
+        <is>
+          <t>Archana KUMARI</t>
+        </is>
+      </c>
+      <c r="E819" t="inlineStr">
+        <is>
+          <t>IX</t>
+        </is>
+      </c>
+      <c r="F819" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="820">
+      <c r="A820" t="inlineStr">
+        <is>
+          <t>25,Feb</t>
+        </is>
+      </c>
+      <c r="B820" t="inlineStr">
+        <is>
+          <t>Shourya Raj</t>
+        </is>
+      </c>
+      <c r="C820" t="inlineStr">
+        <is>
+          <t>Ritesh Sharma</t>
+        </is>
+      </c>
+      <c r="D820" t="inlineStr">
+        <is>
+          <t>Prity Kumari</t>
+        </is>
+      </c>
+      <c r="E820" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F820" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="821">
+      <c r="A821" t="inlineStr">
+        <is>
+          <t>25,Feb</t>
+        </is>
+      </c>
+      <c r="B821" t="inlineStr">
+        <is>
+          <t>Aradhya Prakash</t>
+        </is>
+      </c>
+      <c r="C821" t="inlineStr">
+        <is>
+          <t>DR Dharam Prakash</t>
+        </is>
+      </c>
+      <c r="D821" t="inlineStr">
+        <is>
+          <t>Bindu Bharti</t>
+        </is>
+      </c>
+      <c r="E821" t="inlineStr">
+        <is>
+          <t>IX</t>
+        </is>
+      </c>
+      <c r="F821" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+    </row>
+    <row r="822">
+      <c r="A822" t="inlineStr">
+        <is>
+          <t>25,Feb</t>
+        </is>
+      </c>
+      <c r="B822" t="inlineStr">
+        <is>
+          <t>Vaishnavi Gupta</t>
+        </is>
+      </c>
+      <c r="C822" t="inlineStr">
+        <is>
+          <t>Vinay Das</t>
+        </is>
+      </c>
+      <c r="D822" t="inlineStr">
+        <is>
+          <t>Reeta Devi</t>
+        </is>
+      </c>
+      <c r="E822" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F822" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="823">
+      <c r="A823" t="inlineStr">
+        <is>
+          <t>25,Feb</t>
+        </is>
+      </c>
+      <c r="B823" t="inlineStr">
+        <is>
+          <t>AKANKSHA KUMARI</t>
+        </is>
+      </c>
+      <c r="C823" t="inlineStr">
+        <is>
+          <t>PINTU KUMAR</t>
+        </is>
+      </c>
+      <c r="D823" t="inlineStr">
+        <is>
+          <t>RINKU KUMARI</t>
+        </is>
+      </c>
+      <c r="E823" t="inlineStr">
+        <is>
+          <t>XII</t>
+        </is>
+      </c>
+      <c r="F823" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="824">
+      <c r="A824" t="inlineStr">
+        <is>
+          <t>25,Feb</t>
+        </is>
+      </c>
+      <c r="B824" t="inlineStr">
+        <is>
+          <t>AJIT KUMAR</t>
+        </is>
+      </c>
+      <c r="C824" t="inlineStr">
+        <is>
+          <t>YOGENDRA KUMAR</t>
+        </is>
+      </c>
+      <c r="D824" t="inlineStr">
+        <is>
+          <t>ANITA DEVI</t>
+        </is>
+      </c>
+      <c r="E824" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="F824" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="825">
+      <c r="A825" t="inlineStr">
+        <is>
+          <t>25,Feb</t>
+        </is>
+      </c>
+      <c r="B825" t="inlineStr">
+        <is>
+          <t>HARSHITA RAJ</t>
+        </is>
+      </c>
+      <c r="C825" t="inlineStr">
+        <is>
+          <t>BHUSHAN KUMAR</t>
+        </is>
+      </c>
+      <c r="D825" t="inlineStr">
+        <is>
+          <t>PRIYANKA KUMARI</t>
+        </is>
+      </c>
+      <c r="E825" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="F825" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="826">
+      <c r="A826" t="inlineStr">
+        <is>
+          <t>25,Feb</t>
+        </is>
+      </c>
+      <c r="B826" t="inlineStr">
+        <is>
+          <t>ASHLOK KUMAR</t>
+        </is>
+      </c>
+      <c r="C826" t="inlineStr">
+        <is>
+          <t>UMESH KUMAR</t>
+        </is>
+      </c>
+      <c r="D826" t="inlineStr">
+        <is>
+          <t>RINKI KUMARI</t>
+        </is>
+      </c>
+      <c r="E826" t="inlineStr">
+        <is>
+          <t>VII</t>
+        </is>
+      </c>
+      <c r="F826" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="827">
+      <c r="A827" t="inlineStr">
+        <is>
+          <t>25,Feb</t>
+        </is>
+      </c>
+      <c r="B827" t="inlineStr">
+        <is>
+          <t>VISHNU KUMAR</t>
+        </is>
+      </c>
+      <c r="C827" t="inlineStr">
+        <is>
+          <t>PRAVIND SINGH</t>
+        </is>
+      </c>
+      <c r="D827" t="inlineStr">
+        <is>
+          <t>PUJA DEVI</t>
+        </is>
+      </c>
+      <c r="E827" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="F827" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="828">
+      <c r="A828" t="inlineStr">
+        <is>
+          <t>25,Feb</t>
+        </is>
+      </c>
+      <c r="B828" t="inlineStr">
+        <is>
+          <t>Kirti Sharma</t>
+        </is>
+      </c>
+      <c r="C828" t="inlineStr">
+        <is>
+          <t>Navlesh Kumar</t>
+        </is>
+      </c>
+      <c r="D828" t="inlineStr">
+        <is>
+          <t>Lalsa Kumari</t>
+        </is>
+      </c>
+      <c r="E828" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F828" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="829">
+      <c r="A829" t="inlineStr">
+        <is>
+          <t>25,Feb</t>
+        </is>
+      </c>
+      <c r="B829" t="inlineStr">
+        <is>
+          <t>Sudhanshu Kumar</t>
+        </is>
+      </c>
+      <c r="C829" t="inlineStr">
+        <is>
+          <t>Sunil Kumar</t>
+        </is>
+      </c>
+      <c r="D829" t="inlineStr">
+        <is>
+          <t>Anju Devi</t>
+        </is>
+      </c>
+      <c r="E829" t="inlineStr">
+        <is>
+          <t>IX</t>
+        </is>
+      </c>
+      <c r="F829" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="830">
+      <c r="A830" t="inlineStr">
+        <is>
+          <t>25,Feb</t>
+        </is>
+      </c>
+      <c r="B830" t="inlineStr">
+        <is>
+          <t>ARYAN KUMAR</t>
+        </is>
+      </c>
+      <c r="C830" t="inlineStr">
+        <is>
+          <t>PRANAV KUMAR</t>
+        </is>
+      </c>
+      <c r="D830" t="inlineStr">
+        <is>
+          <t>SONI DEVI</t>
+        </is>
+      </c>
+      <c r="E830" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="F830" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+    </row>
+    <row r="831">
+      <c r="A831" t="inlineStr">
+        <is>
+          <t>25,Feb</t>
+        </is>
+      </c>
+      <c r="B831" t="inlineStr">
+        <is>
+          <t>Shambhavi Kumari</t>
+        </is>
+      </c>
+      <c r="C831" t="inlineStr">
+        <is>
+          <t>Rajesh Kumar</t>
+        </is>
+      </c>
+      <c r="D831" t="inlineStr">
+        <is>
+          <t>Lalima Devi</t>
+        </is>
+      </c>
+      <c r="E831" t="inlineStr">
+        <is>
+          <t>IX</t>
+        </is>
+      </c>
+      <c r="F831" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="832">
+      <c r="A832" t="inlineStr">
+        <is>
+          <t>25,Feb</t>
+        </is>
+      </c>
+      <c r="B832" t="inlineStr">
+        <is>
+          <t>DIVYANSH GUPTA</t>
+        </is>
+      </c>
+      <c r="C832" t="inlineStr">
+        <is>
+          <t>MANOJ KR GUPTA</t>
+        </is>
+      </c>
+      <c r="D832" t="inlineStr">
+        <is>
+          <t>PUJA KUMARI</t>
+        </is>
+      </c>
+      <c r="E832" t="inlineStr">
+        <is>
+          <t>UKG</t>
+        </is>
+      </c>
+      <c r="F832" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="833">
+      <c r="A833" t="inlineStr">
+        <is>
+          <t>25,Feb</t>
+        </is>
+      </c>
+      <c r="B833" t="inlineStr">
+        <is>
+          <t>PRINCE KUMAR</t>
+        </is>
+      </c>
+      <c r="C833" t="inlineStr">
+        <is>
+          <t>SATYENDRA CHAUDHARY</t>
+        </is>
+      </c>
+      <c r="D833" t="inlineStr">
+        <is>
+          <t>SARITA DEVI</t>
+        </is>
+      </c>
+      <c r="E833" t="inlineStr">
+        <is>
+          <t>VII</t>
+        </is>
+      </c>
+      <c r="F833" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="834">
+      <c r="A834" t="inlineStr">
+        <is>
+          <t>25,Feb</t>
+        </is>
+      </c>
+      <c r="B834" t="inlineStr">
+        <is>
+          <t>VIBHUTI KASHYAP</t>
+        </is>
+      </c>
+      <c r="C834" t="inlineStr">
+        <is>
+          <t>MR LOVE KUMAR</t>
+        </is>
+      </c>
+      <c r="D834" t="inlineStr">
+        <is>
+          <t>ARTI VATS</t>
+        </is>
+      </c>
+      <c r="E834" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="F834" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Birthday Data Master.xlsx
+++ b/Birthday Data Master.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F834"/>
+  <dimension ref="A1:F841"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.6" customWidth="1" min="1" max="1"/>
@@ -27112,6 +27112,230 @@
         </is>
       </c>
     </row>
+    <row r="835">
+      <c r="A835" t="inlineStr">
+        <is>
+          <t>26,Feb</t>
+        </is>
+      </c>
+      <c r="B835" t="inlineStr">
+        <is>
+          <t>Harsh Raj</t>
+        </is>
+      </c>
+      <c r="C835" t="inlineStr">
+        <is>
+          <t>Munna Kumar</t>
+        </is>
+      </c>
+      <c r="D835" t="inlineStr">
+        <is>
+          <t>Babita Kumari</t>
+        </is>
+      </c>
+      <c r="E835" t="inlineStr">
+        <is>
+          <t>VIII</t>
+        </is>
+      </c>
+      <c r="F835" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="836">
+      <c r="A836" t="inlineStr">
+        <is>
+          <t>26,Feb</t>
+        </is>
+      </c>
+      <c r="B836" t="inlineStr">
+        <is>
+          <t>HARSIKA KUMARI</t>
+        </is>
+      </c>
+      <c r="C836" t="inlineStr">
+        <is>
+          <t>SUDHANSHU KUMAR</t>
+        </is>
+      </c>
+      <c r="D836" t="inlineStr">
+        <is>
+          <t>SEEMA KUMARI</t>
+        </is>
+      </c>
+      <c r="E836" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="F836" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="837">
+      <c r="A837" t="inlineStr">
+        <is>
+          <t>26,Feb</t>
+        </is>
+      </c>
+      <c r="B837" t="inlineStr">
+        <is>
+          <t>HARSH RAJ</t>
+        </is>
+      </c>
+      <c r="C837" t="inlineStr">
+        <is>
+          <t>BIJENDRA KUMAR</t>
+        </is>
+      </c>
+      <c r="D837" t="inlineStr">
+        <is>
+          <t>RINKI DEVI</t>
+        </is>
+      </c>
+      <c r="E837" t="inlineStr">
+        <is>
+          <t>VII</t>
+        </is>
+      </c>
+      <c r="F837" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="838">
+      <c r="A838" t="inlineStr">
+        <is>
+          <t>26,Feb</t>
+        </is>
+      </c>
+      <c r="B838" t="inlineStr">
+        <is>
+          <t>KALADHAR TULSI</t>
+        </is>
+      </c>
+      <c r="C838" t="inlineStr">
+        <is>
+          <t>MRITYUNJAY KUMAR</t>
+        </is>
+      </c>
+      <c r="D838" t="inlineStr">
+        <is>
+          <t>ASMITA KUMARI</t>
+        </is>
+      </c>
+      <c r="E838" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F838" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="839">
+      <c r="A839" t="inlineStr">
+        <is>
+          <t>26,Feb</t>
+        </is>
+      </c>
+      <c r="B839" t="inlineStr">
+        <is>
+          <t>Riya Kumari</t>
+        </is>
+      </c>
+      <c r="C839" t="inlineStr">
+        <is>
+          <t>Sanjay Kumar</t>
+        </is>
+      </c>
+      <c r="D839" t="inlineStr">
+        <is>
+          <t>Anjana Devi</t>
+        </is>
+      </c>
+      <c r="E839" t="inlineStr">
+        <is>
+          <t>IX</t>
+        </is>
+      </c>
+      <c r="F839" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="840">
+      <c r="A840" t="inlineStr">
+        <is>
+          <t>26,Feb</t>
+        </is>
+      </c>
+      <c r="B840" t="inlineStr">
+        <is>
+          <t>DIVYA  KUMARI</t>
+        </is>
+      </c>
+      <c r="C840" t="inlineStr">
+        <is>
+          <t>RAMDEEP KUMAR</t>
+        </is>
+      </c>
+      <c r="D840" t="inlineStr">
+        <is>
+          <t>RUBI DEVI</t>
+        </is>
+      </c>
+      <c r="E840" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="F840" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="841">
+      <c r="A841" t="inlineStr">
+        <is>
+          <t>26,Feb</t>
+        </is>
+      </c>
+      <c r="B841" t="inlineStr">
+        <is>
+          <t>MOHIT RAJ</t>
+        </is>
+      </c>
+      <c r="C841" t="inlineStr">
+        <is>
+          <t>SUNIL KUMAR</t>
+        </is>
+      </c>
+      <c r="D841" t="inlineStr">
+        <is>
+          <t>RANJU KUMARI</t>
+        </is>
+      </c>
+      <c r="E841" t="inlineStr">
+        <is>
+          <t>IV</t>
+        </is>
+      </c>
+      <c r="F841" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Birthday Data Master.xlsx
+++ b/Birthday Data Master.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F841"/>
+  <dimension ref="A1:F851"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.6" customWidth="1" min="1" max="1"/>
@@ -27336,6 +27336,326 @@
         </is>
       </c>
     </row>
+    <row r="842">
+      <c r="A842" t="inlineStr">
+        <is>
+          <t>27,Feb</t>
+        </is>
+      </c>
+      <c r="B842" t="inlineStr">
+        <is>
+          <t>SIMRAN KUMARI</t>
+        </is>
+      </c>
+      <c r="C842" t="inlineStr">
+        <is>
+          <t>PANKAJ KUMAR</t>
+        </is>
+      </c>
+      <c r="D842" t="inlineStr">
+        <is>
+          <t>SNEHLATA</t>
+        </is>
+      </c>
+      <c r="E842" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="F842" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="843">
+      <c r="A843" t="inlineStr">
+        <is>
+          <t>27,Feb</t>
+        </is>
+      </c>
+      <c r="B843" t="inlineStr">
+        <is>
+          <t>Rudra keshri</t>
+        </is>
+      </c>
+      <c r="C843" t="inlineStr">
+        <is>
+          <t>Amit Kumar</t>
+        </is>
+      </c>
+      <c r="D843" t="inlineStr">
+        <is>
+          <t>Pallavi Kumari</t>
+        </is>
+      </c>
+      <c r="E843" t="inlineStr">
+        <is>
+          <t>VIII</t>
+        </is>
+      </c>
+      <c r="F843" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="844">
+      <c r="A844" t="inlineStr">
+        <is>
+          <t>27,Feb</t>
+        </is>
+      </c>
+      <c r="B844" t="inlineStr">
+        <is>
+          <t>SHIVANSH RAJ</t>
+        </is>
+      </c>
+      <c r="C844" t="inlineStr">
+        <is>
+          <t>SAWRAV KUMAR</t>
+        </is>
+      </c>
+      <c r="D844" t="inlineStr">
+        <is>
+          <t>BIBHA BHARTI</t>
+        </is>
+      </c>
+      <c r="E844" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="F844" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="845">
+      <c r="A845" t="inlineStr">
+        <is>
+          <t>27,Feb</t>
+        </is>
+      </c>
+      <c r="B845" t="inlineStr">
+        <is>
+          <t>Khushbala Jee</t>
+        </is>
+      </c>
+      <c r="C845" t="inlineStr">
+        <is>
+          <t>Sudhir Kumar</t>
+        </is>
+      </c>
+      <c r="D845" t="inlineStr">
+        <is>
+          <t>Pinki Kumari</t>
+        </is>
+      </c>
+      <c r="E845" t="inlineStr">
+        <is>
+          <t>IX</t>
+        </is>
+      </c>
+      <c r="F845" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="846">
+      <c r="A846" t="inlineStr">
+        <is>
+          <t>27,Feb</t>
+        </is>
+      </c>
+      <c r="B846" t="inlineStr">
+        <is>
+          <t>SANVI CHANDRA</t>
+        </is>
+      </c>
+      <c r="C846" t="inlineStr">
+        <is>
+          <t>DR RAJESH CHANDRA</t>
+        </is>
+      </c>
+      <c r="D846" t="inlineStr">
+        <is>
+          <t>PRATIBHA KUMARI</t>
+        </is>
+      </c>
+      <c r="E846" t="inlineStr">
+        <is>
+          <t>VIII</t>
+        </is>
+      </c>
+      <c r="F846" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+    </row>
+    <row r="847">
+      <c r="A847" t="inlineStr">
+        <is>
+          <t>27,Feb</t>
+        </is>
+      </c>
+      <c r="B847" t="inlineStr">
+        <is>
+          <t>AKSHAJ KUMAR</t>
+        </is>
+      </c>
+      <c r="C847" t="inlineStr">
+        <is>
+          <t>GAJENDRA KUMAR</t>
+        </is>
+      </c>
+      <c r="D847" t="inlineStr">
+        <is>
+          <t>ARCHANA SINGH</t>
+        </is>
+      </c>
+      <c r="E847" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="F847" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="848">
+      <c r="A848" t="inlineStr">
+        <is>
+          <t>27,Feb</t>
+        </is>
+      </c>
+      <c r="B848" t="inlineStr">
+        <is>
+          <t>SIMRAN  KUMARI</t>
+        </is>
+      </c>
+      <c r="C848" t="inlineStr">
+        <is>
+          <t>AVINASH KUMAR</t>
+        </is>
+      </c>
+      <c r="D848" t="inlineStr">
+        <is>
+          <t>ANITA KUMARI</t>
+        </is>
+      </c>
+      <c r="E848" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="F848" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="849">
+      <c r="A849" t="inlineStr">
+        <is>
+          <t>27,Feb</t>
+        </is>
+      </c>
+      <c r="B849" t="inlineStr">
+        <is>
+          <t>ARYAN RAJ</t>
+        </is>
+      </c>
+      <c r="C849" t="inlineStr">
+        <is>
+          <t>SANTOSH KUMAR</t>
+        </is>
+      </c>
+      <c r="D849" t="inlineStr">
+        <is>
+          <t>REENA KUMARI</t>
+        </is>
+      </c>
+      <c r="E849" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="F849" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="850">
+      <c r="A850" t="inlineStr">
+        <is>
+          <t>27,Feb</t>
+        </is>
+      </c>
+      <c r="B850" t="inlineStr">
+        <is>
+          <t>MAYURI KUMARI</t>
+        </is>
+      </c>
+      <c r="C850" t="inlineStr">
+        <is>
+          <t>RANJEET PASWAN</t>
+        </is>
+      </c>
+      <c r="D850" t="inlineStr">
+        <is>
+          <t>MAMTA KUMARI</t>
+        </is>
+      </c>
+      <c r="E850" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="F850" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="851">
+      <c r="A851" t="inlineStr">
+        <is>
+          <t>27,Feb</t>
+        </is>
+      </c>
+      <c r="B851" t="inlineStr">
+        <is>
+          <t>ANURAG KRISHNA</t>
+        </is>
+      </c>
+      <c r="C851" t="inlineStr">
+        <is>
+          <t>ABHYANAND</t>
+        </is>
+      </c>
+      <c r="D851" t="inlineStr">
+        <is>
+          <t>PRITEE KUMARI</t>
+        </is>
+      </c>
+      <c r="E851" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F851" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Birthday Data Master.xlsx
+++ b/Birthday Data Master.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F851"/>
+  <dimension ref="A1:F862"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.6" customWidth="1" min="1" max="1"/>
@@ -27656,6 +27656,358 @@
         </is>
       </c>
     </row>
+    <row r="852">
+      <c r="A852" t="inlineStr">
+        <is>
+          <t>28,Feb</t>
+        </is>
+      </c>
+      <c r="B852" t="inlineStr">
+        <is>
+          <t>NANDANI KUMARI</t>
+        </is>
+      </c>
+      <c r="C852" t="inlineStr">
+        <is>
+          <t>ANJAN KUMAR</t>
+        </is>
+      </c>
+      <c r="D852" t="inlineStr">
+        <is>
+          <t>NIGAM KUMARI</t>
+        </is>
+      </c>
+      <c r="E852" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F852" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="853">
+      <c r="A853" t="inlineStr">
+        <is>
+          <t>28,Feb</t>
+        </is>
+      </c>
+      <c r="B853" t="inlineStr">
+        <is>
+          <t>UJJAWAL KANT</t>
+        </is>
+      </c>
+      <c r="C853" t="inlineStr">
+        <is>
+          <t>SANJAY KUMAR</t>
+        </is>
+      </c>
+      <c r="D853" t="inlineStr">
+        <is>
+          <t>BABY DEVI</t>
+        </is>
+      </c>
+      <c r="E853" t="inlineStr">
+        <is>
+          <t>VIII</t>
+        </is>
+      </c>
+      <c r="F853" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="854">
+      <c r="A854" t="inlineStr">
+        <is>
+          <t>28,Feb</t>
+        </is>
+      </c>
+      <c r="B854" t="inlineStr">
+        <is>
+          <t>MAHI RAJ</t>
+        </is>
+      </c>
+      <c r="C854" t="inlineStr">
+        <is>
+          <t>SUNIL KUMAR</t>
+        </is>
+      </c>
+      <c r="D854" t="inlineStr">
+        <is>
+          <t>RANJU KUMARI</t>
+        </is>
+      </c>
+      <c r="E854" t="inlineStr">
+        <is>
+          <t>VII</t>
+        </is>
+      </c>
+      <c r="F854" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="855">
+      <c r="A855" t="inlineStr">
+        <is>
+          <t>28,Feb</t>
+        </is>
+      </c>
+      <c r="B855" t="inlineStr">
+        <is>
+          <t>AYUSH RAJ</t>
+        </is>
+      </c>
+      <c r="C855" t="inlineStr">
+        <is>
+          <t>SUNIL KUMAR</t>
+        </is>
+      </c>
+      <c r="D855" t="inlineStr">
+        <is>
+          <t>SUNITA DEVI</t>
+        </is>
+      </c>
+      <c r="E855" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="F855" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="856">
+      <c r="A856" t="inlineStr">
+        <is>
+          <t>28,Feb</t>
+        </is>
+      </c>
+      <c r="B856" t="inlineStr">
+        <is>
+          <t>Komal Raj</t>
+        </is>
+      </c>
+      <c r="C856" t="inlineStr">
+        <is>
+          <t>Ajay Kumar</t>
+        </is>
+      </c>
+      <c r="D856" t="inlineStr">
+        <is>
+          <t>Sanjusha Kumari</t>
+        </is>
+      </c>
+      <c r="E856" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F856" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="857">
+      <c r="A857" t="inlineStr">
+        <is>
+          <t>28,Feb</t>
+        </is>
+      </c>
+      <c r="B857" t="inlineStr">
+        <is>
+          <t>Radhesh Sharma</t>
+        </is>
+      </c>
+      <c r="C857" t="inlineStr">
+        <is>
+          <t>Abhay Kumar</t>
+        </is>
+      </c>
+      <c r="D857" t="inlineStr">
+        <is>
+          <t>Dharmshila</t>
+        </is>
+      </c>
+      <c r="E857" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F857" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="858">
+      <c r="A858" t="inlineStr">
+        <is>
+          <t>28,Feb</t>
+        </is>
+      </c>
+      <c r="B858" t="inlineStr">
+        <is>
+          <t>ISHAN DWIJ</t>
+        </is>
+      </c>
+      <c r="C858" t="inlineStr">
+        <is>
+          <t>RANJAN KUMAR</t>
+        </is>
+      </c>
+      <c r="D858" t="inlineStr">
+        <is>
+          <t>PRIYANKA KUMARI</t>
+        </is>
+      </c>
+      <c r="E858" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="F858" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="859">
+      <c r="A859" t="inlineStr">
+        <is>
+          <t>28,Feb</t>
+        </is>
+      </c>
+      <c r="B859" t="inlineStr">
+        <is>
+          <t>Ankit  Kumar</t>
+        </is>
+      </c>
+      <c r="C859" t="inlineStr">
+        <is>
+          <t>Vinod Kumar</t>
+        </is>
+      </c>
+      <c r="D859" t="inlineStr">
+        <is>
+          <t>Reshmi Kumari</t>
+        </is>
+      </c>
+      <c r="E859" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F859" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="860">
+      <c r="A860" t="inlineStr">
+        <is>
+          <t>28,Feb</t>
+        </is>
+      </c>
+      <c r="B860" t="inlineStr">
+        <is>
+          <t>Sristi Suman</t>
+        </is>
+      </c>
+      <c r="C860" t="inlineStr">
+        <is>
+          <t>Rajeev Ranjan</t>
+        </is>
+      </c>
+      <c r="D860" t="inlineStr">
+        <is>
+          <t>Pramila Yadav</t>
+        </is>
+      </c>
+      <c r="E860" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F860" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="861">
+      <c r="A861" t="inlineStr">
+        <is>
+          <t>28,Feb</t>
+        </is>
+      </c>
+      <c r="B861" t="inlineStr">
+        <is>
+          <t>ZAINAB FATIMA</t>
+        </is>
+      </c>
+      <c r="C861" t="inlineStr">
+        <is>
+          <t>SHAHID MALLICK</t>
+        </is>
+      </c>
+      <c r="D861" t="inlineStr">
+        <is>
+          <t>NAHID KHATOON</t>
+        </is>
+      </c>
+      <c r="E861" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F861" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="862">
+      <c r="A862" t="inlineStr">
+        <is>
+          <t>29,Feb</t>
+        </is>
+      </c>
+      <c r="B862" t="inlineStr">
+        <is>
+          <t>ISHANI RANI</t>
+        </is>
+      </c>
+      <c r="C862" t="inlineStr">
+        <is>
+          <t>RAVINDRA KUMAR</t>
+        </is>
+      </c>
+      <c r="D862" t="inlineStr">
+        <is>
+          <t>PRITI KUMARI</t>
+        </is>
+      </c>
+      <c r="E862" t="inlineStr">
+        <is>
+          <t>IV</t>
+        </is>
+      </c>
+      <c r="F862" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Birthday Data Master.xlsx
+++ b/Birthday Data Master.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F862"/>
+  <dimension ref="A1:F875"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.6" customWidth="1" min="1" max="1"/>
@@ -28008,6 +28008,422 @@
         </is>
       </c>
     </row>
+    <row r="863">
+      <c r="A863" t="inlineStr">
+        <is>
+          <t>01,Mar</t>
+        </is>
+      </c>
+      <c r="B863" t="inlineStr">
+        <is>
+          <t>Abhayjeet Kashyap</t>
+        </is>
+      </c>
+      <c r="C863" t="inlineStr">
+        <is>
+          <t>Arun Kumar</t>
+        </is>
+      </c>
+      <c r="D863" t="inlineStr">
+        <is>
+          <t>Minta Kumari</t>
+        </is>
+      </c>
+      <c r="E863" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F863" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="864">
+      <c r="A864" t="inlineStr">
+        <is>
+          <t>01,Mar</t>
+        </is>
+      </c>
+      <c r="B864" t="inlineStr">
+        <is>
+          <t>SALINI KUMARI</t>
+        </is>
+      </c>
+      <c r="C864" t="inlineStr">
+        <is>
+          <t>Sonu Kumar</t>
+        </is>
+      </c>
+      <c r="D864" t="inlineStr">
+        <is>
+          <t>RANJU KUMARI</t>
+        </is>
+      </c>
+      <c r="E864" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F864" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="865">
+      <c r="A865" t="inlineStr">
+        <is>
+          <t>01,Mar</t>
+        </is>
+      </c>
+      <c r="B865" t="inlineStr">
+        <is>
+          <t>GIRISH KUMAR</t>
+        </is>
+      </c>
+      <c r="C865" t="inlineStr">
+        <is>
+          <t>RAVI SHEKHAR</t>
+        </is>
+      </c>
+      <c r="D865" t="inlineStr">
+        <is>
+          <t>PRIYANKA DEVI</t>
+        </is>
+      </c>
+      <c r="E865" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F865" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="866">
+      <c r="A866" t="inlineStr">
+        <is>
+          <t>01,Mar</t>
+        </is>
+      </c>
+      <c r="B866" t="inlineStr">
+        <is>
+          <t>Piyush Kumar</t>
+        </is>
+      </c>
+      <c r="C866" t="inlineStr">
+        <is>
+          <t>Ramashray Yadav</t>
+        </is>
+      </c>
+      <c r="D866" t="inlineStr">
+        <is>
+          <t>Ranju Devi</t>
+        </is>
+      </c>
+      <c r="E866" t="inlineStr">
+        <is>
+          <t>IX</t>
+        </is>
+      </c>
+      <c r="F866" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="867">
+      <c r="A867" t="inlineStr">
+        <is>
+          <t>01,Mar</t>
+        </is>
+      </c>
+      <c r="B867" t="inlineStr">
+        <is>
+          <t>Ayush Ranjan</t>
+        </is>
+      </c>
+      <c r="C867" t="inlineStr">
+        <is>
+          <t>Rajdeo Kumar</t>
+        </is>
+      </c>
+      <c r="D867" t="inlineStr">
+        <is>
+          <t>Babita Kumari</t>
+        </is>
+      </c>
+      <c r="E867" t="inlineStr">
+        <is>
+          <t>IX</t>
+        </is>
+      </c>
+      <c r="F867" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="868">
+      <c r="A868" t="inlineStr">
+        <is>
+          <t>01,Mar</t>
+        </is>
+      </c>
+      <c r="B868" t="inlineStr">
+        <is>
+          <t>NITIKA KUMARI</t>
+        </is>
+      </c>
+      <c r="C868" t="inlineStr">
+        <is>
+          <t>RAJEEV KUMAR RANJAN</t>
+        </is>
+      </c>
+      <c r="D868" t="inlineStr">
+        <is>
+          <t>SANJEETA KUMARI</t>
+        </is>
+      </c>
+      <c r="E868" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="F868" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="869">
+      <c r="A869" t="inlineStr">
+        <is>
+          <t>01,Mar</t>
+        </is>
+      </c>
+      <c r="B869" t="inlineStr">
+        <is>
+          <t>JYOTI RANI</t>
+        </is>
+      </c>
+      <c r="C869" t="inlineStr">
+        <is>
+          <t>ARJUN KUMAR</t>
+        </is>
+      </c>
+      <c r="D869" t="inlineStr">
+        <is>
+          <t>RENU KUMARI</t>
+        </is>
+      </c>
+      <c r="E869" t="inlineStr">
+        <is>
+          <t>IX</t>
+        </is>
+      </c>
+      <c r="F869" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="870">
+      <c r="A870" t="inlineStr">
+        <is>
+          <t>01,Mar</t>
+        </is>
+      </c>
+      <c r="B870" t="inlineStr">
+        <is>
+          <t>Mohit Kumar</t>
+        </is>
+      </c>
+      <c r="C870" t="inlineStr">
+        <is>
+          <t>AJit Kumar</t>
+        </is>
+      </c>
+      <c r="D870" t="inlineStr">
+        <is>
+          <t>Vinita Kumari</t>
+        </is>
+      </c>
+      <c r="E870" t="inlineStr">
+        <is>
+          <t>IX</t>
+        </is>
+      </c>
+      <c r="F870" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="871">
+      <c r="A871" t="inlineStr">
+        <is>
+          <t>01,Mar</t>
+        </is>
+      </c>
+      <c r="B871" t="inlineStr">
+        <is>
+          <t>MONASHER HASSAN</t>
+        </is>
+      </c>
+      <c r="C871" t="inlineStr">
+        <is>
+          <t>ABID HASSAN</t>
+        </is>
+      </c>
+      <c r="D871" t="inlineStr">
+        <is>
+          <t>FATMA KHATOON</t>
+        </is>
+      </c>
+      <c r="E871" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="F871" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="872">
+      <c r="A872" t="inlineStr">
+        <is>
+          <t>01,Mar</t>
+        </is>
+      </c>
+      <c r="B872" t="inlineStr">
+        <is>
+          <t>NITIKA SHARMA</t>
+        </is>
+      </c>
+      <c r="C872" t="inlineStr">
+        <is>
+          <t>Nitinj Kumar</t>
+        </is>
+      </c>
+      <c r="D872" t="inlineStr">
+        <is>
+          <t>Anshu Mala</t>
+        </is>
+      </c>
+      <c r="E872" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F872" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="873">
+      <c r="A873" t="inlineStr">
+        <is>
+          <t>01,Mar</t>
+        </is>
+      </c>
+      <c r="B873" t="inlineStr">
+        <is>
+          <t>Himanshu Raj</t>
+        </is>
+      </c>
+      <c r="C873" t="inlineStr">
+        <is>
+          <t>Dhiraj Kumar</t>
+        </is>
+      </c>
+      <c r="D873" t="inlineStr">
+        <is>
+          <t>Sarita Kumari</t>
+        </is>
+      </c>
+      <c r="E873" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F873" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="874">
+      <c r="A874" t="inlineStr">
+        <is>
+          <t>01,Mar</t>
+        </is>
+      </c>
+      <c r="B874" t="inlineStr">
+        <is>
+          <t>MOZAMMIL HASSAN</t>
+        </is>
+      </c>
+      <c r="C874" t="inlineStr">
+        <is>
+          <t>ABID HASSAN</t>
+        </is>
+      </c>
+      <c r="D874" t="inlineStr">
+        <is>
+          <t>FATMA KHATOON</t>
+        </is>
+      </c>
+      <c r="E874" t="inlineStr">
+        <is>
+          <t>IV</t>
+        </is>
+      </c>
+      <c r="F874" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="875">
+      <c r="A875" t="inlineStr">
+        <is>
+          <t>01,Mar</t>
+        </is>
+      </c>
+      <c r="B875" t="inlineStr">
+        <is>
+          <t>SHAURYA RAJ</t>
+        </is>
+      </c>
+      <c r="C875" t="inlineStr">
+        <is>
+          <t>BHUSHAN PRASAD</t>
+        </is>
+      </c>
+      <c r="D875" t="inlineStr">
+        <is>
+          <t>ALPANA KUMARI</t>
+        </is>
+      </c>
+      <c r="E875" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="F875" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Birthday Data Master.xlsx
+++ b/Birthday Data Master.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F875"/>
+  <dimension ref="A1:F886"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.6" customWidth="1" min="1" max="1"/>
@@ -28424,6 +28424,358 @@
         </is>
       </c>
     </row>
+    <row r="876">
+      <c r="A876" t="inlineStr">
+        <is>
+          <t>02,Mar</t>
+        </is>
+      </c>
+      <c r="B876" t="inlineStr">
+        <is>
+          <t>SAKSHI PATEL</t>
+        </is>
+      </c>
+      <c r="C876" t="inlineStr">
+        <is>
+          <t>KRISHNA KUMAR SINGH</t>
+        </is>
+      </c>
+      <c r="D876" t="inlineStr">
+        <is>
+          <t>MANJU KUMARI</t>
+        </is>
+      </c>
+      <c r="E876" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="F876" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="877">
+      <c r="A877" t="inlineStr">
+        <is>
+          <t>02,Mar</t>
+        </is>
+      </c>
+      <c r="B877" t="inlineStr">
+        <is>
+          <t>BALA JI</t>
+        </is>
+      </c>
+      <c r="C877" t="inlineStr">
+        <is>
+          <t>RAM KUMAR</t>
+        </is>
+      </c>
+      <c r="D877" t="inlineStr">
+        <is>
+          <t>SUSHMA KUMARI</t>
+        </is>
+      </c>
+      <c r="E877" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="F877" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="878">
+      <c r="A878" t="inlineStr">
+        <is>
+          <t>02,Mar</t>
+        </is>
+      </c>
+      <c r="B878" t="inlineStr">
+        <is>
+          <t>RISHAV SAXENA</t>
+        </is>
+      </c>
+      <c r="C878" t="inlineStr">
+        <is>
+          <t>RANJEET PASWAN</t>
+        </is>
+      </c>
+      <c r="D878" t="inlineStr">
+        <is>
+          <t>NISHA KUMARI</t>
+        </is>
+      </c>
+      <c r="E878" t="inlineStr">
+        <is>
+          <t>LKG</t>
+        </is>
+      </c>
+      <c r="F878" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="879">
+      <c r="A879" t="inlineStr">
+        <is>
+          <t>02,Mar</t>
+        </is>
+      </c>
+      <c r="B879" t="inlineStr">
+        <is>
+          <t>PRAGATI ANAND</t>
+        </is>
+      </c>
+      <c r="C879" t="inlineStr">
+        <is>
+          <t>SANJEEV SANGAHI</t>
+        </is>
+      </c>
+      <c r="D879" t="inlineStr">
+        <is>
+          <t>ARYA</t>
+        </is>
+      </c>
+      <c r="E879" t="inlineStr">
+        <is>
+          <t>VII</t>
+        </is>
+      </c>
+      <c r="F879" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="880">
+      <c r="A880" t="inlineStr">
+        <is>
+          <t>02,Mar</t>
+        </is>
+      </c>
+      <c r="B880" t="inlineStr">
+        <is>
+          <t>Mayank Vats</t>
+        </is>
+      </c>
+      <c r="C880" t="inlineStr">
+        <is>
+          <t>Ritesh Ranjan</t>
+        </is>
+      </c>
+      <c r="D880" t="inlineStr">
+        <is>
+          <t>Anisha Kumari</t>
+        </is>
+      </c>
+      <c r="E880" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F880" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="881">
+      <c r="A881" t="inlineStr">
+        <is>
+          <t>02,Mar</t>
+        </is>
+      </c>
+      <c r="B881" t="inlineStr">
+        <is>
+          <t>HARI KRISHNA</t>
+        </is>
+      </c>
+      <c r="C881" t="inlineStr">
+        <is>
+          <t>SANTOSH KUMAR</t>
+        </is>
+      </c>
+      <c r="D881" t="inlineStr">
+        <is>
+          <t>RANJU DEVI</t>
+        </is>
+      </c>
+      <c r="E881" t="inlineStr">
+        <is>
+          <t>IV</t>
+        </is>
+      </c>
+      <c r="F881" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="882">
+      <c r="A882" t="inlineStr">
+        <is>
+          <t>02,Mar</t>
+        </is>
+      </c>
+      <c r="B882" t="inlineStr">
+        <is>
+          <t>ABHAY   KRISHN</t>
+        </is>
+      </c>
+      <c r="C882" t="inlineStr">
+        <is>
+          <t>MUKESH KUMAR</t>
+        </is>
+      </c>
+      <c r="D882" t="inlineStr">
+        <is>
+          <t>RANI ARTI</t>
+        </is>
+      </c>
+      <c r="E882" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="F882" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="883">
+      <c r="A883" t="inlineStr">
+        <is>
+          <t>02,Mar</t>
+        </is>
+      </c>
+      <c r="B883" t="inlineStr">
+        <is>
+          <t>Arpit  Raj</t>
+        </is>
+      </c>
+      <c r="C883" t="inlineStr">
+        <is>
+          <t>Vimal Kumar</t>
+        </is>
+      </c>
+      <c r="D883" t="inlineStr">
+        <is>
+          <t>Kumari Punam Ray</t>
+        </is>
+      </c>
+      <c r="E883" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F883" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="884">
+      <c r="A884" t="inlineStr">
+        <is>
+          <t>02,Mar</t>
+        </is>
+      </c>
+      <c r="B884" t="inlineStr">
+        <is>
+          <t>MAYRA RAJ</t>
+        </is>
+      </c>
+      <c r="C884" t="inlineStr">
+        <is>
+          <t>ANUPAM RAJ</t>
+        </is>
+      </c>
+      <c r="D884" t="inlineStr">
+        <is>
+          <t>PRIYA KUMARI</t>
+        </is>
+      </c>
+      <c r="E884" t="inlineStr">
+        <is>
+          <t>LKG</t>
+        </is>
+      </c>
+      <c r="F884" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="885">
+      <c r="A885" t="inlineStr">
+        <is>
+          <t>02,Mar</t>
+        </is>
+      </c>
+      <c r="B885" t="inlineStr">
+        <is>
+          <t>Abhigyan  Kumar</t>
+        </is>
+      </c>
+      <c r="C885" t="inlineStr">
+        <is>
+          <t>Santosh Kumar</t>
+        </is>
+      </c>
+      <c r="D885" t="inlineStr">
+        <is>
+          <t>Rakhi Devi</t>
+        </is>
+      </c>
+      <c r="E885" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F885" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="886">
+      <c r="A886" t="inlineStr">
+        <is>
+          <t>02,Mar</t>
+        </is>
+      </c>
+      <c r="B886" t="inlineStr">
+        <is>
+          <t>LAKSHMI KUMARI</t>
+        </is>
+      </c>
+      <c r="C886" t="inlineStr">
+        <is>
+          <t>MANOJ KUMAR</t>
+        </is>
+      </c>
+      <c r="D886" t="inlineStr">
+        <is>
+          <t>RINKU KUMARI</t>
+        </is>
+      </c>
+      <c r="E886" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F886" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Birthday Data Master.xlsx
+++ b/Birthday Data Master.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F886"/>
+  <dimension ref="A1:F896"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.6" customWidth="1" min="1" max="1"/>
@@ -28776,6 +28776,326 @@
         </is>
       </c>
     </row>
+    <row r="887">
+      <c r="A887" t="inlineStr">
+        <is>
+          <t>03,Mar</t>
+        </is>
+      </c>
+      <c r="B887" t="inlineStr">
+        <is>
+          <t>SHIVANSH  KUMAR</t>
+        </is>
+      </c>
+      <c r="C887" t="inlineStr">
+        <is>
+          <t>NARAYAN KUMAR</t>
+        </is>
+      </c>
+      <c r="D887" t="inlineStr">
+        <is>
+          <t>ARPANA KUMARI</t>
+        </is>
+      </c>
+      <c r="E887" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="F887" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="888">
+      <c r="A888" t="inlineStr">
+        <is>
+          <t>03,Mar</t>
+        </is>
+      </c>
+      <c r="B888" t="inlineStr">
+        <is>
+          <t>RISHI KUMAR</t>
+        </is>
+      </c>
+      <c r="C888" t="inlineStr">
+        <is>
+          <t>AJIT KUMAR</t>
+        </is>
+      </c>
+      <c r="D888" t="inlineStr">
+        <is>
+          <t>SHANTA DEVI</t>
+        </is>
+      </c>
+      <c r="E888" t="inlineStr">
+        <is>
+          <t>VII</t>
+        </is>
+      </c>
+      <c r="F888" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="889">
+      <c r="A889" t="inlineStr">
+        <is>
+          <t>03,Mar</t>
+        </is>
+      </c>
+      <c r="B889" t="inlineStr">
+        <is>
+          <t>BHARAGAVI KUMARI</t>
+        </is>
+      </c>
+      <c r="C889" t="inlineStr">
+        <is>
+          <t>VIKASH KUMAR</t>
+        </is>
+      </c>
+      <c r="D889" t="inlineStr">
+        <is>
+          <t>NIRMALA KUMARI</t>
+        </is>
+      </c>
+      <c r="E889" t="inlineStr">
+        <is>
+          <t>VII</t>
+        </is>
+      </c>
+      <c r="F889" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="890">
+      <c r="A890" t="inlineStr">
+        <is>
+          <t>03,Mar</t>
+        </is>
+      </c>
+      <c r="B890" t="inlineStr">
+        <is>
+          <t>HIMANSHU RAJ</t>
+        </is>
+      </c>
+      <c r="C890" t="inlineStr">
+        <is>
+          <t>AMAR KUMAR</t>
+        </is>
+      </c>
+      <c r="D890" t="inlineStr">
+        <is>
+          <t>TUNNI KUMARI</t>
+        </is>
+      </c>
+      <c r="E890" t="inlineStr">
+        <is>
+          <t>UKG</t>
+        </is>
+      </c>
+      <c r="F890" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="891">
+      <c r="A891" t="inlineStr">
+        <is>
+          <t>03,Mar</t>
+        </is>
+      </c>
+      <c r="B891" t="inlineStr">
+        <is>
+          <t>Priyanshu  Kumar</t>
+        </is>
+      </c>
+      <c r="C891" t="inlineStr">
+        <is>
+          <t>Jitendra Kumar Pandey</t>
+        </is>
+      </c>
+      <c r="D891" t="inlineStr">
+        <is>
+          <t>Veena Devi</t>
+        </is>
+      </c>
+      <c r="E891" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F891" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="892">
+      <c r="A892" t="inlineStr">
+        <is>
+          <t>03,Mar</t>
+        </is>
+      </c>
+      <c r="B892" t="inlineStr">
+        <is>
+          <t>AASHI SHARMA</t>
+        </is>
+      </c>
+      <c r="C892" t="inlineStr">
+        <is>
+          <t>RAUSHAN KUMAR</t>
+        </is>
+      </c>
+      <c r="D892" t="inlineStr">
+        <is>
+          <t>HEMLATA KUMARI</t>
+        </is>
+      </c>
+      <c r="E892" t="inlineStr">
+        <is>
+          <t>IV</t>
+        </is>
+      </c>
+      <c r="F892" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="893">
+      <c r="A893" t="inlineStr">
+        <is>
+          <t>03,Mar</t>
+        </is>
+      </c>
+      <c r="B893" t="inlineStr">
+        <is>
+          <t>FAIJANUR  RAHMAN</t>
+        </is>
+      </c>
+      <c r="C893" t="inlineStr">
+        <is>
+          <t>MD. ZAKAULLA KHAN</t>
+        </is>
+      </c>
+      <c r="D893" t="inlineStr">
+        <is>
+          <t>SABA KHATOON</t>
+        </is>
+      </c>
+      <c r="E893" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="F893" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="894">
+      <c r="A894" t="inlineStr">
+        <is>
+          <t>03,Mar</t>
+        </is>
+      </c>
+      <c r="B894" t="inlineStr">
+        <is>
+          <t>ABHINAV PRITAM</t>
+        </is>
+      </c>
+      <c r="C894" t="inlineStr">
+        <is>
+          <t>AMRENDRA KUMAR</t>
+        </is>
+      </c>
+      <c r="D894" t="inlineStr">
+        <is>
+          <t>BANDANA KUMARI</t>
+        </is>
+      </c>
+      <c r="E894" t="inlineStr">
+        <is>
+          <t>IV</t>
+        </is>
+      </c>
+      <c r="F894" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="895">
+      <c r="A895" t="inlineStr">
+        <is>
+          <t>03,Mar</t>
+        </is>
+      </c>
+      <c r="B895" t="inlineStr">
+        <is>
+          <t>RITIKA ANAND</t>
+        </is>
+      </c>
+      <c r="C895" t="inlineStr">
+        <is>
+          <t>RAHUL ANAND</t>
+        </is>
+      </c>
+      <c r="D895" t="inlineStr">
+        <is>
+          <t>NITU KUMARI</t>
+        </is>
+      </c>
+      <c r="E895" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="F895" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="896">
+      <c r="A896" t="inlineStr">
+        <is>
+          <t>03,Mar</t>
+        </is>
+      </c>
+      <c r="B896" t="inlineStr">
+        <is>
+          <t>SRISHTY  GUPTA</t>
+        </is>
+      </c>
+      <c r="C896" t="inlineStr">
+        <is>
+          <t>HARENDRA KUMAR</t>
+        </is>
+      </c>
+      <c r="D896" t="inlineStr">
+        <is>
+          <t>ANJU KUMARI</t>
+        </is>
+      </c>
+      <c r="E896" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="F896" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Birthday Data Master.xlsx
+++ b/Birthday Data Master.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F896"/>
+  <dimension ref="A1:F900"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.6" customWidth="1" min="1" max="1"/>
@@ -29096,6 +29096,134 @@
         </is>
       </c>
     </row>
+    <row r="897">
+      <c r="A897" t="inlineStr">
+        <is>
+          <t>04,Mar</t>
+        </is>
+      </c>
+      <c r="B897" t="inlineStr">
+        <is>
+          <t>Aman  Kumar</t>
+        </is>
+      </c>
+      <c r="C897" t="inlineStr">
+        <is>
+          <t>Arvind Kumar</t>
+        </is>
+      </c>
+      <c r="D897" t="inlineStr">
+        <is>
+          <t>Anjali Kumari</t>
+        </is>
+      </c>
+      <c r="E897" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F897" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="898">
+      <c r="A898" t="inlineStr">
+        <is>
+          <t>04,Mar</t>
+        </is>
+      </c>
+      <c r="B898" t="inlineStr">
+        <is>
+          <t>AYUSHMAAN KUMAR</t>
+        </is>
+      </c>
+      <c r="C898" t="inlineStr">
+        <is>
+          <t>MAHANAND KUMAR</t>
+        </is>
+      </c>
+      <c r="D898" t="inlineStr">
+        <is>
+          <t>NANDANI KUMARI</t>
+        </is>
+      </c>
+      <c r="E898" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F898" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="899">
+      <c r="A899" t="inlineStr">
+        <is>
+          <t>04,Mar</t>
+        </is>
+      </c>
+      <c r="B899" t="inlineStr">
+        <is>
+          <t>Ankit Raj</t>
+        </is>
+      </c>
+      <c r="C899" t="inlineStr">
+        <is>
+          <t>RajeevRanjan Kumar</t>
+        </is>
+      </c>
+      <c r="D899" t="inlineStr">
+        <is>
+          <t>Pinki Kumari</t>
+        </is>
+      </c>
+      <c r="E899" t="inlineStr">
+        <is>
+          <t>IX</t>
+        </is>
+      </c>
+      <c r="F899" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="900">
+      <c r="A900" t="inlineStr">
+        <is>
+          <t>04,Mar</t>
+        </is>
+      </c>
+      <c r="B900" t="inlineStr">
+        <is>
+          <t>FAIQA IMAM</t>
+        </is>
+      </c>
+      <c r="C900" t="inlineStr">
+        <is>
+          <t>SAFDAR IMAM</t>
+        </is>
+      </c>
+      <c r="D900" t="inlineStr">
+        <is>
+          <t>KAHKASHAN RASHEED</t>
+        </is>
+      </c>
+      <c r="E900" t="inlineStr">
+        <is>
+          <t>UKG</t>
+        </is>
+      </c>
+      <c r="F900" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Birthday Data Master.xlsx
+++ b/Birthday Data Master.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F900"/>
+  <dimension ref="A1:F918"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.6" customWidth="1" min="1" max="1"/>
@@ -29224,6 +29224,582 @@
         </is>
       </c>
     </row>
+    <row r="901">
+      <c r="A901" t="inlineStr">
+        <is>
+          <t>05,Mar</t>
+        </is>
+      </c>
+      <c r="B901" t="inlineStr">
+        <is>
+          <t>MAAN SINGH</t>
+        </is>
+      </c>
+      <c r="C901" t="inlineStr">
+        <is>
+          <t>MANTU KUMAR SINGH</t>
+        </is>
+      </c>
+      <c r="D901" t="inlineStr">
+        <is>
+          <t>MAAHI SINGH</t>
+        </is>
+      </c>
+      <c r="E901" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="F901" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="902">
+      <c r="A902" t="inlineStr">
+        <is>
+          <t>05,Mar</t>
+        </is>
+      </c>
+      <c r="B902" t="inlineStr">
+        <is>
+          <t>Om Ji</t>
+        </is>
+      </c>
+      <c r="C902" t="inlineStr">
+        <is>
+          <t>Baliram Kumar</t>
+        </is>
+      </c>
+      <c r="D902" t="inlineStr">
+        <is>
+          <t>MadhuMala Devi</t>
+        </is>
+      </c>
+      <c r="E902" t="inlineStr">
+        <is>
+          <t>VIII</t>
+        </is>
+      </c>
+      <c r="F902" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="903">
+      <c r="A903" t="inlineStr">
+        <is>
+          <t>05,Mar</t>
+        </is>
+      </c>
+      <c r="B903" t="inlineStr">
+        <is>
+          <t>Anand Raj</t>
+        </is>
+      </c>
+      <c r="C903" t="inlineStr">
+        <is>
+          <t>Rajnish Kumar</t>
+        </is>
+      </c>
+      <c r="D903" t="inlineStr">
+        <is>
+          <t>Khushboo Kumari</t>
+        </is>
+      </c>
+      <c r="E903" t="inlineStr">
+        <is>
+          <t>VIII</t>
+        </is>
+      </c>
+      <c r="F903" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="904">
+      <c r="A904" t="inlineStr">
+        <is>
+          <t>05,Mar</t>
+        </is>
+      </c>
+      <c r="B904" t="inlineStr">
+        <is>
+          <t>RAGHUVIR SHARMA</t>
+        </is>
+      </c>
+      <c r="C904" t="inlineStr">
+        <is>
+          <t>SHYAM KISHOR</t>
+        </is>
+      </c>
+      <c r="D904" t="inlineStr">
+        <is>
+          <t>AMRITA</t>
+        </is>
+      </c>
+      <c r="E904" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="F904" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="905">
+      <c r="A905" t="inlineStr">
+        <is>
+          <t>05,Mar</t>
+        </is>
+      </c>
+      <c r="B905" t="inlineStr">
+        <is>
+          <t>Shalini  Kumari</t>
+        </is>
+      </c>
+      <c r="C905" t="inlineStr">
+        <is>
+          <t>Subodh Kumar</t>
+        </is>
+      </c>
+      <c r="D905" t="inlineStr">
+        <is>
+          <t>Romi Kumari</t>
+        </is>
+      </c>
+      <c r="E905" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F905" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="906">
+      <c r="A906" t="inlineStr">
+        <is>
+          <t>05,Mar</t>
+        </is>
+      </c>
+      <c r="B906" t="inlineStr">
+        <is>
+          <t>ARYAN KUMAR</t>
+        </is>
+      </c>
+      <c r="C906" t="inlineStr">
+        <is>
+          <t>UTTAM KUMAR</t>
+        </is>
+      </c>
+      <c r="D906" t="inlineStr">
+        <is>
+          <t>DIMPI KUMARI</t>
+        </is>
+      </c>
+      <c r="E906" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="F906" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="907">
+      <c r="A907" t="inlineStr">
+        <is>
+          <t>05,Mar</t>
+        </is>
+      </c>
+      <c r="B907" t="inlineStr">
+        <is>
+          <t>GAURAV KUMAR</t>
+        </is>
+      </c>
+      <c r="C907" t="inlineStr">
+        <is>
+          <t>ANIL KUMAR</t>
+        </is>
+      </c>
+      <c r="D907" t="inlineStr">
+        <is>
+          <t>PUNAM DEVI</t>
+        </is>
+      </c>
+      <c r="E907" t="inlineStr">
+        <is>
+          <t>IV</t>
+        </is>
+      </c>
+      <c r="F907" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="908">
+      <c r="A908" t="inlineStr">
+        <is>
+          <t>05,Mar</t>
+        </is>
+      </c>
+      <c r="B908" t="inlineStr">
+        <is>
+          <t>SAKSHAM KUMAR</t>
+        </is>
+      </c>
+      <c r="C908" t="inlineStr">
+        <is>
+          <t>RAVI KANT KUMAR</t>
+        </is>
+      </c>
+      <c r="D908" t="inlineStr">
+        <is>
+          <t>SWATI KUMARI</t>
+        </is>
+      </c>
+      <c r="E908" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="F908" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="909">
+      <c r="A909" t="inlineStr">
+        <is>
+          <t>05,Mar</t>
+        </is>
+      </c>
+      <c r="B909" t="inlineStr">
+        <is>
+          <t>SHRISTY RANI</t>
+        </is>
+      </c>
+      <c r="C909" t="inlineStr">
+        <is>
+          <t>SHAILESH KUMAR</t>
+        </is>
+      </c>
+      <c r="D909" t="inlineStr">
+        <is>
+          <t>RENU DEVI</t>
+        </is>
+      </c>
+      <c r="E909" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="F909" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="910">
+      <c r="A910" t="inlineStr">
+        <is>
+          <t>05,Mar</t>
+        </is>
+      </c>
+      <c r="B910" t="inlineStr">
+        <is>
+          <t>ATHARV RAJ</t>
+        </is>
+      </c>
+      <c r="C910" t="inlineStr">
+        <is>
+          <t>MANISH KUMAR</t>
+        </is>
+      </c>
+      <c r="D910" t="inlineStr">
+        <is>
+          <t>PINKY KUMARI</t>
+        </is>
+      </c>
+      <c r="E910" t="inlineStr">
+        <is>
+          <t>UKG</t>
+        </is>
+      </c>
+      <c r="F910" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="911">
+      <c r="A911" t="inlineStr">
+        <is>
+          <t>05,Mar</t>
+        </is>
+      </c>
+      <c r="B911" t="inlineStr">
+        <is>
+          <t>KOMAL KUMARI</t>
+        </is>
+      </c>
+      <c r="C911" t="inlineStr">
+        <is>
+          <t>KAMLESH KUMAR</t>
+        </is>
+      </c>
+      <c r="D911" t="inlineStr">
+        <is>
+          <t>PUJA DEVI</t>
+        </is>
+      </c>
+      <c r="E911" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="F911" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="912">
+      <c r="A912" t="inlineStr">
+        <is>
+          <t>05,Mar</t>
+        </is>
+      </c>
+      <c r="B912" t="inlineStr">
+        <is>
+          <t>ADARSH  RAJ</t>
+        </is>
+      </c>
+      <c r="C912" t="inlineStr">
+        <is>
+          <t>SHAMBHU KUMAR</t>
+        </is>
+      </c>
+      <c r="D912" t="inlineStr">
+        <is>
+          <t>LALTI KUMARI</t>
+        </is>
+      </c>
+      <c r="E912" t="inlineStr">
+        <is>
+          <t>VII</t>
+        </is>
+      </c>
+      <c r="F912" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="913">
+      <c r="A913" t="inlineStr">
+        <is>
+          <t>05,Mar</t>
+        </is>
+      </c>
+      <c r="B913" t="inlineStr">
+        <is>
+          <t>MD AMAAN TANWEER</t>
+        </is>
+      </c>
+      <c r="C913" t="inlineStr">
+        <is>
+          <t>TANWIRUL HAQUE</t>
+        </is>
+      </c>
+      <c r="D913" t="inlineStr">
+        <is>
+          <t>RAUNAQUE AFROZ</t>
+        </is>
+      </c>
+      <c r="E913" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F913" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="914">
+      <c r="A914" t="inlineStr">
+        <is>
+          <t>05,Mar</t>
+        </is>
+      </c>
+      <c r="B914" t="inlineStr">
+        <is>
+          <t>Ayush  Kumar</t>
+        </is>
+      </c>
+      <c r="C914" t="inlineStr">
+        <is>
+          <t>Paritosh Kumar</t>
+        </is>
+      </c>
+      <c r="D914" t="inlineStr">
+        <is>
+          <t>Anju Kumari</t>
+        </is>
+      </c>
+      <c r="E914" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F914" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="915">
+      <c r="A915" t="inlineStr">
+        <is>
+          <t>05,Mar</t>
+        </is>
+      </c>
+      <c r="B915" t="inlineStr">
+        <is>
+          <t>Asmah Aslam</t>
+        </is>
+      </c>
+      <c r="C915" t="inlineStr">
+        <is>
+          <t>MD Aslam Hussain</t>
+        </is>
+      </c>
+      <c r="D915" t="inlineStr">
+        <is>
+          <t>Suraiya Trannum</t>
+        </is>
+      </c>
+      <c r="E915" t="inlineStr">
+        <is>
+          <t>IX</t>
+        </is>
+      </c>
+      <c r="F915" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="916">
+      <c r="A916" t="inlineStr">
+        <is>
+          <t>05,Mar</t>
+        </is>
+      </c>
+      <c r="B916" t="inlineStr">
+        <is>
+          <t>ANKIT RAJ</t>
+        </is>
+      </c>
+      <c r="C916" t="inlineStr">
+        <is>
+          <t>RANJAY KUMAR</t>
+        </is>
+      </c>
+      <c r="D916" t="inlineStr">
+        <is>
+          <t>ANITA KUMARI</t>
+        </is>
+      </c>
+      <c r="E916" t="inlineStr">
+        <is>
+          <t>VII</t>
+        </is>
+      </c>
+      <c r="F916" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="917">
+      <c r="A917" t="inlineStr">
+        <is>
+          <t>05,Mar</t>
+        </is>
+      </c>
+      <c r="B917" t="inlineStr">
+        <is>
+          <t>RISHABH  KUMAR</t>
+        </is>
+      </c>
+      <c r="C917" t="inlineStr">
+        <is>
+          <t>SUNIL KUMAR MALAKAR</t>
+        </is>
+      </c>
+      <c r="D917" t="inlineStr">
+        <is>
+          <t>RAGINI KUMARI</t>
+        </is>
+      </c>
+      <c r="E917" t="inlineStr">
+        <is>
+          <t>UKG</t>
+        </is>
+      </c>
+      <c r="F917" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="918">
+      <c r="A918" t="inlineStr">
+        <is>
+          <t>05,Mar</t>
+        </is>
+      </c>
+      <c r="B918" t="inlineStr">
+        <is>
+          <t>AMIT KUMAR</t>
+        </is>
+      </c>
+      <c r="C918" t="inlineStr">
+        <is>
+          <t>SUJIT KUMAR GAUTAM</t>
+        </is>
+      </c>
+      <c r="D918" t="inlineStr">
+        <is>
+          <t>AARTI KUMARI</t>
+        </is>
+      </c>
+      <c r="E918" t="inlineStr">
+        <is>
+          <t>LKG</t>
+        </is>
+      </c>
+      <c r="F918" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Birthday Data Master.xlsx
+++ b/Birthday Data Master.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F918"/>
+  <dimension ref="A1:F922"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.6" customWidth="1" min="1" max="1"/>
@@ -29800,6 +29800,134 @@
         </is>
       </c>
     </row>
+    <row r="919">
+      <c r="A919" t="inlineStr">
+        <is>
+          <t>06,Mar</t>
+        </is>
+      </c>
+      <c r="B919" t="inlineStr">
+        <is>
+          <t>Govind Sharan</t>
+        </is>
+      </c>
+      <c r="C919" t="inlineStr">
+        <is>
+          <t>Nirbhay Kumar</t>
+        </is>
+      </c>
+      <c r="D919" t="inlineStr">
+        <is>
+          <t>Mamta Devi</t>
+        </is>
+      </c>
+      <c r="E919" t="inlineStr">
+        <is>
+          <t>IX</t>
+        </is>
+      </c>
+      <c r="F919" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="920">
+      <c r="A920" t="inlineStr">
+        <is>
+          <t>06,Mar</t>
+        </is>
+      </c>
+      <c r="B920" t="inlineStr">
+        <is>
+          <t>LUVKUSH KUMAR LOVYAM</t>
+        </is>
+      </c>
+      <c r="C920" t="inlineStr">
+        <is>
+          <t>BIBEKANAND SINGH</t>
+        </is>
+      </c>
+      <c r="D920" t="inlineStr">
+        <is>
+          <t>KIRAN KUMARI</t>
+        </is>
+      </c>
+      <c r="E920" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="F920" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="921">
+      <c r="A921" t="inlineStr">
+        <is>
+          <t>06,Mar</t>
+        </is>
+      </c>
+      <c r="B921" t="inlineStr">
+        <is>
+          <t>RAJ  NANDANI</t>
+        </is>
+      </c>
+      <c r="C921" t="inlineStr">
+        <is>
+          <t>GAUTAM KUMAR</t>
+        </is>
+      </c>
+      <c r="D921" t="inlineStr">
+        <is>
+          <t>RUPA KUMARI</t>
+        </is>
+      </c>
+      <c r="E921" t="inlineStr">
+        <is>
+          <t>VII</t>
+        </is>
+      </c>
+      <c r="F921" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="922">
+      <c r="A922" t="inlineStr">
+        <is>
+          <t>06,Mar</t>
+        </is>
+      </c>
+      <c r="B922" t="inlineStr">
+        <is>
+          <t>CHAHAT KUMAR</t>
+        </is>
+      </c>
+      <c r="C922" t="inlineStr">
+        <is>
+          <t>Deepak Kumar</t>
+        </is>
+      </c>
+      <c r="D922" t="inlineStr">
+        <is>
+          <t>Dolly Kumari</t>
+        </is>
+      </c>
+      <c r="E922" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F922" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Birthday Data Master.xlsx
+++ b/Birthday Data Master.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F922"/>
+  <dimension ref="A1:F930"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.6" customWidth="1" min="1" max="1"/>
@@ -29928,6 +29928,262 @@
         </is>
       </c>
     </row>
+    <row r="923">
+      <c r="A923" t="inlineStr">
+        <is>
+          <t>07,Mar</t>
+        </is>
+      </c>
+      <c r="B923" t="inlineStr">
+        <is>
+          <t>Ankita  Ranjan</t>
+        </is>
+      </c>
+      <c r="C923" t="inlineStr">
+        <is>
+          <t>Rajeev Ranjan</t>
+        </is>
+      </c>
+      <c r="D923" t="inlineStr">
+        <is>
+          <t>Nilam Kumari</t>
+        </is>
+      </c>
+      <c r="E923" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F923" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="924">
+      <c r="A924" t="inlineStr">
+        <is>
+          <t>07,Mar</t>
+        </is>
+      </c>
+      <c r="B924" t="inlineStr">
+        <is>
+          <t>Manashvi Shree</t>
+        </is>
+      </c>
+      <c r="C924" t="inlineStr">
+        <is>
+          <t>Manoj Kumar</t>
+        </is>
+      </c>
+      <c r="D924" t="inlineStr">
+        <is>
+          <t>Bina Kumari</t>
+        </is>
+      </c>
+      <c r="E924" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F924" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="925">
+      <c r="A925" t="inlineStr">
+        <is>
+          <t>07,Mar</t>
+        </is>
+      </c>
+      <c r="B925" t="inlineStr">
+        <is>
+          <t>ANANYA KUMARI</t>
+        </is>
+      </c>
+      <c r="C925" t="inlineStr">
+        <is>
+          <t>ARUN KUMAR</t>
+        </is>
+      </c>
+      <c r="D925" t="inlineStr">
+        <is>
+          <t>SABITA KUMARI</t>
+        </is>
+      </c>
+      <c r="E925" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="F925" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="926">
+      <c r="A926" t="inlineStr">
+        <is>
+          <t>07,Mar</t>
+        </is>
+      </c>
+      <c r="B926" t="inlineStr">
+        <is>
+          <t>RANJAN RAJ</t>
+        </is>
+      </c>
+      <c r="C926" t="inlineStr">
+        <is>
+          <t>RANJEET PASWAN</t>
+        </is>
+      </c>
+      <c r="D926" t="inlineStr">
+        <is>
+          <t>MAMTA KUMARI</t>
+        </is>
+      </c>
+      <c r="E926" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="F926" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="927">
+      <c r="A927" t="inlineStr">
+        <is>
+          <t>07,Mar</t>
+        </is>
+      </c>
+      <c r="B927" t="inlineStr">
+        <is>
+          <t>NIKSHIT SINGH</t>
+        </is>
+      </c>
+      <c r="C927" t="inlineStr">
+        <is>
+          <t>ABADH KUMAR SINGH</t>
+        </is>
+      </c>
+      <c r="D927" t="inlineStr">
+        <is>
+          <t>NITU SINGH</t>
+        </is>
+      </c>
+      <c r="E927" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="F927" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="928">
+      <c r="A928" t="inlineStr">
+        <is>
+          <t>07,Mar</t>
+        </is>
+      </c>
+      <c r="B928" t="inlineStr">
+        <is>
+          <t>SHIVANSH KUMAR</t>
+        </is>
+      </c>
+      <c r="C928" t="inlineStr">
+        <is>
+          <t>SURYA BHUSHAN KUMAR</t>
+        </is>
+      </c>
+      <c r="D928" t="inlineStr">
+        <is>
+          <t>SURBHI KUMARI</t>
+        </is>
+      </c>
+      <c r="E928" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="F928" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="929">
+      <c r="A929" t="inlineStr">
+        <is>
+          <t>07,Mar</t>
+        </is>
+      </c>
+      <c r="B929" t="inlineStr">
+        <is>
+          <t>RISHI RAJ</t>
+        </is>
+      </c>
+      <c r="C929" t="inlineStr">
+        <is>
+          <t>ANIL KUMAR RANJAN</t>
+        </is>
+      </c>
+      <c r="D929" t="inlineStr">
+        <is>
+          <t>USHA KUMARI</t>
+        </is>
+      </c>
+      <c r="E929" t="inlineStr">
+        <is>
+          <t>IV</t>
+        </is>
+      </c>
+      <c r="F929" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="930">
+      <c r="A930" t="inlineStr">
+        <is>
+          <t>07,Mar</t>
+        </is>
+      </c>
+      <c r="B930" t="inlineStr">
+        <is>
+          <t>ARIHANT SINGH</t>
+        </is>
+      </c>
+      <c r="C930" t="inlineStr">
+        <is>
+          <t>DEEPAK KUMAR</t>
+        </is>
+      </c>
+      <c r="D930" t="inlineStr">
+        <is>
+          <t>SINGH RACHITA PRIYA</t>
+        </is>
+      </c>
+      <c r="E930" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="F930" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Birthday Data Master.xlsx
+++ b/Birthday Data Master.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F930"/>
+  <dimension ref="A1:F941"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.6" customWidth="1" min="1" max="1"/>
@@ -30184,6 +30184,358 @@
         </is>
       </c>
     </row>
+    <row r="931">
+      <c r="A931" t="inlineStr">
+        <is>
+          <t>08,Mar</t>
+        </is>
+      </c>
+      <c r="B931" t="inlineStr">
+        <is>
+          <t>AMRIT RAJ</t>
+        </is>
+      </c>
+      <c r="C931" t="inlineStr">
+        <is>
+          <t>ABHISHEK KUMAR</t>
+        </is>
+      </c>
+      <c r="D931" t="inlineStr">
+        <is>
+          <t>RINA GUPTA</t>
+        </is>
+      </c>
+      <c r="E931" t="inlineStr">
+        <is>
+          <t>IV</t>
+        </is>
+      </c>
+      <c r="F931" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="932">
+      <c r="A932" t="inlineStr">
+        <is>
+          <t>08,Mar</t>
+        </is>
+      </c>
+      <c r="B932" t="inlineStr">
+        <is>
+          <t>DIVYANSHU RAJ</t>
+        </is>
+      </c>
+      <c r="C932" t="inlineStr">
+        <is>
+          <t>ABHIMANYU</t>
+        </is>
+      </c>
+      <c r="D932" t="inlineStr">
+        <is>
+          <t>ARCHANA KUMARI</t>
+        </is>
+      </c>
+      <c r="E932" t="inlineStr">
+        <is>
+          <t>IV</t>
+        </is>
+      </c>
+      <c r="F932" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="933">
+      <c r="A933" t="inlineStr">
+        <is>
+          <t>08,Mar</t>
+        </is>
+      </c>
+      <c r="B933" t="inlineStr">
+        <is>
+          <t>VAISHNAVI KUMARI</t>
+        </is>
+      </c>
+      <c r="C933" t="inlineStr">
+        <is>
+          <t>AJIT KUMAR</t>
+        </is>
+      </c>
+      <c r="D933" t="inlineStr">
+        <is>
+          <t>KHUSHBU KUMARI</t>
+        </is>
+      </c>
+      <c r="E933" t="inlineStr">
+        <is>
+          <t>IV</t>
+        </is>
+      </c>
+      <c r="F933" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="934">
+      <c r="A934" t="inlineStr">
+        <is>
+          <t>08,Mar</t>
+        </is>
+      </c>
+      <c r="B934" t="inlineStr">
+        <is>
+          <t>Nitish Kumar</t>
+        </is>
+      </c>
+      <c r="C934" t="inlineStr">
+        <is>
+          <t>Krishna Murari Pandey</t>
+        </is>
+      </c>
+      <c r="D934" t="inlineStr">
+        <is>
+          <t>Renu Devi</t>
+        </is>
+      </c>
+      <c r="E934" t="inlineStr">
+        <is>
+          <t>VIII</t>
+        </is>
+      </c>
+      <c r="F934" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="935">
+      <c r="A935" t="inlineStr">
+        <is>
+          <t>08,Mar</t>
+        </is>
+      </c>
+      <c r="B935" t="inlineStr">
+        <is>
+          <t>SAHIL RAJ</t>
+        </is>
+      </c>
+      <c r="C935" t="inlineStr">
+        <is>
+          <t>SANTOSH KUMAR</t>
+        </is>
+      </c>
+      <c r="D935" t="inlineStr">
+        <is>
+          <t>PINKY KUMARI</t>
+        </is>
+      </c>
+      <c r="E935" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="F935" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="936">
+      <c r="A936" t="inlineStr">
+        <is>
+          <t>08,Mar</t>
+        </is>
+      </c>
+      <c r="B936" t="inlineStr">
+        <is>
+          <t>Shailja Gauri</t>
+        </is>
+      </c>
+      <c r="C936" t="inlineStr">
+        <is>
+          <t>Mani Bhushan PRASAD Sinha</t>
+        </is>
+      </c>
+      <c r="D936" t="inlineStr">
+        <is>
+          <t>Anita Sinha</t>
+        </is>
+      </c>
+      <c r="E936" t="inlineStr">
+        <is>
+          <t>VIII</t>
+        </is>
+      </c>
+      <c r="F936" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+    </row>
+    <row r="937">
+      <c r="A937" t="inlineStr">
+        <is>
+          <t>08,Mar</t>
+        </is>
+      </c>
+      <c r="B937" t="inlineStr">
+        <is>
+          <t>AAROHI KUMARI</t>
+        </is>
+      </c>
+      <c r="C937" t="inlineStr">
+        <is>
+          <t>SURAJ KUMAR</t>
+        </is>
+      </c>
+      <c r="D937" t="inlineStr">
+        <is>
+          <t>HEMLATA SINHA</t>
+        </is>
+      </c>
+      <c r="E937" t="inlineStr">
+        <is>
+          <t>LKG</t>
+        </is>
+      </c>
+      <c r="F937" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="938">
+      <c r="A938" t="inlineStr">
+        <is>
+          <t>08,Mar</t>
+        </is>
+      </c>
+      <c r="B938" t="inlineStr">
+        <is>
+          <t>Lucky Raj</t>
+        </is>
+      </c>
+      <c r="C938" t="inlineStr">
+        <is>
+          <t>Rajiv Ranjan Kumar</t>
+        </is>
+      </c>
+      <c r="D938" t="inlineStr">
+        <is>
+          <t>Pinki Kumari</t>
+        </is>
+      </c>
+      <c r="E938" t="inlineStr">
+        <is>
+          <t>VIII</t>
+        </is>
+      </c>
+      <c r="F938" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="939">
+      <c r="A939" t="inlineStr">
+        <is>
+          <t>08,Mar</t>
+        </is>
+      </c>
+      <c r="B939" t="inlineStr">
+        <is>
+          <t>ANIKET VERMA</t>
+        </is>
+      </c>
+      <c r="C939" t="inlineStr">
+        <is>
+          <t>RAJEEV RANJAN</t>
+        </is>
+      </c>
+      <c r="D939" t="inlineStr">
+        <is>
+          <t>NEELAM KUMARI</t>
+        </is>
+      </c>
+      <c r="E939" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F939" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="940">
+      <c r="A940" t="inlineStr">
+        <is>
+          <t>08,Mar</t>
+        </is>
+      </c>
+      <c r="B940" t="inlineStr">
+        <is>
+          <t>ASHTHA RANI</t>
+        </is>
+      </c>
+      <c r="C940" t="inlineStr">
+        <is>
+          <t>SUDHIR KUMAR</t>
+        </is>
+      </c>
+      <c r="D940" t="inlineStr">
+        <is>
+          <t>KUMARI PRIYANKA</t>
+        </is>
+      </c>
+      <c r="E940" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="F940" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+    </row>
+    <row r="941">
+      <c r="A941" t="inlineStr">
+        <is>
+          <t>08,Mar</t>
+        </is>
+      </c>
+      <c r="B941" t="inlineStr">
+        <is>
+          <t>MUNIBA FATMA</t>
+        </is>
+      </c>
+      <c r="C941" t="inlineStr">
+        <is>
+          <t>SYED MOHAMMAD SAIFULLAH</t>
+        </is>
+      </c>
+      <c r="D941" t="inlineStr">
+        <is>
+          <t>SHAHINA ANWAR</t>
+        </is>
+      </c>
+      <c r="E941" t="inlineStr">
+        <is>
+          <t>LKG</t>
+        </is>
+      </c>
+      <c r="F941" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Birthday Data Master.xlsx
+++ b/Birthday Data Master.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F941"/>
+  <dimension ref="A1:F959"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.6" customWidth="1" min="1" max="1"/>
@@ -30536,6 +30536,582 @@
         </is>
       </c>
     </row>
+    <row r="942">
+      <c r="A942" t="inlineStr">
+        <is>
+          <t>09,Mar</t>
+        </is>
+      </c>
+      <c r="B942" t="inlineStr">
+        <is>
+          <t>MEGHA KUMARI</t>
+        </is>
+      </c>
+      <c r="C942" t="inlineStr">
+        <is>
+          <t>PURUSHOTTAM KUMAR</t>
+        </is>
+      </c>
+      <c r="D942" t="inlineStr">
+        <is>
+          <t>SUSHMA KUMARI</t>
+        </is>
+      </c>
+      <c r="E942" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F942" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="943">
+      <c r="A943" t="inlineStr">
+        <is>
+          <t>09,Mar</t>
+        </is>
+      </c>
+      <c r="B943" t="inlineStr">
+        <is>
+          <t>ARNAV PATHAK</t>
+        </is>
+      </c>
+      <c r="C943" t="inlineStr">
+        <is>
+          <t>UMAKANT PATHAK</t>
+        </is>
+      </c>
+      <c r="D943" t="inlineStr">
+        <is>
+          <t>ARCHANA PATHAK</t>
+        </is>
+      </c>
+      <c r="E943" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F943" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="944">
+      <c r="A944" t="inlineStr">
+        <is>
+          <t>09,Mar</t>
+        </is>
+      </c>
+      <c r="B944" t="inlineStr">
+        <is>
+          <t>SHIVAM  KUMAR</t>
+        </is>
+      </c>
+      <c r="C944" t="inlineStr">
+        <is>
+          <t>RAJIV RANJAN</t>
+        </is>
+      </c>
+      <c r="D944" t="inlineStr">
+        <is>
+          <t>ANJANI KUMARI</t>
+        </is>
+      </c>
+      <c r="E944" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="F944" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="945">
+      <c r="A945" t="inlineStr">
+        <is>
+          <t>09,Mar</t>
+        </is>
+      </c>
+      <c r="B945" t="inlineStr">
+        <is>
+          <t>Prashant Kumar</t>
+        </is>
+      </c>
+      <c r="C945" t="inlineStr">
+        <is>
+          <t>Santosh Choudhary</t>
+        </is>
+      </c>
+      <c r="D945" t="inlineStr">
+        <is>
+          <t>Pushpa Kumari</t>
+        </is>
+      </c>
+      <c r="E945" t="inlineStr">
+        <is>
+          <t>VIII</t>
+        </is>
+      </c>
+      <c r="F945" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="946">
+      <c r="A946" t="inlineStr">
+        <is>
+          <t>10,Mar</t>
+        </is>
+      </c>
+      <c r="B946" t="inlineStr">
+        <is>
+          <t>Rakhi Kumari</t>
+        </is>
+      </c>
+      <c r="C946" t="inlineStr">
+        <is>
+          <t>Bhola Kumar</t>
+        </is>
+      </c>
+      <c r="D946" t="inlineStr">
+        <is>
+          <t>Seema Kumari</t>
+        </is>
+      </c>
+      <c r="E946" t="inlineStr">
+        <is>
+          <t>VIII</t>
+        </is>
+      </c>
+      <c r="F946" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="947">
+      <c r="A947" t="inlineStr">
+        <is>
+          <t>10,Mar</t>
+        </is>
+      </c>
+      <c r="B947" t="inlineStr">
+        <is>
+          <t>Shashank Vats</t>
+        </is>
+      </c>
+      <c r="C947" t="inlineStr">
+        <is>
+          <t>Mukesh Kumar</t>
+        </is>
+      </c>
+      <c r="D947" t="inlineStr">
+        <is>
+          <t>Pammi Kumari</t>
+        </is>
+      </c>
+      <c r="E947" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F947" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="948">
+      <c r="A948" t="inlineStr">
+        <is>
+          <t>10,Mar</t>
+        </is>
+      </c>
+      <c r="B948" t="inlineStr">
+        <is>
+          <t>Satkar Kumar</t>
+        </is>
+      </c>
+      <c r="C948" t="inlineStr">
+        <is>
+          <t>Shravan Kumar</t>
+        </is>
+      </c>
+      <c r="D948" t="inlineStr">
+        <is>
+          <t>Reena Devi</t>
+        </is>
+      </c>
+      <c r="E948" t="inlineStr">
+        <is>
+          <t>VIII</t>
+        </is>
+      </c>
+      <c r="F948" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="949">
+      <c r="A949" t="inlineStr">
+        <is>
+          <t>10,Mar</t>
+        </is>
+      </c>
+      <c r="B949" t="inlineStr">
+        <is>
+          <t>ABHINAV  KUMAR</t>
+        </is>
+      </c>
+      <c r="C949" t="inlineStr">
+        <is>
+          <t>RAM VIKASH KUMAR</t>
+        </is>
+      </c>
+      <c r="D949" t="inlineStr">
+        <is>
+          <t>REENA KUMARI</t>
+        </is>
+      </c>
+      <c r="E949" t="inlineStr">
+        <is>
+          <t>VII</t>
+        </is>
+      </c>
+      <c r="F949" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="950">
+      <c r="A950" t="inlineStr">
+        <is>
+          <t>10,Mar</t>
+        </is>
+      </c>
+      <c r="B950" t="inlineStr">
+        <is>
+          <t>Asmita</t>
+        </is>
+      </c>
+      <c r="C950" t="inlineStr">
+        <is>
+          <t>Arun Kumar Sah</t>
+        </is>
+      </c>
+      <c r="D950" t="inlineStr">
+        <is>
+          <t>Shivandana Kumari</t>
+        </is>
+      </c>
+      <c r="E950" t="inlineStr">
+        <is>
+          <t>IX</t>
+        </is>
+      </c>
+      <c r="F950" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="951">
+      <c r="A951" t="inlineStr">
+        <is>
+          <t>10,Mar</t>
+        </is>
+      </c>
+      <c r="B951" t="inlineStr">
+        <is>
+          <t>SAURABH KUMAR</t>
+        </is>
+      </c>
+      <c r="C951" t="inlineStr">
+        <is>
+          <t>RAVI CHAUDHARI</t>
+        </is>
+      </c>
+      <c r="D951" t="inlineStr">
+        <is>
+          <t>GEETA DEVI</t>
+        </is>
+      </c>
+      <c r="E951" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="F951" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="952">
+      <c r="A952" t="inlineStr">
+        <is>
+          <t>10,Mar</t>
+        </is>
+      </c>
+      <c r="B952" t="inlineStr">
+        <is>
+          <t>RAGNI KUMARI</t>
+        </is>
+      </c>
+      <c r="C952" t="inlineStr">
+        <is>
+          <t>GAUTAM KUMAR</t>
+        </is>
+      </c>
+      <c r="D952" t="inlineStr">
+        <is>
+          <t>PRIYANKA KUMARI</t>
+        </is>
+      </c>
+      <c r="E952" t="inlineStr">
+        <is>
+          <t>UKG</t>
+        </is>
+      </c>
+      <c r="F952" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="953">
+      <c r="A953" t="inlineStr">
+        <is>
+          <t>10,Mar</t>
+        </is>
+      </c>
+      <c r="B953" t="inlineStr">
+        <is>
+          <t>Sundaram Kumar Singh</t>
+        </is>
+      </c>
+      <c r="C953" t="inlineStr">
+        <is>
+          <t>Santosh Kumar</t>
+        </is>
+      </c>
+      <c r="D953" t="inlineStr">
+        <is>
+          <t>Pushpa Devi</t>
+        </is>
+      </c>
+      <c r="E953" t="inlineStr">
+        <is>
+          <t>IX</t>
+        </is>
+      </c>
+      <c r="F953" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="954">
+      <c r="A954" t="inlineStr">
+        <is>
+          <t>10,Mar</t>
+        </is>
+      </c>
+      <c r="B954" t="inlineStr">
+        <is>
+          <t>SRISHTY KUMARI</t>
+        </is>
+      </c>
+      <c r="C954" t="inlineStr">
+        <is>
+          <t>PRANAW KUMAR</t>
+        </is>
+      </c>
+      <c r="D954" t="inlineStr">
+        <is>
+          <t>RUBY KUMARI</t>
+        </is>
+      </c>
+      <c r="E954" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="F954" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="955">
+      <c r="A955" t="inlineStr">
+        <is>
+          <t>10,Mar</t>
+        </is>
+      </c>
+      <c r="B955" t="inlineStr">
+        <is>
+          <t>ARYAN</t>
+        </is>
+      </c>
+      <c r="C955" t="inlineStr">
+        <is>
+          <t>PRAVIN KUMAR</t>
+        </is>
+      </c>
+      <c r="D955" t="inlineStr">
+        <is>
+          <t>PRIYANKA KUMARI</t>
+        </is>
+      </c>
+      <c r="E955" t="inlineStr">
+        <is>
+          <t>UKG</t>
+        </is>
+      </c>
+      <c r="F955" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="956">
+      <c r="A956" t="inlineStr">
+        <is>
+          <t>10,Mar</t>
+        </is>
+      </c>
+      <c r="B956" t="inlineStr">
+        <is>
+          <t>ARADHYA  KUMARI</t>
+        </is>
+      </c>
+      <c r="C956" t="inlineStr">
+        <is>
+          <t>PANKAJ KUMAR</t>
+        </is>
+      </c>
+      <c r="D956" t="inlineStr">
+        <is>
+          <t>SWETA DEVI</t>
+        </is>
+      </c>
+      <c r="E956" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="F956" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="957">
+      <c r="A957" t="inlineStr">
+        <is>
+          <t>10,Mar</t>
+        </is>
+      </c>
+      <c r="B957" t="inlineStr">
+        <is>
+          <t>CHAHAT SINGH</t>
+        </is>
+      </c>
+      <c r="C957" t="inlineStr">
+        <is>
+          <t>SHANKAR PRASAD</t>
+        </is>
+      </c>
+      <c r="D957" t="inlineStr">
+        <is>
+          <t>ARCHANA KUMARI</t>
+        </is>
+      </c>
+      <c r="E957" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="F957" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="958">
+      <c r="A958" t="inlineStr">
+        <is>
+          <t>10,Mar</t>
+        </is>
+      </c>
+      <c r="B958" t="inlineStr">
+        <is>
+          <t>Viraj Gupta</t>
+        </is>
+      </c>
+      <c r="C958" t="inlineStr">
+        <is>
+          <t>Deepak Kumar</t>
+        </is>
+      </c>
+      <c r="D958" t="inlineStr">
+        <is>
+          <t>Sushma Kumari</t>
+        </is>
+      </c>
+      <c r="E958" t="inlineStr">
+        <is>
+          <t>VIII</t>
+        </is>
+      </c>
+      <c r="F958" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="959">
+      <c r="A959" t="inlineStr">
+        <is>
+          <t>10,Mar</t>
+        </is>
+      </c>
+      <c r="B959" t="inlineStr">
+        <is>
+          <t>AKASH RAJ</t>
+        </is>
+      </c>
+      <c r="C959" t="inlineStr">
+        <is>
+          <t>OM PRAKASH KUMAR</t>
+        </is>
+      </c>
+      <c r="D959" t="inlineStr">
+        <is>
+          <t>RINKU DEVI</t>
+        </is>
+      </c>
+      <c r="E959" t="inlineStr">
+        <is>
+          <t>IV</t>
+        </is>
+      </c>
+      <c r="F959" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Birthday Data Master.xlsx
+++ b/Birthday Data Master.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F959"/>
+  <dimension ref="A1:F967"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.6" customWidth="1" min="1" max="1"/>
@@ -31112,6 +31112,262 @@
         </is>
       </c>
     </row>
+    <row r="960">
+      <c r="A960" t="inlineStr">
+        <is>
+          <t>11,Mar</t>
+        </is>
+      </c>
+      <c r="B960" t="inlineStr">
+        <is>
+          <t>Anushka Priya</t>
+        </is>
+      </c>
+      <c r="C960" t="inlineStr">
+        <is>
+          <t>Birendra Prasad</t>
+        </is>
+      </c>
+      <c r="D960" t="inlineStr">
+        <is>
+          <t>Sarita Kumari</t>
+        </is>
+      </c>
+      <c r="E960" t="inlineStr">
+        <is>
+          <t>IX</t>
+        </is>
+      </c>
+      <c r="F960" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+    </row>
+    <row r="961">
+      <c r="A961" t="inlineStr">
+        <is>
+          <t>11,Mar</t>
+        </is>
+      </c>
+      <c r="B961" t="inlineStr">
+        <is>
+          <t>ARNAV RAJ</t>
+        </is>
+      </c>
+      <c r="C961" t="inlineStr">
+        <is>
+          <t>RAJEEV KUMAR</t>
+        </is>
+      </c>
+      <c r="D961" t="inlineStr">
+        <is>
+          <t>ARTI KUMARI</t>
+        </is>
+      </c>
+      <c r="E961" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="F961" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+    </row>
+    <row r="962">
+      <c r="A962" t="inlineStr">
+        <is>
+          <t>11,Mar</t>
+        </is>
+      </c>
+      <c r="B962" t="inlineStr">
+        <is>
+          <t>ADITYA RAJ</t>
+        </is>
+      </c>
+      <c r="C962" t="inlineStr">
+        <is>
+          <t>DEEPAK KUMAR</t>
+        </is>
+      </c>
+      <c r="D962" t="inlineStr">
+        <is>
+          <t>KHUSHBOO KUMARI</t>
+        </is>
+      </c>
+      <c r="E962" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="F962" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="963">
+      <c r="A963" t="inlineStr">
+        <is>
+          <t>11,Mar</t>
+        </is>
+      </c>
+      <c r="B963" t="inlineStr">
+        <is>
+          <t>Adarsh Raj</t>
+        </is>
+      </c>
+      <c r="C963" t="inlineStr">
+        <is>
+          <t>Sudhir Kumar</t>
+        </is>
+      </c>
+      <c r="D963" t="inlineStr">
+        <is>
+          <t>KUMARI Priyanka</t>
+        </is>
+      </c>
+      <c r="E963" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F963" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="964">
+      <c r="A964" t="inlineStr">
+        <is>
+          <t>11,Mar</t>
+        </is>
+      </c>
+      <c r="B964" t="inlineStr">
+        <is>
+          <t>ARMITA BHARTI</t>
+        </is>
+      </c>
+      <c r="C964" t="inlineStr">
+        <is>
+          <t>RAJEEV KUMAR</t>
+        </is>
+      </c>
+      <c r="D964" t="inlineStr">
+        <is>
+          <t>ARTI KUMARI</t>
+        </is>
+      </c>
+      <c r="E964" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="F964" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="965">
+      <c r="A965" t="inlineStr">
+        <is>
+          <t>11,Mar</t>
+        </is>
+      </c>
+      <c r="B965" t="inlineStr">
+        <is>
+          <t>AISHWARYA NANDAN</t>
+        </is>
+      </c>
+      <c r="C965" t="inlineStr">
+        <is>
+          <t>RADHASHARAN KUMAR</t>
+        </is>
+      </c>
+      <c r="D965" t="inlineStr">
+        <is>
+          <t>MINA KUMARI</t>
+        </is>
+      </c>
+      <c r="E965" t="inlineStr">
+        <is>
+          <t>VII</t>
+        </is>
+      </c>
+      <c r="F965" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="966">
+      <c r="A966" t="inlineStr">
+        <is>
+          <t>11,Mar</t>
+        </is>
+      </c>
+      <c r="B966" t="inlineStr">
+        <is>
+          <t>KESHAV KUMAR</t>
+        </is>
+      </c>
+      <c r="C966" t="inlineStr">
+        <is>
+          <t>ALOK KUMAR</t>
+        </is>
+      </c>
+      <c r="D966" t="inlineStr">
+        <is>
+          <t>GAYATRI KUMARI</t>
+        </is>
+      </c>
+      <c r="E966" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="F966" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="967">
+      <c r="A967" t="inlineStr">
+        <is>
+          <t>11,Mar</t>
+        </is>
+      </c>
+      <c r="B967" t="inlineStr">
+        <is>
+          <t>HAMDA ATHAR</t>
+        </is>
+      </c>
+      <c r="C967" t="inlineStr">
+        <is>
+          <t>SHAHBAZ ATHAR</t>
+        </is>
+      </c>
+      <c r="D967" t="inlineStr">
+        <is>
+          <t>ZEENAT PARWEEN</t>
+        </is>
+      </c>
+      <c r="E967" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="F967" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Birthday Data Master.xlsx
+++ b/Birthday Data Master.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F967"/>
+  <dimension ref="A1:F972"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.6" customWidth="1" min="1" max="1"/>
@@ -31368,6 +31368,166 @@
         </is>
       </c>
     </row>
+    <row r="968">
+      <c r="A968" t="inlineStr">
+        <is>
+          <t>12,Mar</t>
+        </is>
+      </c>
+      <c r="B968" t="inlineStr">
+        <is>
+          <t>Uday Kumar</t>
+        </is>
+      </c>
+      <c r="C968" t="inlineStr">
+        <is>
+          <t>Om Prakash .</t>
+        </is>
+      </c>
+      <c r="D968" t="inlineStr">
+        <is>
+          <t>Poonam Kumari</t>
+        </is>
+      </c>
+      <c r="E968" t="inlineStr">
+        <is>
+          <t>IX</t>
+        </is>
+      </c>
+      <c r="F968" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+    </row>
+    <row r="969">
+      <c r="A969" t="inlineStr">
+        <is>
+          <t>12,Mar</t>
+        </is>
+      </c>
+      <c r="B969" t="inlineStr">
+        <is>
+          <t>TEJASH KUMAR</t>
+        </is>
+      </c>
+      <c r="C969" t="inlineStr">
+        <is>
+          <t>RANJAN KUMAR</t>
+        </is>
+      </c>
+      <c r="D969" t="inlineStr">
+        <is>
+          <t>RINKI KUMARI</t>
+        </is>
+      </c>
+      <c r="E969" t="inlineStr">
+        <is>
+          <t>IV</t>
+        </is>
+      </c>
+      <c r="F969" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="970">
+      <c r="A970" t="inlineStr">
+        <is>
+          <t>12,Mar</t>
+        </is>
+      </c>
+      <c r="B970" t="inlineStr">
+        <is>
+          <t>HARSHIT RAJ</t>
+        </is>
+      </c>
+      <c r="C970" t="inlineStr">
+        <is>
+          <t>MANISH KUMAR</t>
+        </is>
+      </c>
+      <c r="D970" t="inlineStr">
+        <is>
+          <t>SONI KUMARI</t>
+        </is>
+      </c>
+      <c r="E970" t="inlineStr">
+        <is>
+          <t>IV</t>
+        </is>
+      </c>
+      <c r="F970" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="971">
+      <c r="A971" t="inlineStr">
+        <is>
+          <t>12,Mar</t>
+        </is>
+      </c>
+      <c r="B971" t="inlineStr">
+        <is>
+          <t>ANKIT  KUMAR</t>
+        </is>
+      </c>
+      <c r="C971" t="inlineStr">
+        <is>
+          <t>BHARAT KUMAR</t>
+        </is>
+      </c>
+      <c r="D971" t="inlineStr">
+        <is>
+          <t>RUPA DEVI</t>
+        </is>
+      </c>
+      <c r="E971" t="inlineStr">
+        <is>
+          <t>XII</t>
+        </is>
+      </c>
+      <c r="F971" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="972">
+      <c r="A972" t="inlineStr">
+        <is>
+          <t>12,Mar</t>
+        </is>
+      </c>
+      <c r="B972" t="inlineStr">
+        <is>
+          <t>AMAN KUMAR</t>
+        </is>
+      </c>
+      <c r="C972" t="inlineStr">
+        <is>
+          <t>ANIL KUMAR</t>
+        </is>
+      </c>
+      <c r="D972" t="inlineStr">
+        <is>
+          <t>RUPA KUMARI</t>
+        </is>
+      </c>
+      <c r="E972" t="inlineStr">
+        <is>
+          <t>UKG</t>
+        </is>
+      </c>
+      <c r="F972" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Birthday Data Master.xlsx
+++ b/Birthday Data Master.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F972"/>
+  <dimension ref="A1:F975"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.6" customWidth="1" min="1" max="1"/>
@@ -31528,6 +31528,102 @@
         </is>
       </c>
     </row>
+    <row r="973">
+      <c r="A973" t="inlineStr">
+        <is>
+          <t>13,Mar</t>
+        </is>
+      </c>
+      <c r="B973" t="inlineStr">
+        <is>
+          <t>KRISH KUMAR</t>
+        </is>
+      </c>
+      <c r="C973" t="inlineStr">
+        <is>
+          <t>SUDHIR KUMAR</t>
+        </is>
+      </c>
+      <c r="D973" t="inlineStr">
+        <is>
+          <t>RITA DEVI</t>
+        </is>
+      </c>
+      <c r="E973" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="F973" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="974">
+      <c r="A974" t="inlineStr">
+        <is>
+          <t>13,Mar</t>
+        </is>
+      </c>
+      <c r="B974" t="inlineStr">
+        <is>
+          <t>PIYUSH  KUMAR</t>
+        </is>
+      </c>
+      <c r="C974" t="inlineStr">
+        <is>
+          <t>RAJIV KUMAR</t>
+        </is>
+      </c>
+      <c r="D974" t="inlineStr">
+        <is>
+          <t>ANKITA KUMARI</t>
+        </is>
+      </c>
+      <c r="E974" t="inlineStr">
+        <is>
+          <t>IV</t>
+        </is>
+      </c>
+      <c r="F974" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="975">
+      <c r="A975" t="inlineStr">
+        <is>
+          <t>13,Mar</t>
+        </is>
+      </c>
+      <c r="B975" t="inlineStr">
+        <is>
+          <t>KESHAV RAJ</t>
+        </is>
+      </c>
+      <c r="C975" t="inlineStr">
+        <is>
+          <t>GAUTAM KUMAR</t>
+        </is>
+      </c>
+      <c r="D975" t="inlineStr">
+        <is>
+          <t>RASHMI KUMARI</t>
+        </is>
+      </c>
+      <c r="E975" t="inlineStr">
+        <is>
+          <t>IV</t>
+        </is>
+      </c>
+      <c r="F975" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Birthday Data Master.xlsx
+++ b/Birthday Data Master.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F975"/>
+  <dimension ref="A1:F979"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.6" customWidth="1" min="1" max="1"/>
@@ -31624,6 +31624,134 @@
         </is>
       </c>
     </row>
+    <row r="976">
+      <c r="A976" t="inlineStr">
+        <is>
+          <t>14,Mar</t>
+        </is>
+      </c>
+      <c r="B976" t="inlineStr">
+        <is>
+          <t>AVI RAJ</t>
+        </is>
+      </c>
+      <c r="C976" t="inlineStr">
+        <is>
+          <t>AJEET KUMAR</t>
+        </is>
+      </c>
+      <c r="D976" t="inlineStr">
+        <is>
+          <t>VIBHA KUMARI</t>
+        </is>
+      </c>
+      <c r="E976" t="inlineStr">
+        <is>
+          <t>VII</t>
+        </is>
+      </c>
+      <c r="F976" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="977">
+      <c r="A977" t="inlineStr">
+        <is>
+          <t>14,Mar</t>
+        </is>
+      </c>
+      <c r="B977" t="inlineStr">
+        <is>
+          <t>VAISHNAVI KUMARI</t>
+        </is>
+      </c>
+      <c r="C977" t="inlineStr">
+        <is>
+          <t>SUJIT KUMAR</t>
+        </is>
+      </c>
+      <c r="D977" t="inlineStr">
+        <is>
+          <t>BINITA KUMARI</t>
+        </is>
+      </c>
+      <c r="E977" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F977" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="978">
+      <c r="A978" t="inlineStr">
+        <is>
+          <t>14,Mar</t>
+        </is>
+      </c>
+      <c r="B978" t="inlineStr">
+        <is>
+          <t>PRIYANSHU RAJ</t>
+        </is>
+      </c>
+      <c r="C978" t="inlineStr">
+        <is>
+          <t>DHARMENDRA KUMAR</t>
+        </is>
+      </c>
+      <c r="D978" t="inlineStr">
+        <is>
+          <t>ARCHANA KUMARI</t>
+        </is>
+      </c>
+      <c r="E978" t="inlineStr">
+        <is>
+          <t>VII</t>
+        </is>
+      </c>
+      <c r="F978" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+    </row>
+    <row r="979">
+      <c r="A979" t="inlineStr">
+        <is>
+          <t>14,Mar</t>
+        </is>
+      </c>
+      <c r="B979" t="inlineStr">
+        <is>
+          <t>Aastha Aanand</t>
+        </is>
+      </c>
+      <c r="C979" t="inlineStr">
+        <is>
+          <t>Brajendra Kumar</t>
+        </is>
+      </c>
+      <c r="D979" t="inlineStr">
+        <is>
+          <t>Kumari Pallavi Sinha</t>
+        </is>
+      </c>
+      <c r="E979" t="inlineStr">
+        <is>
+          <t>VIII</t>
+        </is>
+      </c>
+      <c r="F979" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Birthday Data Master.xlsx
+++ b/Birthday Data Master.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F979"/>
+  <dimension ref="A1:F987"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.6" customWidth="1" min="1" max="1"/>
@@ -31752,6 +31752,262 @@
         </is>
       </c>
     </row>
+    <row r="980">
+      <c r="A980" t="inlineStr">
+        <is>
+          <t>15,Mar</t>
+        </is>
+      </c>
+      <c r="B980" t="inlineStr">
+        <is>
+          <t>VEDANT KASHYAP</t>
+        </is>
+      </c>
+      <c r="C980" t="inlineStr">
+        <is>
+          <t>VIVEK KUMAR</t>
+        </is>
+      </c>
+      <c r="D980" t="inlineStr">
+        <is>
+          <t>GUNJAN KUMARI</t>
+        </is>
+      </c>
+      <c r="E980" t="inlineStr">
+        <is>
+          <t>LKG</t>
+        </is>
+      </c>
+      <c r="F980" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="981">
+      <c r="A981" t="inlineStr">
+        <is>
+          <t>15,Mar</t>
+        </is>
+      </c>
+      <c r="B981" t="inlineStr">
+        <is>
+          <t>SAUMYA BHARTI</t>
+        </is>
+      </c>
+      <c r="C981" t="inlineStr">
+        <is>
+          <t>SUSHANT KUMAR PATHAK</t>
+        </is>
+      </c>
+      <c r="D981" t="inlineStr">
+        <is>
+          <t>MALA KUMARI</t>
+        </is>
+      </c>
+      <c r="E981" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="F981" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="982">
+      <c r="A982" t="inlineStr">
+        <is>
+          <t>15,Mar</t>
+        </is>
+      </c>
+      <c r="B982" t="inlineStr">
+        <is>
+          <t>PRATYUSH RAJ</t>
+        </is>
+      </c>
+      <c r="C982" t="inlineStr">
+        <is>
+          <t>ARUN KUMAR</t>
+        </is>
+      </c>
+      <c r="D982" t="inlineStr">
+        <is>
+          <t>SUSHMA KUMARI</t>
+        </is>
+      </c>
+      <c r="E982" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F982" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="983">
+      <c r="A983" t="inlineStr">
+        <is>
+          <t>15,Mar</t>
+        </is>
+      </c>
+      <c r="B983" t="inlineStr">
+        <is>
+          <t>HARE RAM KASHYAP</t>
+        </is>
+      </c>
+      <c r="C983" t="inlineStr">
+        <is>
+          <t>GOUTAM KUMAR</t>
+        </is>
+      </c>
+      <c r="D983" t="inlineStr">
+        <is>
+          <t>CHANDANI KUMARI</t>
+        </is>
+      </c>
+      <c r="E983" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="F983" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="984">
+      <c r="A984" t="inlineStr">
+        <is>
+          <t>15,Mar</t>
+        </is>
+      </c>
+      <c r="B984" t="inlineStr">
+        <is>
+          <t>ROHIT KUMAR</t>
+        </is>
+      </c>
+      <c r="C984" t="inlineStr">
+        <is>
+          <t>SUDHIR KUMAR</t>
+        </is>
+      </c>
+      <c r="D984" t="inlineStr">
+        <is>
+          <t>INDU DEVI</t>
+        </is>
+      </c>
+      <c r="E984" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F984" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="985">
+      <c r="A985" t="inlineStr">
+        <is>
+          <t>15,Mar</t>
+        </is>
+      </c>
+      <c r="B985" t="inlineStr">
+        <is>
+          <t>SATYAM KUMAR</t>
+        </is>
+      </c>
+      <c r="C985" t="inlineStr">
+        <is>
+          <t>SHIV RANJAN PRASAD</t>
+        </is>
+      </c>
+      <c r="D985" t="inlineStr">
+        <is>
+          <t>NISHA KUMARI</t>
+        </is>
+      </c>
+      <c r="E985" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F985" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="986">
+      <c r="A986" t="inlineStr">
+        <is>
+          <t>15,Mar</t>
+        </is>
+      </c>
+      <c r="B986" t="inlineStr">
+        <is>
+          <t>Roushan Kumar</t>
+        </is>
+      </c>
+      <c r="C986" t="inlineStr">
+        <is>
+          <t>Brajesh Kumar</t>
+        </is>
+      </c>
+      <c r="D986" t="inlineStr">
+        <is>
+          <t>Anshu Devi</t>
+        </is>
+      </c>
+      <c r="E986" t="inlineStr">
+        <is>
+          <t>VIII</t>
+        </is>
+      </c>
+      <c r="F986" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="987">
+      <c r="A987" t="inlineStr">
+        <is>
+          <t>15,Mar</t>
+        </is>
+      </c>
+      <c r="B987" t="inlineStr">
+        <is>
+          <t>Jay Prakash Kumar</t>
+        </is>
+      </c>
+      <c r="C987" t="inlineStr">
+        <is>
+          <t>Indra Kumar Singh</t>
+        </is>
+      </c>
+      <c r="D987" t="inlineStr">
+        <is>
+          <t>Parwati Devi</t>
+        </is>
+      </c>
+      <c r="E987" t="inlineStr">
+        <is>
+          <t>VIII</t>
+        </is>
+      </c>
+      <c r="F987" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Birthday Data Master.xlsx
+++ b/Birthday Data Master.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F987"/>
+  <dimension ref="A1:F993"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.6" customWidth="1" min="1" max="1"/>
@@ -32008,6 +32008,198 @@
         </is>
       </c>
     </row>
+    <row r="988">
+      <c r="A988" t="inlineStr">
+        <is>
+          <t>16,Mar</t>
+        </is>
+      </c>
+      <c r="B988" t="inlineStr">
+        <is>
+          <t>AAYU KUMAR</t>
+        </is>
+      </c>
+      <c r="C988" t="inlineStr">
+        <is>
+          <t>AMIT KUMAR</t>
+        </is>
+      </c>
+      <c r="D988" t="inlineStr">
+        <is>
+          <t>BABITA KUMARI</t>
+        </is>
+      </c>
+      <c r="E988" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="F988" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="989">
+      <c r="A989" t="inlineStr">
+        <is>
+          <t>16,Mar</t>
+        </is>
+      </c>
+      <c r="B989" t="inlineStr">
+        <is>
+          <t>VIDHAN SHARMA</t>
+        </is>
+      </c>
+      <c r="C989" t="inlineStr">
+        <is>
+          <t>KUNJ BIHARI</t>
+        </is>
+      </c>
+      <c r="D989" t="inlineStr">
+        <is>
+          <t>NIDHI KUMARI</t>
+        </is>
+      </c>
+      <c r="E989" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F989" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="990">
+      <c r="A990" t="inlineStr">
+        <is>
+          <t>16,Mar</t>
+        </is>
+      </c>
+      <c r="B990" t="inlineStr">
+        <is>
+          <t>KHUSHI KUMARI NISHAD</t>
+        </is>
+      </c>
+      <c r="C990" t="inlineStr">
+        <is>
+          <t>BIRJU KUMAR</t>
+        </is>
+      </c>
+      <c r="D990" t="inlineStr">
+        <is>
+          <t>KIRAN KUMARI</t>
+        </is>
+      </c>
+      <c r="E990" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="F990" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="991">
+      <c r="A991" t="inlineStr">
+        <is>
+          <t>16,Mar</t>
+        </is>
+      </c>
+      <c r="B991" t="inlineStr">
+        <is>
+          <t>AKHIL KUMAR</t>
+        </is>
+      </c>
+      <c r="C991" t="inlineStr">
+        <is>
+          <t>AJEET KUMAR</t>
+        </is>
+      </c>
+      <c r="D991" t="inlineStr">
+        <is>
+          <t>SAVITA DEVI</t>
+        </is>
+      </c>
+      <c r="E991" t="inlineStr">
+        <is>
+          <t>XII</t>
+        </is>
+      </c>
+      <c r="F991" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="992">
+      <c r="A992" t="inlineStr">
+        <is>
+          <t>16,Mar</t>
+        </is>
+      </c>
+      <c r="B992" t="inlineStr">
+        <is>
+          <t>RITIK RAJ</t>
+        </is>
+      </c>
+      <c r="C992" t="inlineStr">
+        <is>
+          <t>RAJEEV KUMAR</t>
+        </is>
+      </c>
+      <c r="D992" t="inlineStr">
+        <is>
+          <t>NILU KUMARI</t>
+        </is>
+      </c>
+      <c r="E992" t="inlineStr">
+        <is>
+          <t>IV</t>
+        </is>
+      </c>
+      <c r="F992" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="993">
+      <c r="A993" t="inlineStr">
+        <is>
+          <t>16,Mar</t>
+        </is>
+      </c>
+      <c r="B993" t="inlineStr">
+        <is>
+          <t>ANSH PATEL</t>
+        </is>
+      </c>
+      <c r="C993" t="inlineStr">
+        <is>
+          <t>ACHYUT KUMAR</t>
+        </is>
+      </c>
+      <c r="D993" t="inlineStr">
+        <is>
+          <t>PRITEE SINHA</t>
+        </is>
+      </c>
+      <c r="E993" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="F993" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Birthday Data Master.xlsx
+++ b/Birthday Data Master.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F993"/>
+  <dimension ref="A1:F997"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.6" customWidth="1" min="1" max="1"/>
@@ -32200,6 +32200,134 @@
         </is>
       </c>
     </row>
+    <row r="994">
+      <c r="A994" t="inlineStr">
+        <is>
+          <t>17,Mar</t>
+        </is>
+      </c>
+      <c r="B994" t="inlineStr">
+        <is>
+          <t>ARYA SHARMA</t>
+        </is>
+      </c>
+      <c r="C994" t="inlineStr">
+        <is>
+          <t>PRAMOD KUMAR</t>
+        </is>
+      </c>
+      <c r="D994" t="inlineStr">
+        <is>
+          <t>AMRITA KUMARI</t>
+        </is>
+      </c>
+      <c r="E994" t="inlineStr">
+        <is>
+          <t>IV</t>
+        </is>
+      </c>
+      <c r="F994" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="995">
+      <c r="A995" t="inlineStr">
+        <is>
+          <t>17,Mar</t>
+        </is>
+      </c>
+      <c r="B995" t="inlineStr">
+        <is>
+          <t>Archana Kumari</t>
+        </is>
+      </c>
+      <c r="C995" t="inlineStr">
+        <is>
+          <t>Ramesh Kumar</t>
+        </is>
+      </c>
+      <c r="D995" t="inlineStr">
+        <is>
+          <t>Kiran Kumari</t>
+        </is>
+      </c>
+      <c r="E995" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F995" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="996">
+      <c r="A996" t="inlineStr">
+        <is>
+          <t>17,Mar</t>
+        </is>
+      </c>
+      <c r="B996" t="inlineStr">
+        <is>
+          <t>Anvita Kumari</t>
+        </is>
+      </c>
+      <c r="C996" t="inlineStr">
+        <is>
+          <t>Mukesh Kumar</t>
+        </is>
+      </c>
+      <c r="D996" t="inlineStr">
+        <is>
+          <t>Sweta Kumari</t>
+        </is>
+      </c>
+      <c r="E996" t="inlineStr">
+        <is>
+          <t>VIII</t>
+        </is>
+      </c>
+      <c r="F996" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+    </row>
+    <row r="997">
+      <c r="A997" t="inlineStr">
+        <is>
+          <t>17,Mar</t>
+        </is>
+      </c>
+      <c r="B997" t="inlineStr">
+        <is>
+          <t>Vaishnavi Kumari</t>
+        </is>
+      </c>
+      <c r="C997" t="inlineStr">
+        <is>
+          <t>Om Prakash</t>
+        </is>
+      </c>
+      <c r="D997" t="inlineStr">
+        <is>
+          <t>Anamika Kumari</t>
+        </is>
+      </c>
+      <c r="E997" t="inlineStr">
+        <is>
+          <t>VIII</t>
+        </is>
+      </c>
+      <c r="F997" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Birthday Data Master.xlsx
+++ b/Birthday Data Master.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F997"/>
+  <dimension ref="A1:F1003"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.6" customWidth="1" min="1" max="1"/>
@@ -32328,6 +32328,198 @@
         </is>
       </c>
     </row>
+    <row r="998">
+      <c r="A998" t="inlineStr">
+        <is>
+          <t>18,Mar</t>
+        </is>
+      </c>
+      <c r="B998" t="inlineStr">
+        <is>
+          <t>Ritik Raj</t>
+        </is>
+      </c>
+      <c r="C998" t="inlineStr">
+        <is>
+          <t>Bablu Kumar</t>
+        </is>
+      </c>
+      <c r="D998" t="inlineStr">
+        <is>
+          <t>RACHANA DEVI</t>
+        </is>
+      </c>
+      <c r="E998" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F998" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="999">
+      <c r="A999" t="inlineStr">
+        <is>
+          <t>18,Mar</t>
+        </is>
+      </c>
+      <c r="B999" t="inlineStr">
+        <is>
+          <t>LAKSHAY KUMAR</t>
+        </is>
+      </c>
+      <c r="C999" t="inlineStr">
+        <is>
+          <t>LALAN KUMAR</t>
+        </is>
+      </c>
+      <c r="D999" t="inlineStr">
+        <is>
+          <t>SIMPI KUMARI</t>
+        </is>
+      </c>
+      <c r="E999" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="F999" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="1000">
+      <c r="A1000" t="inlineStr">
+        <is>
+          <t>18,Mar</t>
+        </is>
+      </c>
+      <c r="B1000" t="inlineStr">
+        <is>
+          <t>TANYA SINHA</t>
+        </is>
+      </c>
+      <c r="C1000" t="inlineStr">
+        <is>
+          <t>JAY PRAKASH NARAYAN</t>
+        </is>
+      </c>
+      <c r="D1000" t="inlineStr">
+        <is>
+          <t>PRANITA SINHA</t>
+        </is>
+      </c>
+      <c r="E1000" t="inlineStr">
+        <is>
+          <t>VII</t>
+        </is>
+      </c>
+      <c r="F1000" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="1001">
+      <c r="A1001" t="inlineStr">
+        <is>
+          <t>18,Mar</t>
+        </is>
+      </c>
+      <c r="B1001" t="inlineStr">
+        <is>
+          <t>AYANSH SHARMA</t>
+        </is>
+      </c>
+      <c r="C1001" t="inlineStr">
+        <is>
+          <t>BABLU KUMAR</t>
+        </is>
+      </c>
+      <c r="D1001" t="inlineStr">
+        <is>
+          <t>ANSHUMALA</t>
+        </is>
+      </c>
+      <c r="E1001" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="F1001" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="1002">
+      <c r="A1002" t="inlineStr">
+        <is>
+          <t>18,Mar</t>
+        </is>
+      </c>
+      <c r="B1002" t="inlineStr">
+        <is>
+          <t>Pratigya Kumari</t>
+        </is>
+      </c>
+      <c r="C1002" t="inlineStr">
+        <is>
+          <t>Shivam Kumar</t>
+        </is>
+      </c>
+      <c r="D1002" t="inlineStr">
+        <is>
+          <t>Anuradha Kumari</t>
+        </is>
+      </c>
+      <c r="E1002" t="inlineStr">
+        <is>
+          <t>VIII</t>
+        </is>
+      </c>
+      <c r="F1002" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+    </row>
+    <row r="1003">
+      <c r="A1003" t="inlineStr">
+        <is>
+          <t>18,Mar</t>
+        </is>
+      </c>
+      <c r="B1003" t="inlineStr">
+        <is>
+          <t>SWARA SHUBH</t>
+        </is>
+      </c>
+      <c r="C1003" t="inlineStr">
+        <is>
+          <t>ANIL KUMAR</t>
+        </is>
+      </c>
+      <c r="D1003" t="inlineStr">
+        <is>
+          <t>KHUSHBU KUMARI</t>
+        </is>
+      </c>
+      <c r="E1003" t="inlineStr">
+        <is>
+          <t>VII</t>
+        </is>
+      </c>
+      <c r="F1003" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Birthday Data Master.xlsx
+++ b/Birthday Data Master.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1003"/>
+  <dimension ref="A1:F1013"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.6" customWidth="1" min="1" max="1"/>
@@ -32520,6 +32520,326 @@
         </is>
       </c>
     </row>
+    <row r="1004">
+      <c r="A1004" t="inlineStr">
+        <is>
+          <t>19,Mar</t>
+        </is>
+      </c>
+      <c r="B1004" t="inlineStr">
+        <is>
+          <t>ARYAN  RAJ</t>
+        </is>
+      </c>
+      <c r="C1004" t="inlineStr">
+        <is>
+          <t>AJAY KUMAR</t>
+        </is>
+      </c>
+      <c r="D1004" t="inlineStr">
+        <is>
+          <t>ANITA KUMARI</t>
+        </is>
+      </c>
+      <c r="E1004" t="inlineStr">
+        <is>
+          <t>VII</t>
+        </is>
+      </c>
+      <c r="F1004" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="1005">
+      <c r="A1005" t="inlineStr">
+        <is>
+          <t>19,Mar</t>
+        </is>
+      </c>
+      <c r="B1005" t="inlineStr">
+        <is>
+          <t>AARADHYA MAHI</t>
+        </is>
+      </c>
+      <c r="C1005" t="inlineStr">
+        <is>
+          <t>RAVISH KUMAR</t>
+        </is>
+      </c>
+      <c r="D1005" t="inlineStr">
+        <is>
+          <t>ANJALI KUMARI</t>
+        </is>
+      </c>
+      <c r="E1005" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="F1005" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="1006">
+      <c r="A1006" t="inlineStr">
+        <is>
+          <t>19,Mar</t>
+        </is>
+      </c>
+      <c r="B1006" t="inlineStr">
+        <is>
+          <t>ROHIT KUMAR</t>
+        </is>
+      </c>
+      <c r="C1006" t="inlineStr">
+        <is>
+          <t>SUNIL KUMAR</t>
+        </is>
+      </c>
+      <c r="D1006" t="inlineStr">
+        <is>
+          <t>ANURADHA DEVI</t>
+        </is>
+      </c>
+      <c r="E1006" t="inlineStr">
+        <is>
+          <t>VII</t>
+        </is>
+      </c>
+      <c r="F1006" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="1007">
+      <c r="A1007" t="inlineStr">
+        <is>
+          <t>19,Mar</t>
+        </is>
+      </c>
+      <c r="B1007" t="inlineStr">
+        <is>
+          <t>Amish Kumar</t>
+        </is>
+      </c>
+      <c r="C1007" t="inlineStr">
+        <is>
+          <t>Santosh Kumar</t>
+        </is>
+      </c>
+      <c r="D1007" t="inlineStr">
+        <is>
+          <t>Guddi Devi</t>
+        </is>
+      </c>
+      <c r="E1007" t="inlineStr">
+        <is>
+          <t>IV</t>
+        </is>
+      </c>
+      <c r="F1007" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="1008">
+      <c r="A1008" t="inlineStr">
+        <is>
+          <t>19,Mar</t>
+        </is>
+      </c>
+      <c r="B1008" t="inlineStr">
+        <is>
+          <t>ADITI SINGH</t>
+        </is>
+      </c>
+      <c r="C1008" t="inlineStr">
+        <is>
+          <t>RAVISH KUMAR</t>
+        </is>
+      </c>
+      <c r="D1008" t="inlineStr">
+        <is>
+          <t>ANJALI KUMARI</t>
+        </is>
+      </c>
+      <c r="E1008" t="inlineStr">
+        <is>
+          <t>IV</t>
+        </is>
+      </c>
+      <c r="F1008" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="1009">
+      <c r="A1009" t="inlineStr">
+        <is>
+          <t>19,Mar</t>
+        </is>
+      </c>
+      <c r="B1009" t="inlineStr">
+        <is>
+          <t>SARAS KUMAR GUPTA</t>
+        </is>
+      </c>
+      <c r="C1009" t="inlineStr">
+        <is>
+          <t>DHANANJAY KUMAR</t>
+        </is>
+      </c>
+      <c r="D1009" t="inlineStr">
+        <is>
+          <t>SANJU DEVI</t>
+        </is>
+      </c>
+      <c r="E1009" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="F1009" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="1010">
+      <c r="A1010" t="inlineStr">
+        <is>
+          <t>19,Mar</t>
+        </is>
+      </c>
+      <c r="B1010" t="inlineStr">
+        <is>
+          <t>SHIVAANSH KUMAR</t>
+        </is>
+      </c>
+      <c r="C1010" t="inlineStr">
+        <is>
+          <t>SANDESH KUMAR</t>
+        </is>
+      </c>
+      <c r="D1010" t="inlineStr">
+        <is>
+          <t>SIMA KUMARI</t>
+        </is>
+      </c>
+      <c r="E1010" t="inlineStr">
+        <is>
+          <t>LKG</t>
+        </is>
+      </c>
+      <c r="F1010" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="1011">
+      <c r="A1011" t="inlineStr">
+        <is>
+          <t>19,Mar</t>
+        </is>
+      </c>
+      <c r="B1011" t="inlineStr">
+        <is>
+          <t>PRINCE KUMAR</t>
+        </is>
+      </c>
+      <c r="C1011" t="inlineStr">
+        <is>
+          <t>JAY PRAKASH</t>
+        </is>
+      </c>
+      <c r="D1011" t="inlineStr">
+        <is>
+          <t>RINKI KUMARI</t>
+        </is>
+      </c>
+      <c r="E1011" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="F1011" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="1012">
+      <c r="A1012" t="inlineStr">
+        <is>
+          <t>19,Mar</t>
+        </is>
+      </c>
+      <c r="B1012" t="inlineStr">
+        <is>
+          <t>AYUSH KUMAR</t>
+        </is>
+      </c>
+      <c r="C1012" t="inlineStr">
+        <is>
+          <t>AMIT KUMAR</t>
+        </is>
+      </c>
+      <c r="D1012" t="inlineStr">
+        <is>
+          <t>PUNAM DEVI</t>
+        </is>
+      </c>
+      <c r="E1012" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="F1012" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="1013">
+      <c r="A1013" t="inlineStr">
+        <is>
+          <t>19,Mar</t>
+        </is>
+      </c>
+      <c r="B1013" t="inlineStr">
+        <is>
+          <t>AKSHITANAND KUMARI</t>
+        </is>
+      </c>
+      <c r="C1013" t="inlineStr">
+        <is>
+          <t>MANOJ KUMAR</t>
+        </is>
+      </c>
+      <c r="D1013" t="inlineStr">
+        <is>
+          <t>SARITA GUPTA</t>
+        </is>
+      </c>
+      <c r="E1013" t="inlineStr">
+        <is>
+          <t>XI</t>
+        </is>
+      </c>
+      <c r="F1013" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Birthday Data Master.xlsx
+++ b/Birthday Data Master.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1013"/>
+  <dimension ref="A1:F1022"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.6" customWidth="1" min="1" max="1"/>
@@ -32840,6 +32840,294 @@
         </is>
       </c>
     </row>
+    <row r="1014">
+      <c r="A1014" t="inlineStr">
+        <is>
+          <t>20,Mar</t>
+        </is>
+      </c>
+      <c r="B1014" t="inlineStr">
+        <is>
+          <t>SAMIKSHA  KUMARI SHARMA</t>
+        </is>
+      </c>
+      <c r="C1014" t="inlineStr">
+        <is>
+          <t>UDAY KUMAR</t>
+        </is>
+      </c>
+      <c r="D1014" t="inlineStr">
+        <is>
+          <t>PRITI KUMARI</t>
+        </is>
+      </c>
+      <c r="E1014" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="F1014" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="1015">
+      <c r="A1015" t="inlineStr">
+        <is>
+          <t>20,Mar</t>
+        </is>
+      </c>
+      <c r="B1015" t="inlineStr">
+        <is>
+          <t>ADITI RAJ</t>
+        </is>
+      </c>
+      <c r="C1015" t="inlineStr">
+        <is>
+          <t>TINKU KUMAR SINGH</t>
+        </is>
+      </c>
+      <c r="D1015" t="inlineStr">
+        <is>
+          <t>MANORAMA DEVI</t>
+        </is>
+      </c>
+      <c r="E1015" t="inlineStr">
+        <is>
+          <t>VII</t>
+        </is>
+      </c>
+      <c r="F1015" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="1016">
+      <c r="A1016" t="inlineStr">
+        <is>
+          <t>20,Mar</t>
+        </is>
+      </c>
+      <c r="B1016" t="inlineStr">
+        <is>
+          <t>SONAKSHI KUMARI</t>
+        </is>
+      </c>
+      <c r="C1016" t="inlineStr">
+        <is>
+          <t>ABHISHEK RAJ</t>
+        </is>
+      </c>
+      <c r="D1016" t="inlineStr">
+        <is>
+          <t>MADHURI KUMARI</t>
+        </is>
+      </c>
+      <c r="E1016" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="F1016" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="1017">
+      <c r="A1017" t="inlineStr">
+        <is>
+          <t>20,Mar</t>
+        </is>
+      </c>
+      <c r="B1017" t="inlineStr">
+        <is>
+          <t>ARADHYA GUPTA</t>
+        </is>
+      </c>
+      <c r="C1017" t="inlineStr">
+        <is>
+          <t>LALIT KUMAR</t>
+        </is>
+      </c>
+      <c r="D1017" t="inlineStr">
+        <is>
+          <t>SONY GUPTA</t>
+        </is>
+      </c>
+      <c r="E1017" t="inlineStr">
+        <is>
+          <t>IV</t>
+        </is>
+      </c>
+      <c r="F1017" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="1018">
+      <c r="A1018" t="inlineStr">
+        <is>
+          <t>20,Mar</t>
+        </is>
+      </c>
+      <c r="B1018" t="inlineStr">
+        <is>
+          <t>ARPIT RAJ</t>
+        </is>
+      </c>
+      <c r="C1018" t="inlineStr">
+        <is>
+          <t>ANIL KUMAR GUPTA</t>
+        </is>
+      </c>
+      <c r="D1018" t="inlineStr">
+        <is>
+          <t>RANI KUMARI</t>
+        </is>
+      </c>
+      <c r="E1018" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F1018" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="1019">
+      <c r="A1019" t="inlineStr">
+        <is>
+          <t>20,Mar</t>
+        </is>
+      </c>
+      <c r="B1019" t="inlineStr">
+        <is>
+          <t>MAANVIK KUMAR</t>
+        </is>
+      </c>
+      <c r="C1019" t="inlineStr">
+        <is>
+          <t>MAHANAND KUMAR</t>
+        </is>
+      </c>
+      <c r="D1019" t="inlineStr">
+        <is>
+          <t>NANDANI KUMARI</t>
+        </is>
+      </c>
+      <c r="E1019" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="F1019" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="1020">
+      <c r="A1020" t="inlineStr">
+        <is>
+          <t>20,Mar</t>
+        </is>
+      </c>
+      <c r="B1020" t="inlineStr">
+        <is>
+          <t>SWATI KUMARI</t>
+        </is>
+      </c>
+      <c r="C1020" t="inlineStr">
+        <is>
+          <t>SUDHIR KUMAR</t>
+        </is>
+      </c>
+      <c r="D1020" t="inlineStr">
+        <is>
+          <t>ASHA KUMARI</t>
+        </is>
+      </c>
+      <c r="E1020" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="F1020" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="1021">
+      <c r="A1021" t="inlineStr">
+        <is>
+          <t>20,Mar</t>
+        </is>
+      </c>
+      <c r="B1021" t="inlineStr">
+        <is>
+          <t>RITIKA KUMARI</t>
+        </is>
+      </c>
+      <c r="C1021" t="inlineStr">
+        <is>
+          <t>DHIRENDRA KUMAR</t>
+        </is>
+      </c>
+      <c r="D1021" t="inlineStr">
+        <is>
+          <t>ARCHANA KUMARI</t>
+        </is>
+      </c>
+      <c r="E1021" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="F1021" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="1022">
+      <c r="A1022" t="inlineStr">
+        <is>
+          <t>20,Mar</t>
+        </is>
+      </c>
+      <c r="B1022" t="inlineStr">
+        <is>
+          <t>Ayush Raj</t>
+        </is>
+      </c>
+      <c r="C1022" t="inlineStr">
+        <is>
+          <t>Makhan Kumar</t>
+        </is>
+      </c>
+      <c r="D1022" t="inlineStr">
+        <is>
+          <t>Archana Devi</t>
+        </is>
+      </c>
+      <c r="E1022" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F1022" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Birthday Data Master.xlsx
+++ b/Birthday Data Master.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1022"/>
+  <dimension ref="A1:F1030"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.6" customWidth="1" min="1" max="1"/>
@@ -33128,6 +33128,262 @@
         </is>
       </c>
     </row>
+    <row r="1023">
+      <c r="A1023" t="inlineStr">
+        <is>
+          <t>21,Mar</t>
+        </is>
+      </c>
+      <c r="B1023" t="inlineStr">
+        <is>
+          <t>TEJASWANI BHARTI</t>
+        </is>
+      </c>
+      <c r="C1023" t="inlineStr">
+        <is>
+          <t>RAVI KUMAR</t>
+        </is>
+      </c>
+      <c r="D1023" t="inlineStr">
+        <is>
+          <t>PRACHI KUMARI</t>
+        </is>
+      </c>
+      <c r="E1023" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="F1023" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+    </row>
+    <row r="1024">
+      <c r="A1024" t="inlineStr">
+        <is>
+          <t>21,Mar</t>
+        </is>
+      </c>
+      <c r="B1024" t="inlineStr">
+        <is>
+          <t>SUBHRANSH KUMAR</t>
+        </is>
+      </c>
+      <c r="C1024" t="inlineStr">
+        <is>
+          <t>UPNIT KUMAR</t>
+        </is>
+      </c>
+      <c r="D1024" t="inlineStr">
+        <is>
+          <t>PAMMI KUMARI</t>
+        </is>
+      </c>
+      <c r="E1024" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F1024" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="1025">
+      <c r="A1025" t="inlineStr">
+        <is>
+          <t>21,Mar</t>
+        </is>
+      </c>
+      <c r="B1025" t="inlineStr">
+        <is>
+          <t>Aditya Raj</t>
+        </is>
+      </c>
+      <c r="C1025" t="inlineStr">
+        <is>
+          <t>Mahenndra Kumar</t>
+        </is>
+      </c>
+      <c r="D1025" t="inlineStr">
+        <is>
+          <t>Babita Devi</t>
+        </is>
+      </c>
+      <c r="E1025" t="inlineStr">
+        <is>
+          <t>VIII</t>
+        </is>
+      </c>
+      <c r="F1025" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="1026">
+      <c r="A1026" t="inlineStr">
+        <is>
+          <t>21,Mar</t>
+        </is>
+      </c>
+      <c r="B1026" t="inlineStr">
+        <is>
+          <t>Tamanna Kumari</t>
+        </is>
+      </c>
+      <c r="C1026" t="inlineStr">
+        <is>
+          <t>Bablu Kumar</t>
+        </is>
+      </c>
+      <c r="D1026" t="inlineStr">
+        <is>
+          <t>Pinki Devi</t>
+        </is>
+      </c>
+      <c r="E1026" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F1026" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="1027">
+      <c r="A1027" t="inlineStr">
+        <is>
+          <t>21,Mar</t>
+        </is>
+      </c>
+      <c r="B1027" t="inlineStr">
+        <is>
+          <t>AYUSH RAJ</t>
+        </is>
+      </c>
+      <c r="C1027" t="inlineStr">
+        <is>
+          <t>RANJEET KUMAR</t>
+        </is>
+      </c>
+      <c r="D1027" t="inlineStr">
+        <is>
+          <t>RENU KUMARI</t>
+        </is>
+      </c>
+      <c r="E1027" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="F1027" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="1028">
+      <c r="A1028" t="inlineStr">
+        <is>
+          <t>21,Mar</t>
+        </is>
+      </c>
+      <c r="B1028" t="inlineStr">
+        <is>
+          <t>YASHASVI</t>
+        </is>
+      </c>
+      <c r="C1028" t="inlineStr">
+        <is>
+          <t>SUNIL KUMAR MALAKAR</t>
+        </is>
+      </c>
+      <c r="D1028" t="inlineStr">
+        <is>
+          <t>RAGINI KUMARI</t>
+        </is>
+      </c>
+      <c r="E1028" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="F1028" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="1029">
+      <c r="A1029" t="inlineStr">
+        <is>
+          <t>21,Mar</t>
+        </is>
+      </c>
+      <c r="B1029" t="inlineStr">
+        <is>
+          <t>AHANA KUMARI</t>
+        </is>
+      </c>
+      <c r="C1029" t="inlineStr">
+        <is>
+          <t>GAUTAM NANDAN</t>
+        </is>
+      </c>
+      <c r="D1029" t="inlineStr">
+        <is>
+          <t>ARTEE KUMARI</t>
+        </is>
+      </c>
+      <c r="E1029" t="inlineStr">
+        <is>
+          <t>VII</t>
+        </is>
+      </c>
+      <c r="F1029" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="1030">
+      <c r="A1030" t="inlineStr">
+        <is>
+          <t>21,Mar</t>
+        </is>
+      </c>
+      <c r="B1030" t="inlineStr">
+        <is>
+          <t>Aditi Sharma</t>
+        </is>
+      </c>
+      <c r="C1030" t="inlineStr">
+        <is>
+          <t>Shiva Kant Kumar</t>
+        </is>
+      </c>
+      <c r="D1030" t="inlineStr">
+        <is>
+          <t>Khushbu Kumari</t>
+        </is>
+      </c>
+      <c r="E1030" t="inlineStr">
+        <is>
+          <t>VIII</t>
+        </is>
+      </c>
+      <c r="F1030" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Birthday Data Master.xlsx
+++ b/Birthday Data Master.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1030"/>
+  <dimension ref="A1:F1037"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.6" customWidth="1" min="1" max="1"/>
@@ -33384,6 +33384,230 @@
         </is>
       </c>
     </row>
+    <row r="1031">
+      <c r="A1031" t="inlineStr">
+        <is>
+          <t>22,Mar</t>
+        </is>
+      </c>
+      <c r="B1031" t="inlineStr">
+        <is>
+          <t>Nandni Kumari</t>
+        </is>
+      </c>
+      <c r="C1031" t="inlineStr">
+        <is>
+          <t>Shashi Ranjan KUMAR</t>
+        </is>
+      </c>
+      <c r="D1031" t="inlineStr">
+        <is>
+          <t>Guriya Kumari</t>
+        </is>
+      </c>
+      <c r="E1031" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F1031" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="1032">
+      <c r="A1032" t="inlineStr">
+        <is>
+          <t>22,Mar</t>
+        </is>
+      </c>
+      <c r="B1032" t="inlineStr">
+        <is>
+          <t>SHIVAM KUMAR</t>
+        </is>
+      </c>
+      <c r="C1032" t="inlineStr">
+        <is>
+          <t>RAJEEV KUMAR</t>
+        </is>
+      </c>
+      <c r="D1032" t="inlineStr">
+        <is>
+          <t>SANGITA DEVI</t>
+        </is>
+      </c>
+      <c r="E1032" t="inlineStr">
+        <is>
+          <t>XII</t>
+        </is>
+      </c>
+      <c r="F1032" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1033">
+      <c r="A1033" t="inlineStr">
+        <is>
+          <t>22,Mar</t>
+        </is>
+      </c>
+      <c r="B1033" t="inlineStr">
+        <is>
+          <t>ADITYA KUMAR</t>
+        </is>
+      </c>
+      <c r="C1033" t="inlineStr">
+        <is>
+          <t>MUKESH KUMAR</t>
+        </is>
+      </c>
+      <c r="D1033" t="inlineStr">
+        <is>
+          <t>ARCHANA KUMARI</t>
+        </is>
+      </c>
+      <c r="E1033" t="inlineStr">
+        <is>
+          <t>VII</t>
+        </is>
+      </c>
+      <c r="F1033" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+    </row>
+    <row r="1034">
+      <c r="A1034" t="inlineStr">
+        <is>
+          <t>22,Mar</t>
+        </is>
+      </c>
+      <c r="B1034" t="inlineStr">
+        <is>
+          <t>JAHANVI KUMARI</t>
+        </is>
+      </c>
+      <c r="C1034" t="inlineStr">
+        <is>
+          <t>SUDARSHAN KUMAR</t>
+        </is>
+      </c>
+      <c r="D1034" t="inlineStr">
+        <is>
+          <t>REKHA KUMARI</t>
+        </is>
+      </c>
+      <c r="E1034" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F1034" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="1035">
+      <c r="A1035" t="inlineStr">
+        <is>
+          <t>22,Mar</t>
+        </is>
+      </c>
+      <c r="B1035" t="inlineStr">
+        <is>
+          <t>ADITYA KUMAR</t>
+        </is>
+      </c>
+      <c r="C1035" t="inlineStr">
+        <is>
+          <t>ALOK KUMAR</t>
+        </is>
+      </c>
+      <c r="D1035" t="inlineStr">
+        <is>
+          <t>FRUTI KUMARI</t>
+        </is>
+      </c>
+      <c r="E1035" t="inlineStr">
+        <is>
+          <t>IV</t>
+        </is>
+      </c>
+      <c r="F1035" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="1036">
+      <c r="A1036" t="inlineStr">
+        <is>
+          <t>22,Mar</t>
+        </is>
+      </c>
+      <c r="B1036" t="inlineStr">
+        <is>
+          <t>Dharmika Yadav</t>
+        </is>
+      </c>
+      <c r="C1036" t="inlineStr">
+        <is>
+          <t>Dinesh Kumar</t>
+        </is>
+      </c>
+      <c r="D1036" t="inlineStr">
+        <is>
+          <t>Indu</t>
+        </is>
+      </c>
+      <c r="E1036" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F1036" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="1037">
+      <c r="A1037" t="inlineStr">
+        <is>
+          <t>22,Mar</t>
+        </is>
+      </c>
+      <c r="B1037" t="inlineStr">
+        <is>
+          <t>ADVIKA SHARMA</t>
+        </is>
+      </c>
+      <c r="C1037" t="inlineStr">
+        <is>
+          <t>ONKAR KUMAR</t>
+        </is>
+      </c>
+      <c r="D1037" t="inlineStr">
+        <is>
+          <t>ARTI KUMARI</t>
+        </is>
+      </c>
+      <c r="E1037" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="F1037" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Birthday Data Master.xlsx
+++ b/Birthday Data Master.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1037"/>
+  <dimension ref="A1:F1044"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.6" customWidth="1" min="1" max="1"/>
@@ -33608,6 +33608,230 @@
         </is>
       </c>
     </row>
+    <row r="1038">
+      <c r="A1038" t="inlineStr">
+        <is>
+          <t>23,Mar</t>
+        </is>
+      </c>
+      <c r="B1038" t="inlineStr">
+        <is>
+          <t>DEEPA  KUMARI</t>
+        </is>
+      </c>
+      <c r="C1038" t="inlineStr">
+        <is>
+          <t>SUDHIR KUMAR</t>
+        </is>
+      </c>
+      <c r="D1038" t="inlineStr">
+        <is>
+          <t>BIBHA DEVI</t>
+        </is>
+      </c>
+      <c r="E1038" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="F1038" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="1039">
+      <c r="A1039" t="inlineStr">
+        <is>
+          <t>23,Mar</t>
+        </is>
+      </c>
+      <c r="B1039" t="inlineStr">
+        <is>
+          <t>ANAMIKA KUMARI</t>
+        </is>
+      </c>
+      <c r="C1039" t="inlineStr">
+        <is>
+          <t>RAVI RANJAN KUMAR</t>
+        </is>
+      </c>
+      <c r="D1039" t="inlineStr">
+        <is>
+          <t>GURIYA KUMARI</t>
+        </is>
+      </c>
+      <c r="E1039" t="inlineStr">
+        <is>
+          <t>VII</t>
+        </is>
+      </c>
+      <c r="F1039" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="1040">
+      <c r="A1040" t="inlineStr">
+        <is>
+          <t>23,Mar</t>
+        </is>
+      </c>
+      <c r="B1040" t="inlineStr">
+        <is>
+          <t>DIKSHIKA BHARTI</t>
+        </is>
+      </c>
+      <c r="C1040" t="inlineStr">
+        <is>
+          <t>RAHUL KUMAR</t>
+        </is>
+      </c>
+      <c r="D1040" t="inlineStr">
+        <is>
+          <t>PRITI KUMARI</t>
+        </is>
+      </c>
+      <c r="E1040" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="F1040" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="1041">
+      <c r="A1041" t="inlineStr">
+        <is>
+          <t>23,Mar</t>
+        </is>
+      </c>
+      <c r="B1041" t="inlineStr">
+        <is>
+          <t>Rajdeep KESHARI</t>
+        </is>
+      </c>
+      <c r="C1041" t="inlineStr">
+        <is>
+          <t>Deepak KUMAR</t>
+        </is>
+      </c>
+      <c r="D1041" t="inlineStr">
+        <is>
+          <t>Nutan DEVI</t>
+        </is>
+      </c>
+      <c r="E1041" t="inlineStr">
+        <is>
+          <t>IX</t>
+        </is>
+      </c>
+      <c r="F1041" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="1042">
+      <c r="A1042" t="inlineStr">
+        <is>
+          <t>23,Mar</t>
+        </is>
+      </c>
+      <c r="B1042" t="inlineStr">
+        <is>
+          <t>PRANAB  KUMAR</t>
+        </is>
+      </c>
+      <c r="C1042" t="inlineStr">
+        <is>
+          <t>ALOK KUMAR</t>
+        </is>
+      </c>
+      <c r="D1042" t="inlineStr">
+        <is>
+          <t>RAKHI KUMARI</t>
+        </is>
+      </c>
+      <c r="E1042" t="inlineStr">
+        <is>
+          <t>VII</t>
+        </is>
+      </c>
+      <c r="F1042" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="1043">
+      <c r="A1043" t="inlineStr">
+        <is>
+          <t>23,Mar</t>
+        </is>
+      </c>
+      <c r="B1043" t="inlineStr">
+        <is>
+          <t>ROUSHANI KUMARI</t>
+        </is>
+      </c>
+      <c r="C1043" t="inlineStr">
+        <is>
+          <t>RAJESH KUMAR</t>
+        </is>
+      </c>
+      <c r="D1043" t="inlineStr">
+        <is>
+          <t>KANCHAN DEVI</t>
+        </is>
+      </c>
+      <c r="E1043" t="inlineStr">
+        <is>
+          <t>IV</t>
+        </is>
+      </c>
+      <c r="F1043" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="1044">
+      <c r="A1044" t="inlineStr">
+        <is>
+          <t>23,Mar</t>
+        </is>
+      </c>
+      <c r="B1044" t="inlineStr">
+        <is>
+          <t>RITIKA KUMARI</t>
+        </is>
+      </c>
+      <c r="C1044" t="inlineStr">
+        <is>
+          <t>AJIT KUMAR</t>
+        </is>
+      </c>
+      <c r="D1044" t="inlineStr">
+        <is>
+          <t>SHANTA DEVI</t>
+        </is>
+      </c>
+      <c r="E1044" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="F1044" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Birthday Data Master.xlsx
+++ b/Birthday Data Master.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1044"/>
+  <dimension ref="A1:F1051"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.6" customWidth="1" min="1" max="1"/>
@@ -33832,6 +33832,230 @@
         </is>
       </c>
     </row>
+    <row r="1045">
+      <c r="A1045" t="inlineStr">
+        <is>
+          <t>24,Mar</t>
+        </is>
+      </c>
+      <c r="B1045" t="inlineStr">
+        <is>
+          <t>Gaurav Kumar</t>
+        </is>
+      </c>
+      <c r="C1045" t="inlineStr">
+        <is>
+          <t>Raju Kumar</t>
+        </is>
+      </c>
+      <c r="D1045" t="inlineStr">
+        <is>
+          <t>Rubi Kumari</t>
+        </is>
+      </c>
+      <c r="E1045" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F1045" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="1046">
+      <c r="A1046" t="inlineStr">
+        <is>
+          <t>24,Mar</t>
+        </is>
+      </c>
+      <c r="B1046" t="inlineStr">
+        <is>
+          <t>SHIVU SHIVANSH</t>
+        </is>
+      </c>
+      <c r="C1046" t="inlineStr">
+        <is>
+          <t>CHAKRA SUDERSHAN</t>
+        </is>
+      </c>
+      <c r="D1046" t="inlineStr">
+        <is>
+          <t>SANDHYA KUMARI</t>
+        </is>
+      </c>
+      <c r="E1046" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="F1046" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="1047">
+      <c r="A1047" t="inlineStr">
+        <is>
+          <t>24,Mar</t>
+        </is>
+      </c>
+      <c r="B1047" t="inlineStr">
+        <is>
+          <t>Abhinav  Sinha</t>
+        </is>
+      </c>
+      <c r="C1047" t="inlineStr">
+        <is>
+          <t>Lakshmi kant Sinha</t>
+        </is>
+      </c>
+      <c r="D1047" t="inlineStr">
+        <is>
+          <t>Prerna Sinha</t>
+        </is>
+      </c>
+      <c r="E1047" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F1047" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="1048">
+      <c r="A1048" t="inlineStr">
+        <is>
+          <t>24,Mar</t>
+        </is>
+      </c>
+      <c r="B1048" t="inlineStr">
+        <is>
+          <t>Navya Shree</t>
+        </is>
+      </c>
+      <c r="C1048" t="inlineStr">
+        <is>
+          <t>Abhimanyu Kumar</t>
+        </is>
+      </c>
+      <c r="D1048" t="inlineStr">
+        <is>
+          <t>Preety Devi</t>
+        </is>
+      </c>
+      <c r="E1048" t="inlineStr">
+        <is>
+          <t>VIII</t>
+        </is>
+      </c>
+      <c r="F1048" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="1049">
+      <c r="A1049" t="inlineStr">
+        <is>
+          <t>24,Mar</t>
+        </is>
+      </c>
+      <c r="B1049" t="inlineStr">
+        <is>
+          <t>ANANYA</t>
+        </is>
+      </c>
+      <c r="C1049" t="inlineStr">
+        <is>
+          <t>ALOK KUMAR</t>
+        </is>
+      </c>
+      <c r="D1049" t="inlineStr">
+        <is>
+          <t>GAYATRI KUMARI</t>
+        </is>
+      </c>
+      <c r="E1049" t="inlineStr">
+        <is>
+          <t>VII</t>
+        </is>
+      </c>
+      <c r="F1049" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="1050">
+      <c r="A1050" t="inlineStr">
+        <is>
+          <t>24,Mar</t>
+        </is>
+      </c>
+      <c r="B1050" t="inlineStr">
+        <is>
+          <t>SHIV SHAKTI</t>
+        </is>
+      </c>
+      <c r="C1050" t="inlineStr">
+        <is>
+          <t>CHANDAN KUMAR</t>
+        </is>
+      </c>
+      <c r="D1050" t="inlineStr">
+        <is>
+          <t>BEAUTY KUMARI</t>
+        </is>
+      </c>
+      <c r="E1050" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="F1050" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="1051">
+      <c r="A1051" t="inlineStr">
+        <is>
+          <t>24,Mar</t>
+        </is>
+      </c>
+      <c r="B1051" t="inlineStr">
+        <is>
+          <t>SWATI PRIYA</t>
+        </is>
+      </c>
+      <c r="C1051" t="inlineStr">
+        <is>
+          <t>NAVIN KUMAR</t>
+        </is>
+      </c>
+      <c r="D1051" t="inlineStr">
+        <is>
+          <t>PUSHPA DEVI</t>
+        </is>
+      </c>
+      <c r="E1051" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="F1051" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Birthday Data Master.xlsx
+++ b/Birthday Data Master.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1051"/>
+  <dimension ref="A1:F1055"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.6" customWidth="1" min="1" max="1"/>
@@ -34056,6 +34056,134 @@
         </is>
       </c>
     </row>
+    <row r="1052">
+      <c r="A1052" t="inlineStr">
+        <is>
+          <t>25,Mar</t>
+        </is>
+      </c>
+      <c r="B1052" t="inlineStr">
+        <is>
+          <t>HARSHIKA KUMARI</t>
+        </is>
+      </c>
+      <c r="C1052" t="inlineStr">
+        <is>
+          <t>DHIRAJ KUMAR</t>
+        </is>
+      </c>
+      <c r="D1052" t="inlineStr">
+        <is>
+          <t>PRITI KUMARI</t>
+        </is>
+      </c>
+      <c r="E1052" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F1052" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="1053">
+      <c r="A1053" t="inlineStr">
+        <is>
+          <t>25,Mar</t>
+        </is>
+      </c>
+      <c r="B1053" t="inlineStr">
+        <is>
+          <t>ADITYA KUMAR</t>
+        </is>
+      </c>
+      <c r="C1053" t="inlineStr">
+        <is>
+          <t>RAJESH KUMAR</t>
+        </is>
+      </c>
+      <c r="D1053" t="inlineStr">
+        <is>
+          <t>PUSHPA KUMARI</t>
+        </is>
+      </c>
+      <c r="E1053" t="inlineStr">
+        <is>
+          <t>IV</t>
+        </is>
+      </c>
+      <c r="F1053" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="1054">
+      <c r="A1054" t="inlineStr">
+        <is>
+          <t>25,Mar</t>
+        </is>
+      </c>
+      <c r="B1054" t="inlineStr">
+        <is>
+          <t>JUHI KUMARI</t>
+        </is>
+      </c>
+      <c r="C1054" t="inlineStr">
+        <is>
+          <t>MRITUNJAY KUMAR</t>
+        </is>
+      </c>
+      <c r="D1054" t="inlineStr">
+        <is>
+          <t>SUMITRA DEVI</t>
+        </is>
+      </c>
+      <c r="E1054" t="inlineStr">
+        <is>
+          <t>XII</t>
+        </is>
+      </c>
+      <c r="F1054" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1055">
+      <c r="A1055" t="inlineStr">
+        <is>
+          <t>25,Mar</t>
+        </is>
+      </c>
+      <c r="B1055" t="inlineStr">
+        <is>
+          <t>ANAMIKA KUMARI</t>
+        </is>
+      </c>
+      <c r="C1055" t="inlineStr">
+        <is>
+          <t>HARENDRA KUMAR</t>
+        </is>
+      </c>
+      <c r="D1055" t="inlineStr">
+        <is>
+          <t>CHANCHAL KUMARI</t>
+        </is>
+      </c>
+      <c r="E1055" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="F1055" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Birthday Data Master.xlsx
+++ b/Birthday Data Master.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1055"/>
+  <dimension ref="A1:F1060"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.6" customWidth="1" min="1" max="1"/>
@@ -34184,6 +34184,166 @@
         </is>
       </c>
     </row>
+    <row r="1056">
+      <c r="A1056" t="inlineStr">
+        <is>
+          <t>26,Mar</t>
+        </is>
+      </c>
+      <c r="B1056" t="inlineStr">
+        <is>
+          <t>HARDIK VAIBHAV</t>
+        </is>
+      </c>
+      <c r="C1056" t="inlineStr">
+        <is>
+          <t>SANJEEV KUMAR</t>
+        </is>
+      </c>
+      <c r="D1056" t="inlineStr">
+        <is>
+          <t>PRIYANKA KUMARI</t>
+        </is>
+      </c>
+      <c r="E1056" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="F1056" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="1057">
+      <c r="A1057" t="inlineStr">
+        <is>
+          <t>26,Mar</t>
+        </is>
+      </c>
+      <c r="B1057" t="inlineStr">
+        <is>
+          <t>Shubham Kumar</t>
+        </is>
+      </c>
+      <c r="C1057" t="inlineStr">
+        <is>
+          <t>Ranjeet Kumar</t>
+        </is>
+      </c>
+      <c r="D1057" t="inlineStr">
+        <is>
+          <t>Ranju Devi</t>
+        </is>
+      </c>
+      <c r="E1057" t="inlineStr">
+        <is>
+          <t>IX</t>
+        </is>
+      </c>
+      <c r="F1057" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="1058">
+      <c r="A1058" t="inlineStr">
+        <is>
+          <t>26,Mar</t>
+        </is>
+      </c>
+      <c r="B1058" t="inlineStr">
+        <is>
+          <t>SHANVI PRANJAL</t>
+        </is>
+      </c>
+      <c r="C1058" t="inlineStr">
+        <is>
+          <t>RANJEET KUMAR</t>
+        </is>
+      </c>
+      <c r="D1058" t="inlineStr">
+        <is>
+          <t>KUMARI JYOTSNA</t>
+        </is>
+      </c>
+      <c r="E1058" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="F1058" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="1059">
+      <c r="A1059" t="inlineStr">
+        <is>
+          <t>26,Mar</t>
+        </is>
+      </c>
+      <c r="B1059" t="inlineStr">
+        <is>
+          <t>SHRISTI PRIYA</t>
+        </is>
+      </c>
+      <c r="C1059" t="inlineStr">
+        <is>
+          <t>CHANDAN KUMAR</t>
+        </is>
+      </c>
+      <c r="D1059" t="inlineStr">
+        <is>
+          <t>ANJANA KUMARI</t>
+        </is>
+      </c>
+      <c r="E1059" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="F1059" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="1060">
+      <c r="A1060" t="inlineStr">
+        <is>
+          <t>26,Mar</t>
+        </is>
+      </c>
+      <c r="B1060" t="inlineStr">
+        <is>
+          <t>PAKHI GUPTA</t>
+        </is>
+      </c>
+      <c r="C1060" t="inlineStr">
+        <is>
+          <t>SURAJ KUMAR GUPTA</t>
+        </is>
+      </c>
+      <c r="D1060" t="inlineStr">
+        <is>
+          <t>PRIYANKA RANJAN</t>
+        </is>
+      </c>
+      <c r="E1060" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="F1060" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Birthday Data Master.xlsx
+++ b/Birthday Data Master.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1060"/>
+  <dimension ref="A1:F1065"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.6" customWidth="1" min="1" max="1"/>
@@ -34344,6 +34344,167 @@
         </is>
       </c>
     </row>
+    <row r="1061">
+      <c r="A1061" t="inlineStr">
+        <is>
+          <t>27,Mar</t>
+        </is>
+      </c>
+      <c r="B1061" t="inlineStr">
+        <is>
+          <t>DEV RAJ KUMAR</t>
+        </is>
+      </c>
+      <c r="C1061" t="inlineStr">
+        <is>
+          <t>MADHUSUDAN KUMAR CHAUDHARY</t>
+        </is>
+      </c>
+      <c r="D1061" t="inlineStr">
+        <is>
+          <t>SANJANA DEVI</t>
+        </is>
+      </c>
+      <c r="E1061" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="F1061" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="1062">
+      <c r="A1062" t="inlineStr">
+        <is>
+          <t>27,Mar</t>
+        </is>
+      </c>
+      <c r="B1062" t="inlineStr">
+        <is>
+          <t>SURYA PRAKASH 
+SINGH</t>
+        </is>
+      </c>
+      <c r="C1062" t="inlineStr">
+        <is>
+          <t>RITESH KUMAR SINGH</t>
+        </is>
+      </c>
+      <c r="D1062" t="inlineStr">
+        <is>
+          <t>GURIYA KUMARI</t>
+        </is>
+      </c>
+      <c r="E1062" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="F1062" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="1063">
+      <c r="A1063" t="inlineStr">
+        <is>
+          <t>27,Mar</t>
+        </is>
+      </c>
+      <c r="B1063" t="inlineStr">
+        <is>
+          <t>Vaishanavi</t>
+        </is>
+      </c>
+      <c r="C1063" t="inlineStr">
+        <is>
+          <t>Ravindra Kumar</t>
+        </is>
+      </c>
+      <c r="D1063" t="inlineStr">
+        <is>
+          <t>Bandana Kumari</t>
+        </is>
+      </c>
+      <c r="E1063" t="inlineStr">
+        <is>
+          <t>VIII</t>
+        </is>
+      </c>
+      <c r="F1063" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="1064">
+      <c r="A1064" t="inlineStr">
+        <is>
+          <t>27,Mar</t>
+        </is>
+      </c>
+      <c r="B1064" t="inlineStr">
+        <is>
+          <t>Aparna Kumari</t>
+        </is>
+      </c>
+      <c r="C1064" t="inlineStr">
+        <is>
+          <t>Vivekanand</t>
+        </is>
+      </c>
+      <c r="D1064" t="inlineStr">
+        <is>
+          <t>Alpana Kumari</t>
+        </is>
+      </c>
+      <c r="E1064" t="inlineStr">
+        <is>
+          <t>VIII</t>
+        </is>
+      </c>
+      <c r="F1064" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="1065">
+      <c r="A1065" t="inlineStr">
+        <is>
+          <t>27,Mar</t>
+        </is>
+      </c>
+      <c r="B1065" t="inlineStr">
+        <is>
+          <t>AYUSHI KUMARI</t>
+        </is>
+      </c>
+      <c r="C1065" t="inlineStr">
+        <is>
+          <t>PRADEEP KUMAR</t>
+        </is>
+      </c>
+      <c r="D1065" t="inlineStr">
+        <is>
+          <t>LALITA KUMARI</t>
+        </is>
+      </c>
+      <c r="E1065" t="inlineStr">
+        <is>
+          <t>UKG</t>
+        </is>
+      </c>
+      <c r="F1065" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Birthday Data Master.xlsx
+++ b/Birthday Data Master.xlsx
@@ -413,11 +413,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1065"/>
+  <dimension ref="A1:F1075"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.6" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="31.2" customWidth="1" min="2" max="2"/>
     <col width="33.6" customWidth="1" min="3" max="3"/>
     <col width="28.8" customWidth="1" min="4" max="4"/>
     <col width="8.4" customWidth="1" min="5" max="5"/>
@@ -34505,6 +34505,326 @@
         </is>
       </c>
     </row>
+    <row r="1066">
+      <c r="A1066" t="inlineStr">
+        <is>
+          <t>28,Mar</t>
+        </is>
+      </c>
+      <c r="B1066" t="inlineStr">
+        <is>
+          <t>AADIT AARAV  SHRIVASTAVA</t>
+        </is>
+      </c>
+      <c r="C1066" t="inlineStr">
+        <is>
+          <t>VIKASH KUMAR SHRIVASTAVA</t>
+        </is>
+      </c>
+      <c r="D1066" t="inlineStr">
+        <is>
+          <t>MANJU KUMARI</t>
+        </is>
+      </c>
+      <c r="E1066" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F1066" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="1067">
+      <c r="A1067" t="inlineStr">
+        <is>
+          <t>28,Mar</t>
+        </is>
+      </c>
+      <c r="B1067" t="inlineStr">
+        <is>
+          <t>GARV KUMAR</t>
+        </is>
+      </c>
+      <c r="C1067" t="inlineStr">
+        <is>
+          <t>VIVEK KUMAR</t>
+        </is>
+      </c>
+      <c r="D1067" t="inlineStr">
+        <is>
+          <t>ARTI KUMARI</t>
+        </is>
+      </c>
+      <c r="E1067" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="F1067" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="1068">
+      <c r="A1068" t="inlineStr">
+        <is>
+          <t>28,Mar</t>
+        </is>
+      </c>
+      <c r="B1068" t="inlineStr">
+        <is>
+          <t>MUSKAN KUMARI</t>
+        </is>
+      </c>
+      <c r="C1068" t="inlineStr">
+        <is>
+          <t>KAMLESH KUMAR</t>
+        </is>
+      </c>
+      <c r="D1068" t="inlineStr">
+        <is>
+          <t>MANJU KUMARI</t>
+        </is>
+      </c>
+      <c r="E1068" t="inlineStr">
+        <is>
+          <t>IV</t>
+        </is>
+      </c>
+      <c r="F1068" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="1069">
+      <c r="A1069" t="inlineStr">
+        <is>
+          <t>28,Mar</t>
+        </is>
+      </c>
+      <c r="B1069" t="inlineStr">
+        <is>
+          <t>AYUSHMAN SHARMA</t>
+        </is>
+      </c>
+      <c r="C1069" t="inlineStr">
+        <is>
+          <t>RUPESH PANKAJ</t>
+        </is>
+      </c>
+      <c r="D1069" t="inlineStr">
+        <is>
+          <t>JYOTI KUMARI</t>
+        </is>
+      </c>
+      <c r="E1069" t="inlineStr">
+        <is>
+          <t>IV</t>
+        </is>
+      </c>
+      <c r="F1069" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="1070">
+      <c r="A1070" t="inlineStr">
+        <is>
+          <t>28,Mar</t>
+        </is>
+      </c>
+      <c r="B1070" t="inlineStr">
+        <is>
+          <t>Simran Kumari</t>
+        </is>
+      </c>
+      <c r="C1070" t="inlineStr">
+        <is>
+          <t>Arvind Kumar Shahi</t>
+        </is>
+      </c>
+      <c r="D1070" t="inlineStr">
+        <is>
+          <t>Dhawanti Kumari</t>
+        </is>
+      </c>
+      <c r="E1070" t="inlineStr">
+        <is>
+          <t>VIII</t>
+        </is>
+      </c>
+      <c r="F1070" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+    </row>
+    <row r="1071">
+      <c r="A1071" t="inlineStr">
+        <is>
+          <t>28,Mar</t>
+        </is>
+      </c>
+      <c r="B1071" t="inlineStr">
+        <is>
+          <t>Aman Raj</t>
+        </is>
+      </c>
+      <c r="C1071" t="inlineStr">
+        <is>
+          <t>Ashit Kumar</t>
+        </is>
+      </c>
+      <c r="D1071" t="inlineStr">
+        <is>
+          <t>Prabha Kumari</t>
+        </is>
+      </c>
+      <c r="E1071" t="inlineStr">
+        <is>
+          <t>IX</t>
+        </is>
+      </c>
+      <c r="F1071" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="1072">
+      <c r="A1072" t="inlineStr">
+        <is>
+          <t>28,Mar</t>
+        </is>
+      </c>
+      <c r="B1072" t="inlineStr">
+        <is>
+          <t>ANANYA KUMARI</t>
+        </is>
+      </c>
+      <c r="C1072" t="inlineStr">
+        <is>
+          <t>PAWAN KUMAR</t>
+        </is>
+      </c>
+      <c r="D1072" t="inlineStr">
+        <is>
+          <t>SMITA KUMARI</t>
+        </is>
+      </c>
+      <c r="E1072" t="inlineStr">
+        <is>
+          <t>UKG</t>
+        </is>
+      </c>
+      <c r="F1072" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="1073">
+      <c r="A1073" t="inlineStr">
+        <is>
+          <t>28,Mar</t>
+        </is>
+      </c>
+      <c r="B1073" t="inlineStr">
+        <is>
+          <t>NALINI KANT</t>
+        </is>
+      </c>
+      <c r="C1073" t="inlineStr">
+        <is>
+          <t>Pankaj Kumar</t>
+        </is>
+      </c>
+      <c r="D1073" t="inlineStr">
+        <is>
+          <t>Kanchan Kumari</t>
+        </is>
+      </c>
+      <c r="E1073" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="F1073" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="1074">
+      <c r="A1074" t="inlineStr">
+        <is>
+          <t>28,Mar</t>
+        </is>
+      </c>
+      <c r="B1074" t="inlineStr">
+        <is>
+          <t>KUMARI GANGA</t>
+        </is>
+      </c>
+      <c r="C1074" t="inlineStr">
+        <is>
+          <t>JOGENDRA CHAUDHARY</t>
+        </is>
+      </c>
+      <c r="D1074" t="inlineStr">
+        <is>
+          <t>PRATIMA DEVI</t>
+        </is>
+      </c>
+      <c r="E1074" t="inlineStr">
+        <is>
+          <t>VII</t>
+        </is>
+      </c>
+      <c r="F1074" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="1075">
+      <c r="A1075" t="inlineStr">
+        <is>
+          <t>28,Mar</t>
+        </is>
+      </c>
+      <c r="B1075" t="inlineStr">
+        <is>
+          <t>ARNAV ARYAN</t>
+        </is>
+      </c>
+      <c r="C1075" t="inlineStr">
+        <is>
+          <t>SANOJ KUMAR</t>
+        </is>
+      </c>
+      <c r="D1075" t="inlineStr">
+        <is>
+          <t>ANITA KUMARI</t>
+        </is>
+      </c>
+      <c r="E1075" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="F1075" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Birthday Data Master.xlsx
+++ b/Birthday Data Master.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1075"/>
+  <dimension ref="A1:F1082"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.6" customWidth="1" min="1" max="1"/>
@@ -34825,6 +34825,230 @@
         </is>
       </c>
     </row>
+    <row r="1076">
+      <c r="A1076" t="inlineStr">
+        <is>
+          <t>29,Mar</t>
+        </is>
+      </c>
+      <c r="B1076" t="inlineStr">
+        <is>
+          <t>SHIVAM  PRAKASH</t>
+        </is>
+      </c>
+      <c r="C1076" t="inlineStr">
+        <is>
+          <t>AKHILESH KUMAR RAY</t>
+        </is>
+      </c>
+      <c r="D1076" t="inlineStr">
+        <is>
+          <t>KUMARI NEERAJ SHARMA</t>
+        </is>
+      </c>
+      <c r="E1076" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="F1076" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="1077">
+      <c r="A1077" t="inlineStr">
+        <is>
+          <t>29,Mar</t>
+        </is>
+      </c>
+      <c r="B1077" t="inlineStr">
+        <is>
+          <t>Gautam Kumar</t>
+        </is>
+      </c>
+      <c r="C1077" t="inlineStr">
+        <is>
+          <t>Raushan Kumar</t>
+        </is>
+      </c>
+      <c r="D1077" t="inlineStr">
+        <is>
+          <t>Asha Kumari</t>
+        </is>
+      </c>
+      <c r="E1077" t="inlineStr">
+        <is>
+          <t>IX</t>
+        </is>
+      </c>
+      <c r="F1077" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="1078">
+      <c r="A1078" t="inlineStr">
+        <is>
+          <t>29,Mar</t>
+        </is>
+      </c>
+      <c r="B1078" t="inlineStr">
+        <is>
+          <t>Anupam  Kumar</t>
+        </is>
+      </c>
+      <c r="C1078" t="inlineStr">
+        <is>
+          <t>Arvind Kumar Shahi</t>
+        </is>
+      </c>
+      <c r="D1078" t="inlineStr">
+        <is>
+          <t>Dhanwanti Kumari</t>
+        </is>
+      </c>
+      <c r="E1078" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F1078" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="1079">
+      <c r="A1079" t="inlineStr">
+        <is>
+          <t>29,Mar</t>
+        </is>
+      </c>
+      <c r="B1079" t="inlineStr">
+        <is>
+          <t>ARPITA SHARMA</t>
+        </is>
+      </c>
+      <c r="C1079" t="inlineStr">
+        <is>
+          <t>RAVI KUMAR SHARMA</t>
+        </is>
+      </c>
+      <c r="D1079" t="inlineStr">
+        <is>
+          <t>NITU SHARMA</t>
+        </is>
+      </c>
+      <c r="E1079" t="inlineStr">
+        <is>
+          <t>VII</t>
+        </is>
+      </c>
+      <c r="F1079" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="1080">
+      <c r="A1080" t="inlineStr">
+        <is>
+          <t>29,Mar</t>
+        </is>
+      </c>
+      <c r="B1080" t="inlineStr">
+        <is>
+          <t>ADARSH RAJ</t>
+        </is>
+      </c>
+      <c r="C1080" t="inlineStr">
+        <is>
+          <t>SURYAKANT TIWARI</t>
+        </is>
+      </c>
+      <c r="D1080" t="inlineStr">
+        <is>
+          <t>NEHA BHARTI</t>
+        </is>
+      </c>
+      <c r="E1080" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="F1080" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="1081">
+      <c r="A1081" t="inlineStr">
+        <is>
+          <t>29,Mar</t>
+        </is>
+      </c>
+      <c r="B1081" t="inlineStr">
+        <is>
+          <t>SAMAR KUMAR</t>
+        </is>
+      </c>
+      <c r="C1081" t="inlineStr">
+        <is>
+          <t>PANKAJ KUMAR</t>
+        </is>
+      </c>
+      <c r="D1081" t="inlineStr">
+        <is>
+          <t>BABY KUMARI</t>
+        </is>
+      </c>
+      <c r="E1081" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="F1081" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="1082">
+      <c r="A1082" t="inlineStr">
+        <is>
+          <t>29,Mar</t>
+        </is>
+      </c>
+      <c r="B1082" t="inlineStr">
+        <is>
+          <t>RITIKA  RANJAN</t>
+        </is>
+      </c>
+      <c r="C1082" t="inlineStr">
+        <is>
+          <t>RAJEEV KUMAR</t>
+        </is>
+      </c>
+      <c r="D1082" t="inlineStr">
+        <is>
+          <t>RUPA RANJAN</t>
+        </is>
+      </c>
+      <c r="E1082" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="F1082" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Birthday Data Master.xlsx
+++ b/Birthday Data Master.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1082"/>
+  <dimension ref="A1:F1088"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.6" customWidth="1" min="1" max="1"/>
@@ -35049,6 +35049,198 @@
         </is>
       </c>
     </row>
+    <row r="1083">
+      <c r="A1083" t="inlineStr">
+        <is>
+          <t>30,Mar</t>
+        </is>
+      </c>
+      <c r="B1083" t="inlineStr">
+        <is>
+          <t>Naitik Raj</t>
+        </is>
+      </c>
+      <c r="C1083" t="inlineStr">
+        <is>
+          <t>Buchani Sharma</t>
+        </is>
+      </c>
+      <c r="D1083" t="inlineStr">
+        <is>
+          <t>Nilu Kumari</t>
+        </is>
+      </c>
+      <c r="E1083" t="inlineStr">
+        <is>
+          <t>IV</t>
+        </is>
+      </c>
+      <c r="F1083" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="1084">
+      <c r="A1084" t="inlineStr">
+        <is>
+          <t>30,Mar</t>
+        </is>
+      </c>
+      <c r="B1084" t="inlineStr">
+        <is>
+          <t>Geetanjali Kumari</t>
+        </is>
+      </c>
+      <c r="C1084" t="inlineStr">
+        <is>
+          <t>Raj kumar Mishra</t>
+        </is>
+      </c>
+      <c r="D1084" t="inlineStr">
+        <is>
+          <t>Anju Devi</t>
+        </is>
+      </c>
+      <c r="E1084" t="inlineStr">
+        <is>
+          <t>IX</t>
+        </is>
+      </c>
+      <c r="F1084" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="1085">
+      <c r="A1085" t="inlineStr">
+        <is>
+          <t>30,Mar</t>
+        </is>
+      </c>
+      <c r="B1085" t="inlineStr">
+        <is>
+          <t>ADARSH KUMAR</t>
+        </is>
+      </c>
+      <c r="C1085" t="inlineStr">
+        <is>
+          <t>SINTU KUMAR</t>
+        </is>
+      </c>
+      <c r="D1085" t="inlineStr">
+        <is>
+          <t>RENU DEVI</t>
+        </is>
+      </c>
+      <c r="E1085" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F1085" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="1086">
+      <c r="A1086" t="inlineStr">
+        <is>
+          <t>30,Mar</t>
+        </is>
+      </c>
+      <c r="B1086" t="inlineStr">
+        <is>
+          <t>YOGESHWARI</t>
+        </is>
+      </c>
+      <c r="C1086" t="inlineStr">
+        <is>
+          <t>CHANCHAL KUMAR GHARWAR</t>
+        </is>
+      </c>
+      <c r="D1086" t="inlineStr">
+        <is>
+          <t>RANJANA KUMARI</t>
+        </is>
+      </c>
+      <c r="E1086" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="F1086" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="1087">
+      <c r="A1087" t="inlineStr">
+        <is>
+          <t>30,Mar</t>
+        </is>
+      </c>
+      <c r="B1087" t="inlineStr">
+        <is>
+          <t>Shivam</t>
+        </is>
+      </c>
+      <c r="C1087" t="inlineStr">
+        <is>
+          <t>Brajmohan Kumar</t>
+        </is>
+      </c>
+      <c r="D1087" t="inlineStr">
+        <is>
+          <t>Kumari Abha Sinha</t>
+        </is>
+      </c>
+      <c r="E1087" t="inlineStr">
+        <is>
+          <t>VIII</t>
+        </is>
+      </c>
+      <c r="F1087" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+    </row>
+    <row r="1088">
+      <c r="A1088" t="inlineStr">
+        <is>
+          <t>30,Mar</t>
+        </is>
+      </c>
+      <c r="B1088" t="inlineStr">
+        <is>
+          <t>MD. Zoomar Athar</t>
+        </is>
+      </c>
+      <c r="C1088" t="inlineStr">
+        <is>
+          <t>Md. Shahbaz Athar</t>
+        </is>
+      </c>
+      <c r="D1088" t="inlineStr">
+        <is>
+          <t>Zeenat Parween</t>
+        </is>
+      </c>
+      <c r="E1088" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F1088" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Birthday Data Master.xlsx
+++ b/Birthday Data Master.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1088"/>
+  <dimension ref="A1:F1092"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.6" customWidth="1" min="1" max="1"/>
@@ -35241,6 +35241,134 @@
         </is>
       </c>
     </row>
+    <row r="1089">
+      <c r="A1089" t="inlineStr">
+        <is>
+          <t>31,Mar</t>
+        </is>
+      </c>
+      <c r="B1089" t="inlineStr">
+        <is>
+          <t>ARPIT KUMAR</t>
+        </is>
+      </c>
+      <c r="C1089" t="inlineStr">
+        <is>
+          <t>KRISHN MOHAN CHOUDHARY</t>
+        </is>
+      </c>
+      <c r="D1089" t="inlineStr">
+        <is>
+          <t>INDU DEVI</t>
+        </is>
+      </c>
+      <c r="E1089" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="F1089" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="1090">
+      <c r="A1090" t="inlineStr">
+        <is>
+          <t>31,Mar</t>
+        </is>
+      </c>
+      <c r="B1090" t="inlineStr">
+        <is>
+          <t>SHOMYA PRAKASH</t>
+        </is>
+      </c>
+      <c r="C1090" t="inlineStr">
+        <is>
+          <t>JIVAN PRAKASH</t>
+        </is>
+      </c>
+      <c r="D1090" t="inlineStr">
+        <is>
+          <t>REKHA PRAKASH</t>
+        </is>
+      </c>
+      <c r="E1090" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="F1090" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="1091">
+      <c r="A1091" t="inlineStr">
+        <is>
+          <t>31,Mar</t>
+        </is>
+      </c>
+      <c r="B1091" t="inlineStr">
+        <is>
+          <t>KHUSHI KUMARI</t>
+        </is>
+      </c>
+      <c r="C1091" t="inlineStr">
+        <is>
+          <t>RAJU KUMAR</t>
+        </is>
+      </c>
+      <c r="D1091" t="inlineStr">
+        <is>
+          <t>ARPAN GAUTAM</t>
+        </is>
+      </c>
+      <c r="E1091" t="inlineStr">
+        <is>
+          <t>VII</t>
+        </is>
+      </c>
+      <c r="F1091" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="1092">
+      <c r="A1092" t="inlineStr">
+        <is>
+          <t>31,Mar</t>
+        </is>
+      </c>
+      <c r="B1092" t="inlineStr">
+        <is>
+          <t>AMAR KISHORE</t>
+        </is>
+      </c>
+      <c r="C1092" t="inlineStr">
+        <is>
+          <t>KAMAKHYA KUMAR</t>
+        </is>
+      </c>
+      <c r="D1092" t="inlineStr">
+        <is>
+          <t>ARTI SINHA</t>
+        </is>
+      </c>
+      <c r="E1092" t="inlineStr">
+        <is>
+          <t>IX</t>
+        </is>
+      </c>
+      <c r="F1092" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Birthday Data Master.xlsx
+++ b/Birthday Data Master.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1092"/>
+  <dimension ref="A1:F1098"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.6" customWidth="1" min="1" max="1"/>
@@ -35369,6 +35369,198 @@
         </is>
       </c>
     </row>
+    <row r="1093">
+      <c r="A1093" t="inlineStr">
+        <is>
+          <t>01,Apr</t>
+        </is>
+      </c>
+      <c r="B1093" t="inlineStr">
+        <is>
+          <t>CHIRANSH BALAJI</t>
+        </is>
+      </c>
+      <c r="C1093" t="inlineStr">
+        <is>
+          <t>RAJEEV RANJAN</t>
+        </is>
+      </c>
+      <c r="D1093" t="inlineStr">
+        <is>
+          <t>RUNAM KUMARI</t>
+        </is>
+      </c>
+      <c r="E1093" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="F1093" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="1094">
+      <c r="A1094" t="inlineStr">
+        <is>
+          <t>01,Apr</t>
+        </is>
+      </c>
+      <c r="B1094" t="inlineStr">
+        <is>
+          <t>SHLOKA SINHA</t>
+        </is>
+      </c>
+      <c r="C1094" t="inlineStr">
+        <is>
+          <t>SANTOSH KUMAR SINHA</t>
+        </is>
+      </c>
+      <c r="D1094" t="inlineStr">
+        <is>
+          <t>PRIYANKA KUMARI</t>
+        </is>
+      </c>
+      <c r="E1094" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F1094" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="1095">
+      <c r="A1095" t="inlineStr">
+        <is>
+          <t>01,Apr</t>
+        </is>
+      </c>
+      <c r="B1095" t="inlineStr">
+        <is>
+          <t>Vinit Kumar</t>
+        </is>
+      </c>
+      <c r="C1095" t="inlineStr">
+        <is>
+          <t>Ranjan Kumar</t>
+        </is>
+      </c>
+      <c r="D1095" t="inlineStr">
+        <is>
+          <t>Sinku DEVI</t>
+        </is>
+      </c>
+      <c r="E1095" t="inlineStr">
+        <is>
+          <t>IX</t>
+        </is>
+      </c>
+      <c r="F1095" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="1096">
+      <c r="A1096" t="inlineStr">
+        <is>
+          <t>01,Apr</t>
+        </is>
+      </c>
+      <c r="B1096" t="inlineStr">
+        <is>
+          <t>Dinesh Kumar</t>
+        </is>
+      </c>
+      <c r="C1096" t="inlineStr">
+        <is>
+          <t>Devendra Kumar</t>
+        </is>
+      </c>
+      <c r="D1096" t="inlineStr">
+        <is>
+          <t>Rinki Kumari</t>
+        </is>
+      </c>
+      <c r="E1096" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F1096" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="1097">
+      <c r="A1097" t="inlineStr">
+        <is>
+          <t>01,Apr</t>
+        </is>
+      </c>
+      <c r="B1097" t="inlineStr">
+        <is>
+          <t>MEHAR HUSSAIN</t>
+        </is>
+      </c>
+      <c r="C1097" t="inlineStr">
+        <is>
+          <t>ARIF HUSSAIN</t>
+        </is>
+      </c>
+      <c r="D1097" t="inlineStr">
+        <is>
+          <t>NISHANT BANO</t>
+        </is>
+      </c>
+      <c r="E1097" t="inlineStr">
+        <is>
+          <t>VII</t>
+        </is>
+      </c>
+      <c r="F1097" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="1098">
+      <c r="A1098" t="inlineStr">
+        <is>
+          <t>01,Apr</t>
+        </is>
+      </c>
+      <c r="B1098" t="inlineStr">
+        <is>
+          <t>Sourav Kumar  Rishav</t>
+        </is>
+      </c>
+      <c r="C1098" t="inlineStr">
+        <is>
+          <t>Sushmakar Basant</t>
+        </is>
+      </c>
+      <c r="D1098" t="inlineStr">
+        <is>
+          <t>Ranju Kumari</t>
+        </is>
+      </c>
+      <c r="E1098" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F1098" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Birthday Data Master.xlsx
+++ b/Birthday Data Master.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1098"/>
+  <dimension ref="A1:F1105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.6" customWidth="1" min="1" max="1"/>
@@ -35561,6 +35561,230 @@
         </is>
       </c>
     </row>
+    <row r="1099">
+      <c r="A1099" t="inlineStr">
+        <is>
+          <t>02,Apr</t>
+        </is>
+      </c>
+      <c r="B1099" t="inlineStr">
+        <is>
+          <t>RAJ  SHREE</t>
+        </is>
+      </c>
+      <c r="C1099" t="inlineStr">
+        <is>
+          <t>DEV BHUSHAN KUMAR</t>
+        </is>
+      </c>
+      <c r="D1099" t="inlineStr">
+        <is>
+          <t>KIRAN KUMARI</t>
+        </is>
+      </c>
+      <c r="E1099" t="inlineStr">
+        <is>
+          <t>UKG</t>
+        </is>
+      </c>
+      <c r="F1099" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="1100">
+      <c r="A1100" t="inlineStr">
+        <is>
+          <t>02,Apr</t>
+        </is>
+      </c>
+      <c r="B1100" t="inlineStr">
+        <is>
+          <t>Ansh Raj</t>
+        </is>
+      </c>
+      <c r="C1100" t="inlineStr">
+        <is>
+          <t>Makhan Kumar</t>
+        </is>
+      </c>
+      <c r="D1100" t="inlineStr">
+        <is>
+          <t>Archana Devi</t>
+        </is>
+      </c>
+      <c r="E1100" t="inlineStr">
+        <is>
+          <t>VIII</t>
+        </is>
+      </c>
+      <c r="F1100" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="1101">
+      <c r="A1101" t="inlineStr">
+        <is>
+          <t>02,Apr</t>
+        </is>
+      </c>
+      <c r="B1101" t="inlineStr">
+        <is>
+          <t>RADHIKA KUMARI</t>
+        </is>
+      </c>
+      <c r="C1101" t="inlineStr">
+        <is>
+          <t>SUJIT KUMAR SINHA</t>
+        </is>
+      </c>
+      <c r="D1101" t="inlineStr">
+        <is>
+          <t>SULEKHA KUMARI</t>
+        </is>
+      </c>
+      <c r="E1101" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="F1101" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="1102">
+      <c r="A1102" t="inlineStr">
+        <is>
+          <t>02,Apr</t>
+        </is>
+      </c>
+      <c r="B1102" t="inlineStr">
+        <is>
+          <t>Ghanshyam Kumar Akela</t>
+        </is>
+      </c>
+      <c r="C1102" t="inlineStr">
+        <is>
+          <t>Santosh Kumar Akela</t>
+        </is>
+      </c>
+      <c r="D1102" t="inlineStr">
+        <is>
+          <t>Rina Kumari</t>
+        </is>
+      </c>
+      <c r="E1102" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F1102" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="1103">
+      <c r="A1103" t="inlineStr">
+        <is>
+          <t>02,Apr</t>
+        </is>
+      </c>
+      <c r="B1103" t="inlineStr">
+        <is>
+          <t>NAVYA  KUMARI</t>
+        </is>
+      </c>
+      <c r="C1103" t="inlineStr">
+        <is>
+          <t>SANTOSH KUMAR GUPTA</t>
+        </is>
+      </c>
+      <c r="D1103" t="inlineStr">
+        <is>
+          <t>KABITA KUMARI</t>
+        </is>
+      </c>
+      <c r="E1103" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="F1103" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="1104">
+      <c r="A1104" t="inlineStr">
+        <is>
+          <t>02,Apr</t>
+        </is>
+      </c>
+      <c r="B1104" t="inlineStr">
+        <is>
+          <t>Ashish Kumar</t>
+        </is>
+      </c>
+      <c r="C1104" t="inlineStr">
+        <is>
+          <t>Vikash Kumar</t>
+        </is>
+      </c>
+      <c r="D1104" t="inlineStr">
+        <is>
+          <t>Suman Devi</t>
+        </is>
+      </c>
+      <c r="E1104" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F1104" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="1105">
+      <c r="A1105" t="inlineStr">
+        <is>
+          <t>03,Apr</t>
+        </is>
+      </c>
+      <c r="B1105" t="inlineStr">
+        <is>
+          <t>PRIYANSHU KUMAR VATS</t>
+        </is>
+      </c>
+      <c r="C1105" t="inlineStr">
+        <is>
+          <t>DHARMENDRA KUMAR</t>
+        </is>
+      </c>
+      <c r="D1105" t="inlineStr">
+        <is>
+          <t>MAMTA KUMARI</t>
+        </is>
+      </c>
+      <c r="E1105" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="F1105" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Birthday Data Master.xlsx
+++ b/Birthday Data Master.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1105"/>
+  <dimension ref="A1:F1115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.6" customWidth="1" min="1" max="1"/>
@@ -35785,6 +35785,326 @@
         </is>
       </c>
     </row>
+    <row r="1106">
+      <c r="A1106" t="inlineStr">
+        <is>
+          <t>04,Apr</t>
+        </is>
+      </c>
+      <c r="B1106" t="inlineStr">
+        <is>
+          <t>PUSKAR KUMAR</t>
+        </is>
+      </c>
+      <c r="C1106" t="inlineStr">
+        <is>
+          <t>MUNNA KUMAR</t>
+        </is>
+      </c>
+      <c r="D1106" t="inlineStr">
+        <is>
+          <t>PRATIBHA DEVI</t>
+        </is>
+      </c>
+      <c r="E1106" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="F1106" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="1107">
+      <c r="A1107" t="inlineStr">
+        <is>
+          <t>04,Apr</t>
+        </is>
+      </c>
+      <c r="B1107" t="inlineStr">
+        <is>
+          <t>HANSHIKA RAJ</t>
+        </is>
+      </c>
+      <c r="C1107" t="inlineStr">
+        <is>
+          <t>RAJEEV RANJAN KUMAR</t>
+        </is>
+      </c>
+      <c r="D1107" t="inlineStr">
+        <is>
+          <t>SIMPI KUMARI</t>
+        </is>
+      </c>
+      <c r="E1107" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="F1107" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="1108">
+      <c r="A1108" t="inlineStr">
+        <is>
+          <t>04,Apr</t>
+        </is>
+      </c>
+      <c r="B1108" t="inlineStr">
+        <is>
+          <t>Akanksha Kumari</t>
+        </is>
+      </c>
+      <c r="C1108" t="inlineStr">
+        <is>
+          <t>Nandan Kumar</t>
+        </is>
+      </c>
+      <c r="D1108" t="inlineStr">
+        <is>
+          <t>Asha Devi</t>
+        </is>
+      </c>
+      <c r="E1108" t="inlineStr">
+        <is>
+          <t>VIII</t>
+        </is>
+      </c>
+      <c r="F1108" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="1109">
+      <c r="A1109" t="inlineStr">
+        <is>
+          <t>04,Apr</t>
+        </is>
+      </c>
+      <c r="B1109" t="inlineStr">
+        <is>
+          <t>UMAIR NASIM</t>
+        </is>
+      </c>
+      <c r="C1109" t="inlineStr">
+        <is>
+          <t>MD. MOZAHIR ASHRAF</t>
+        </is>
+      </c>
+      <c r="D1109" t="inlineStr">
+        <is>
+          <t>SHAFQUT RAHMANI</t>
+        </is>
+      </c>
+      <c r="E1109" t="inlineStr">
+        <is>
+          <t>UKG</t>
+        </is>
+      </c>
+      <c r="F1109" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="1110">
+      <c r="A1110" t="inlineStr">
+        <is>
+          <t>04,Apr</t>
+        </is>
+      </c>
+      <c r="B1110" t="inlineStr">
+        <is>
+          <t>Soni Shankar</t>
+        </is>
+      </c>
+      <c r="C1110" t="inlineStr">
+        <is>
+          <t>Sudesh Kumar</t>
+        </is>
+      </c>
+      <c r="D1110" t="inlineStr">
+        <is>
+          <t>Savita Devi</t>
+        </is>
+      </c>
+      <c r="E1110" t="inlineStr">
+        <is>
+          <t>VIII</t>
+        </is>
+      </c>
+      <c r="F1110" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+    </row>
+    <row r="1111">
+      <c r="A1111" t="inlineStr">
+        <is>
+          <t>05,Apr</t>
+        </is>
+      </c>
+      <c r="B1111" t="inlineStr">
+        <is>
+          <t>AAYANSH ARYA</t>
+        </is>
+      </c>
+      <c r="C1111" t="inlineStr">
+        <is>
+          <t>RAMLAKHAN THAKUR</t>
+        </is>
+      </c>
+      <c r="D1111" t="inlineStr">
+        <is>
+          <t>MENKA RANJAN</t>
+        </is>
+      </c>
+      <c r="E1111" t="inlineStr">
+        <is>
+          <t>UKG</t>
+        </is>
+      </c>
+      <c r="F1111" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="1112">
+      <c r="A1112" t="inlineStr">
+        <is>
+          <t>05,Apr</t>
+        </is>
+      </c>
+      <c r="B1112" t="inlineStr">
+        <is>
+          <t>SHAMEELA AZMAT</t>
+        </is>
+      </c>
+      <c r="C1112" t="inlineStr">
+        <is>
+          <t>MOHAMMAD SHAKIF AKHTAR</t>
+        </is>
+      </c>
+      <c r="D1112" t="inlineStr">
+        <is>
+          <t>SHIMHA RAFFAT</t>
+        </is>
+      </c>
+      <c r="E1112" t="inlineStr">
+        <is>
+          <t>LKG</t>
+        </is>
+      </c>
+      <c r="F1112" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="1113">
+      <c r="A1113" t="inlineStr">
+        <is>
+          <t>05,Apr</t>
+        </is>
+      </c>
+      <c r="B1113" t="inlineStr">
+        <is>
+          <t>RAKSHITA BHARDWAJ</t>
+        </is>
+      </c>
+      <c r="C1113" t="inlineStr">
+        <is>
+          <t>NEERAJ KUMAR</t>
+        </is>
+      </c>
+      <c r="D1113" t="inlineStr">
+        <is>
+          <t>SWEETI KUMARI</t>
+        </is>
+      </c>
+      <c r="E1113" t="inlineStr">
+        <is>
+          <t>LKG</t>
+        </is>
+      </c>
+      <c r="F1113" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="1114">
+      <c r="A1114" t="inlineStr">
+        <is>
+          <t>05,Apr</t>
+        </is>
+      </c>
+      <c r="B1114" t="inlineStr">
+        <is>
+          <t>SUMIT KUMAR</t>
+        </is>
+      </c>
+      <c r="C1114" t="inlineStr">
+        <is>
+          <t>SATISH KUMAR</t>
+        </is>
+      </c>
+      <c r="D1114" t="inlineStr">
+        <is>
+          <t>PINKI DEVI</t>
+        </is>
+      </c>
+      <c r="E1114" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="F1114" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="1115">
+      <c r="A1115" t="inlineStr">
+        <is>
+          <t>05,Apr</t>
+        </is>
+      </c>
+      <c r="B1115" t="inlineStr">
+        <is>
+          <t>ARYAN KUMAR</t>
+        </is>
+      </c>
+      <c r="C1115" t="inlineStr">
+        <is>
+          <t>PANKAJ KUMAR</t>
+        </is>
+      </c>
+      <c r="D1115" t="inlineStr">
+        <is>
+          <t>RUPA KUMARI</t>
+        </is>
+      </c>
+      <c r="E1115" t="inlineStr">
+        <is>
+          <t>UKG</t>
+        </is>
+      </c>
+      <c r="F1115" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Birthday Data Master.xlsx
+++ b/Birthday Data Master.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1115"/>
+  <dimension ref="A1:F1121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.6" customWidth="1" min="1" max="1"/>
@@ -36105,6 +36105,198 @@
         </is>
       </c>
     </row>
+    <row r="1116">
+      <c r="A1116" t="inlineStr">
+        <is>
+          <t>06,Apr</t>
+        </is>
+      </c>
+      <c r="B1116" t="inlineStr">
+        <is>
+          <t>KHULSUM FATIMA</t>
+        </is>
+      </c>
+      <c r="C1116" t="inlineStr">
+        <is>
+          <t>SHAHID MALLICK</t>
+        </is>
+      </c>
+      <c r="D1116" t="inlineStr">
+        <is>
+          <t>LATE NAHID KHATOON</t>
+        </is>
+      </c>
+      <c r="E1116" t="inlineStr">
+        <is>
+          <t>IV</t>
+        </is>
+      </c>
+      <c r="F1116" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="1117">
+      <c r="A1117" t="inlineStr">
+        <is>
+          <t>06,Apr</t>
+        </is>
+      </c>
+      <c r="B1117" t="inlineStr">
+        <is>
+          <t>KHIZIR  MALLICK</t>
+        </is>
+      </c>
+      <c r="C1117" t="inlineStr">
+        <is>
+          <t>SHAHID MALLICK</t>
+        </is>
+      </c>
+      <c r="D1117" t="inlineStr">
+        <is>
+          <t>LATE NAHIDA MALLICK</t>
+        </is>
+      </c>
+      <c r="E1117" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="F1117" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="1118">
+      <c r="A1118" t="inlineStr">
+        <is>
+          <t>06,Apr</t>
+        </is>
+      </c>
+      <c r="B1118" t="inlineStr">
+        <is>
+          <t>SHRISTI RAJ</t>
+        </is>
+      </c>
+      <c r="C1118" t="inlineStr">
+        <is>
+          <t>SANJAY KUMAR</t>
+        </is>
+      </c>
+      <c r="D1118" t="inlineStr">
+        <is>
+          <t>MANDVI KUMARI</t>
+        </is>
+      </c>
+      <c r="E1118" t="inlineStr">
+        <is>
+          <t>UKG</t>
+        </is>
+      </c>
+      <c r="F1118" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="1119">
+      <c r="A1119" t="inlineStr">
+        <is>
+          <t>06,Apr</t>
+        </is>
+      </c>
+      <c r="B1119" t="inlineStr">
+        <is>
+          <t>TEJSW RAJ</t>
+        </is>
+      </c>
+      <c r="C1119" t="inlineStr">
+        <is>
+          <t>GOPAL PRASAD</t>
+        </is>
+      </c>
+      <c r="D1119" t="inlineStr">
+        <is>
+          <t>SUNITA DEVI</t>
+        </is>
+      </c>
+      <c r="E1119" t="inlineStr">
+        <is>
+          <t>VII</t>
+        </is>
+      </c>
+      <c r="F1119" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+    </row>
+    <row r="1120">
+      <c r="A1120" t="inlineStr">
+        <is>
+          <t>06,Apr</t>
+        </is>
+      </c>
+      <c r="B1120" t="inlineStr">
+        <is>
+          <t>AYUSH KUMAR</t>
+        </is>
+      </c>
+      <c r="C1120" t="inlineStr">
+        <is>
+          <t>Ashutosh Kumar</t>
+        </is>
+      </c>
+      <c r="D1120" t="inlineStr">
+        <is>
+          <t>Rimpi Kumari</t>
+        </is>
+      </c>
+      <c r="E1120" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="F1120" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="1121">
+      <c r="A1121" t="inlineStr">
+        <is>
+          <t>06,Apr</t>
+        </is>
+      </c>
+      <c r="B1121" t="inlineStr">
+        <is>
+          <t>ANSH RAJ</t>
+        </is>
+      </c>
+      <c r="C1121" t="inlineStr">
+        <is>
+          <t>AMRENDRA KUMAR SINGH</t>
+        </is>
+      </c>
+      <c r="D1121" t="inlineStr">
+        <is>
+          <t>NISHA NAYAN</t>
+        </is>
+      </c>
+      <c r="E1121" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="F1121" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Birthday Data Master.xlsx
+++ b/Birthday Data Master.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1121"/>
+  <dimension ref="A1:F1123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.6" customWidth="1" min="1" max="1"/>
@@ -36297,6 +36297,70 @@
         </is>
       </c>
     </row>
+    <row r="1122">
+      <c r="A1122" t="inlineStr">
+        <is>
+          <t>07,Apr</t>
+        </is>
+      </c>
+      <c r="B1122" t="inlineStr">
+        <is>
+          <t>HARSH BHARDWAJ</t>
+        </is>
+      </c>
+      <c r="C1122" t="inlineStr">
+        <is>
+          <t>CHANDAN KUMAR SINGH</t>
+        </is>
+      </c>
+      <c r="D1122" t="inlineStr">
+        <is>
+          <t>SWETA RANI</t>
+        </is>
+      </c>
+      <c r="E1122" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="F1122" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="1123">
+      <c r="A1123" t="inlineStr">
+        <is>
+          <t>07,Apr</t>
+        </is>
+      </c>
+      <c r="B1123" t="inlineStr">
+        <is>
+          <t>AAROHI ARNAV</t>
+        </is>
+      </c>
+      <c r="C1123" t="inlineStr">
+        <is>
+          <t>SANJAY KUMAR</t>
+        </is>
+      </c>
+      <c r="D1123" t="inlineStr">
+        <is>
+          <t>SMITA KUMARI</t>
+        </is>
+      </c>
+      <c r="E1123" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="F1123" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Birthday Data Master.xlsx
+++ b/Birthday Data Master.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1123"/>
+  <dimension ref="A1:F1128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.6" customWidth="1" min="1" max="1"/>
@@ -36361,6 +36361,166 @@
         </is>
       </c>
     </row>
+    <row r="1124">
+      <c r="A1124" t="inlineStr">
+        <is>
+          <t>08,Apr</t>
+        </is>
+      </c>
+      <c r="B1124" t="inlineStr">
+        <is>
+          <t>MANVI KUMARI</t>
+        </is>
+      </c>
+      <c r="C1124" t="inlineStr">
+        <is>
+          <t>SUDARSHAN KUMAR</t>
+        </is>
+      </c>
+      <c r="D1124" t="inlineStr">
+        <is>
+          <t>REKHA KUMARI</t>
+        </is>
+      </c>
+      <c r="E1124" t="inlineStr">
+        <is>
+          <t>LKG</t>
+        </is>
+      </c>
+      <c r="F1124" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="1125">
+      <c r="A1125" t="inlineStr">
+        <is>
+          <t>08,Apr</t>
+        </is>
+      </c>
+      <c r="B1125" t="inlineStr">
+        <is>
+          <t>Vaibhav  Kumar</t>
+        </is>
+      </c>
+      <c r="C1125" t="inlineStr">
+        <is>
+          <t>Sudhir Kumar</t>
+        </is>
+      </c>
+      <c r="D1125" t="inlineStr">
+        <is>
+          <t>Bibha Kumari</t>
+        </is>
+      </c>
+      <c r="E1125" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F1125" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="1126">
+      <c r="A1126" t="inlineStr">
+        <is>
+          <t>08,Apr</t>
+        </is>
+      </c>
+      <c r="B1126" t="inlineStr">
+        <is>
+          <t>TANISHKA KUMARI</t>
+        </is>
+      </c>
+      <c r="C1126" t="inlineStr">
+        <is>
+          <t>PRAMOD KUMAR SINHA</t>
+        </is>
+      </c>
+      <c r="D1126" t="inlineStr">
+        <is>
+          <t>PUSPA KUMARI</t>
+        </is>
+      </c>
+      <c r="E1126" t="inlineStr">
+        <is>
+          <t>IX</t>
+        </is>
+      </c>
+      <c r="F1126" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="1127">
+      <c r="A1127" t="inlineStr">
+        <is>
+          <t>08,Apr</t>
+        </is>
+      </c>
+      <c r="B1127" t="inlineStr">
+        <is>
+          <t>NAINSI KUMARI</t>
+        </is>
+      </c>
+      <c r="C1127" t="inlineStr">
+        <is>
+          <t>DHARMVEER KUMAR</t>
+        </is>
+      </c>
+      <c r="D1127" t="inlineStr">
+        <is>
+          <t>VANDANA KUMARI</t>
+        </is>
+      </c>
+      <c r="E1127" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="F1127" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="1128">
+      <c r="A1128" t="inlineStr">
+        <is>
+          <t>08,Apr</t>
+        </is>
+      </c>
+      <c r="B1128" t="inlineStr">
+        <is>
+          <t>Ansh Raj</t>
+        </is>
+      </c>
+      <c r="C1128" t="inlineStr">
+        <is>
+          <t>Ajesh Prasad Pal</t>
+        </is>
+      </c>
+      <c r="D1128" t="inlineStr">
+        <is>
+          <t>Sanju Kumari</t>
+        </is>
+      </c>
+      <c r="E1128" t="inlineStr">
+        <is>
+          <t>VIII</t>
+        </is>
+      </c>
+      <c r="F1128" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Birthday Data Master.xlsx
+++ b/Birthday Data Master.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1128"/>
+  <dimension ref="A1:F1135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.6" customWidth="1" min="1" max="1"/>
@@ -36521,6 +36521,230 @@
         </is>
       </c>
     </row>
+    <row r="1129">
+      <c r="A1129" t="inlineStr">
+        <is>
+          <t>09,Apr</t>
+        </is>
+      </c>
+      <c r="B1129" t="inlineStr">
+        <is>
+          <t>VAISHNAVI KUMARI  VERMA</t>
+        </is>
+      </c>
+      <c r="C1129" t="inlineStr">
+        <is>
+          <t>GUDDU PRASAD VERMA</t>
+        </is>
+      </c>
+      <c r="D1129" t="inlineStr">
+        <is>
+          <t>AMRITA KUMARI VERMA</t>
+        </is>
+      </c>
+      <c r="E1129" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="F1129" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="1130">
+      <c r="A1130" t="inlineStr">
+        <is>
+          <t>09,Apr</t>
+        </is>
+      </c>
+      <c r="B1130" t="inlineStr">
+        <is>
+          <t>AKSHAY KUMAR</t>
+        </is>
+      </c>
+      <c r="C1130" t="inlineStr">
+        <is>
+          <t>MANTU PRASAD</t>
+        </is>
+      </c>
+      <c r="D1130" t="inlineStr">
+        <is>
+          <t>PUJA DEVI</t>
+        </is>
+      </c>
+      <c r="E1130" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F1130" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="1131">
+      <c r="A1131" t="inlineStr">
+        <is>
+          <t>09,Apr</t>
+        </is>
+      </c>
+      <c r="B1131" t="inlineStr">
+        <is>
+          <t>AARAV SINHA</t>
+        </is>
+      </c>
+      <c r="C1131" t="inlineStr">
+        <is>
+          <t>ARVIND KUMAR SINHA</t>
+        </is>
+      </c>
+      <c r="D1131" t="inlineStr">
+        <is>
+          <t>GUNJA KUMARI</t>
+        </is>
+      </c>
+      <c r="E1131" t="inlineStr">
+        <is>
+          <t>LKG</t>
+        </is>
+      </c>
+      <c r="F1131" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="1132">
+      <c r="A1132" t="inlineStr">
+        <is>
+          <t>10,Apr</t>
+        </is>
+      </c>
+      <c r="B1132" t="inlineStr">
+        <is>
+          <t>Rishav Raj</t>
+        </is>
+      </c>
+      <c r="C1132" t="inlineStr">
+        <is>
+          <t>Prashant Kumar</t>
+        </is>
+      </c>
+      <c r="D1132" t="inlineStr">
+        <is>
+          <t>KUMARI SANDHYA</t>
+        </is>
+      </c>
+      <c r="E1132" t="inlineStr">
+        <is>
+          <t>IX</t>
+        </is>
+      </c>
+      <c r="F1132" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="1133">
+      <c r="A1133" t="inlineStr">
+        <is>
+          <t>10,Apr</t>
+        </is>
+      </c>
+      <c r="B1133" t="inlineStr">
+        <is>
+          <t>ARYAN KUMAR</t>
+        </is>
+      </c>
+      <c r="C1133" t="inlineStr">
+        <is>
+          <t>MUKESH KUMAR</t>
+        </is>
+      </c>
+      <c r="D1133" t="inlineStr">
+        <is>
+          <t>RINA KUMARI</t>
+        </is>
+      </c>
+      <c r="E1133" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="F1133" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="1134">
+      <c r="A1134" t="inlineStr">
+        <is>
+          <t>10,Apr</t>
+        </is>
+      </c>
+      <c r="B1134" t="inlineStr">
+        <is>
+          <t>Shruti Kumari</t>
+        </is>
+      </c>
+      <c r="C1134" t="inlineStr">
+        <is>
+          <t>Raju KUMAR</t>
+        </is>
+      </c>
+      <c r="D1134" t="inlineStr">
+        <is>
+          <t>Munni Devi</t>
+        </is>
+      </c>
+      <c r="E1134" t="inlineStr">
+        <is>
+          <t>IX</t>
+        </is>
+      </c>
+      <c r="F1134" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="1135">
+      <c r="A1135" t="inlineStr">
+        <is>
+          <t>10,Apr</t>
+        </is>
+      </c>
+      <c r="B1135" t="inlineStr">
+        <is>
+          <t>MD. AYAAN TANWEER</t>
+        </is>
+      </c>
+      <c r="C1135" t="inlineStr">
+        <is>
+          <t>MD TANWIRUL HAQUE</t>
+        </is>
+      </c>
+      <c r="D1135" t="inlineStr">
+        <is>
+          <t>RAUNAQUE AFROZ</t>
+        </is>
+      </c>
+      <c r="E1135" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="F1135" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Birthday Data Master.xlsx
+++ b/Birthday Data Master.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1135"/>
+  <dimension ref="A1:F1137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.6" customWidth="1" min="1" max="1"/>
@@ -36745,6 +36745,70 @@
         </is>
       </c>
     </row>
+    <row r="1136">
+      <c r="A1136" t="inlineStr">
+        <is>
+          <t>11,Apr</t>
+        </is>
+      </c>
+      <c r="B1136" t="inlineStr">
+        <is>
+          <t>Aryan Kumar</t>
+        </is>
+      </c>
+      <c r="C1136" t="inlineStr">
+        <is>
+          <t>Ankush Kumar</t>
+        </is>
+      </c>
+      <c r="D1136" t="inlineStr">
+        <is>
+          <t>Dimpal DEVI</t>
+        </is>
+      </c>
+      <c r="E1136" t="inlineStr">
+        <is>
+          <t>IX</t>
+        </is>
+      </c>
+      <c r="F1136" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="1137">
+      <c r="A1137" t="inlineStr">
+        <is>
+          <t>11,Apr</t>
+        </is>
+      </c>
+      <c r="B1137" t="inlineStr">
+        <is>
+          <t>GULSHAN KUMAR  SINGH</t>
+        </is>
+      </c>
+      <c r="C1137" t="inlineStr">
+        <is>
+          <t>SANJAY KUMAR</t>
+        </is>
+      </c>
+      <c r="D1137" t="inlineStr">
+        <is>
+          <t>ARCHANA KUMARI</t>
+        </is>
+      </c>
+      <c r="E1137" t="inlineStr">
+        <is>
+          <t>IV</t>
+        </is>
+      </c>
+      <c r="F1137" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Birthday Data Master.xlsx
+++ b/Birthday Data Master.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1137"/>
+  <dimension ref="A1:F1141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.6" customWidth="1" min="1" max="1"/>
@@ -36809,6 +36809,134 @@
         </is>
       </c>
     </row>
+    <row r="1138">
+      <c r="A1138" t="inlineStr">
+        <is>
+          <t>12,Apr</t>
+        </is>
+      </c>
+      <c r="B1138" t="inlineStr">
+        <is>
+          <t>PUSHKAR RAJ</t>
+        </is>
+      </c>
+      <c r="C1138" t="inlineStr">
+        <is>
+          <t>KRISHNA KUMAR</t>
+        </is>
+      </c>
+      <c r="D1138" t="inlineStr">
+        <is>
+          <t>SUSHAMA DEVI</t>
+        </is>
+      </c>
+      <c r="E1138" t="inlineStr">
+        <is>
+          <t>XI</t>
+        </is>
+      </c>
+      <c r="F1138" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="1139">
+      <c r="A1139" t="inlineStr">
+        <is>
+          <t>12,Apr</t>
+        </is>
+      </c>
+      <c r="B1139" t="inlineStr">
+        <is>
+          <t>SHREYANSH KUMAR</t>
+        </is>
+      </c>
+      <c r="C1139" t="inlineStr">
+        <is>
+          <t>SURENDRA KUMAR</t>
+        </is>
+      </c>
+      <c r="D1139" t="inlineStr">
+        <is>
+          <t>SINDHU KUMARI</t>
+        </is>
+      </c>
+      <c r="E1139" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="F1139" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="1140">
+      <c r="A1140" t="inlineStr">
+        <is>
+          <t>12,Apr</t>
+        </is>
+      </c>
+      <c r="B1140" t="inlineStr">
+        <is>
+          <t>Aniket Raj</t>
+        </is>
+      </c>
+      <c r="C1140" t="inlineStr">
+        <is>
+          <t>Gautam Kumar</t>
+        </is>
+      </c>
+      <c r="D1140" t="inlineStr">
+        <is>
+          <t>Nitu Kumari</t>
+        </is>
+      </c>
+      <c r="E1140" t="inlineStr">
+        <is>
+          <t>VIII</t>
+        </is>
+      </c>
+      <c r="F1140" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="1141">
+      <c r="A1141" t="inlineStr">
+        <is>
+          <t>12,Apr</t>
+        </is>
+      </c>
+      <c r="B1141" t="inlineStr">
+        <is>
+          <t>DHRUV PRAKASH</t>
+        </is>
+      </c>
+      <c r="C1141" t="inlineStr">
+        <is>
+          <t>GAUTAM KHAN</t>
+        </is>
+      </c>
+      <c r="D1141" t="inlineStr">
+        <is>
+          <t>SHILPI DEVI</t>
+        </is>
+      </c>
+      <c r="E1141" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F1141" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Birthday Data Master.xlsx
+++ b/Birthday Data Master.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1141"/>
+  <dimension ref="A1:F1150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.6" customWidth="1" min="1" max="1"/>
@@ -36937,6 +36937,294 @@
         </is>
       </c>
     </row>
+    <row r="1142">
+      <c r="A1142" t="inlineStr">
+        <is>
+          <t>13,Apr</t>
+        </is>
+      </c>
+      <c r="B1142" t="inlineStr">
+        <is>
+          <t>AYUSHI SINHA</t>
+        </is>
+      </c>
+      <c r="C1142" t="inlineStr">
+        <is>
+          <t>ASHUTOSH KUMAR</t>
+        </is>
+      </c>
+      <c r="D1142" t="inlineStr">
+        <is>
+          <t>URVASHI KUMARI</t>
+        </is>
+      </c>
+      <c r="E1142" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="F1142" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="1143">
+      <c r="A1143" t="inlineStr">
+        <is>
+          <t>13,Apr</t>
+        </is>
+      </c>
+      <c r="B1143" t="inlineStr">
+        <is>
+          <t>Ojas</t>
+        </is>
+      </c>
+      <c r="C1143" t="inlineStr">
+        <is>
+          <t>Ramchandra Sharma</t>
+        </is>
+      </c>
+      <c r="D1143" t="inlineStr">
+        <is>
+          <t>Manjusha Kumari</t>
+        </is>
+      </c>
+      <c r="E1143" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="F1143" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="1144">
+      <c r="A1144" t="inlineStr">
+        <is>
+          <t>13,Apr</t>
+        </is>
+      </c>
+      <c r="B1144" t="inlineStr">
+        <is>
+          <t>Anuradha Sharma</t>
+        </is>
+      </c>
+      <c r="C1144" t="inlineStr">
+        <is>
+          <t>Subodh Ranjan</t>
+        </is>
+      </c>
+      <c r="D1144" t="inlineStr">
+        <is>
+          <t>Neeru Devi</t>
+        </is>
+      </c>
+      <c r="E1144" t="inlineStr">
+        <is>
+          <t>VIII</t>
+        </is>
+      </c>
+      <c r="F1144" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+    </row>
+    <row r="1145">
+      <c r="A1145" t="inlineStr">
+        <is>
+          <t>14,Apr</t>
+        </is>
+      </c>
+      <c r="B1145" t="inlineStr">
+        <is>
+          <t>ARNAV RANJAN</t>
+        </is>
+      </c>
+      <c r="C1145" t="inlineStr">
+        <is>
+          <t>PRIYA RANJAN KUMAR</t>
+        </is>
+      </c>
+      <c r="D1145" t="inlineStr">
+        <is>
+          <t>SUNITA KUMARI SINHA</t>
+        </is>
+      </c>
+      <c r="E1145" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F1145" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="1146">
+      <c r="A1146" t="inlineStr">
+        <is>
+          <t>14,Apr</t>
+        </is>
+      </c>
+      <c r="B1146" t="inlineStr">
+        <is>
+          <t>MD YUSUF DANISHWAR</t>
+        </is>
+      </c>
+      <c r="C1146" t="inlineStr">
+        <is>
+          <t>MD DANISH</t>
+        </is>
+      </c>
+      <c r="D1146" t="inlineStr">
+        <is>
+          <t>ROQUAIYA AMBREEN</t>
+        </is>
+      </c>
+      <c r="E1146" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="F1146" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="1147">
+      <c r="A1147" t="inlineStr">
+        <is>
+          <t>14,Apr</t>
+        </is>
+      </c>
+      <c r="B1147" t="inlineStr">
+        <is>
+          <t>NAVYA SHARMA</t>
+        </is>
+      </c>
+      <c r="C1147" t="inlineStr">
+        <is>
+          <t>DEEPAK ANAND</t>
+        </is>
+      </c>
+      <c r="D1147" t="inlineStr">
+        <is>
+          <t>SNEHA KUMARI</t>
+        </is>
+      </c>
+      <c r="E1147" t="inlineStr">
+        <is>
+          <t>IV</t>
+        </is>
+      </c>
+      <c r="F1147" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="1148">
+      <c r="A1148" t="inlineStr">
+        <is>
+          <t>14,Apr</t>
+        </is>
+      </c>
+      <c r="B1148" t="inlineStr">
+        <is>
+          <t>Ananya Kumari</t>
+        </is>
+      </c>
+      <c r="C1148" t="inlineStr">
+        <is>
+          <t>Niraj Kumar</t>
+        </is>
+      </c>
+      <c r="D1148" t="inlineStr">
+        <is>
+          <t>Sunita Kumari</t>
+        </is>
+      </c>
+      <c r="E1148" t="inlineStr">
+        <is>
+          <t>VIII</t>
+        </is>
+      </c>
+      <c r="F1148" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="1149">
+      <c r="A1149" t="inlineStr">
+        <is>
+          <t>14,Apr</t>
+        </is>
+      </c>
+      <c r="B1149" t="inlineStr">
+        <is>
+          <t>RITIKA SINGH</t>
+        </is>
+      </c>
+      <c r="C1149" t="inlineStr">
+        <is>
+          <t>VINKATESH KUMAR</t>
+        </is>
+      </c>
+      <c r="D1149" t="inlineStr">
+        <is>
+          <t>PRIYANKA KUMARI</t>
+        </is>
+      </c>
+      <c r="E1149" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="F1149" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="1150">
+      <c r="A1150" t="inlineStr">
+        <is>
+          <t>14,Apr</t>
+        </is>
+      </c>
+      <c r="B1150" t="inlineStr">
+        <is>
+          <t>MANGLAM  KUMAR</t>
+        </is>
+      </c>
+      <c r="C1150" t="inlineStr">
+        <is>
+          <t>AMRESH KUMAR</t>
+        </is>
+      </c>
+      <c r="D1150" t="inlineStr">
+        <is>
+          <t>RUPA KUMARI</t>
+        </is>
+      </c>
+      <c r="E1150" t="inlineStr">
+        <is>
+          <t>IX</t>
+        </is>
+      </c>
+      <c r="F1150" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Birthday Data Master.xlsx
+++ b/Birthday Data Master.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1150"/>
+  <dimension ref="A1:F1160"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.6" customWidth="1" min="1" max="1"/>
@@ -37225,6 +37225,326 @@
         </is>
       </c>
     </row>
+    <row r="1151">
+      <c r="A1151" t="inlineStr">
+        <is>
+          <t>15,Apr</t>
+        </is>
+      </c>
+      <c r="B1151" t="inlineStr">
+        <is>
+          <t>Aliya Mahboob</t>
+        </is>
+      </c>
+      <c r="C1151" t="inlineStr">
+        <is>
+          <t>MD Mahboob Alam</t>
+        </is>
+      </c>
+      <c r="D1151" t="inlineStr">
+        <is>
+          <t>Shabana Khatoon</t>
+        </is>
+      </c>
+      <c r="E1151" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F1151" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="1152">
+      <c r="A1152" t="inlineStr">
+        <is>
+          <t>15,Apr</t>
+        </is>
+      </c>
+      <c r="B1152" t="inlineStr">
+        <is>
+          <t>Mukul kumar</t>
+        </is>
+      </c>
+      <c r="C1152" t="inlineStr">
+        <is>
+          <t>Abhishek Kumar</t>
+        </is>
+      </c>
+      <c r="D1152" t="inlineStr">
+        <is>
+          <t>kajal Kumari</t>
+        </is>
+      </c>
+      <c r="E1152" t="inlineStr">
+        <is>
+          <t>IV</t>
+        </is>
+      </c>
+      <c r="F1152" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="1153">
+      <c r="A1153" t="inlineStr">
+        <is>
+          <t>15,Apr</t>
+        </is>
+      </c>
+      <c r="B1153" t="inlineStr">
+        <is>
+          <t>ARSH AHMADI</t>
+        </is>
+      </c>
+      <c r="C1153" t="inlineStr">
+        <is>
+          <t>AHMAD IFTEKHAR AHMADI</t>
+        </is>
+      </c>
+      <c r="D1153" t="inlineStr">
+        <is>
+          <t>NOOR SHABA</t>
+        </is>
+      </c>
+      <c r="E1153" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F1153" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="1154">
+      <c r="A1154" t="inlineStr">
+        <is>
+          <t>15,Apr</t>
+        </is>
+      </c>
+      <c r="B1154" t="inlineStr">
+        <is>
+          <t>ANANT RAJ</t>
+        </is>
+      </c>
+      <c r="C1154" t="inlineStr">
+        <is>
+          <t>RAVI SHANKAR KUMAR</t>
+        </is>
+      </c>
+      <c r="D1154" t="inlineStr">
+        <is>
+          <t>BEAUTY KUMARI</t>
+        </is>
+      </c>
+      <c r="E1154" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="F1154" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="1155">
+      <c r="A1155" t="inlineStr">
+        <is>
+          <t>15,Apr</t>
+        </is>
+      </c>
+      <c r="B1155" t="inlineStr">
+        <is>
+          <t>PRINCE KUMAR</t>
+        </is>
+      </c>
+      <c r="C1155" t="inlineStr">
+        <is>
+          <t>DINESH KUMAR</t>
+        </is>
+      </c>
+      <c r="D1155" t="inlineStr">
+        <is>
+          <t>URMILA DEVI</t>
+        </is>
+      </c>
+      <c r="E1155" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F1155" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="1156">
+      <c r="A1156" t="inlineStr">
+        <is>
+          <t>15,Apr</t>
+        </is>
+      </c>
+      <c r="B1156" t="inlineStr">
+        <is>
+          <t>Priyanshu Raj</t>
+        </is>
+      </c>
+      <c r="C1156" t="inlineStr">
+        <is>
+          <t>Chandan Kumar</t>
+        </is>
+      </c>
+      <c r="D1156" t="inlineStr">
+        <is>
+          <t>Smita Verma</t>
+        </is>
+      </c>
+      <c r="E1156" t="inlineStr">
+        <is>
+          <t>IX</t>
+        </is>
+      </c>
+      <c r="F1156" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="1157">
+      <c r="A1157" t="inlineStr">
+        <is>
+          <t>15,Apr</t>
+        </is>
+      </c>
+      <c r="B1157" t="inlineStr">
+        <is>
+          <t>Santanu Kumar</t>
+        </is>
+      </c>
+      <c r="C1157" t="inlineStr">
+        <is>
+          <t>Ravindra Kumar</t>
+        </is>
+      </c>
+      <c r="D1157" t="inlineStr">
+        <is>
+          <t>Bibha Kumari</t>
+        </is>
+      </c>
+      <c r="E1157" t="inlineStr">
+        <is>
+          <t>VIII</t>
+        </is>
+      </c>
+      <c r="F1157" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="1158">
+      <c r="A1158" t="inlineStr">
+        <is>
+          <t>15,Apr</t>
+        </is>
+      </c>
+      <c r="B1158" t="inlineStr">
+        <is>
+          <t>SHRISHTI KUMARI</t>
+        </is>
+      </c>
+      <c r="C1158" t="inlineStr">
+        <is>
+          <t>JYOTI KANT KUMAR</t>
+        </is>
+      </c>
+      <c r="D1158" t="inlineStr">
+        <is>
+          <t>PRIYANKA KUMARI</t>
+        </is>
+      </c>
+      <c r="E1158" t="inlineStr">
+        <is>
+          <t>VII</t>
+        </is>
+      </c>
+      <c r="F1158" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="1159">
+      <c r="A1159" t="inlineStr">
+        <is>
+          <t>15,Apr</t>
+        </is>
+      </c>
+      <c r="B1159" t="inlineStr">
+        <is>
+          <t>NITYA KUMARI</t>
+        </is>
+      </c>
+      <c r="C1159" t="inlineStr">
+        <is>
+          <t>VIJAY KUMAR</t>
+        </is>
+      </c>
+      <c r="D1159" t="inlineStr">
+        <is>
+          <t>KAJAL KUMARI</t>
+        </is>
+      </c>
+      <c r="E1159" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="F1159" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="1160">
+      <c r="A1160" t="inlineStr">
+        <is>
+          <t>15,Apr</t>
+        </is>
+      </c>
+      <c r="B1160" t="inlineStr">
+        <is>
+          <t>ANANYA</t>
+        </is>
+      </c>
+      <c r="C1160" t="inlineStr">
+        <is>
+          <t>RANJEET KUMAR</t>
+        </is>
+      </c>
+      <c r="D1160" t="inlineStr">
+        <is>
+          <t>SARITA KUMARI</t>
+        </is>
+      </c>
+      <c r="E1160" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="F1160" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Birthday Data Master.xlsx
+++ b/Birthday Data Master.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1160"/>
+  <dimension ref="A1:F1161"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.6" customWidth="1" min="1" max="1"/>
@@ -37545,6 +37545,38 @@
         </is>
       </c>
     </row>
+    <row r="1161">
+      <c r="A1161" t="inlineStr">
+        <is>
+          <t>16,Apr</t>
+        </is>
+      </c>
+      <c r="B1161" t="inlineStr">
+        <is>
+          <t>Rajnish kumar</t>
+        </is>
+      </c>
+      <c r="C1161" t="inlineStr">
+        <is>
+          <t>Ravi Ranjan Kumar</t>
+        </is>
+      </c>
+      <c r="D1161" t="inlineStr">
+        <is>
+          <t>Nikki Kumari</t>
+        </is>
+      </c>
+      <c r="E1161" t="inlineStr">
+        <is>
+          <t>VIII</t>
+        </is>
+      </c>
+      <c r="F1161" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Birthday Data Master.xlsx
+++ b/Birthday Data Master.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1161"/>
+  <dimension ref="A1:F1163"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.6" customWidth="1" min="1" max="1"/>
@@ -37577,6 +37577,70 @@
         </is>
       </c>
     </row>
+    <row r="1162">
+      <c r="A1162" t="inlineStr">
+        <is>
+          <t>18,Apr</t>
+        </is>
+      </c>
+      <c r="B1162" t="inlineStr">
+        <is>
+          <t>SIMRAN KUMARI</t>
+        </is>
+      </c>
+      <c r="C1162" t="inlineStr">
+        <is>
+          <t>SHASHI RANJAN KUMAR</t>
+        </is>
+      </c>
+      <c r="D1162" t="inlineStr">
+        <is>
+          <t>PRATIMA KUMARI</t>
+        </is>
+      </c>
+      <c r="E1162" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F1162" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="1163">
+      <c r="A1163" t="inlineStr">
+        <is>
+          <t>18,Apr</t>
+        </is>
+      </c>
+      <c r="B1163" t="inlineStr">
+        <is>
+          <t>ISHIKA KUMARI</t>
+        </is>
+      </c>
+      <c r="C1163" t="inlineStr">
+        <is>
+          <t>MUKTESH KUMAR</t>
+        </is>
+      </c>
+      <c r="D1163" t="inlineStr">
+        <is>
+          <t>KHUSHBOO KUMARI</t>
+        </is>
+      </c>
+      <c r="E1163" t="inlineStr">
+        <is>
+          <t>IV</t>
+        </is>
+      </c>
+      <c r="F1163" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Birthday Data Master.xlsx
+++ b/Birthday Data Master.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1163"/>
+  <dimension ref="A1:F1171"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.6" customWidth="1" min="1" max="1"/>
@@ -37641,6 +37641,262 @@
         </is>
       </c>
     </row>
+    <row r="1164">
+      <c r="A1164" t="inlineStr">
+        <is>
+          <t>19,Apr</t>
+        </is>
+      </c>
+      <c r="B1164" t="inlineStr">
+        <is>
+          <t>SHIVAM KUMAR</t>
+        </is>
+      </c>
+      <c r="C1164" t="inlineStr">
+        <is>
+          <t>SARUN KUMAR</t>
+        </is>
+      </c>
+      <c r="D1164" t="inlineStr">
+        <is>
+          <t>SONI KUMARI</t>
+        </is>
+      </c>
+      <c r="E1164" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F1164" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="1165">
+      <c r="A1165" t="inlineStr">
+        <is>
+          <t>19,Apr</t>
+        </is>
+      </c>
+      <c r="B1165" t="inlineStr">
+        <is>
+          <t>KASHIF EHRAAN</t>
+        </is>
+      </c>
+      <c r="C1165" t="inlineStr">
+        <is>
+          <t>MD EQUBAL ALAM</t>
+        </is>
+      </c>
+      <c r="D1165" t="inlineStr">
+        <is>
+          <t>MUSSARAT NAAZ</t>
+        </is>
+      </c>
+      <c r="E1165" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="F1165" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="1166">
+      <c r="A1166" t="inlineStr">
+        <is>
+          <t>19,Apr</t>
+        </is>
+      </c>
+      <c r="B1166" t="inlineStr">
+        <is>
+          <t>PUSHKER KUMAR</t>
+        </is>
+      </c>
+      <c r="C1166" t="inlineStr">
+        <is>
+          <t>Vikash Kumar</t>
+        </is>
+      </c>
+      <c r="D1166" t="inlineStr">
+        <is>
+          <t>Jhunni Devi</t>
+        </is>
+      </c>
+      <c r="E1166" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="F1166" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="1167">
+      <c r="A1167" t="inlineStr">
+        <is>
+          <t>19,Apr</t>
+        </is>
+      </c>
+      <c r="B1167" t="inlineStr">
+        <is>
+          <t>SRI HARI  OM</t>
+        </is>
+      </c>
+      <c r="C1167" t="inlineStr">
+        <is>
+          <t>CHANDRA SHEKHAR AZAD</t>
+        </is>
+      </c>
+      <c r="D1167" t="inlineStr">
+        <is>
+          <t>GURIYA KUMARI</t>
+        </is>
+      </c>
+      <c r="E1167" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="F1167" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="1168">
+      <c r="A1168" t="inlineStr">
+        <is>
+          <t>19,Apr</t>
+        </is>
+      </c>
+      <c r="B1168" t="inlineStr">
+        <is>
+          <t>Vidya Vani</t>
+        </is>
+      </c>
+      <c r="C1168" t="inlineStr">
+        <is>
+          <t>Ranjan Kumar</t>
+        </is>
+      </c>
+      <c r="D1168" t="inlineStr">
+        <is>
+          <t>Pinki Kumari</t>
+        </is>
+      </c>
+      <c r="E1168" t="inlineStr">
+        <is>
+          <t>VIII</t>
+        </is>
+      </c>
+      <c r="F1168" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="1169">
+      <c r="A1169" t="inlineStr">
+        <is>
+          <t>19,Apr</t>
+        </is>
+      </c>
+      <c r="B1169" t="inlineStr">
+        <is>
+          <t>RAUNAK  KUMAR</t>
+        </is>
+      </c>
+      <c r="C1169" t="inlineStr">
+        <is>
+          <t>RAKESH KUMAR</t>
+        </is>
+      </c>
+      <c r="D1169" t="inlineStr">
+        <is>
+          <t>BANTI DEVI SHARMA</t>
+        </is>
+      </c>
+      <c r="E1169" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="F1169" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="1170">
+      <c r="A1170" t="inlineStr">
+        <is>
+          <t>19,Apr</t>
+        </is>
+      </c>
+      <c r="B1170" t="inlineStr">
+        <is>
+          <t>Pratiyush Kumar</t>
+        </is>
+      </c>
+      <c r="C1170" t="inlineStr">
+        <is>
+          <t>Pankaj Kumar</t>
+        </is>
+      </c>
+      <c r="D1170" t="inlineStr">
+        <is>
+          <t>Smita Kumari</t>
+        </is>
+      </c>
+      <c r="E1170" t="inlineStr">
+        <is>
+          <t>VIII</t>
+        </is>
+      </c>
+      <c r="F1170" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="1171">
+      <c r="A1171" t="inlineStr">
+        <is>
+          <t>19,Apr</t>
+        </is>
+      </c>
+      <c r="B1171" t="inlineStr">
+        <is>
+          <t>LAVANYA PRAKASH</t>
+        </is>
+      </c>
+      <c r="C1171" t="inlineStr">
+        <is>
+          <t>PREM PRAKASH</t>
+        </is>
+      </c>
+      <c r="D1171" t="inlineStr">
+        <is>
+          <t>LAXMI KUMARI GUPTA</t>
+        </is>
+      </c>
+      <c r="E1171" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F1171" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Birthday Data Master.xlsx
+++ b/Birthday Data Master.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1171"/>
+  <dimension ref="A1:F1175"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.6" customWidth="1" min="1" max="1"/>
@@ -37897,6 +37897,134 @@
         </is>
       </c>
     </row>
+    <row r="1172">
+      <c r="A1172" t="inlineStr">
+        <is>
+          <t>20,Apr</t>
+        </is>
+      </c>
+      <c r="B1172" t="inlineStr">
+        <is>
+          <t>Punya Anand</t>
+        </is>
+      </c>
+      <c r="C1172" t="inlineStr">
+        <is>
+          <t>Shashi Bhushan</t>
+        </is>
+      </c>
+      <c r="D1172" t="inlineStr">
+        <is>
+          <t>Rita Sharma</t>
+        </is>
+      </c>
+      <c r="E1172" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F1172" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="1173">
+      <c r="A1173" t="inlineStr">
+        <is>
+          <t>20,Apr</t>
+        </is>
+      </c>
+      <c r="B1173" t="inlineStr">
+        <is>
+          <t>AISHRI SINGH</t>
+        </is>
+      </c>
+      <c r="C1173" t="inlineStr">
+        <is>
+          <t>BIRMANI SINGH</t>
+        </is>
+      </c>
+      <c r="D1173" t="inlineStr">
+        <is>
+          <t>MAMTA SINGH</t>
+        </is>
+      </c>
+      <c r="E1173" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F1173" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="1174">
+      <c r="A1174" t="inlineStr">
+        <is>
+          <t>20,Apr</t>
+        </is>
+      </c>
+      <c r="B1174" t="inlineStr">
+        <is>
+          <t>Srishti Kumari</t>
+        </is>
+      </c>
+      <c r="C1174" t="inlineStr">
+        <is>
+          <t>Shashikant Kumar</t>
+        </is>
+      </c>
+      <c r="D1174" t="inlineStr">
+        <is>
+          <t>Gyanti Devi</t>
+        </is>
+      </c>
+      <c r="E1174" t="inlineStr">
+        <is>
+          <t>IX</t>
+        </is>
+      </c>
+      <c r="F1174" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="1175">
+      <c r="A1175" t="inlineStr">
+        <is>
+          <t>20,Apr</t>
+        </is>
+      </c>
+      <c r="B1175" t="inlineStr">
+        <is>
+          <t>Anushka Kumari</t>
+        </is>
+      </c>
+      <c r="C1175" t="inlineStr">
+        <is>
+          <t>Sumant Kumar</t>
+        </is>
+      </c>
+      <c r="D1175" t="inlineStr">
+        <is>
+          <t>Navjoyti Kumari</t>
+        </is>
+      </c>
+      <c r="E1175" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F1175" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Birthday Data Master.xlsx
+++ b/Birthday Data Master.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1175"/>
+  <dimension ref="A1:F1178"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.6" customWidth="1" min="1" max="1"/>
@@ -38025,6 +38025,102 @@
         </is>
       </c>
     </row>
+    <row r="1176">
+      <c r="A1176" t="inlineStr">
+        <is>
+          <t>21,Apr</t>
+        </is>
+      </c>
+      <c r="B1176" t="inlineStr">
+        <is>
+          <t>ANANYA VAISHNAVI SHREE</t>
+        </is>
+      </c>
+      <c r="C1176" t="inlineStr">
+        <is>
+          <t>MANOJ KUMAR SINHA</t>
+        </is>
+      </c>
+      <c r="D1176" t="inlineStr">
+        <is>
+          <t>HEMANTI SINHA</t>
+        </is>
+      </c>
+      <c r="E1176" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="F1176" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="1177">
+      <c r="A1177" t="inlineStr">
+        <is>
+          <t>21,Apr</t>
+        </is>
+      </c>
+      <c r="B1177" t="inlineStr">
+        <is>
+          <t>Shivansh Singh</t>
+        </is>
+      </c>
+      <c r="C1177" t="inlineStr">
+        <is>
+          <t>Rahul Kumar</t>
+        </is>
+      </c>
+      <c r="D1177" t="inlineStr">
+        <is>
+          <t>Rekha Singh</t>
+        </is>
+      </c>
+      <c r="E1177" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="F1177" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="1178">
+      <c r="A1178" t="inlineStr">
+        <is>
+          <t>21,Apr</t>
+        </is>
+      </c>
+      <c r="B1178" t="inlineStr">
+        <is>
+          <t>ANIRUDH KUMAR</t>
+        </is>
+      </c>
+      <c r="C1178" t="inlineStr">
+        <is>
+          <t>SUNIL KUMAR</t>
+        </is>
+      </c>
+      <c r="D1178" t="inlineStr">
+        <is>
+          <t>SONI DEVI</t>
+        </is>
+      </c>
+      <c r="E1178" t="inlineStr">
+        <is>
+          <t>IV</t>
+        </is>
+      </c>
+      <c r="F1178" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Birthday Data Master.xlsx
+++ b/Birthday Data Master.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1178"/>
+  <dimension ref="A1:F1180"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.6" customWidth="1" min="1" max="1"/>
@@ -38121,6 +38121,70 @@
         </is>
       </c>
     </row>
+    <row r="1179">
+      <c r="A1179" t="inlineStr">
+        <is>
+          <t>22,Apr</t>
+        </is>
+      </c>
+      <c r="B1179" t="inlineStr">
+        <is>
+          <t>SHIZA SHAHID</t>
+        </is>
+      </c>
+      <c r="C1179" t="inlineStr">
+        <is>
+          <t>SHAHID JAMA</t>
+        </is>
+      </c>
+      <c r="D1179" t="inlineStr">
+        <is>
+          <t>GAZALA SHAHIN</t>
+        </is>
+      </c>
+      <c r="E1179" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="F1179" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="1180">
+      <c r="A1180" t="inlineStr">
+        <is>
+          <t>22,Apr</t>
+        </is>
+      </c>
+      <c r="B1180" t="inlineStr">
+        <is>
+          <t>AYUSH RAJ</t>
+        </is>
+      </c>
+      <c r="C1180" t="inlineStr">
+        <is>
+          <t>BRAJESH KUMAR</t>
+        </is>
+      </c>
+      <c r="D1180" t="inlineStr">
+        <is>
+          <t>PINKI DEVI</t>
+        </is>
+      </c>
+      <c r="E1180" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="F1180" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Birthday Data Master.xlsx
+++ b/Birthday Data Master.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1180"/>
+  <dimension ref="A1:F1193"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.6" customWidth="1" min="1" max="1"/>
@@ -38185,6 +38185,422 @@
         </is>
       </c>
     </row>
+    <row r="1181">
+      <c r="A1181" t="inlineStr">
+        <is>
+          <t>23,Apr</t>
+        </is>
+      </c>
+      <c r="B1181" t="inlineStr">
+        <is>
+          <t>SNEHA  RAJ</t>
+        </is>
+      </c>
+      <c r="C1181" t="inlineStr">
+        <is>
+          <t>KUMAR TRIPURARI</t>
+        </is>
+      </c>
+      <c r="D1181" t="inlineStr">
+        <is>
+          <t>MANORAMA KUMARI</t>
+        </is>
+      </c>
+      <c r="E1181" t="inlineStr">
+        <is>
+          <t>XII</t>
+        </is>
+      </c>
+      <c r="F1181" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1182">
+      <c r="A1182" t="inlineStr">
+        <is>
+          <t>23,Apr</t>
+        </is>
+      </c>
+      <c r="B1182" t="inlineStr">
+        <is>
+          <t>VAISHNAVI KUMARI</t>
+        </is>
+      </c>
+      <c r="C1182" t="inlineStr">
+        <is>
+          <t>SARVESH KUMAR</t>
+        </is>
+      </c>
+      <c r="D1182" t="inlineStr">
+        <is>
+          <t>DEEPA KUMARI</t>
+        </is>
+      </c>
+      <c r="E1182" t="inlineStr">
+        <is>
+          <t>UKG</t>
+        </is>
+      </c>
+      <c r="F1182" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="1183">
+      <c r="A1183" t="inlineStr">
+        <is>
+          <t>23,Apr</t>
+        </is>
+      </c>
+      <c r="B1183" t="inlineStr">
+        <is>
+          <t>ADITYA SHARMA</t>
+        </is>
+      </c>
+      <c r="C1183" t="inlineStr">
+        <is>
+          <t>OM PRAKASH</t>
+        </is>
+      </c>
+      <c r="D1183" t="inlineStr">
+        <is>
+          <t>ANAMIKA KUMARI</t>
+        </is>
+      </c>
+      <c r="E1183" t="inlineStr">
+        <is>
+          <t>IV</t>
+        </is>
+      </c>
+      <c r="F1183" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="1184">
+      <c r="A1184" t="inlineStr">
+        <is>
+          <t>23,Apr</t>
+        </is>
+      </c>
+      <c r="B1184" t="inlineStr">
+        <is>
+          <t>Harish Kumar</t>
+        </is>
+      </c>
+      <c r="C1184" t="inlineStr">
+        <is>
+          <t>Subodh Kumar</t>
+        </is>
+      </c>
+      <c r="D1184" t="inlineStr">
+        <is>
+          <t>Romi Kumari</t>
+        </is>
+      </c>
+      <c r="E1184" t="inlineStr">
+        <is>
+          <t>VIII</t>
+        </is>
+      </c>
+      <c r="F1184" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="1185">
+      <c r="A1185" t="inlineStr">
+        <is>
+          <t>23,Apr</t>
+        </is>
+      </c>
+      <c r="B1185" t="inlineStr">
+        <is>
+          <t>DIVYANSH</t>
+        </is>
+      </c>
+      <c r="C1185" t="inlineStr">
+        <is>
+          <t>SANTOSH KUMAR</t>
+        </is>
+      </c>
+      <c r="D1185" t="inlineStr">
+        <is>
+          <t>RAMBHA</t>
+        </is>
+      </c>
+      <c r="E1185" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="F1185" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="1186">
+      <c r="A1186" t="inlineStr">
+        <is>
+          <t>23,Apr</t>
+        </is>
+      </c>
+      <c r="B1186" t="inlineStr">
+        <is>
+          <t>Yash SHARMA</t>
+        </is>
+      </c>
+      <c r="C1186" t="inlineStr">
+        <is>
+          <t>Rajesh Kumar</t>
+        </is>
+      </c>
+      <c r="D1186" t="inlineStr">
+        <is>
+          <t>Saroj Devi</t>
+        </is>
+      </c>
+      <c r="E1186" t="inlineStr">
+        <is>
+          <t>IX</t>
+        </is>
+      </c>
+      <c r="F1186" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="1187">
+      <c r="A1187" t="inlineStr">
+        <is>
+          <t>23,Apr</t>
+        </is>
+      </c>
+      <c r="B1187" t="inlineStr">
+        <is>
+          <t>Divya</t>
+        </is>
+      </c>
+      <c r="C1187" t="inlineStr">
+        <is>
+          <t>Ramekbal SHARMA</t>
+        </is>
+      </c>
+      <c r="D1187" t="inlineStr">
+        <is>
+          <t>Pummy Devi</t>
+        </is>
+      </c>
+      <c r="E1187" t="inlineStr">
+        <is>
+          <t>IX</t>
+        </is>
+      </c>
+      <c r="F1187" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+    </row>
+    <row r="1188">
+      <c r="A1188" t="inlineStr">
+        <is>
+          <t>23,Apr</t>
+        </is>
+      </c>
+      <c r="B1188" t="inlineStr">
+        <is>
+          <t>PRATYANSH VERMA</t>
+        </is>
+      </c>
+      <c r="C1188" t="inlineStr">
+        <is>
+          <t>RAJESH KUMAR VERMA</t>
+        </is>
+      </c>
+      <c r="D1188" t="inlineStr">
+        <is>
+          <t>ARTI VERMA</t>
+        </is>
+      </c>
+      <c r="E1188" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F1188" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="1189">
+      <c r="A1189" t="inlineStr">
+        <is>
+          <t>24,Apr</t>
+        </is>
+      </c>
+      <c r="B1189" t="inlineStr">
+        <is>
+          <t>MD YASEEN</t>
+        </is>
+      </c>
+      <c r="C1189" t="inlineStr">
+        <is>
+          <t>MD PERWEJ</t>
+        </is>
+      </c>
+      <c r="D1189" t="inlineStr">
+        <is>
+          <t>AFSANA</t>
+        </is>
+      </c>
+      <c r="E1189" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="F1189" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="1190">
+      <c r="A1190" t="inlineStr">
+        <is>
+          <t>24,Apr</t>
+        </is>
+      </c>
+      <c r="B1190" t="inlineStr">
+        <is>
+          <t>SHUBHAM KUMAR</t>
+        </is>
+      </c>
+      <c r="C1190" t="inlineStr">
+        <is>
+          <t>SUBODH KUMAR</t>
+        </is>
+      </c>
+      <c r="D1190" t="inlineStr">
+        <is>
+          <t>PRIYANKA KUMARI</t>
+        </is>
+      </c>
+      <c r="E1190" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="F1190" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="1191">
+      <c r="A1191" t="inlineStr">
+        <is>
+          <t>24,Apr</t>
+        </is>
+      </c>
+      <c r="B1191" t="inlineStr">
+        <is>
+          <t>AKSHAY MOON</t>
+        </is>
+      </c>
+      <c r="C1191" t="inlineStr">
+        <is>
+          <t>RANJAN KUMAR</t>
+        </is>
+      </c>
+      <c r="D1191" t="inlineStr">
+        <is>
+          <t>PRIYANKA KUMARI</t>
+        </is>
+      </c>
+      <c r="E1191" t="inlineStr">
+        <is>
+          <t>VII</t>
+        </is>
+      </c>
+      <c r="F1191" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="1192">
+      <c r="A1192" t="inlineStr">
+        <is>
+          <t>24,Apr</t>
+        </is>
+      </c>
+      <c r="B1192" t="inlineStr">
+        <is>
+          <t>Annu Priya</t>
+        </is>
+      </c>
+      <c r="C1192" t="inlineStr">
+        <is>
+          <t>Ranjeet Kumar</t>
+        </is>
+      </c>
+      <c r="D1192" t="inlineStr">
+        <is>
+          <t>Nitu Devi</t>
+        </is>
+      </c>
+      <c r="E1192" t="inlineStr">
+        <is>
+          <t>VIII</t>
+        </is>
+      </c>
+      <c r="F1192" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="1193">
+      <c r="A1193" t="inlineStr">
+        <is>
+          <t>24,Apr</t>
+        </is>
+      </c>
+      <c r="B1193" t="inlineStr">
+        <is>
+          <t>ANKUSH KUMAR</t>
+        </is>
+      </c>
+      <c r="C1193" t="inlineStr">
+        <is>
+          <t>SANTOSH KUMAR</t>
+        </is>
+      </c>
+      <c r="D1193" t="inlineStr">
+        <is>
+          <t>PUSHPA SINHA</t>
+        </is>
+      </c>
+      <c r="E1193" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="F1193" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Birthday Data Master.xlsx
+++ b/Birthday Data Master.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1193"/>
+  <dimension ref="A1:F1196"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.6" customWidth="1" min="1" max="1"/>
@@ -38601,6 +38601,102 @@
         </is>
       </c>
     </row>
+    <row r="1194">
+      <c r="A1194" t="inlineStr">
+        <is>
+          <t>25,Apr</t>
+        </is>
+      </c>
+      <c r="B1194" t="inlineStr">
+        <is>
+          <t>Komal Kumari</t>
+        </is>
+      </c>
+      <c r="C1194" t="inlineStr">
+        <is>
+          <t>Amit Kumar</t>
+        </is>
+      </c>
+      <c r="D1194" t="inlineStr">
+        <is>
+          <t>Sunita Devi</t>
+        </is>
+      </c>
+      <c r="E1194" t="inlineStr">
+        <is>
+          <t>IX</t>
+        </is>
+      </c>
+      <c r="F1194" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="1195">
+      <c r="A1195" t="inlineStr">
+        <is>
+          <t>25,Apr</t>
+        </is>
+      </c>
+      <c r="B1195" t="inlineStr">
+        <is>
+          <t>Sonali Kumari</t>
+        </is>
+      </c>
+      <c r="C1195" t="inlineStr">
+        <is>
+          <t>Ram Sumiran Sharma</t>
+        </is>
+      </c>
+      <c r="D1195" t="inlineStr">
+        <is>
+          <t>Rubi Devi</t>
+        </is>
+      </c>
+      <c r="E1195" t="inlineStr">
+        <is>
+          <t>IX</t>
+        </is>
+      </c>
+      <c r="F1195" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="1196">
+      <c r="A1196" t="inlineStr">
+        <is>
+          <t>25,Apr</t>
+        </is>
+      </c>
+      <c r="B1196" t="inlineStr">
+        <is>
+          <t>Nupur  Sinha</t>
+        </is>
+      </c>
+      <c r="C1196" t="inlineStr">
+        <is>
+          <t>Prashant Kumar Sinha</t>
+        </is>
+      </c>
+      <c r="D1196" t="inlineStr">
+        <is>
+          <t>Sushma Sinha</t>
+        </is>
+      </c>
+      <c r="E1196" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F1196" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Birthday Data Master.xlsx
+++ b/Birthday Data Master.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1196"/>
+  <dimension ref="A1:F1201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.6" customWidth="1" min="1" max="1"/>
@@ -38697,6 +38697,166 @@
         </is>
       </c>
     </row>
+    <row r="1197">
+      <c r="A1197" t="inlineStr">
+        <is>
+          <t>26,Apr</t>
+        </is>
+      </c>
+      <c r="B1197" t="inlineStr">
+        <is>
+          <t>NEHA KUMARI</t>
+        </is>
+      </c>
+      <c r="C1197" t="inlineStr">
+        <is>
+          <t>PRAVIN KUMAR</t>
+        </is>
+      </c>
+      <c r="D1197" t="inlineStr">
+        <is>
+          <t>SONI DEVI</t>
+        </is>
+      </c>
+      <c r="E1197" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="F1197" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="1198">
+      <c r="A1198" t="inlineStr">
+        <is>
+          <t>26,Apr</t>
+        </is>
+      </c>
+      <c r="B1198" t="inlineStr">
+        <is>
+          <t>SHANVI VERMA</t>
+        </is>
+      </c>
+      <c r="C1198" t="inlineStr">
+        <is>
+          <t>NITISH KUMAR</t>
+        </is>
+      </c>
+      <c r="D1198" t="inlineStr">
+        <is>
+          <t>BIBHA KUMARI</t>
+        </is>
+      </c>
+      <c r="E1198" t="inlineStr">
+        <is>
+          <t>UKG</t>
+        </is>
+      </c>
+      <c r="F1198" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="1199">
+      <c r="A1199" t="inlineStr">
+        <is>
+          <t>26,Apr</t>
+        </is>
+      </c>
+      <c r="B1199" t="inlineStr">
+        <is>
+          <t>SRISHTY SHREE</t>
+        </is>
+      </c>
+      <c r="C1199" t="inlineStr">
+        <is>
+          <t>SADHU VISHWAKARMA</t>
+        </is>
+      </c>
+      <c r="D1199" t="inlineStr">
+        <is>
+          <t>ARUNA KUMARI</t>
+        </is>
+      </c>
+      <c r="E1199" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="F1199" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="1200">
+      <c r="A1200" t="inlineStr">
+        <is>
+          <t>26,Apr</t>
+        </is>
+      </c>
+      <c r="B1200" t="inlineStr">
+        <is>
+          <t>Utkarsh Kumar</t>
+        </is>
+      </c>
+      <c r="C1200" t="inlineStr">
+        <is>
+          <t>Upendra Kumar</t>
+        </is>
+      </c>
+      <c r="D1200" t="inlineStr">
+        <is>
+          <t>Anu Kumari</t>
+        </is>
+      </c>
+      <c r="E1200" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F1200" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="1201">
+      <c r="A1201" t="inlineStr">
+        <is>
+          <t>26,Apr</t>
+        </is>
+      </c>
+      <c r="B1201" t="inlineStr">
+        <is>
+          <t>SHREYA  SHREE</t>
+        </is>
+      </c>
+      <c r="C1201" t="inlineStr">
+        <is>
+          <t>SADHU VISHWAKARMA</t>
+        </is>
+      </c>
+      <c r="D1201" t="inlineStr">
+        <is>
+          <t>ARUNA KUMARI</t>
+        </is>
+      </c>
+      <c r="E1201" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="F1201" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Birthday Data Master.xlsx
+++ b/Birthday Data Master.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1201"/>
+  <dimension ref="A1:F1206"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.6" customWidth="1" min="1" max="1"/>
@@ -38857,6 +38857,166 @@
         </is>
       </c>
     </row>
+    <row r="1202">
+      <c r="A1202" t="inlineStr">
+        <is>
+          <t>27,Apr</t>
+        </is>
+      </c>
+      <c r="B1202" t="inlineStr">
+        <is>
+          <t>Lucky Raj</t>
+        </is>
+      </c>
+      <c r="C1202" t="inlineStr">
+        <is>
+          <t>Ranjay Kumar</t>
+        </is>
+      </c>
+      <c r="D1202" t="inlineStr">
+        <is>
+          <t>Nibha Kumari</t>
+        </is>
+      </c>
+      <c r="E1202" t="inlineStr">
+        <is>
+          <t>IX</t>
+        </is>
+      </c>
+      <c r="F1202" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="1203">
+      <c r="A1203" t="inlineStr">
+        <is>
+          <t>27,Apr</t>
+        </is>
+      </c>
+      <c r="B1203" t="inlineStr">
+        <is>
+          <t>VIJAY SHALINI</t>
+        </is>
+      </c>
+      <c r="C1203" t="inlineStr">
+        <is>
+          <t>RAHUL KUMAR</t>
+        </is>
+      </c>
+      <c r="D1203" t="inlineStr">
+        <is>
+          <t>SHALINI RANJAN</t>
+        </is>
+      </c>
+      <c r="E1203" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="F1203" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="1204">
+      <c r="A1204" t="inlineStr">
+        <is>
+          <t>27,Apr</t>
+        </is>
+      </c>
+      <c r="B1204" t="inlineStr">
+        <is>
+          <t>Ayush Raj</t>
+        </is>
+      </c>
+      <c r="C1204" t="inlineStr">
+        <is>
+          <t>Suresh Kumar</t>
+        </is>
+      </c>
+      <c r="D1204" t="inlineStr">
+        <is>
+          <t>Nibha Devi</t>
+        </is>
+      </c>
+      <c r="E1204" t="inlineStr">
+        <is>
+          <t>VIII</t>
+        </is>
+      </c>
+      <c r="F1204" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="1205">
+      <c r="A1205" t="inlineStr">
+        <is>
+          <t>27,Apr</t>
+        </is>
+      </c>
+      <c r="B1205" t="inlineStr">
+        <is>
+          <t>SURAJ KUMAR</t>
+        </is>
+      </c>
+      <c r="C1205" t="inlineStr">
+        <is>
+          <t>SUNIL KUMAR TIWARI</t>
+        </is>
+      </c>
+      <c r="D1205" t="inlineStr">
+        <is>
+          <t>GUNJAN DEVI</t>
+        </is>
+      </c>
+      <c r="E1205" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F1205" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="1206">
+      <c r="A1206" t="inlineStr">
+        <is>
+          <t>27,Apr</t>
+        </is>
+      </c>
+      <c r="B1206" t="inlineStr">
+        <is>
+          <t>ADITYA PRAKASH</t>
+        </is>
+      </c>
+      <c r="C1206" t="inlineStr">
+        <is>
+          <t>ANJANI PRAKASH</t>
+        </is>
+      </c>
+      <c r="D1206" t="inlineStr">
+        <is>
+          <t>SUDHA KUMARI</t>
+        </is>
+      </c>
+      <c r="E1206" t="inlineStr">
+        <is>
+          <t>UKG</t>
+        </is>
+      </c>
+      <c r="F1206" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Birthday Data Master.xlsx
+++ b/Birthday Data Master.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1206"/>
+  <dimension ref="A1:F1210"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.6" customWidth="1" min="1" max="1"/>
@@ -39017,6 +39017,134 @@
         </is>
       </c>
     </row>
+    <row r="1207">
+      <c r="A1207" t="inlineStr">
+        <is>
+          <t>28,Apr</t>
+        </is>
+      </c>
+      <c r="B1207" t="inlineStr">
+        <is>
+          <t>Kamal  Nayan</t>
+        </is>
+      </c>
+      <c r="C1207" t="inlineStr">
+        <is>
+          <t>Manoranjan Kumar</t>
+        </is>
+      </c>
+      <c r="D1207" t="inlineStr">
+        <is>
+          <t>Bindu Devi</t>
+        </is>
+      </c>
+      <c r="E1207" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F1207" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="1208">
+      <c r="A1208" t="inlineStr">
+        <is>
+          <t>28,Apr</t>
+        </is>
+      </c>
+      <c r="B1208" t="inlineStr">
+        <is>
+          <t>ADITYA   SHARAN</t>
+        </is>
+      </c>
+      <c r="C1208" t="inlineStr">
+        <is>
+          <t>BAIDEHI SHARAN</t>
+        </is>
+      </c>
+      <c r="D1208" t="inlineStr">
+        <is>
+          <t>PRIYANKA KUMARI</t>
+        </is>
+      </c>
+      <c r="E1208" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="F1208" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="1209">
+      <c r="A1209" t="inlineStr">
+        <is>
+          <t>28,Apr</t>
+        </is>
+      </c>
+      <c r="B1209" t="inlineStr">
+        <is>
+          <t>MAHI SHEKHAR</t>
+        </is>
+      </c>
+      <c r="C1209" t="inlineStr">
+        <is>
+          <t>SUDHANSHU SINGH</t>
+        </is>
+      </c>
+      <c r="D1209" t="inlineStr">
+        <is>
+          <t>SUBHASINI KUMARI</t>
+        </is>
+      </c>
+      <c r="E1209" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="F1209" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="1210">
+      <c r="A1210" t="inlineStr">
+        <is>
+          <t>28,Apr</t>
+        </is>
+      </c>
+      <c r="B1210" t="inlineStr">
+        <is>
+          <t>NAVYA MISHRA</t>
+        </is>
+      </c>
+      <c r="C1210" t="inlineStr">
+        <is>
+          <t>DHIRAJ KUMAR</t>
+        </is>
+      </c>
+      <c r="D1210" t="inlineStr">
+        <is>
+          <t>KUMARI NIVEDITA</t>
+        </is>
+      </c>
+      <c r="E1210" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="F1210" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Birthday Data Master.xlsx
+++ b/Birthday Data Master.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1210"/>
+  <dimension ref="A1:F1216"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.6" customWidth="1" min="1" max="1"/>
@@ -39145,6 +39145,198 @@
         </is>
       </c>
     </row>
+    <row r="1211">
+      <c r="A1211" t="inlineStr">
+        <is>
+          <t>29,Apr</t>
+        </is>
+      </c>
+      <c r="B1211" t="inlineStr">
+        <is>
+          <t>ACHINTYA KUMAR</t>
+        </is>
+      </c>
+      <c r="C1211" t="inlineStr">
+        <is>
+          <t>AJIT KUMAR</t>
+        </is>
+      </c>
+      <c r="D1211" t="inlineStr">
+        <is>
+          <t>PINKI GUPTA</t>
+        </is>
+      </c>
+      <c r="E1211" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="F1211" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="1212">
+      <c r="A1212" t="inlineStr">
+        <is>
+          <t>29,Apr</t>
+        </is>
+      </c>
+      <c r="B1212" t="inlineStr">
+        <is>
+          <t>YASH RAJ</t>
+        </is>
+      </c>
+      <c r="C1212" t="inlineStr">
+        <is>
+          <t>ASHOK KUMAR</t>
+        </is>
+      </c>
+      <c r="D1212" t="inlineStr">
+        <is>
+          <t>SANDHYA KUMARI</t>
+        </is>
+      </c>
+      <c r="E1212" t="inlineStr">
+        <is>
+          <t>IX</t>
+        </is>
+      </c>
+      <c r="F1212" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+    </row>
+    <row r="1213">
+      <c r="A1213" t="inlineStr">
+        <is>
+          <t>29,Apr</t>
+        </is>
+      </c>
+      <c r="B1213" t="inlineStr">
+        <is>
+          <t>Shree Bal Krishna Govind</t>
+        </is>
+      </c>
+      <c r="C1213" t="inlineStr">
+        <is>
+          <t>Sanjeet Kumar</t>
+        </is>
+      </c>
+      <c r="D1213" t="inlineStr">
+        <is>
+          <t>Pinki Devi</t>
+        </is>
+      </c>
+      <c r="E1213" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F1213" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="1214">
+      <c r="A1214" t="inlineStr">
+        <is>
+          <t>29,Apr</t>
+        </is>
+      </c>
+      <c r="B1214" t="inlineStr">
+        <is>
+          <t>DEEPU KUMAR</t>
+        </is>
+      </c>
+      <c r="C1214" t="inlineStr">
+        <is>
+          <t>RANJEET KUMAR</t>
+        </is>
+      </c>
+      <c r="D1214" t="inlineStr">
+        <is>
+          <t>SHAKUNTALA KUMARI</t>
+        </is>
+      </c>
+      <c r="E1214" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="F1214" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="1215">
+      <c r="A1215" t="inlineStr">
+        <is>
+          <t>29,Apr</t>
+        </is>
+      </c>
+      <c r="B1215" t="inlineStr">
+        <is>
+          <t>YASHASVI KUMAR</t>
+        </is>
+      </c>
+      <c r="C1215" t="inlineStr">
+        <is>
+          <t>VIVEKANAND</t>
+        </is>
+      </c>
+      <c r="D1215" t="inlineStr">
+        <is>
+          <t>SUSHMITA KUMARI</t>
+        </is>
+      </c>
+      <c r="E1215" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="F1215" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="1216">
+      <c r="A1216" t="inlineStr">
+        <is>
+          <t>29,Apr</t>
+        </is>
+      </c>
+      <c r="B1216" t="inlineStr">
+        <is>
+          <t>AAYU RAJ</t>
+        </is>
+      </c>
+      <c r="C1216" t="inlineStr">
+        <is>
+          <t>BHISHMA NARAYAN SINGH</t>
+        </is>
+      </c>
+      <c r="D1216" t="inlineStr">
+        <is>
+          <t>PRIYANKA DEVI</t>
+        </is>
+      </c>
+      <c r="E1216" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="F1216" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Birthday Data Master.xlsx
+++ b/Birthday Data Master.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1216"/>
+  <dimension ref="A1:F1225"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.6" customWidth="1" min="1" max="1"/>
@@ -39337,6 +39337,294 @@
         </is>
       </c>
     </row>
+    <row r="1217">
+      <c r="A1217" t="inlineStr">
+        <is>
+          <t>01,May</t>
+        </is>
+      </c>
+      <c r="B1217" t="inlineStr">
+        <is>
+          <t>ANANYA KUMARI</t>
+        </is>
+      </c>
+      <c r="C1217" t="inlineStr">
+        <is>
+          <t>SUDHIR KUMAR</t>
+        </is>
+      </c>
+      <c r="D1217" t="inlineStr">
+        <is>
+          <t>KAVITA DEVI</t>
+        </is>
+      </c>
+      <c r="E1217" t="inlineStr">
+        <is>
+          <t>IV</t>
+        </is>
+      </c>
+      <c r="F1217" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="1218">
+      <c r="A1218" t="inlineStr">
+        <is>
+          <t>01,May</t>
+        </is>
+      </c>
+      <c r="B1218" t="inlineStr">
+        <is>
+          <t>SMITA KUMARI</t>
+        </is>
+      </c>
+      <c r="C1218" t="inlineStr">
+        <is>
+          <t>LAKSHMAN PRASAD SINGH</t>
+        </is>
+      </c>
+      <c r="D1218" t="inlineStr">
+        <is>
+          <t>SANJU KUMARI</t>
+        </is>
+      </c>
+      <c r="E1218" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="F1218" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+    </row>
+    <row r="1219">
+      <c r="A1219" t="inlineStr">
+        <is>
+          <t>01,May</t>
+        </is>
+      </c>
+      <c r="B1219" t="inlineStr">
+        <is>
+          <t>Ayushi  Singh</t>
+        </is>
+      </c>
+      <c r="C1219" t="inlineStr">
+        <is>
+          <t>Pankaj Kumar</t>
+        </is>
+      </c>
+      <c r="D1219" t="inlineStr">
+        <is>
+          <t>Mamta Kumari</t>
+        </is>
+      </c>
+      <c r="E1219" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F1219" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="1220">
+      <c r="A1220" t="inlineStr">
+        <is>
+          <t>01,May</t>
+        </is>
+      </c>
+      <c r="B1220" t="inlineStr">
+        <is>
+          <t>Vidya Kumari</t>
+        </is>
+      </c>
+      <c r="C1220" t="inlineStr">
+        <is>
+          <t>Binod Kumar</t>
+        </is>
+      </c>
+      <c r="D1220" t="inlineStr">
+        <is>
+          <t>Kumari Bandana</t>
+        </is>
+      </c>
+      <c r="E1220" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F1220" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="1221">
+      <c r="A1221" t="inlineStr">
+        <is>
+          <t>01,May</t>
+        </is>
+      </c>
+      <c r="B1221" t="inlineStr">
+        <is>
+          <t>SAURABH KUMAR</t>
+        </is>
+      </c>
+      <c r="C1221" t="inlineStr">
+        <is>
+          <t>RANJEET KUMAR</t>
+        </is>
+      </c>
+      <c r="D1221" t="inlineStr">
+        <is>
+          <t>REKHA DEVI</t>
+        </is>
+      </c>
+      <c r="E1221" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="F1221" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="1222">
+      <c r="A1222" t="inlineStr">
+        <is>
+          <t>01,May</t>
+        </is>
+      </c>
+      <c r="B1222" t="inlineStr">
+        <is>
+          <t>Purshottam Kumar</t>
+        </is>
+      </c>
+      <c r="C1222" t="inlineStr">
+        <is>
+          <t>Pramod Kumar</t>
+        </is>
+      </c>
+      <c r="D1222" t="inlineStr">
+        <is>
+          <t>Lalita Kumari</t>
+        </is>
+      </c>
+      <c r="E1222" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F1222" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="1223">
+      <c r="A1223" t="inlineStr">
+        <is>
+          <t>01,May</t>
+        </is>
+      </c>
+      <c r="B1223" t="inlineStr">
+        <is>
+          <t>Aditya Kumar</t>
+        </is>
+      </c>
+      <c r="C1223" t="inlineStr">
+        <is>
+          <t>Sanjay Kumar</t>
+        </is>
+      </c>
+      <c r="D1223" t="inlineStr">
+        <is>
+          <t>Durga Devi</t>
+        </is>
+      </c>
+      <c r="E1223" t="inlineStr">
+        <is>
+          <t>IX</t>
+        </is>
+      </c>
+      <c r="F1223" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="1224">
+      <c r="A1224" t="inlineStr">
+        <is>
+          <t>01,May</t>
+        </is>
+      </c>
+      <c r="B1224" t="inlineStr">
+        <is>
+          <t>GAURAV KUMAR</t>
+        </is>
+      </c>
+      <c r="C1224" t="inlineStr">
+        <is>
+          <t>TEJ NARAYAN DIVAKAR</t>
+        </is>
+      </c>
+      <c r="D1224" t="inlineStr">
+        <is>
+          <t>SANJU DEVI</t>
+        </is>
+      </c>
+      <c r="E1224" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F1224" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="1225">
+      <c r="A1225" t="inlineStr">
+        <is>
+          <t>01,May</t>
+        </is>
+      </c>
+      <c r="B1225" t="inlineStr">
+        <is>
+          <t>ADITYA  KANT</t>
+        </is>
+      </c>
+      <c r="C1225" t="inlineStr">
+        <is>
+          <t>SASHIKANT KUMAR</t>
+        </is>
+      </c>
+      <c r="D1225" t="inlineStr">
+        <is>
+          <t>SUJATA KUMARI</t>
+        </is>
+      </c>
+      <c r="E1225" t="inlineStr">
+        <is>
+          <t>VII</t>
+        </is>
+      </c>
+      <c r="F1225" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Birthday Data Master.xlsx
+++ b/Birthday Data Master.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1225"/>
+  <dimension ref="A1:F1230"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.6" customWidth="1" min="1" max="1"/>
@@ -39625,6 +39625,166 @@
         </is>
       </c>
     </row>
+    <row r="1226">
+      <c r="A1226" t="inlineStr">
+        <is>
+          <t>02,May</t>
+        </is>
+      </c>
+      <c r="B1226" t="inlineStr">
+        <is>
+          <t>PRISHA SHARAN</t>
+        </is>
+      </c>
+      <c r="C1226" t="inlineStr">
+        <is>
+          <t>BAIDEHI SHARAN</t>
+        </is>
+      </c>
+      <c r="D1226" t="inlineStr">
+        <is>
+          <t>PRIYANKA KUMARI</t>
+        </is>
+      </c>
+      <c r="E1226" t="inlineStr">
+        <is>
+          <t>UKG</t>
+        </is>
+      </c>
+      <c r="F1226" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="1227">
+      <c r="A1227" t="inlineStr">
+        <is>
+          <t>02,May</t>
+        </is>
+      </c>
+      <c r="B1227" t="inlineStr">
+        <is>
+          <t>AYUSHI KUMARI</t>
+        </is>
+      </c>
+      <c r="C1227" t="inlineStr">
+        <is>
+          <t>KUNDAN KUMAR</t>
+        </is>
+      </c>
+      <c r="D1227" t="inlineStr">
+        <is>
+          <t>KHUSBOO KUMARI</t>
+        </is>
+      </c>
+      <c r="E1227" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="F1227" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="1228">
+      <c r="A1228" t="inlineStr">
+        <is>
+          <t>02,May</t>
+        </is>
+      </c>
+      <c r="B1228" t="inlineStr">
+        <is>
+          <t>Kumari Raunak</t>
+        </is>
+      </c>
+      <c r="C1228" t="inlineStr">
+        <is>
+          <t>Raju Kumar</t>
+        </is>
+      </c>
+      <c r="D1228" t="inlineStr">
+        <is>
+          <t>Sarju Devi</t>
+        </is>
+      </c>
+      <c r="E1228" t="inlineStr">
+        <is>
+          <t>VIII</t>
+        </is>
+      </c>
+      <c r="F1228" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="1229">
+      <c r="A1229" t="inlineStr">
+        <is>
+          <t>02,May</t>
+        </is>
+      </c>
+      <c r="B1229" t="inlineStr">
+        <is>
+          <t>Aman Raj</t>
+        </is>
+      </c>
+      <c r="C1229" t="inlineStr">
+        <is>
+          <t>Ajit Kumar</t>
+        </is>
+      </c>
+      <c r="D1229" t="inlineStr">
+        <is>
+          <t>Suchitra Devi</t>
+        </is>
+      </c>
+      <c r="E1229" t="inlineStr">
+        <is>
+          <t>VIII</t>
+        </is>
+      </c>
+      <c r="F1229" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="1230">
+      <c r="A1230" t="inlineStr">
+        <is>
+          <t>02,May</t>
+        </is>
+      </c>
+      <c r="B1230" t="inlineStr">
+        <is>
+          <t>UJJWAL KUMAR</t>
+        </is>
+      </c>
+      <c r="C1230" t="inlineStr">
+        <is>
+          <t>NITYANAND PATHAK</t>
+        </is>
+      </c>
+      <c r="D1230" t="inlineStr">
+        <is>
+          <t>PUNITA KUMARI</t>
+        </is>
+      </c>
+      <c r="E1230" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="F1230" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Birthday Data Master.xlsx
+++ b/Birthday Data Master.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1230"/>
+  <dimension ref="A1:F1233"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.6" customWidth="1" min="1" max="1"/>
@@ -39785,6 +39785,102 @@
         </is>
       </c>
     </row>
+    <row r="1231">
+      <c r="A1231" t="inlineStr">
+        <is>
+          <t>03,May</t>
+        </is>
+      </c>
+      <c r="B1231" t="inlineStr">
+        <is>
+          <t>SANKET  RANJAN</t>
+        </is>
+      </c>
+      <c r="C1231" t="inlineStr">
+        <is>
+          <t>AMIT RANJAN</t>
+        </is>
+      </c>
+      <c r="D1231" t="inlineStr">
+        <is>
+          <t>RIMJHIM KUMARI</t>
+        </is>
+      </c>
+      <c r="E1231" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="F1231" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="1232">
+      <c r="A1232" t="inlineStr">
+        <is>
+          <t>03,May</t>
+        </is>
+      </c>
+      <c r="B1232" t="inlineStr">
+        <is>
+          <t>Ezan Alam</t>
+        </is>
+      </c>
+      <c r="C1232" t="inlineStr">
+        <is>
+          <t>Md Mahboob Alam</t>
+        </is>
+      </c>
+      <c r="D1232" t="inlineStr">
+        <is>
+          <t>Shahin Parween</t>
+        </is>
+      </c>
+      <c r="E1232" t="inlineStr">
+        <is>
+          <t>VIII</t>
+        </is>
+      </c>
+      <c r="F1232" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="1233">
+      <c r="A1233" t="inlineStr">
+        <is>
+          <t>03,May</t>
+        </is>
+      </c>
+      <c r="B1233" t="inlineStr">
+        <is>
+          <t>RUPANJALI GAUTAM</t>
+        </is>
+      </c>
+      <c r="C1233" t="inlineStr">
+        <is>
+          <t>KAMALESH KUMAR GAUTAM</t>
+        </is>
+      </c>
+      <c r="D1233" t="inlineStr">
+        <is>
+          <t>SHASHI KALA</t>
+        </is>
+      </c>
+      <c r="E1233" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="F1233" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Birthday Data Master.xlsx
+++ b/Birthday Data Master.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1233"/>
+  <dimension ref="A1:F1237"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.6" customWidth="1" min="1" max="1"/>
@@ -39881,6 +39881,134 @@
         </is>
       </c>
     </row>
+    <row r="1234">
+      <c r="A1234" t="inlineStr">
+        <is>
+          <t>04,May</t>
+        </is>
+      </c>
+      <c r="B1234" t="inlineStr">
+        <is>
+          <t>ABHINAV  SHARMA</t>
+        </is>
+      </c>
+      <c r="C1234" t="inlineStr">
+        <is>
+          <t>PRABHAT KUMAR</t>
+        </is>
+      </c>
+      <c r="D1234" t="inlineStr">
+        <is>
+          <t>ANJULI KUMARI</t>
+        </is>
+      </c>
+      <c r="E1234" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F1234" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="1235">
+      <c r="A1235" t="inlineStr">
+        <is>
+          <t>04,May</t>
+        </is>
+      </c>
+      <c r="B1235" t="inlineStr">
+        <is>
+          <t>Saumya Kumari</t>
+        </is>
+      </c>
+      <c r="C1235" t="inlineStr">
+        <is>
+          <t>Rajesh Kumar</t>
+        </is>
+      </c>
+      <c r="D1235" t="inlineStr">
+        <is>
+          <t>Vinita Kumari</t>
+        </is>
+      </c>
+      <c r="E1235" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F1235" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="1236">
+      <c r="A1236" t="inlineStr">
+        <is>
+          <t>04,May</t>
+        </is>
+      </c>
+      <c r="B1236" t="inlineStr">
+        <is>
+          <t>Anupam  Kumari</t>
+        </is>
+      </c>
+      <c r="C1236" t="inlineStr">
+        <is>
+          <t>Vinay kumar Singh</t>
+        </is>
+      </c>
+      <c r="D1236" t="inlineStr">
+        <is>
+          <t>Anju Kumari</t>
+        </is>
+      </c>
+      <c r="E1236" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F1236" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="1237">
+      <c r="A1237" t="inlineStr">
+        <is>
+          <t>04,May</t>
+        </is>
+      </c>
+      <c r="B1237" t="inlineStr">
+        <is>
+          <t>PURNIMA KUMARI</t>
+        </is>
+      </c>
+      <c r="C1237" t="inlineStr">
+        <is>
+          <t>RANJAN KUMAR</t>
+        </is>
+      </c>
+      <c r="D1237" t="inlineStr">
+        <is>
+          <t>PINKY KUMARI</t>
+        </is>
+      </c>
+      <c r="E1237" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="F1237" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Birthday Data Master.xlsx
+++ b/Birthday Data Master.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1237"/>
+  <dimension ref="A1:F1247"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.6" customWidth="1" min="1" max="1"/>
@@ -40009,6 +40009,326 @@
         </is>
       </c>
     </row>
+    <row r="1238">
+      <c r="A1238" t="inlineStr">
+        <is>
+          <t>05,May</t>
+        </is>
+      </c>
+      <c r="B1238" t="inlineStr">
+        <is>
+          <t>ANNU KUMARI</t>
+        </is>
+      </c>
+      <c r="C1238" t="inlineStr">
+        <is>
+          <t>AJAY KUMAR</t>
+        </is>
+      </c>
+      <c r="D1238" t="inlineStr">
+        <is>
+          <t>MUNNI DEVI</t>
+        </is>
+      </c>
+      <c r="E1238" t="inlineStr">
+        <is>
+          <t>XII</t>
+        </is>
+      </c>
+      <c r="F1238" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1239">
+      <c r="A1239" t="inlineStr">
+        <is>
+          <t>05,May</t>
+        </is>
+      </c>
+      <c r="B1239" t="inlineStr">
+        <is>
+          <t>ANKUSH KUMAR</t>
+        </is>
+      </c>
+      <c r="C1239" t="inlineStr">
+        <is>
+          <t>SHAMBHU KUMAR</t>
+        </is>
+      </c>
+      <c r="D1239" t="inlineStr">
+        <is>
+          <t>BEENA KUMARI</t>
+        </is>
+      </c>
+      <c r="E1239" t="inlineStr">
+        <is>
+          <t>UKG</t>
+        </is>
+      </c>
+      <c r="F1239" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="1240">
+      <c r="A1240" t="inlineStr">
+        <is>
+          <t>05,May</t>
+        </is>
+      </c>
+      <c r="B1240" t="inlineStr">
+        <is>
+          <t>PIYUSH KUMAR</t>
+        </is>
+      </c>
+      <c r="C1240" t="inlineStr">
+        <is>
+          <t>PAPPU SHARMA</t>
+        </is>
+      </c>
+      <c r="D1240" t="inlineStr">
+        <is>
+          <t>JYOTI DEVI</t>
+        </is>
+      </c>
+      <c r="E1240" t="inlineStr">
+        <is>
+          <t>VII</t>
+        </is>
+      </c>
+      <c r="F1240" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="1241">
+      <c r="A1241" t="inlineStr">
+        <is>
+          <t>05,May</t>
+        </is>
+      </c>
+      <c r="B1241" t="inlineStr">
+        <is>
+          <t>VARSHA KUMARI</t>
+        </is>
+      </c>
+      <c r="C1241" t="inlineStr">
+        <is>
+          <t>ASHOK KUMAR</t>
+        </is>
+      </c>
+      <c r="D1241" t="inlineStr">
+        <is>
+          <t>SANJU DEVI</t>
+        </is>
+      </c>
+      <c r="E1241" t="inlineStr">
+        <is>
+          <t>IX</t>
+        </is>
+      </c>
+      <c r="F1241" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="1242">
+      <c r="A1242" t="inlineStr">
+        <is>
+          <t>05,May</t>
+        </is>
+      </c>
+      <c r="B1242" t="inlineStr">
+        <is>
+          <t>Shashi Ranjan</t>
+        </is>
+      </c>
+      <c r="C1242" t="inlineStr">
+        <is>
+          <t>Bablu Kumar</t>
+        </is>
+      </c>
+      <c r="D1242" t="inlineStr">
+        <is>
+          <t>Anju Kumari</t>
+        </is>
+      </c>
+      <c r="E1242" t="inlineStr">
+        <is>
+          <t>IX</t>
+        </is>
+      </c>
+      <c r="F1242" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="1243">
+      <c r="A1243" t="inlineStr">
+        <is>
+          <t>05,May</t>
+        </is>
+      </c>
+      <c r="B1243" t="inlineStr">
+        <is>
+          <t>NEHA KUMARI</t>
+        </is>
+      </c>
+      <c r="C1243" t="inlineStr">
+        <is>
+          <t>BIJENDRA PRASAD</t>
+        </is>
+      </c>
+      <c r="D1243" t="inlineStr">
+        <is>
+          <t>ANJU KUMARI</t>
+        </is>
+      </c>
+      <c r="E1243" t="inlineStr">
+        <is>
+          <t>VII</t>
+        </is>
+      </c>
+      <c r="F1243" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+    </row>
+    <row r="1244">
+      <c r="A1244" t="inlineStr">
+        <is>
+          <t>05,May</t>
+        </is>
+      </c>
+      <c r="B1244" t="inlineStr">
+        <is>
+          <t>HARSH RAJ</t>
+        </is>
+      </c>
+      <c r="C1244" t="inlineStr">
+        <is>
+          <t>RAJU KUMAR</t>
+        </is>
+      </c>
+      <c r="D1244" t="inlineStr">
+        <is>
+          <t>SANJU DEVI</t>
+        </is>
+      </c>
+      <c r="E1244" t="inlineStr">
+        <is>
+          <t>VII</t>
+        </is>
+      </c>
+      <c r="F1244" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="1245">
+      <c r="A1245" t="inlineStr">
+        <is>
+          <t>05,May</t>
+        </is>
+      </c>
+      <c r="B1245" t="inlineStr">
+        <is>
+          <t>VAIBHAV RAJ</t>
+        </is>
+      </c>
+      <c r="C1245" t="inlineStr">
+        <is>
+          <t>NAWLESH KUMAR</t>
+        </is>
+      </c>
+      <c r="D1245" t="inlineStr">
+        <is>
+          <t>NISHU DEVI</t>
+        </is>
+      </c>
+      <c r="E1245" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="F1245" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="1246">
+      <c r="A1246" t="inlineStr">
+        <is>
+          <t>05,May</t>
+        </is>
+      </c>
+      <c r="B1246" t="inlineStr">
+        <is>
+          <t>RICHA KUMARI</t>
+        </is>
+      </c>
+      <c r="C1246" t="inlineStr">
+        <is>
+          <t>NAWLESH KUMAR</t>
+        </is>
+      </c>
+      <c r="D1246" t="inlineStr">
+        <is>
+          <t>NISHU DEVI</t>
+        </is>
+      </c>
+      <c r="E1246" t="inlineStr">
+        <is>
+          <t>IV</t>
+        </is>
+      </c>
+      <c r="F1246" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="1247">
+      <c r="A1247" t="inlineStr">
+        <is>
+          <t>05,May</t>
+        </is>
+      </c>
+      <c r="B1247" t="inlineStr">
+        <is>
+          <t>Harsh Raj</t>
+        </is>
+      </c>
+      <c r="C1247" t="inlineStr">
+        <is>
+          <t>Dinesh Prasad</t>
+        </is>
+      </c>
+      <c r="D1247" t="inlineStr">
+        <is>
+          <t>Arti Kumari</t>
+        </is>
+      </c>
+      <c r="E1247" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F1247" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Birthday Data Master.xlsx
+++ b/Birthday Data Master.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1247"/>
+  <dimension ref="A1:F1255"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.6" customWidth="1" min="1" max="1"/>
@@ -40329,6 +40329,262 @@
         </is>
       </c>
     </row>
+    <row r="1248">
+      <c r="A1248" t="inlineStr">
+        <is>
+          <t>06,May</t>
+        </is>
+      </c>
+      <c r="B1248" t="inlineStr">
+        <is>
+          <t>NISHANT KUMAR</t>
+        </is>
+      </c>
+      <c r="C1248" t="inlineStr">
+        <is>
+          <t>AJAY KUMAR</t>
+        </is>
+      </c>
+      <c r="D1248" t="inlineStr">
+        <is>
+          <t>SONIA RANI</t>
+        </is>
+      </c>
+      <c r="E1248" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="F1248" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="1249">
+      <c r="A1249" t="inlineStr">
+        <is>
+          <t>06,May</t>
+        </is>
+      </c>
+      <c r="B1249" t="inlineStr">
+        <is>
+          <t>Akriti Kumari</t>
+        </is>
+      </c>
+      <c r="C1249" t="inlineStr">
+        <is>
+          <t>Ajesh Pd.Pal</t>
+        </is>
+      </c>
+      <c r="D1249" t="inlineStr">
+        <is>
+          <t>Sanju Kumari</t>
+        </is>
+      </c>
+      <c r="E1249" t="inlineStr">
+        <is>
+          <t>IX</t>
+        </is>
+      </c>
+      <c r="F1249" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="1250">
+      <c r="A1250" t="inlineStr">
+        <is>
+          <t>06,May</t>
+        </is>
+      </c>
+      <c r="B1250" t="inlineStr">
+        <is>
+          <t>Sri Priam</t>
+        </is>
+      </c>
+      <c r="C1250" t="inlineStr">
+        <is>
+          <t>Sukesh Ranjan</t>
+        </is>
+      </c>
+      <c r="D1250" t="inlineStr">
+        <is>
+          <t>Pummy Kumari</t>
+        </is>
+      </c>
+      <c r="E1250" t="inlineStr">
+        <is>
+          <t>IX</t>
+        </is>
+      </c>
+      <c r="F1250" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="1251">
+      <c r="A1251" t="inlineStr">
+        <is>
+          <t>06,May</t>
+        </is>
+      </c>
+      <c r="B1251" t="inlineStr">
+        <is>
+          <t>Prabhat Kumar Shahi</t>
+        </is>
+      </c>
+      <c r="C1251" t="inlineStr">
+        <is>
+          <t>Saket Prasad Shahi</t>
+        </is>
+      </c>
+      <c r="D1251" t="inlineStr">
+        <is>
+          <t>Ranju Shahi</t>
+        </is>
+      </c>
+      <c r="E1251" t="inlineStr">
+        <is>
+          <t>IX</t>
+        </is>
+      </c>
+      <c r="F1251" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="1252">
+      <c r="A1252" t="inlineStr">
+        <is>
+          <t>06,May</t>
+        </is>
+      </c>
+      <c r="B1252" t="inlineStr">
+        <is>
+          <t>Ritik Ranjan</t>
+        </is>
+      </c>
+      <c r="C1252" t="inlineStr">
+        <is>
+          <t>Rajeev Ranjan kumar</t>
+        </is>
+      </c>
+      <c r="D1252" t="inlineStr">
+        <is>
+          <t>Gudiya Kumari</t>
+        </is>
+      </c>
+      <c r="E1252" t="inlineStr">
+        <is>
+          <t>VIII</t>
+        </is>
+      </c>
+      <c r="F1252" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="1253">
+      <c r="A1253" t="inlineStr">
+        <is>
+          <t>06,May</t>
+        </is>
+      </c>
+      <c r="B1253" t="inlineStr">
+        <is>
+          <t>MD FAIZAL ANSARI</t>
+        </is>
+      </c>
+      <c r="C1253" t="inlineStr">
+        <is>
+          <t>MD FIROZ ANSARI</t>
+        </is>
+      </c>
+      <c r="D1253" t="inlineStr">
+        <is>
+          <t>CHANDNI PERWEEN</t>
+        </is>
+      </c>
+      <c r="E1253" t="inlineStr">
+        <is>
+          <t>UKG</t>
+        </is>
+      </c>
+      <c r="F1253" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="1254">
+      <c r="A1254" t="inlineStr">
+        <is>
+          <t>06,May</t>
+        </is>
+      </c>
+      <c r="B1254" t="inlineStr">
+        <is>
+          <t>Simaran Kumari</t>
+        </is>
+      </c>
+      <c r="C1254" t="inlineStr">
+        <is>
+          <t>Brajesh Kumar</t>
+        </is>
+      </c>
+      <c r="D1254" t="inlineStr">
+        <is>
+          <t>Punam Devi</t>
+        </is>
+      </c>
+      <c r="E1254" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F1254" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="1255">
+      <c r="A1255" t="inlineStr">
+        <is>
+          <t>06,May</t>
+        </is>
+      </c>
+      <c r="B1255" t="inlineStr">
+        <is>
+          <t>SAUMYA SHREE</t>
+        </is>
+      </c>
+      <c r="C1255" t="inlineStr">
+        <is>
+          <t>PRASHANT KUMAR</t>
+        </is>
+      </c>
+      <c r="D1255" t="inlineStr">
+        <is>
+          <t>JIYA KUMARI</t>
+        </is>
+      </c>
+      <c r="E1255" t="inlineStr">
+        <is>
+          <t>IV</t>
+        </is>
+      </c>
+      <c r="F1255" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Birthday Data Master.xlsx
+++ b/Birthday Data Master.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1255"/>
+  <dimension ref="A1:F1264"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.6" customWidth="1" min="1" max="1"/>
@@ -40585,6 +40585,294 @@
         </is>
       </c>
     </row>
+    <row r="1256">
+      <c r="A1256" t="inlineStr">
+        <is>
+          <t>07,May</t>
+        </is>
+      </c>
+      <c r="B1256" t="inlineStr">
+        <is>
+          <t>SHAURYA RAJ</t>
+        </is>
+      </c>
+      <c r="C1256" t="inlineStr">
+        <is>
+          <t>LATE AJAY KUMAR</t>
+        </is>
+      </c>
+      <c r="D1256" t="inlineStr">
+        <is>
+          <t>ANITA KUMARI</t>
+        </is>
+      </c>
+      <c r="E1256" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="F1256" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="1257">
+      <c r="A1257" t="inlineStr">
+        <is>
+          <t>07,May</t>
+        </is>
+      </c>
+      <c r="B1257" t="inlineStr">
+        <is>
+          <t>AVYAAN KUMAR</t>
+        </is>
+      </c>
+      <c r="C1257" t="inlineStr">
+        <is>
+          <t>AMBUJ KUMAR</t>
+        </is>
+      </c>
+      <c r="D1257" t="inlineStr">
+        <is>
+          <t>JYOTI KUMARI</t>
+        </is>
+      </c>
+      <c r="E1257" t="inlineStr">
+        <is>
+          <t>LKG</t>
+        </is>
+      </c>
+      <c r="F1257" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="1258">
+      <c r="A1258" t="inlineStr">
+        <is>
+          <t>07,May</t>
+        </is>
+      </c>
+      <c r="B1258" t="inlineStr">
+        <is>
+          <t>Kumari Anamika Sinha</t>
+        </is>
+      </c>
+      <c r="C1258" t="inlineStr">
+        <is>
+          <t>Shailesh Singh</t>
+        </is>
+      </c>
+      <c r="D1258" t="inlineStr">
+        <is>
+          <t>Kumari Amrita Sinha</t>
+        </is>
+      </c>
+      <c r="E1258" t="inlineStr">
+        <is>
+          <t>IX</t>
+        </is>
+      </c>
+      <c r="F1258" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="1259">
+      <c r="A1259" t="inlineStr">
+        <is>
+          <t>07,May</t>
+        </is>
+      </c>
+      <c r="B1259" t="inlineStr">
+        <is>
+          <t>DIVYANSHU KUMAR</t>
+        </is>
+      </c>
+      <c r="C1259" t="inlineStr">
+        <is>
+          <t>DIPAK KUMAR</t>
+        </is>
+      </c>
+      <c r="D1259" t="inlineStr">
+        <is>
+          <t>SANGITA KUMARI</t>
+        </is>
+      </c>
+      <c r="E1259" t="inlineStr">
+        <is>
+          <t>LKG</t>
+        </is>
+      </c>
+      <c r="F1259" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="1260">
+      <c r="A1260" t="inlineStr">
+        <is>
+          <t>07,May</t>
+        </is>
+      </c>
+      <c r="B1260" t="inlineStr">
+        <is>
+          <t>Mehnaj Perween</t>
+        </is>
+      </c>
+      <c r="C1260" t="inlineStr">
+        <is>
+          <t>Md Kaish Ansari</t>
+        </is>
+      </c>
+      <c r="D1260" t="inlineStr">
+        <is>
+          <t>Nazni Perween</t>
+        </is>
+      </c>
+      <c r="E1260" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F1260" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="1261">
+      <c r="A1261" t="inlineStr">
+        <is>
+          <t>07,May</t>
+        </is>
+      </c>
+      <c r="B1261" t="inlineStr">
+        <is>
+          <t>Vrinda Kumari</t>
+        </is>
+      </c>
+      <c r="C1261" t="inlineStr">
+        <is>
+          <t>Gopal Prasad</t>
+        </is>
+      </c>
+      <c r="D1261" t="inlineStr">
+        <is>
+          <t>Sunita Devi</t>
+        </is>
+      </c>
+      <c r="E1261" t="inlineStr">
+        <is>
+          <t>IX</t>
+        </is>
+      </c>
+      <c r="F1261" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="1262">
+      <c r="A1262" t="inlineStr">
+        <is>
+          <t>07,May</t>
+        </is>
+      </c>
+      <c r="B1262" t="inlineStr">
+        <is>
+          <t>SHRISTI SHARMA</t>
+        </is>
+      </c>
+      <c r="C1262" t="inlineStr">
+        <is>
+          <t>SHIV SHANKAR KUMAR</t>
+        </is>
+      </c>
+      <c r="D1262" t="inlineStr">
+        <is>
+          <t>GURIYA KUMARI</t>
+        </is>
+      </c>
+      <c r="E1262" t="inlineStr">
+        <is>
+          <t>UKG</t>
+        </is>
+      </c>
+      <c r="F1262" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="1263">
+      <c r="A1263" t="inlineStr">
+        <is>
+          <t>07,May</t>
+        </is>
+      </c>
+      <c r="B1263" t="inlineStr">
+        <is>
+          <t>ARPIT RAJ</t>
+        </is>
+      </c>
+      <c r="C1263" t="inlineStr">
+        <is>
+          <t>NAVIN KUMAR</t>
+        </is>
+      </c>
+      <c r="D1263" t="inlineStr">
+        <is>
+          <t>SONALI KUMARI</t>
+        </is>
+      </c>
+      <c r="E1263" t="inlineStr">
+        <is>
+          <t>IV</t>
+        </is>
+      </c>
+      <c r="F1263" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="1264">
+      <c r="A1264" t="inlineStr">
+        <is>
+          <t>07,May</t>
+        </is>
+      </c>
+      <c r="B1264" t="inlineStr">
+        <is>
+          <t>Samriddhi Suman</t>
+        </is>
+      </c>
+      <c r="C1264" t="inlineStr">
+        <is>
+          <t>Sanjay Kumar SUMAN</t>
+        </is>
+      </c>
+      <c r="D1264" t="inlineStr">
+        <is>
+          <t>Sushma Saurabh</t>
+        </is>
+      </c>
+      <c r="E1264" t="inlineStr">
+        <is>
+          <t>IX</t>
+        </is>
+      </c>
+      <c r="F1264" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Birthday Data Master.xlsx
+++ b/Birthday Data Master.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1264"/>
+  <dimension ref="A1:F1268"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.6" customWidth="1" min="1" max="1"/>
@@ -40873,6 +40873,134 @@
         </is>
       </c>
     </row>
+    <row r="1265">
+      <c r="A1265" t="inlineStr">
+        <is>
+          <t>08,May</t>
+        </is>
+      </c>
+      <c r="B1265" t="inlineStr">
+        <is>
+          <t>RAM SHARMA</t>
+        </is>
+      </c>
+      <c r="C1265" t="inlineStr">
+        <is>
+          <t>RAKESH KUMAR SHARMA</t>
+        </is>
+      </c>
+      <c r="D1265" t="inlineStr">
+        <is>
+          <t>PAMMI SHARMA</t>
+        </is>
+      </c>
+      <c r="E1265" t="inlineStr">
+        <is>
+          <t>VII</t>
+        </is>
+      </c>
+      <c r="F1265" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="1266">
+      <c r="A1266" t="inlineStr">
+        <is>
+          <t>08,May</t>
+        </is>
+      </c>
+      <c r="B1266" t="inlineStr">
+        <is>
+          <t>SATYAM` KUMAR</t>
+        </is>
+      </c>
+      <c r="C1266" t="inlineStr">
+        <is>
+          <t>SANJAY KUMAR BHARDWAJ</t>
+        </is>
+      </c>
+      <c r="D1266" t="inlineStr">
+        <is>
+          <t>SUNEHA KUMARI</t>
+        </is>
+      </c>
+      <c r="E1266" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="F1266" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="1267">
+      <c r="A1267" t="inlineStr">
+        <is>
+          <t>08,May</t>
+        </is>
+      </c>
+      <c r="B1267" t="inlineStr">
+        <is>
+          <t>Parth Kumar</t>
+        </is>
+      </c>
+      <c r="C1267" t="inlineStr">
+        <is>
+          <t>Ajit Kumar Vats</t>
+        </is>
+      </c>
+      <c r="D1267" t="inlineStr">
+        <is>
+          <t>Renu Devi</t>
+        </is>
+      </c>
+      <c r="E1267" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F1267" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="1268">
+      <c r="A1268" t="inlineStr">
+        <is>
+          <t>08,May</t>
+        </is>
+      </c>
+      <c r="B1268" t="inlineStr">
+        <is>
+          <t>Kritika Sharma</t>
+        </is>
+      </c>
+      <c r="C1268" t="inlineStr">
+        <is>
+          <t>Amit Sharma</t>
+        </is>
+      </c>
+      <c r="D1268" t="inlineStr">
+        <is>
+          <t>Nilam Sharma</t>
+        </is>
+      </c>
+      <c r="E1268" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F1268" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Birthday Data Master.xlsx
+++ b/Birthday Data Master.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1268"/>
+  <dimension ref="A1:F1269"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.6" customWidth="1" min="1" max="1"/>
@@ -41001,6 +41001,38 @@
         </is>
       </c>
     </row>
+    <row r="1269">
+      <c r="A1269" t="inlineStr">
+        <is>
+          <t>09,May</t>
+        </is>
+      </c>
+      <c r="B1269" t="inlineStr">
+        <is>
+          <t>AYUSH KUMAR</t>
+        </is>
+      </c>
+      <c r="C1269" t="inlineStr">
+        <is>
+          <t>PANKAJ KUMAR</t>
+        </is>
+      </c>
+      <c r="D1269" t="inlineStr">
+        <is>
+          <t>RUPA KUMARI</t>
+        </is>
+      </c>
+      <c r="E1269" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F1269" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Birthday Data Master.xlsx
+++ b/Birthday Data Master.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1269"/>
+  <dimension ref="A1:F1273"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.6" customWidth="1" min="1" max="1"/>
@@ -41033,6 +41033,134 @@
         </is>
       </c>
     </row>
+    <row r="1270">
+      <c r="A1270" t="inlineStr">
+        <is>
+          <t>10,May</t>
+        </is>
+      </c>
+      <c r="B1270" t="inlineStr">
+        <is>
+          <t>HIMANSHU KUMAR</t>
+        </is>
+      </c>
+      <c r="C1270" t="inlineStr">
+        <is>
+          <t>RAM PYARE KUMAR</t>
+        </is>
+      </c>
+      <c r="D1270" t="inlineStr">
+        <is>
+          <t>INDU KUMARI</t>
+        </is>
+      </c>
+      <c r="E1270" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="F1270" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="1271">
+      <c r="A1271" t="inlineStr">
+        <is>
+          <t>10,May</t>
+        </is>
+      </c>
+      <c r="B1271" t="inlineStr">
+        <is>
+          <t>UTKARSH KUMAR</t>
+        </is>
+      </c>
+      <c r="C1271" t="inlineStr">
+        <is>
+          <t>VIJAY KUMAR</t>
+        </is>
+      </c>
+      <c r="D1271" t="inlineStr">
+        <is>
+          <t>MONI KUMARI</t>
+        </is>
+      </c>
+      <c r="E1271" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="F1271" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="1272">
+      <c r="A1272" t="inlineStr">
+        <is>
+          <t>10,May</t>
+        </is>
+      </c>
+      <c r="B1272" t="inlineStr">
+        <is>
+          <t>PRIYANSHU RAJ</t>
+        </is>
+      </c>
+      <c r="C1272" t="inlineStr">
+        <is>
+          <t>SUBODH KUMAR</t>
+        </is>
+      </c>
+      <c r="D1272" t="inlineStr">
+        <is>
+          <t>PUJA KUMARI</t>
+        </is>
+      </c>
+      <c r="E1272" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="F1272" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="1273">
+      <c r="A1273" t="inlineStr">
+        <is>
+          <t>10,May</t>
+        </is>
+      </c>
+      <c r="B1273" t="inlineStr">
+        <is>
+          <t>PIYUSH KUMAR</t>
+        </is>
+      </c>
+      <c r="C1273" t="inlineStr">
+        <is>
+          <t>PREM KUMAR</t>
+        </is>
+      </c>
+      <c r="D1273" t="inlineStr">
+        <is>
+          <t>SANGITA KUMARI</t>
+        </is>
+      </c>
+      <c r="E1273" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="F1273" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Birthday Data Master.xlsx
+++ b/Birthday Data Master.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1273"/>
+  <dimension ref="A1:F1277"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.6" customWidth="1" min="1" max="1"/>
@@ -41161,6 +41161,134 @@
         </is>
       </c>
     </row>
+    <row r="1274">
+      <c r="A1274" t="inlineStr">
+        <is>
+          <t>11,May</t>
+        </is>
+      </c>
+      <c r="B1274" t="inlineStr">
+        <is>
+          <t>VISHWAJEET KUMAR</t>
+        </is>
+      </c>
+      <c r="C1274" t="inlineStr">
+        <is>
+          <t>RAMADHIN PRASAD</t>
+        </is>
+      </c>
+      <c r="D1274" t="inlineStr">
+        <is>
+          <t>PINKI DEVI</t>
+        </is>
+      </c>
+      <c r="E1274" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="F1274" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="1275">
+      <c r="A1275" t="inlineStr">
+        <is>
+          <t>11,May</t>
+        </is>
+      </c>
+      <c r="B1275" t="inlineStr">
+        <is>
+          <t>Krishu Goswami</t>
+        </is>
+      </c>
+      <c r="C1275" t="inlineStr">
+        <is>
+          <t>Puran Goswami</t>
+        </is>
+      </c>
+      <c r="D1275" t="inlineStr">
+        <is>
+          <t>Tinki Devi</t>
+        </is>
+      </c>
+      <c r="E1275" t="inlineStr">
+        <is>
+          <t>VIII</t>
+        </is>
+      </c>
+      <c r="F1275" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="1276">
+      <c r="A1276" t="inlineStr">
+        <is>
+          <t>11,May</t>
+        </is>
+      </c>
+      <c r="B1276" t="inlineStr">
+        <is>
+          <t>AYUSH RAJ</t>
+        </is>
+      </c>
+      <c r="C1276" t="inlineStr">
+        <is>
+          <t>ARVIND KUMAR</t>
+        </is>
+      </c>
+      <c r="D1276" t="inlineStr">
+        <is>
+          <t>KUMARI ANJU RAY</t>
+        </is>
+      </c>
+      <c r="E1276" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="F1276" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="1277">
+      <c r="A1277" t="inlineStr">
+        <is>
+          <t>11,May</t>
+        </is>
+      </c>
+      <c r="B1277" t="inlineStr">
+        <is>
+          <t>AYUSH RAJ</t>
+        </is>
+      </c>
+      <c r="C1277" t="inlineStr">
+        <is>
+          <t>RAHUL RANJAN</t>
+        </is>
+      </c>
+      <c r="D1277" t="inlineStr">
+        <is>
+          <t>CHANDA KUMARI</t>
+        </is>
+      </c>
+      <c r="E1277" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="F1277" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Birthday Data Master.xlsx
+++ b/Birthday Data Master.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1277"/>
+  <dimension ref="A1:F1285"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.6" customWidth="1" min="1" max="1"/>
@@ -41289,6 +41289,262 @@
         </is>
       </c>
     </row>
+    <row r="1278">
+      <c r="A1278" t="inlineStr">
+        <is>
+          <t>12,May</t>
+        </is>
+      </c>
+      <c r="B1278" t="inlineStr">
+        <is>
+          <t>RITIKA KUMARI</t>
+        </is>
+      </c>
+      <c r="C1278" t="inlineStr">
+        <is>
+          <t>RAJESH KUMAR</t>
+        </is>
+      </c>
+      <c r="D1278" t="inlineStr">
+        <is>
+          <t>SEEMA KUMARI</t>
+        </is>
+      </c>
+      <c r="E1278" t="inlineStr">
+        <is>
+          <t>IV</t>
+        </is>
+      </c>
+      <c r="F1278" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="1279">
+      <c r="A1279" t="inlineStr">
+        <is>
+          <t>12,May</t>
+        </is>
+      </c>
+      <c r="B1279" t="inlineStr">
+        <is>
+          <t>ASHWINI SHARMA</t>
+        </is>
+      </c>
+      <c r="C1279" t="inlineStr">
+        <is>
+          <t>BABLU KUMAR</t>
+        </is>
+      </c>
+      <c r="D1279" t="inlineStr">
+        <is>
+          <t>ANSHUMALA KUMARI</t>
+        </is>
+      </c>
+      <c r="E1279" t="inlineStr">
+        <is>
+          <t>VII</t>
+        </is>
+      </c>
+      <c r="F1279" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+    </row>
+    <row r="1280">
+      <c r="A1280" t="inlineStr">
+        <is>
+          <t>12,May</t>
+        </is>
+      </c>
+      <c r="B1280" t="inlineStr">
+        <is>
+          <t>ASHMITA CHAUDHARY</t>
+        </is>
+      </c>
+      <c r="C1280" t="inlineStr">
+        <is>
+          <t>ANUJ KUMAR</t>
+        </is>
+      </c>
+      <c r="D1280" t="inlineStr">
+        <is>
+          <t>SONI KUMARI</t>
+        </is>
+      </c>
+      <c r="E1280" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F1280" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="1281">
+      <c r="A1281" t="inlineStr">
+        <is>
+          <t>12,May</t>
+        </is>
+      </c>
+      <c r="B1281" t="inlineStr">
+        <is>
+          <t>Pratyush kumar</t>
+        </is>
+      </c>
+      <c r="C1281" t="inlineStr">
+        <is>
+          <t>Jaymangal kumar Sharma</t>
+        </is>
+      </c>
+      <c r="D1281" t="inlineStr">
+        <is>
+          <t>PRITEE KUMARI</t>
+        </is>
+      </c>
+      <c r="E1281" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="F1281" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="1282">
+      <c r="A1282" t="inlineStr">
+        <is>
+          <t>12,May</t>
+        </is>
+      </c>
+      <c r="B1282" t="inlineStr">
+        <is>
+          <t>Yash Kumar</t>
+        </is>
+      </c>
+      <c r="C1282" t="inlineStr">
+        <is>
+          <t>Late Kush Kumar</t>
+        </is>
+      </c>
+      <c r="D1282" t="inlineStr">
+        <is>
+          <t>Archana Kumari</t>
+        </is>
+      </c>
+      <c r="E1282" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F1282" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="1283">
+      <c r="A1283" t="inlineStr">
+        <is>
+          <t>12,May</t>
+        </is>
+      </c>
+      <c r="B1283" t="inlineStr">
+        <is>
+          <t>ARADHYA KUMARI</t>
+        </is>
+      </c>
+      <c r="C1283" t="inlineStr">
+        <is>
+          <t>SURESH KEVAT</t>
+        </is>
+      </c>
+      <c r="D1283" t="inlineStr">
+        <is>
+          <t>KHUSHBU KUMARI</t>
+        </is>
+      </c>
+      <c r="E1283" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F1283" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="1284">
+      <c r="A1284" t="inlineStr">
+        <is>
+          <t>12,May</t>
+        </is>
+      </c>
+      <c r="B1284" t="inlineStr">
+        <is>
+          <t>ANKIT RAJ</t>
+        </is>
+      </c>
+      <c r="C1284" t="inlineStr">
+        <is>
+          <t>SANJAY KUMAR</t>
+        </is>
+      </c>
+      <c r="D1284" t="inlineStr">
+        <is>
+          <t>POONAM KUMARI</t>
+        </is>
+      </c>
+      <c r="E1284" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="F1284" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="1285">
+      <c r="A1285" t="inlineStr">
+        <is>
+          <t>12,May</t>
+        </is>
+      </c>
+      <c r="B1285" t="inlineStr">
+        <is>
+          <t>Khushi Kashyap</t>
+        </is>
+      </c>
+      <c r="C1285" t="inlineStr">
+        <is>
+          <t>Rajeev Kumar</t>
+        </is>
+      </c>
+      <c r="D1285" t="inlineStr">
+        <is>
+          <t>Priyanka</t>
+        </is>
+      </c>
+      <c r="E1285" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F1285" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Birthday Data Master.xlsx
+++ b/Birthday Data Master.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1285"/>
+  <dimension ref="A1:F1291"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.6" customWidth="1" min="1" max="1"/>
@@ -41545,6 +41545,198 @@
         </is>
       </c>
     </row>
+    <row r="1286">
+      <c r="A1286" t="inlineStr">
+        <is>
+          <t>13,May</t>
+        </is>
+      </c>
+      <c r="B1286" t="inlineStr">
+        <is>
+          <t>YASH KUMAR</t>
+        </is>
+      </c>
+      <c r="C1286" t="inlineStr">
+        <is>
+          <t>PANKAJ KUMAR</t>
+        </is>
+      </c>
+      <c r="D1286" t="inlineStr">
+        <is>
+          <t>ANSHU KUMARI</t>
+        </is>
+      </c>
+      <c r="E1286" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F1286" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="1287">
+      <c r="A1287" t="inlineStr">
+        <is>
+          <t>13,May</t>
+        </is>
+      </c>
+      <c r="B1287" t="inlineStr">
+        <is>
+          <t>DARSHIL KESHRI</t>
+        </is>
+      </c>
+      <c r="C1287" t="inlineStr">
+        <is>
+          <t>Sudhir Kumar Keshri</t>
+        </is>
+      </c>
+      <c r="D1287" t="inlineStr">
+        <is>
+          <t>Deepa Keshri</t>
+        </is>
+      </c>
+      <c r="E1287" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="F1287" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="1288">
+      <c r="A1288" t="inlineStr">
+        <is>
+          <t>13,May</t>
+        </is>
+      </c>
+      <c r="B1288" t="inlineStr">
+        <is>
+          <t>RAUNAK KUMAR</t>
+        </is>
+      </c>
+      <c r="C1288" t="inlineStr">
+        <is>
+          <t>PULENDRA KUMAR</t>
+        </is>
+      </c>
+      <c r="D1288" t="inlineStr">
+        <is>
+          <t>SIYANTI KUMARI</t>
+        </is>
+      </c>
+      <c r="E1288" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="F1288" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="1289">
+      <c r="A1289" t="inlineStr">
+        <is>
+          <t>13,May</t>
+        </is>
+      </c>
+      <c r="B1289" t="inlineStr">
+        <is>
+          <t>ROUNAK RAJ</t>
+        </is>
+      </c>
+      <c r="C1289" t="inlineStr">
+        <is>
+          <t>DEEPAK KUMAR</t>
+        </is>
+      </c>
+      <c r="D1289" t="inlineStr">
+        <is>
+          <t>NEHA KUMARI</t>
+        </is>
+      </c>
+      <c r="E1289" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F1289" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="1290">
+      <c r="A1290" t="inlineStr">
+        <is>
+          <t>13,May</t>
+        </is>
+      </c>
+      <c r="B1290" t="inlineStr">
+        <is>
+          <t>SHREYASH</t>
+        </is>
+      </c>
+      <c r="C1290" t="inlineStr">
+        <is>
+          <t>RAJESH KUMAR</t>
+        </is>
+      </c>
+      <c r="D1290" t="inlineStr">
+        <is>
+          <t>Asha BHARTI</t>
+        </is>
+      </c>
+      <c r="E1290" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="F1290" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="1291">
+      <c r="A1291" t="inlineStr">
+        <is>
+          <t>13,May</t>
+        </is>
+      </c>
+      <c r="B1291" t="inlineStr">
+        <is>
+          <t>ADITYA  KUMAR</t>
+        </is>
+      </c>
+      <c r="C1291" t="inlineStr">
+        <is>
+          <t>SANKET SHARMA</t>
+        </is>
+      </c>
+      <c r="D1291" t="inlineStr">
+        <is>
+          <t>NITU DEVI</t>
+        </is>
+      </c>
+      <c r="E1291" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="F1291" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Birthday Data Master.xlsx
+++ b/Birthday Data Master.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1291"/>
+  <dimension ref="A1:F1295"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.6" customWidth="1" min="1" max="1"/>
@@ -41737,6 +41737,134 @@
         </is>
       </c>
     </row>
+    <row r="1292">
+      <c r="A1292" t="inlineStr">
+        <is>
+          <t>14,May</t>
+        </is>
+      </c>
+      <c r="B1292" t="inlineStr">
+        <is>
+          <t>ISHU RAJ</t>
+        </is>
+      </c>
+      <c r="C1292" t="inlineStr">
+        <is>
+          <t>RAJ KUMAR</t>
+        </is>
+      </c>
+      <c r="D1292" t="inlineStr">
+        <is>
+          <t>JYOTI KUMARI</t>
+        </is>
+      </c>
+      <c r="E1292" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="F1292" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="1293">
+      <c r="A1293" t="inlineStr">
+        <is>
+          <t>14,May</t>
+        </is>
+      </c>
+      <c r="B1293" t="inlineStr">
+        <is>
+          <t>SUMIT KUMAR</t>
+        </is>
+      </c>
+      <c r="C1293" t="inlineStr">
+        <is>
+          <t>SUNIL KUMAR TIWARY</t>
+        </is>
+      </c>
+      <c r="D1293" t="inlineStr">
+        <is>
+          <t>GUNJAN DEVI</t>
+        </is>
+      </c>
+      <c r="E1293" t="inlineStr">
+        <is>
+          <t>IV</t>
+        </is>
+      </c>
+      <c r="F1293" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="1294">
+      <c r="A1294" t="inlineStr">
+        <is>
+          <t>14,May</t>
+        </is>
+      </c>
+      <c r="B1294" t="inlineStr">
+        <is>
+          <t>ANURAG DEV</t>
+        </is>
+      </c>
+      <c r="C1294" t="inlineStr">
+        <is>
+          <t>RANDHIR SINGH</t>
+        </is>
+      </c>
+      <c r="D1294" t="inlineStr">
+        <is>
+          <t>SWET RASHMI</t>
+        </is>
+      </c>
+      <c r="E1294" t="inlineStr">
+        <is>
+          <t>XI</t>
+        </is>
+      </c>
+      <c r="F1294" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="1295">
+      <c r="A1295" t="inlineStr">
+        <is>
+          <t>14,May</t>
+        </is>
+      </c>
+      <c r="B1295" t="inlineStr">
+        <is>
+          <t>SARTHAK KUMAR</t>
+        </is>
+      </c>
+      <c r="C1295" t="inlineStr">
+        <is>
+          <t>PINTU KUMAR</t>
+        </is>
+      </c>
+      <c r="D1295" t="inlineStr">
+        <is>
+          <t>SALONI KUMARI</t>
+        </is>
+      </c>
+      <c r="E1295" t="inlineStr">
+        <is>
+          <t>LKG</t>
+        </is>
+      </c>
+      <c r="F1295" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Birthday Data Master.xlsx
+++ b/Birthday Data Master.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1295"/>
+  <dimension ref="A1:F1301"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.6" customWidth="1" min="1" max="1"/>
@@ -41865,6 +41865,198 @@
         </is>
       </c>
     </row>
+    <row r="1296">
+      <c r="A1296" t="inlineStr">
+        <is>
+          <t>15,May</t>
+        </is>
+      </c>
+      <c r="B1296" t="inlineStr">
+        <is>
+          <t>OM Kashyap</t>
+        </is>
+      </c>
+      <c r="C1296" t="inlineStr">
+        <is>
+          <t>Abhishek Kumar</t>
+        </is>
+      </c>
+      <c r="D1296" t="inlineStr">
+        <is>
+          <t>Neha Kumari</t>
+        </is>
+      </c>
+      <c r="E1296" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="F1296" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="1297">
+      <c r="A1297" t="inlineStr">
+        <is>
+          <t>15,May</t>
+        </is>
+      </c>
+      <c r="B1297" t="inlineStr">
+        <is>
+          <t>Sri Bhushan</t>
+        </is>
+      </c>
+      <c r="C1297" t="inlineStr">
+        <is>
+          <t>Sunil Kumar</t>
+        </is>
+      </c>
+      <c r="D1297" t="inlineStr">
+        <is>
+          <t>Pinki Kumari</t>
+        </is>
+      </c>
+      <c r="E1297" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F1297" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="1298">
+      <c r="A1298" t="inlineStr">
+        <is>
+          <t>15,May</t>
+        </is>
+      </c>
+      <c r="B1298" t="inlineStr">
+        <is>
+          <t>ADITI PRABHA</t>
+        </is>
+      </c>
+      <c r="C1298" t="inlineStr">
+        <is>
+          <t>RAJNISH KUMAR</t>
+        </is>
+      </c>
+      <c r="D1298" t="inlineStr">
+        <is>
+          <t>ALKA KUMARI</t>
+        </is>
+      </c>
+      <c r="E1298" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="F1298" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="1299">
+      <c r="A1299" t="inlineStr">
+        <is>
+          <t>15,May</t>
+        </is>
+      </c>
+      <c r="B1299" t="inlineStr">
+        <is>
+          <t>VIDHI SHARMA</t>
+        </is>
+      </c>
+      <c r="C1299" t="inlineStr">
+        <is>
+          <t>KUNJ BIHARI</t>
+        </is>
+      </c>
+      <c r="D1299" t="inlineStr">
+        <is>
+          <t>NIDHI KUMARI</t>
+        </is>
+      </c>
+      <c r="E1299" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="F1299" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="1300">
+      <c r="A1300" t="inlineStr">
+        <is>
+          <t>15,May</t>
+        </is>
+      </c>
+      <c r="B1300" t="inlineStr">
+        <is>
+          <t>AARADHYA BHARTI</t>
+        </is>
+      </c>
+      <c r="C1300" t="inlineStr">
+        <is>
+          <t>AMIT KUMAR</t>
+        </is>
+      </c>
+      <c r="D1300" t="inlineStr">
+        <is>
+          <t>BEAUTY KUMARI</t>
+        </is>
+      </c>
+      <c r="E1300" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F1300" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="1301">
+      <c r="A1301" t="inlineStr">
+        <is>
+          <t>15,May</t>
+        </is>
+      </c>
+      <c r="B1301" t="inlineStr">
+        <is>
+          <t>RADHIKA RANI</t>
+        </is>
+      </c>
+      <c r="C1301" t="inlineStr">
+        <is>
+          <t>RAJESH KUMAR</t>
+        </is>
+      </c>
+      <c r="D1301" t="inlineStr">
+        <is>
+          <t>PINKI KUMARI</t>
+        </is>
+      </c>
+      <c r="E1301" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="F1301" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Birthday Data Master.xlsx
+++ b/Birthday Data Master.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1301"/>
+  <dimension ref="A1:F1309"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.6" customWidth="1" min="1" max="1"/>
@@ -42057,6 +42057,262 @@
         </is>
       </c>
     </row>
+    <row r="1302">
+      <c r="A1302" t="inlineStr">
+        <is>
+          <t>16,May</t>
+        </is>
+      </c>
+      <c r="B1302" t="inlineStr">
+        <is>
+          <t>PUSHPI KUMARI</t>
+        </is>
+      </c>
+      <c r="C1302" t="inlineStr">
+        <is>
+          <t>KAMAL KUMAR CHAKRAVARTI</t>
+        </is>
+      </c>
+      <c r="D1302" t="inlineStr">
+        <is>
+          <t>SHOBHA KUMARI</t>
+        </is>
+      </c>
+      <c r="E1302" t="inlineStr">
+        <is>
+          <t>VII</t>
+        </is>
+      </c>
+      <c r="F1302" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="1303">
+      <c r="A1303" t="inlineStr">
+        <is>
+          <t>16,May</t>
+        </is>
+      </c>
+      <c r="B1303" t="inlineStr">
+        <is>
+          <t>AYUSH RAJ</t>
+        </is>
+      </c>
+      <c r="C1303" t="inlineStr">
+        <is>
+          <t>Late Manoranjan Kumar</t>
+        </is>
+      </c>
+      <c r="D1303" t="inlineStr">
+        <is>
+          <t>Khushboo</t>
+        </is>
+      </c>
+      <c r="E1303" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="F1303" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="1304">
+      <c r="A1304" t="inlineStr">
+        <is>
+          <t>16,May</t>
+        </is>
+      </c>
+      <c r="B1304" t="inlineStr">
+        <is>
+          <t>IRA SUHASINI</t>
+        </is>
+      </c>
+      <c r="C1304" t="inlineStr">
+        <is>
+          <t>MAHENDRA PRASAD</t>
+        </is>
+      </c>
+      <c r="D1304" t="inlineStr">
+        <is>
+          <t>MANJU KUMARI</t>
+        </is>
+      </c>
+      <c r="E1304" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="F1304" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="1305">
+      <c r="A1305" t="inlineStr">
+        <is>
+          <t>16,May</t>
+        </is>
+      </c>
+      <c r="B1305" t="inlineStr">
+        <is>
+          <t>NAVNEET KUMAR</t>
+        </is>
+      </c>
+      <c r="C1305" t="inlineStr">
+        <is>
+          <t>RAUSHAN KUMAR</t>
+        </is>
+      </c>
+      <c r="D1305" t="inlineStr">
+        <is>
+          <t>VANDNA KUMARI</t>
+        </is>
+      </c>
+      <c r="E1305" t="inlineStr">
+        <is>
+          <t>LKG</t>
+        </is>
+      </c>
+      <c r="F1305" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="1306">
+      <c r="A1306" t="inlineStr">
+        <is>
+          <t>16,May</t>
+        </is>
+      </c>
+      <c r="B1306" t="inlineStr">
+        <is>
+          <t>PRANSHU SHARMA</t>
+        </is>
+      </c>
+      <c r="C1306" t="inlineStr">
+        <is>
+          <t>RAJU KUMAR</t>
+        </is>
+      </c>
+      <c r="D1306" t="inlineStr">
+        <is>
+          <t>SMITA KUMARI</t>
+        </is>
+      </c>
+      <c r="E1306" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="F1306" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="1307">
+      <c r="A1307" t="inlineStr">
+        <is>
+          <t>16,May</t>
+        </is>
+      </c>
+      <c r="B1307" t="inlineStr">
+        <is>
+          <t>Arpita Kumari</t>
+        </is>
+      </c>
+      <c r="C1307" t="inlineStr">
+        <is>
+          <t>Manoj Kumar</t>
+        </is>
+      </c>
+      <c r="D1307" t="inlineStr">
+        <is>
+          <t>Juli Kumari</t>
+        </is>
+      </c>
+      <c r="E1307" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="F1307" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="1308">
+      <c r="A1308" t="inlineStr">
+        <is>
+          <t>16,May</t>
+        </is>
+      </c>
+      <c r="B1308" t="inlineStr">
+        <is>
+          <t>SHUBHAM KUMAR</t>
+        </is>
+      </c>
+      <c r="C1308" t="inlineStr">
+        <is>
+          <t>BISHRAM SINGH</t>
+        </is>
+      </c>
+      <c r="D1308" t="inlineStr">
+        <is>
+          <t>KUMARI NIBHA SINHA</t>
+        </is>
+      </c>
+      <c r="E1308" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="F1308" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="1309">
+      <c r="A1309" t="inlineStr">
+        <is>
+          <t>16,May</t>
+        </is>
+      </c>
+      <c r="B1309" t="inlineStr">
+        <is>
+          <t>HARIOM KUMAR</t>
+        </is>
+      </c>
+      <c r="C1309" t="inlineStr">
+        <is>
+          <t>RAVIJEET KUMAR</t>
+        </is>
+      </c>
+      <c r="D1309" t="inlineStr">
+        <is>
+          <t>POOJA KUMARI</t>
+        </is>
+      </c>
+      <c r="E1309" t="inlineStr">
+        <is>
+          <t>UKG</t>
+        </is>
+      </c>
+      <c r="F1309" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Birthday Data Master.xlsx
+++ b/Birthday Data Master.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1309"/>
+  <dimension ref="A1:F1315"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.6" customWidth="1" min="1" max="1"/>
@@ -42313,6 +42313,198 @@
         </is>
       </c>
     </row>
+    <row r="1310">
+      <c r="A1310" t="inlineStr">
+        <is>
+          <t>17,May</t>
+        </is>
+      </c>
+      <c r="B1310" t="inlineStr">
+        <is>
+          <t>RISHAV RAJ</t>
+        </is>
+      </c>
+      <c r="C1310" t="inlineStr">
+        <is>
+          <t>SANJAY KUMAR</t>
+        </is>
+      </c>
+      <c r="D1310" t="inlineStr">
+        <is>
+          <t>MANDVI KUMARI</t>
+        </is>
+      </c>
+      <c r="E1310" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F1310" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="1311">
+      <c r="A1311" t="inlineStr">
+        <is>
+          <t>17,May</t>
+        </is>
+      </c>
+      <c r="B1311" t="inlineStr">
+        <is>
+          <t>AAYU RAJ</t>
+        </is>
+      </c>
+      <c r="C1311" t="inlineStr">
+        <is>
+          <t>DHANANJAY KUMAR</t>
+        </is>
+      </c>
+      <c r="D1311" t="inlineStr">
+        <is>
+          <t>NICKY KUMARI</t>
+        </is>
+      </c>
+      <c r="E1311" t="inlineStr">
+        <is>
+          <t>IV</t>
+        </is>
+      </c>
+      <c r="F1311" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="1312">
+      <c r="A1312" t="inlineStr">
+        <is>
+          <t>17,May</t>
+        </is>
+      </c>
+      <c r="B1312" t="inlineStr">
+        <is>
+          <t>RISHI RAJ KING</t>
+        </is>
+      </c>
+      <c r="C1312" t="inlineStr">
+        <is>
+          <t>RAVI RANJAN KUMAR</t>
+        </is>
+      </c>
+      <c r="D1312" t="inlineStr">
+        <is>
+          <t>CHANDNEE KUMARI</t>
+        </is>
+      </c>
+      <c r="E1312" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="F1312" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="1313">
+      <c r="A1313" t="inlineStr">
+        <is>
+          <t>17,May</t>
+        </is>
+      </c>
+      <c r="B1313" t="inlineStr">
+        <is>
+          <t>Aryan Raj</t>
+        </is>
+      </c>
+      <c r="C1313" t="inlineStr">
+        <is>
+          <t>Nagendra Kumar</t>
+        </is>
+      </c>
+      <c r="D1313" t="inlineStr">
+        <is>
+          <t>Punam Kumari</t>
+        </is>
+      </c>
+      <c r="E1313" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="F1313" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="1314">
+      <c r="A1314" t="inlineStr">
+        <is>
+          <t>17,May</t>
+        </is>
+      </c>
+      <c r="B1314" t="inlineStr">
+        <is>
+          <t>Divyanka Kumari</t>
+        </is>
+      </c>
+      <c r="C1314" t="inlineStr">
+        <is>
+          <t>Dinesh Chandra</t>
+        </is>
+      </c>
+      <c r="D1314" t="inlineStr">
+        <is>
+          <t>Sima Kumari</t>
+        </is>
+      </c>
+      <c r="E1314" t="inlineStr">
+        <is>
+          <t>VIII</t>
+        </is>
+      </c>
+      <c r="F1314" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="1315">
+      <c r="A1315" t="inlineStr">
+        <is>
+          <t>17,May</t>
+        </is>
+      </c>
+      <c r="B1315" t="inlineStr">
+        <is>
+          <t>ANUSHKA KESHRI</t>
+        </is>
+      </c>
+      <c r="C1315" t="inlineStr">
+        <is>
+          <t>PRAKASH RANJAN</t>
+        </is>
+      </c>
+      <c r="D1315" t="inlineStr">
+        <is>
+          <t>MOHITA RANI</t>
+        </is>
+      </c>
+      <c r="E1315" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F1315" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Birthday Data Master.xlsx
+++ b/Birthday Data Master.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1315"/>
+  <dimension ref="A1:F1320"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.6" customWidth="1" min="1" max="1"/>
@@ -42505,6 +42505,166 @@
         </is>
       </c>
     </row>
+    <row r="1316">
+      <c r="A1316" t="inlineStr">
+        <is>
+          <t>18,May</t>
+        </is>
+      </c>
+      <c r="B1316" t="inlineStr">
+        <is>
+          <t>SHIVANSH KUMAR</t>
+        </is>
+      </c>
+      <c r="C1316" t="inlineStr">
+        <is>
+          <t>PRINSH KUMAR</t>
+        </is>
+      </c>
+      <c r="D1316" t="inlineStr">
+        <is>
+          <t>POONAM KUMARI</t>
+        </is>
+      </c>
+      <c r="E1316" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="F1316" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="1317">
+      <c r="A1317" t="inlineStr">
+        <is>
+          <t>18,May</t>
+        </is>
+      </c>
+      <c r="B1317" t="inlineStr">
+        <is>
+          <t>HIMANSHU RANJAN KUMAR</t>
+        </is>
+      </c>
+      <c r="C1317" t="inlineStr">
+        <is>
+          <t>AMIT RANJAN KUMAR</t>
+        </is>
+      </c>
+      <c r="D1317" t="inlineStr">
+        <is>
+          <t>CHANCHALA KUMARI</t>
+        </is>
+      </c>
+      <c r="E1317" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="F1317" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="1318">
+      <c r="A1318" t="inlineStr">
+        <is>
+          <t>18,May</t>
+        </is>
+      </c>
+      <c r="B1318" t="inlineStr">
+        <is>
+          <t>RUHI SHARMA</t>
+        </is>
+      </c>
+      <c r="C1318" t="inlineStr">
+        <is>
+          <t>ALOK KUMAR</t>
+        </is>
+      </c>
+      <c r="D1318" t="inlineStr">
+        <is>
+          <t>BHAGYA LAXMI</t>
+        </is>
+      </c>
+      <c r="E1318" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F1318" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="1319">
+      <c r="A1319" t="inlineStr">
+        <is>
+          <t>18,May</t>
+        </is>
+      </c>
+      <c r="B1319" t="inlineStr">
+        <is>
+          <t>Nishant Raj</t>
+        </is>
+      </c>
+      <c r="C1319" t="inlineStr">
+        <is>
+          <t>Pankaj Kumar</t>
+        </is>
+      </c>
+      <c r="D1319" t="inlineStr">
+        <is>
+          <t>Anjali Rai</t>
+        </is>
+      </c>
+      <c r="E1319" t="inlineStr">
+        <is>
+          <t>IX</t>
+        </is>
+      </c>
+      <c r="F1319" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="1320">
+      <c r="A1320" t="inlineStr">
+        <is>
+          <t>18,May</t>
+        </is>
+      </c>
+      <c r="B1320" t="inlineStr">
+        <is>
+          <t>MD AFAAN MUNTASIR</t>
+        </is>
+      </c>
+      <c r="C1320" t="inlineStr">
+        <is>
+          <t>MD TAUSEEF AHMAD</t>
+        </is>
+      </c>
+      <c r="D1320" t="inlineStr">
+        <is>
+          <t>SHABISTHAN NAAZ</t>
+        </is>
+      </c>
+      <c r="E1320" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="F1320" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Birthday Data Master.xlsx
+++ b/Birthday Data Master.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1320"/>
+  <dimension ref="A1:F1322"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.6" customWidth="1" min="1" max="1"/>
@@ -42665,6 +42665,70 @@
         </is>
       </c>
     </row>
+    <row r="1321">
+      <c r="A1321" t="inlineStr">
+        <is>
+          <t>19,May</t>
+        </is>
+      </c>
+      <c r="B1321" t="inlineStr">
+        <is>
+          <t>MANYA  S</t>
+        </is>
+      </c>
+      <c r="C1321" t="inlineStr">
+        <is>
+          <t>SANJAY KUMAR</t>
+        </is>
+      </c>
+      <c r="D1321" t="inlineStr">
+        <is>
+          <t>SHARMILA KUMARI</t>
+        </is>
+      </c>
+      <c r="E1321" t="inlineStr">
+        <is>
+          <t>XI</t>
+        </is>
+      </c>
+      <c r="F1321" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="1322">
+      <c r="A1322" t="inlineStr">
+        <is>
+          <t>19,May</t>
+        </is>
+      </c>
+      <c r="B1322" t="inlineStr">
+        <is>
+          <t>ALHAN KALAM</t>
+        </is>
+      </c>
+      <c r="C1322" t="inlineStr">
+        <is>
+          <t>ABUL HAYAT</t>
+        </is>
+      </c>
+      <c r="D1322" t="inlineStr">
+        <is>
+          <t>MARIAM BEGUM</t>
+        </is>
+      </c>
+      <c r="E1322" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="F1322" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Birthday Data Master.xlsx
+++ b/Birthday Data Master.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1322"/>
+  <dimension ref="A1:F1329"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.6" customWidth="1" min="1" max="1"/>
@@ -42729,6 +42729,230 @@
         </is>
       </c>
     </row>
+    <row r="1323">
+      <c r="A1323" t="inlineStr">
+        <is>
+          <t>20,May</t>
+        </is>
+      </c>
+      <c r="B1323" t="inlineStr">
+        <is>
+          <t>PRIYANSHU RAJ</t>
+        </is>
+      </c>
+      <c r="C1323" t="inlineStr">
+        <is>
+          <t>RANDHIR KUMAR</t>
+        </is>
+      </c>
+      <c r="D1323" t="inlineStr">
+        <is>
+          <t>SHEMPI KUMARI</t>
+        </is>
+      </c>
+      <c r="E1323" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F1323" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="1324">
+      <c r="A1324" t="inlineStr">
+        <is>
+          <t>20,May</t>
+        </is>
+      </c>
+      <c r="B1324" t="inlineStr">
+        <is>
+          <t>DIVYANSH RAJ</t>
+        </is>
+      </c>
+      <c r="C1324" t="inlineStr">
+        <is>
+          <t>RAKESH KUMAR</t>
+        </is>
+      </c>
+      <c r="D1324" t="inlineStr">
+        <is>
+          <t>RAJNI KUMARI</t>
+        </is>
+      </c>
+      <c r="E1324" t="inlineStr">
+        <is>
+          <t>LKG</t>
+        </is>
+      </c>
+      <c r="F1324" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="1325">
+      <c r="A1325" t="inlineStr">
+        <is>
+          <t>20,May</t>
+        </is>
+      </c>
+      <c r="B1325" t="inlineStr">
+        <is>
+          <t>SAKSHI  KUMARI</t>
+        </is>
+      </c>
+      <c r="C1325" t="inlineStr">
+        <is>
+          <t>RANDHIR KUMAR dhiraj</t>
+        </is>
+      </c>
+      <c r="D1325" t="inlineStr">
+        <is>
+          <t>SWETA KUMARI</t>
+        </is>
+      </c>
+      <c r="E1325" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="F1325" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="1326">
+      <c r="A1326" t="inlineStr">
+        <is>
+          <t>20,May</t>
+        </is>
+      </c>
+      <c r="B1326" t="inlineStr">
+        <is>
+          <t>RAHUL PRIYADARSHI</t>
+        </is>
+      </c>
+      <c r="C1326" t="inlineStr">
+        <is>
+          <t>MITHILESH KUMAR</t>
+        </is>
+      </c>
+      <c r="D1326" t="inlineStr">
+        <is>
+          <t>PRATIMA KUMARI</t>
+        </is>
+      </c>
+      <c r="E1326" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="F1326" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="1327">
+      <c r="A1327" t="inlineStr">
+        <is>
+          <t>20,May</t>
+        </is>
+      </c>
+      <c r="B1327" t="inlineStr">
+        <is>
+          <t>Ritika Rani</t>
+        </is>
+      </c>
+      <c r="C1327" t="inlineStr">
+        <is>
+          <t>Randhir Kumar</t>
+        </is>
+      </c>
+      <c r="D1327" t="inlineStr">
+        <is>
+          <t>Nirmala Kumari</t>
+        </is>
+      </c>
+      <c r="E1327" t="inlineStr">
+        <is>
+          <t>IX</t>
+        </is>
+      </c>
+      <c r="F1327" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="1328">
+      <c r="A1328" t="inlineStr">
+        <is>
+          <t>20,May</t>
+        </is>
+      </c>
+      <c r="B1328" t="inlineStr">
+        <is>
+          <t>Navneeta  Kumari</t>
+        </is>
+      </c>
+      <c r="C1328" t="inlineStr">
+        <is>
+          <t>Dharmendra Kumar</t>
+        </is>
+      </c>
+      <c r="D1328" t="inlineStr">
+        <is>
+          <t>Rina Kumari</t>
+        </is>
+      </c>
+      <c r="E1328" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F1328" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="1329">
+      <c r="A1329" t="inlineStr">
+        <is>
+          <t>20,May</t>
+        </is>
+      </c>
+      <c r="B1329" t="inlineStr">
+        <is>
+          <t>Tanu Kumari</t>
+        </is>
+      </c>
+      <c r="C1329" t="inlineStr">
+        <is>
+          <t>Ujjaval Kant</t>
+        </is>
+      </c>
+      <c r="D1329" t="inlineStr">
+        <is>
+          <t>Rita Kumari</t>
+        </is>
+      </c>
+      <c r="E1329" t="inlineStr">
+        <is>
+          <t>IX</t>
+        </is>
+      </c>
+      <c r="F1329" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Birthday Data Master.xlsx
+++ b/Birthday Data Master.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1329"/>
+  <dimension ref="A1:F1330"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.6" customWidth="1" min="1" max="1"/>
@@ -42953,6 +42953,38 @@
         </is>
       </c>
     </row>
+    <row r="1330">
+      <c r="A1330" t="inlineStr">
+        <is>
+          <t>21,May</t>
+        </is>
+      </c>
+      <c r="B1330" t="inlineStr">
+        <is>
+          <t>ANANYA KUMARI</t>
+        </is>
+      </c>
+      <c r="C1330" t="inlineStr">
+        <is>
+          <t>AJEET KUMAR</t>
+        </is>
+      </c>
+      <c r="D1330" t="inlineStr">
+        <is>
+          <t>BIDAYA RANI</t>
+        </is>
+      </c>
+      <c r="E1330" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="F1330" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Birthday Data Master.xlsx
+++ b/Birthday Data Master.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1330"/>
+  <dimension ref="A1:F1333"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.6" customWidth="1" min="1" max="1"/>
@@ -42985,6 +42985,102 @@
         </is>
       </c>
     </row>
+    <row r="1331">
+      <c r="A1331" t="inlineStr">
+        <is>
+          <t>22,May</t>
+        </is>
+      </c>
+      <c r="B1331" t="inlineStr">
+        <is>
+          <t>ANJALI KUMARI</t>
+        </is>
+      </c>
+      <c r="C1331" t="inlineStr">
+        <is>
+          <t>SARUN KUMAR</t>
+        </is>
+      </c>
+      <c r="D1331" t="inlineStr">
+        <is>
+          <t>SONI KUMARI</t>
+        </is>
+      </c>
+      <c r="E1331" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="F1331" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="1332">
+      <c r="A1332" t="inlineStr">
+        <is>
+          <t>22,May</t>
+        </is>
+      </c>
+      <c r="B1332" t="inlineStr">
+        <is>
+          <t>Harsh Raj</t>
+        </is>
+      </c>
+      <c r="C1332" t="inlineStr">
+        <is>
+          <t>Bhushan Kumar</t>
+        </is>
+      </c>
+      <c r="D1332" t="inlineStr">
+        <is>
+          <t>Priyanka Kumari</t>
+        </is>
+      </c>
+      <c r="E1332" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F1332" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="1333">
+      <c r="A1333" t="inlineStr">
+        <is>
+          <t>22,May</t>
+        </is>
+      </c>
+      <c r="B1333" t="inlineStr">
+        <is>
+          <t>AISHWARAY BHUSHAN</t>
+        </is>
+      </c>
+      <c r="C1333" t="inlineStr">
+        <is>
+          <t>SHASHI BHUSHAN</t>
+        </is>
+      </c>
+      <c r="D1333" t="inlineStr">
+        <is>
+          <t>VIJETA KUMARI</t>
+        </is>
+      </c>
+      <c r="E1333" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="F1333" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Birthday Data Master.xlsx
+++ b/Birthday Data Master.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1333"/>
+  <dimension ref="A1:F1340"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.6" customWidth="1" min="1" max="1"/>
@@ -43081,6 +43081,230 @@
         </is>
       </c>
     </row>
+    <row r="1334">
+      <c r="A1334" t="inlineStr">
+        <is>
+          <t>23,May</t>
+        </is>
+      </c>
+      <c r="B1334" t="inlineStr">
+        <is>
+          <t>HIMANSHU KUMAR</t>
+        </is>
+      </c>
+      <c r="C1334" t="inlineStr">
+        <is>
+          <t>SONU KANT PANDEY</t>
+        </is>
+      </c>
+      <c r="D1334" t="inlineStr">
+        <is>
+          <t>LOVLI KUMARI</t>
+        </is>
+      </c>
+      <c r="E1334" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="F1334" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="1335">
+      <c r="A1335" t="inlineStr">
+        <is>
+          <t>23,May</t>
+        </is>
+      </c>
+      <c r="B1335" t="inlineStr">
+        <is>
+          <t>MAYANK  KUMAR</t>
+        </is>
+      </c>
+      <c r="C1335" t="inlineStr">
+        <is>
+          <t>LAVKUSH KUMAR</t>
+        </is>
+      </c>
+      <c r="D1335" t="inlineStr">
+        <is>
+          <t>DIMPI KUMARI</t>
+        </is>
+      </c>
+      <c r="E1335" t="inlineStr">
+        <is>
+          <t>UKG</t>
+        </is>
+      </c>
+      <c r="F1335" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="1336">
+      <c r="A1336" t="inlineStr">
+        <is>
+          <t>23,May</t>
+        </is>
+      </c>
+      <c r="B1336" t="inlineStr">
+        <is>
+          <t>TRIPA SINHA</t>
+        </is>
+      </c>
+      <c r="C1336" t="inlineStr">
+        <is>
+          <t>MITESH KUMAR SINHA</t>
+        </is>
+      </c>
+      <c r="D1336" t="inlineStr">
+        <is>
+          <t>RINKU KUMARI</t>
+        </is>
+      </c>
+      <c r="E1336" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F1336" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="1337">
+      <c r="A1337" t="inlineStr">
+        <is>
+          <t>23,May</t>
+        </is>
+      </c>
+      <c r="B1337" t="inlineStr">
+        <is>
+          <t>RISHU RAJ</t>
+        </is>
+      </c>
+      <c r="C1337" t="inlineStr">
+        <is>
+          <t>BHISHAM PAL ROY</t>
+        </is>
+      </c>
+      <c r="D1337" t="inlineStr">
+        <is>
+          <t>NITU DEVI</t>
+        </is>
+      </c>
+      <c r="E1337" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="F1337" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="1338">
+      <c r="A1338" t="inlineStr">
+        <is>
+          <t>23,May</t>
+        </is>
+      </c>
+      <c r="B1338" t="inlineStr">
+        <is>
+          <t>SRISHTI KUMARI</t>
+        </is>
+      </c>
+      <c r="C1338" t="inlineStr">
+        <is>
+          <t>SHASHI KANT KUMAR</t>
+        </is>
+      </c>
+      <c r="D1338" t="inlineStr">
+        <is>
+          <t>SANGITA KUMARI</t>
+        </is>
+      </c>
+      <c r="E1338" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="F1338" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="1339">
+      <c r="A1339" t="inlineStr">
+        <is>
+          <t>23,May</t>
+        </is>
+      </c>
+      <c r="B1339" t="inlineStr">
+        <is>
+          <t>ARADHYA KUMARI</t>
+        </is>
+      </c>
+      <c r="C1339" t="inlineStr">
+        <is>
+          <t>VIVEKANAND KUMAR</t>
+        </is>
+      </c>
+      <c r="D1339" t="inlineStr">
+        <is>
+          <t>KUMARI RASHMI</t>
+        </is>
+      </c>
+      <c r="E1339" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F1339" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="1340">
+      <c r="A1340" t="inlineStr">
+        <is>
+          <t>23,May</t>
+        </is>
+      </c>
+      <c r="B1340" t="inlineStr">
+        <is>
+          <t>KARTIK KUMAR</t>
+        </is>
+      </c>
+      <c r="C1340" t="inlineStr">
+        <is>
+          <t>RAJEEV KUMAR</t>
+        </is>
+      </c>
+      <c r="D1340" t="inlineStr">
+        <is>
+          <t>MAHIMA KUMARI</t>
+        </is>
+      </c>
+      <c r="E1340" t="inlineStr">
+        <is>
+          <t>IV</t>
+        </is>
+      </c>
+      <c r="F1340" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Birthday Data Master.xlsx
+++ b/Birthday Data Master.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1340"/>
+  <dimension ref="A1:F1344"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.6" customWidth="1" min="1" max="1"/>
@@ -43305,6 +43305,134 @@
         </is>
       </c>
     </row>
+    <row r="1341">
+      <c r="A1341" t="inlineStr">
+        <is>
+          <t>24,May</t>
+        </is>
+      </c>
+      <c r="B1341" t="inlineStr">
+        <is>
+          <t>SURYANSH SINGH</t>
+        </is>
+      </c>
+      <c r="C1341" t="inlineStr">
+        <is>
+          <t>SHASHI KUMAR</t>
+        </is>
+      </c>
+      <c r="D1341" t="inlineStr">
+        <is>
+          <t>PINKI KUMARI</t>
+        </is>
+      </c>
+      <c r="E1341" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F1341" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="1342">
+      <c r="A1342" t="inlineStr">
+        <is>
+          <t>24,May</t>
+        </is>
+      </c>
+      <c r="B1342" t="inlineStr">
+        <is>
+          <t>AKSHAJ YASHA</t>
+        </is>
+      </c>
+      <c r="C1342" t="inlineStr">
+        <is>
+          <t>LALIT SHANKAR PATHAK</t>
+        </is>
+      </c>
+      <c r="D1342" t="inlineStr">
+        <is>
+          <t>ANURADHA KUMARI</t>
+        </is>
+      </c>
+      <c r="E1342" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="F1342" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="1343">
+      <c r="A1343" t="inlineStr">
+        <is>
+          <t>24,May</t>
+        </is>
+      </c>
+      <c r="B1343" t="inlineStr">
+        <is>
+          <t>RUDRA PRATAP SINGH</t>
+        </is>
+      </c>
+      <c r="C1343" t="inlineStr">
+        <is>
+          <t>AMIT KUMAR SINGH</t>
+        </is>
+      </c>
+      <c r="D1343" t="inlineStr">
+        <is>
+          <t>BIBHA SINGH</t>
+        </is>
+      </c>
+      <c r="E1343" t="inlineStr">
+        <is>
+          <t>XI</t>
+        </is>
+      </c>
+      <c r="F1343" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="1344">
+      <c r="A1344" t="inlineStr">
+        <is>
+          <t>24,May</t>
+        </is>
+      </c>
+      <c r="B1344" t="inlineStr">
+        <is>
+          <t>Hari Om</t>
+        </is>
+      </c>
+      <c r="C1344" t="inlineStr">
+        <is>
+          <t>Pawan Kumar Singh</t>
+        </is>
+      </c>
+      <c r="D1344" t="inlineStr">
+        <is>
+          <t>Shweta Singh</t>
+        </is>
+      </c>
+      <c r="E1344" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F1344" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Birthday Data Master.xlsx
+++ b/Birthday Data Master.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1344"/>
+  <dimension ref="A1:F1347"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.6" customWidth="1" min="1" max="1"/>
@@ -43433,6 +43433,102 @@
         </is>
       </c>
     </row>
+    <row r="1345">
+      <c r="A1345" t="inlineStr">
+        <is>
+          <t>25,May</t>
+        </is>
+      </c>
+      <c r="B1345" t="inlineStr">
+        <is>
+          <t>Tanshu Kumar Srivastav</t>
+        </is>
+      </c>
+      <c r="C1345" t="inlineStr">
+        <is>
+          <t>Satish Kumar</t>
+        </is>
+      </c>
+      <c r="D1345" t="inlineStr">
+        <is>
+          <t>Ruby Kumari Srivastav</t>
+        </is>
+      </c>
+      <c r="E1345" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F1345" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="1346">
+      <c r="A1346" t="inlineStr">
+        <is>
+          <t>25,May</t>
+        </is>
+      </c>
+      <c r="B1346" t="inlineStr">
+        <is>
+          <t>KRITI PAL</t>
+        </is>
+      </c>
+      <c r="C1346" t="inlineStr">
+        <is>
+          <t>SAHENDRA KUMAR</t>
+        </is>
+      </c>
+      <c r="D1346" t="inlineStr">
+        <is>
+          <t>SHIMPI DEVI</t>
+        </is>
+      </c>
+      <c r="E1346" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F1346" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="1347">
+      <c r="A1347" t="inlineStr">
+        <is>
+          <t>25,May</t>
+        </is>
+      </c>
+      <c r="B1347" t="inlineStr">
+        <is>
+          <t>DIVYANSHU RAJ</t>
+        </is>
+      </c>
+      <c r="C1347" t="inlineStr">
+        <is>
+          <t>RAVI RANJAN KUMAR</t>
+        </is>
+      </c>
+      <c r="D1347" t="inlineStr">
+        <is>
+          <t>PRAVINA KUMARI</t>
+        </is>
+      </c>
+      <c r="E1347" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="F1347" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Birthday Data Master.xlsx
+++ b/Birthday Data Master.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1347"/>
+  <dimension ref="A1:F1354"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.6" customWidth="1" min="1" max="1"/>
@@ -43529,6 +43529,230 @@
         </is>
       </c>
     </row>
+    <row r="1348">
+      <c r="A1348" t="inlineStr">
+        <is>
+          <t>26,May</t>
+        </is>
+      </c>
+      <c r="B1348" t="inlineStr">
+        <is>
+          <t>Mayank Kumar</t>
+        </is>
+      </c>
+      <c r="C1348" t="inlineStr">
+        <is>
+          <t>Sanyog Kumar</t>
+        </is>
+      </c>
+      <c r="D1348" t="inlineStr">
+        <is>
+          <t>KALAVATI KUMARI</t>
+        </is>
+      </c>
+      <c r="E1348" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="F1348" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="1349">
+      <c r="A1349" t="inlineStr">
+        <is>
+          <t>26,May</t>
+        </is>
+      </c>
+      <c r="B1349" t="inlineStr">
+        <is>
+          <t>Ankush Kumar</t>
+        </is>
+      </c>
+      <c r="C1349" t="inlineStr">
+        <is>
+          <t>Niraj Kumar</t>
+        </is>
+      </c>
+      <c r="D1349" t="inlineStr">
+        <is>
+          <t>Nilam Sharma</t>
+        </is>
+      </c>
+      <c r="E1349" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F1349" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="1350">
+      <c r="A1350" t="inlineStr">
+        <is>
+          <t>26,May</t>
+        </is>
+      </c>
+      <c r="B1350" t="inlineStr">
+        <is>
+          <t>HARSHIKA VATS</t>
+        </is>
+      </c>
+      <c r="C1350" t="inlineStr">
+        <is>
+          <t>RAHUL KUMAR</t>
+        </is>
+      </c>
+      <c r="D1350" t="inlineStr">
+        <is>
+          <t>ARUNDHATEE</t>
+        </is>
+      </c>
+      <c r="E1350" t="inlineStr">
+        <is>
+          <t>LKG</t>
+        </is>
+      </c>
+      <c r="F1350" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="1351">
+      <c r="A1351" t="inlineStr">
+        <is>
+          <t>26,May</t>
+        </is>
+      </c>
+      <c r="B1351" t="inlineStr">
+        <is>
+          <t>Harsh Ranjan</t>
+        </is>
+      </c>
+      <c r="C1351" t="inlineStr">
+        <is>
+          <t>Brajesh Kumar</t>
+        </is>
+      </c>
+      <c r="D1351" t="inlineStr">
+        <is>
+          <t>Rekha Kumari</t>
+        </is>
+      </c>
+      <c r="E1351" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F1351" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="1352">
+      <c r="A1352" t="inlineStr">
+        <is>
+          <t>26,May</t>
+        </is>
+      </c>
+      <c r="B1352" t="inlineStr">
+        <is>
+          <t>Ananya Bhardwaj</t>
+        </is>
+      </c>
+      <c r="C1352" t="inlineStr">
+        <is>
+          <t>Rajeev Ranjan</t>
+        </is>
+      </c>
+      <c r="D1352" t="inlineStr">
+        <is>
+          <t>Khushbu Kumari</t>
+        </is>
+      </c>
+      <c r="E1352" t="inlineStr">
+        <is>
+          <t>VIII</t>
+        </is>
+      </c>
+      <c r="F1352" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="1353">
+      <c r="A1353" t="inlineStr">
+        <is>
+          <t>26,May</t>
+        </is>
+      </c>
+      <c r="B1353" t="inlineStr">
+        <is>
+          <t>Aditi Singh Payal</t>
+        </is>
+      </c>
+      <c r="C1353" t="inlineStr">
+        <is>
+          <t>Deepak Kumar</t>
+        </is>
+      </c>
+      <c r="D1353" t="inlineStr">
+        <is>
+          <t>Sadhana Kumari</t>
+        </is>
+      </c>
+      <c r="E1353" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F1353" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="1354">
+      <c r="A1354" t="inlineStr">
+        <is>
+          <t>26,May</t>
+        </is>
+      </c>
+      <c r="B1354" t="inlineStr">
+        <is>
+          <t>VAISHNAVI SHARMA</t>
+        </is>
+      </c>
+      <c r="C1354" t="inlineStr">
+        <is>
+          <t>VIKASH KUMAR AZAD</t>
+        </is>
+      </c>
+      <c r="D1354" t="inlineStr">
+        <is>
+          <t>SONAM KUMARI</t>
+        </is>
+      </c>
+      <c r="E1354" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F1354" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Birthday Data Master.xlsx
+++ b/Birthday Data Master.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1354"/>
+  <dimension ref="A1:F1356"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.6" customWidth="1" min="1" max="1"/>
@@ -43753,6 +43753,70 @@
         </is>
       </c>
     </row>
+    <row r="1355">
+      <c r="A1355" t="inlineStr">
+        <is>
+          <t>27,May</t>
+        </is>
+      </c>
+      <c r="B1355" t="inlineStr">
+        <is>
+          <t>KRISHNA MURTI</t>
+        </is>
+      </c>
+      <c r="C1355" t="inlineStr">
+        <is>
+          <t>SHIV MURTI</t>
+        </is>
+      </c>
+      <c r="D1355" t="inlineStr">
+        <is>
+          <t>SMITA VERMA</t>
+        </is>
+      </c>
+      <c r="E1355" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="F1355" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="1356">
+      <c r="A1356" t="inlineStr">
+        <is>
+          <t>27,May</t>
+        </is>
+      </c>
+      <c r="B1356" t="inlineStr">
+        <is>
+          <t>AKSHAT KUMAR</t>
+        </is>
+      </c>
+      <c r="C1356" t="inlineStr">
+        <is>
+          <t>SATYENDRA YADAV</t>
+        </is>
+      </c>
+      <c r="D1356" t="inlineStr">
+        <is>
+          <t>SANGITA KUMARI</t>
+        </is>
+      </c>
+      <c r="E1356" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="F1356" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Birthday Data Master.xlsx
+++ b/Birthday Data Master.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1356"/>
+  <dimension ref="A1:F1361"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.6" customWidth="1" min="1" max="1"/>
@@ -43817,6 +43817,166 @@
         </is>
       </c>
     </row>
+    <row r="1357">
+      <c r="A1357" t="inlineStr">
+        <is>
+          <t>28,May</t>
+        </is>
+      </c>
+      <c r="B1357" t="inlineStr">
+        <is>
+          <t>Satyam Sri Krishna</t>
+        </is>
+      </c>
+      <c r="C1357" t="inlineStr">
+        <is>
+          <t>Sanjay Kumar</t>
+        </is>
+      </c>
+      <c r="D1357" t="inlineStr">
+        <is>
+          <t>Roully Kumari</t>
+        </is>
+      </c>
+      <c r="E1357" t="inlineStr">
+        <is>
+          <t>VIII</t>
+        </is>
+      </c>
+      <c r="F1357" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="1358">
+      <c r="A1358" t="inlineStr">
+        <is>
+          <t>28,May</t>
+        </is>
+      </c>
+      <c r="B1358" t="inlineStr">
+        <is>
+          <t>PIYUSH KASHYAP</t>
+        </is>
+      </c>
+      <c r="C1358" t="inlineStr">
+        <is>
+          <t>ASHOK KUMAR</t>
+        </is>
+      </c>
+      <c r="D1358" t="inlineStr">
+        <is>
+          <t>MAMTA KUMARI</t>
+        </is>
+      </c>
+      <c r="E1358" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F1358" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="1359">
+      <c r="A1359" t="inlineStr">
+        <is>
+          <t>28,May</t>
+        </is>
+      </c>
+      <c r="B1359" t="inlineStr">
+        <is>
+          <t>SHIVAM KUMAR  SHARMA</t>
+        </is>
+      </c>
+      <c r="C1359" t="inlineStr">
+        <is>
+          <t>SHIV SHANKAR KUMAR</t>
+        </is>
+      </c>
+      <c r="D1359" t="inlineStr">
+        <is>
+          <t>GITA KUMARI</t>
+        </is>
+      </c>
+      <c r="E1359" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="F1359" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="1360">
+      <c r="A1360" t="inlineStr">
+        <is>
+          <t>28,May</t>
+        </is>
+      </c>
+      <c r="B1360" t="inlineStr">
+        <is>
+          <t>AMAN  RAJ</t>
+        </is>
+      </c>
+      <c r="C1360" t="inlineStr">
+        <is>
+          <t>RAJESH KUMAR</t>
+        </is>
+      </c>
+      <c r="D1360" t="inlineStr">
+        <is>
+          <t>PINKY KUMARI</t>
+        </is>
+      </c>
+      <c r="E1360" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="F1360" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="1361">
+      <c r="A1361" t="inlineStr">
+        <is>
+          <t>28,May</t>
+        </is>
+      </c>
+      <c r="B1361" t="inlineStr">
+        <is>
+          <t>PRINCE RAJ</t>
+        </is>
+      </c>
+      <c r="C1361" t="inlineStr">
+        <is>
+          <t>SAMDARSHI PRASAD RAUSHAN</t>
+        </is>
+      </c>
+      <c r="D1361" t="inlineStr">
+        <is>
+          <t>MIRA ROY</t>
+        </is>
+      </c>
+      <c r="E1361" t="inlineStr">
+        <is>
+          <t>IV</t>
+        </is>
+      </c>
+      <c r="F1361" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Birthday Data Master.xlsx
+++ b/Birthday Data Master.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1361"/>
+  <dimension ref="A1:F1363"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.6" customWidth="1" min="1" max="1"/>
@@ -43977,6 +43977,70 @@
         </is>
       </c>
     </row>
+    <row r="1362">
+      <c r="A1362" t="inlineStr">
+        <is>
+          <t>29,May</t>
+        </is>
+      </c>
+      <c r="B1362" t="inlineStr">
+        <is>
+          <t>ANANYA SHARMA</t>
+        </is>
+      </c>
+      <c r="C1362" t="inlineStr">
+        <is>
+          <t>GIRIJESH KUMAR</t>
+        </is>
+      </c>
+      <c r="D1362" t="inlineStr">
+        <is>
+          <t>NEETU RANI</t>
+        </is>
+      </c>
+      <c r="E1362" t="inlineStr">
+        <is>
+          <t>IV</t>
+        </is>
+      </c>
+      <c r="F1362" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="1363">
+      <c r="A1363" t="inlineStr">
+        <is>
+          <t>29,May</t>
+        </is>
+      </c>
+      <c r="B1363" t="inlineStr">
+        <is>
+          <t>MD ATIF AHSHAN</t>
+        </is>
+      </c>
+      <c r="C1363" t="inlineStr">
+        <is>
+          <t>AHSHAN ALAM</t>
+        </is>
+      </c>
+      <c r="D1363" t="inlineStr">
+        <is>
+          <t>ASIYA PERWEEN</t>
+        </is>
+      </c>
+      <c r="E1363" t="inlineStr">
+        <is>
+          <t>LKG</t>
+        </is>
+      </c>
+      <c r="F1363" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Birthday Data Master.xlsx
+++ b/Birthday Data Master.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1363"/>
+  <dimension ref="A1:F1370"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.6" customWidth="1" min="1" max="1"/>
@@ -44041,6 +44041,230 @@
         </is>
       </c>
     </row>
+    <row r="1364">
+      <c r="A1364" t="inlineStr">
+        <is>
+          <t>30,May</t>
+        </is>
+      </c>
+      <c r="B1364" t="inlineStr">
+        <is>
+          <t>ABHINAV RAJ</t>
+        </is>
+      </c>
+      <c r="C1364" t="inlineStr">
+        <is>
+          <t>DINA NATH PRASAD</t>
+        </is>
+      </c>
+      <c r="D1364" t="inlineStr">
+        <is>
+          <t>BABITA RANI</t>
+        </is>
+      </c>
+      <c r="E1364" t="inlineStr">
+        <is>
+          <t>IV</t>
+        </is>
+      </c>
+      <c r="F1364" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="1365">
+      <c r="A1365" t="inlineStr">
+        <is>
+          <t>30,May</t>
+        </is>
+      </c>
+      <c r="B1365" t="inlineStr">
+        <is>
+          <t>DIVYA  KUMARI</t>
+        </is>
+      </c>
+      <c r="C1365" t="inlineStr">
+        <is>
+          <t>CHANDAN KUMAR</t>
+        </is>
+      </c>
+      <c r="D1365" t="inlineStr">
+        <is>
+          <t>MADHU KUMARI</t>
+        </is>
+      </c>
+      <c r="E1365" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="F1365" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="1366">
+      <c r="A1366" t="inlineStr">
+        <is>
+          <t>30,May</t>
+        </is>
+      </c>
+      <c r="B1366" t="inlineStr">
+        <is>
+          <t>SRISTI KUMARI</t>
+        </is>
+      </c>
+      <c r="C1366" t="inlineStr">
+        <is>
+          <t>SANTOSH KUMAR</t>
+        </is>
+      </c>
+      <c r="D1366" t="inlineStr">
+        <is>
+          <t>ANSHU KUMARI</t>
+        </is>
+      </c>
+      <c r="E1366" t="inlineStr">
+        <is>
+          <t>IV</t>
+        </is>
+      </c>
+      <c r="F1366" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="1367">
+      <c r="A1367" t="inlineStr">
+        <is>
+          <t>30,May</t>
+        </is>
+      </c>
+      <c r="B1367" t="inlineStr">
+        <is>
+          <t>ANJALI KUMARI</t>
+        </is>
+      </c>
+      <c r="C1367" t="inlineStr">
+        <is>
+          <t>OM PRAKASH KUMAR</t>
+        </is>
+      </c>
+      <c r="D1367" t="inlineStr">
+        <is>
+          <t>RINKU DEVI</t>
+        </is>
+      </c>
+      <c r="E1367" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="F1367" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="1368">
+      <c r="A1368" t="inlineStr">
+        <is>
+          <t>30,May</t>
+        </is>
+      </c>
+      <c r="B1368" t="inlineStr">
+        <is>
+          <t>DIKSHA KUMARI</t>
+        </is>
+      </c>
+      <c r="C1368" t="inlineStr">
+        <is>
+          <t>JAY PRAKASH</t>
+        </is>
+      </c>
+      <c r="D1368" t="inlineStr">
+        <is>
+          <t>PRITI KUMARI</t>
+        </is>
+      </c>
+      <c r="E1368" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="F1368" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="1369">
+      <c r="A1369" t="inlineStr">
+        <is>
+          <t>30,May</t>
+        </is>
+      </c>
+      <c r="B1369" t="inlineStr">
+        <is>
+          <t>Amrisha Kumari</t>
+        </is>
+      </c>
+      <c r="C1369" t="inlineStr">
+        <is>
+          <t>Arvind Kumar</t>
+        </is>
+      </c>
+      <c r="D1369" t="inlineStr">
+        <is>
+          <t>Durgesh Kumari</t>
+        </is>
+      </c>
+      <c r="E1369" t="inlineStr">
+        <is>
+          <t>IX</t>
+        </is>
+      </c>
+      <c r="F1369" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="1370">
+      <c r="A1370" t="inlineStr">
+        <is>
+          <t>30,May</t>
+        </is>
+      </c>
+      <c r="B1370" t="inlineStr">
+        <is>
+          <t>ASHISH KUMAR</t>
+        </is>
+      </c>
+      <c r="C1370" t="inlineStr">
+        <is>
+          <t>CHANDAN KUMAR</t>
+        </is>
+      </c>
+      <c r="D1370" t="inlineStr">
+        <is>
+          <t>MADHU KUMARI</t>
+        </is>
+      </c>
+      <c r="E1370" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="F1370" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Birthday Data Master.xlsx
+++ b/Birthday Data Master.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1370"/>
+  <dimension ref="A1:F1374"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.6" customWidth="1" min="1" max="1"/>
@@ -44265,6 +44265,134 @@
         </is>
       </c>
     </row>
+    <row r="1371">
+      <c r="A1371" t="inlineStr">
+        <is>
+          <t>31,May</t>
+        </is>
+      </c>
+      <c r="B1371" t="inlineStr">
+        <is>
+          <t>Kumari Narayani</t>
+        </is>
+      </c>
+      <c r="C1371" t="inlineStr">
+        <is>
+          <t>Pankaj Kumar</t>
+        </is>
+      </c>
+      <c r="D1371" t="inlineStr">
+        <is>
+          <t>Nitu Kumari</t>
+        </is>
+      </c>
+      <c r="E1371" t="inlineStr">
+        <is>
+          <t>IX</t>
+        </is>
+      </c>
+      <c r="F1371" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="1372">
+      <c r="A1372" t="inlineStr">
+        <is>
+          <t>31,May</t>
+        </is>
+      </c>
+      <c r="B1372" t="inlineStr">
+        <is>
+          <t>AFEEFA  ARFIN</t>
+        </is>
+      </c>
+      <c r="C1372" t="inlineStr">
+        <is>
+          <t>MD SHAMSHUL ARFIN</t>
+        </is>
+      </c>
+      <c r="D1372" t="inlineStr">
+        <is>
+          <t>AKTARI KHATUN</t>
+        </is>
+      </c>
+      <c r="E1372" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="F1372" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="1373">
+      <c r="A1373" t="inlineStr">
+        <is>
+          <t>31,May</t>
+        </is>
+      </c>
+      <c r="B1373" t="inlineStr">
+        <is>
+          <t>SONAKSHI VERMA</t>
+        </is>
+      </c>
+      <c r="C1373" t="inlineStr">
+        <is>
+          <t>HIMANSHU VERMA</t>
+        </is>
+      </c>
+      <c r="D1373" t="inlineStr">
+        <is>
+          <t>SONI VERMA</t>
+        </is>
+      </c>
+      <c r="E1373" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="F1373" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="1374">
+      <c r="A1374" t="inlineStr">
+        <is>
+          <t>31,May</t>
+        </is>
+      </c>
+      <c r="B1374" t="inlineStr">
+        <is>
+          <t>Mukesh Kumar</t>
+        </is>
+      </c>
+      <c r="C1374" t="inlineStr">
+        <is>
+          <t>Munna Kumar</t>
+        </is>
+      </c>
+      <c r="D1374" t="inlineStr">
+        <is>
+          <t>Kiran Devi</t>
+        </is>
+      </c>
+      <c r="E1374" t="inlineStr">
+        <is>
+          <t>VIII</t>
+        </is>
+      </c>
+      <c r="F1374" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Birthday Data Master.xlsx
+++ b/Birthday Data Master.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3188"/>
+  <dimension ref="A1:F3194"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.6" customWidth="1" min="1" max="1"/>
@@ -102441,6 +102441,198 @@
         </is>
       </c>
     </row>
+    <row r="3189">
+      <c r="A3189" t="inlineStr">
+        <is>
+          <t>12,Jun</t>
+        </is>
+      </c>
+      <c r="B3189" t="inlineStr">
+        <is>
+          <t>BAL KRISHNA MURARI</t>
+        </is>
+      </c>
+      <c r="C3189" t="inlineStr">
+        <is>
+          <t>CHANDAN KUMAR</t>
+        </is>
+      </c>
+      <c r="D3189" t="inlineStr">
+        <is>
+          <t>BEAUTY KUMARI</t>
+        </is>
+      </c>
+      <c r="E3189" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="F3189" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="3190">
+      <c r="A3190" t="inlineStr">
+        <is>
+          <t>12,Jun</t>
+        </is>
+      </c>
+      <c r="B3190" t="inlineStr">
+        <is>
+          <t>ANSH ANAND</t>
+        </is>
+      </c>
+      <c r="C3190" t="inlineStr">
+        <is>
+          <t>PINTU KUMAR</t>
+        </is>
+      </c>
+      <c r="D3190" t="inlineStr">
+        <is>
+          <t>MAMTA KUMARI</t>
+        </is>
+      </c>
+      <c r="E3190" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="F3190" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="3191">
+      <c r="A3191" t="inlineStr">
+        <is>
+          <t>12,Jun</t>
+        </is>
+      </c>
+      <c r="B3191" t="inlineStr">
+        <is>
+          <t>RITIKA SINGH</t>
+        </is>
+      </c>
+      <c r="C3191" t="inlineStr">
+        <is>
+          <t>PRAMOD KUMAR</t>
+        </is>
+      </c>
+      <c r="D3191" t="inlineStr">
+        <is>
+          <t>RAKHI SINGH</t>
+        </is>
+      </c>
+      <c r="E3191" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="F3191" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="3192">
+      <c r="A3192" t="inlineStr">
+        <is>
+          <t>12,Jun</t>
+        </is>
+      </c>
+      <c r="B3192" t="inlineStr">
+        <is>
+          <t>Ritik Raj</t>
+        </is>
+      </c>
+      <c r="C3192" t="inlineStr">
+        <is>
+          <t>RajNarayan Sharma</t>
+        </is>
+      </c>
+      <c r="D3192" t="inlineStr">
+        <is>
+          <t>Priyanka Kumari</t>
+        </is>
+      </c>
+      <c r="E3192" t="inlineStr">
+        <is>
+          <t>VIII</t>
+        </is>
+      </c>
+      <c r="F3192" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="3193">
+      <c r="A3193" t="inlineStr">
+        <is>
+          <t>12,Jun</t>
+        </is>
+      </c>
+      <c r="B3193" t="inlineStr">
+        <is>
+          <t>SAKSHI BHARTI</t>
+        </is>
+      </c>
+      <c r="C3193" t="inlineStr">
+        <is>
+          <t>PREM PRAKASH KUMAR</t>
+        </is>
+      </c>
+      <c r="D3193" t="inlineStr">
+        <is>
+          <t>DIVYA BHARTI</t>
+        </is>
+      </c>
+      <c r="E3193" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="F3193" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="3194">
+      <c r="A3194" t="inlineStr">
+        <is>
+          <t>12,Jun</t>
+        </is>
+      </c>
+      <c r="B3194" t="inlineStr">
+        <is>
+          <t>SHITAL KUMARI</t>
+        </is>
+      </c>
+      <c r="C3194" t="inlineStr">
+        <is>
+          <t>VIKRAM SHARAN SINGH</t>
+        </is>
+      </c>
+      <c r="D3194" t="inlineStr">
+        <is>
+          <t>MUNNI DEVI</t>
+        </is>
+      </c>
+      <c r="E3194" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F3194" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Birthday Data Master.xlsx
+++ b/Birthday Data Master.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3194"/>
+  <dimension ref="A1:F3198"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.6" customWidth="1" min="1" max="1"/>
@@ -102633,6 +102633,134 @@
         </is>
       </c>
     </row>
+    <row r="3195">
+      <c r="A3195" t="inlineStr">
+        <is>
+          <t>27,Jun</t>
+        </is>
+      </c>
+      <c r="B3195" t="inlineStr">
+        <is>
+          <t>ANURAG TIWARI</t>
+        </is>
+      </c>
+      <c r="C3195" t="inlineStr">
+        <is>
+          <t>MANOJ KUMAR TIWARY</t>
+        </is>
+      </c>
+      <c r="D3195" t="inlineStr">
+        <is>
+          <t>POONAM TIWARY</t>
+        </is>
+      </c>
+      <c r="E3195" t="inlineStr">
+        <is>
+          <t>VIII</t>
+        </is>
+      </c>
+      <c r="F3195" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="3196">
+      <c r="A3196" t="inlineStr">
+        <is>
+          <t>27,Jun</t>
+        </is>
+      </c>
+      <c r="B3196" t="inlineStr">
+        <is>
+          <t>ANMOLA SINHA</t>
+        </is>
+      </c>
+      <c r="C3196" t="inlineStr">
+        <is>
+          <t>AMIT KUMAR</t>
+        </is>
+      </c>
+      <c r="D3196" t="inlineStr">
+        <is>
+          <t>PUSHPA KUMARI</t>
+        </is>
+      </c>
+      <c r="E3196" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F3196" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="3197">
+      <c r="A3197" t="inlineStr">
+        <is>
+          <t>27,Jun</t>
+        </is>
+      </c>
+      <c r="B3197" t="inlineStr">
+        <is>
+          <t>Riya  Kumari</t>
+        </is>
+      </c>
+      <c r="C3197" t="inlineStr">
+        <is>
+          <t>Hareram Kumar</t>
+        </is>
+      </c>
+      <c r="D3197" t="inlineStr">
+        <is>
+          <t>Ragani Devi</t>
+        </is>
+      </c>
+      <c r="E3197" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F3197" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="3198">
+      <c r="A3198" t="inlineStr">
+        <is>
+          <t>27,Jun</t>
+        </is>
+      </c>
+      <c r="B3198" t="inlineStr">
+        <is>
+          <t>HARIOM KASHYAP</t>
+        </is>
+      </c>
+      <c r="C3198" t="inlineStr">
+        <is>
+          <t>GOUTAM KUMAR</t>
+        </is>
+      </c>
+      <c r="D3198" t="inlineStr">
+        <is>
+          <t>CHANDANI KUMARI</t>
+        </is>
+      </c>
+      <c r="E3198" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="F3198" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Birthday Data Master.xlsx
+++ b/Birthday Data Master.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3198"/>
+  <dimension ref="A1:F3204"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.6" customWidth="1" min="1" max="1"/>
@@ -102761,6 +102761,198 @@
         </is>
       </c>
     </row>
+    <row r="3199">
+      <c r="A3199" t="inlineStr">
+        <is>
+          <t>03,Jul</t>
+        </is>
+      </c>
+      <c r="B3199" t="inlineStr">
+        <is>
+          <t>HARSH  RAJ</t>
+        </is>
+      </c>
+      <c r="C3199" t="inlineStr">
+        <is>
+          <t>VIJAY KUMAR</t>
+        </is>
+      </c>
+      <c r="D3199" t="inlineStr">
+        <is>
+          <t>POONAM DEVI</t>
+        </is>
+      </c>
+      <c r="E3199" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="F3199" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="3200">
+      <c r="A3200" t="inlineStr">
+        <is>
+          <t>03,Jul</t>
+        </is>
+      </c>
+      <c r="B3200" t="inlineStr">
+        <is>
+          <t>ARNAV DEV</t>
+        </is>
+      </c>
+      <c r="C3200" t="inlineStr">
+        <is>
+          <t>SATISH KUMAR</t>
+        </is>
+      </c>
+      <c r="D3200" t="inlineStr">
+        <is>
+          <t>SUNITA KUMARI</t>
+        </is>
+      </c>
+      <c r="E3200" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="F3200" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="3201">
+      <c r="A3201" t="inlineStr">
+        <is>
+          <t>03,Jul</t>
+        </is>
+      </c>
+      <c r="B3201" t="inlineStr">
+        <is>
+          <t>Piyush  Raj</t>
+        </is>
+      </c>
+      <c r="C3201" t="inlineStr">
+        <is>
+          <t>Ramesh Kumar Singh</t>
+        </is>
+      </c>
+      <c r="D3201" t="inlineStr">
+        <is>
+          <t>Ruby</t>
+        </is>
+      </c>
+      <c r="E3201" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F3201" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="3202">
+      <c r="A3202" t="inlineStr">
+        <is>
+          <t>03,Jul</t>
+        </is>
+      </c>
+      <c r="B3202" t="inlineStr">
+        <is>
+          <t>Ragani Kumari</t>
+        </is>
+      </c>
+      <c r="C3202" t="inlineStr">
+        <is>
+          <t>Ranjeet Kumar Das</t>
+        </is>
+      </c>
+      <c r="D3202" t="inlineStr">
+        <is>
+          <t>Rekha Kumari</t>
+        </is>
+      </c>
+      <c r="E3202" t="inlineStr">
+        <is>
+          <t>VIII</t>
+        </is>
+      </c>
+      <c r="F3202" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="3203">
+      <c r="A3203" t="inlineStr">
+        <is>
+          <t>03,Jul</t>
+        </is>
+      </c>
+      <c r="B3203" t="inlineStr">
+        <is>
+          <t>KAUSTUBH RANJAN</t>
+        </is>
+      </c>
+      <c r="C3203" t="inlineStr">
+        <is>
+          <t>Rahul Kumar</t>
+        </is>
+      </c>
+      <c r="D3203" t="inlineStr">
+        <is>
+          <t>Pinki Kumari</t>
+        </is>
+      </c>
+      <c r="E3203" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="F3203" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="3204">
+      <c r="A3204" t="inlineStr">
+        <is>
+          <t>03,Jul</t>
+        </is>
+      </c>
+      <c r="B3204" t="inlineStr">
+        <is>
+          <t>HARSH   KUMAR</t>
+        </is>
+      </c>
+      <c r="C3204" t="inlineStr">
+        <is>
+          <t>HRITIK KUMAR</t>
+        </is>
+      </c>
+      <c r="D3204" t="inlineStr">
+        <is>
+          <t>SANGEETA KUMARI</t>
+        </is>
+      </c>
+      <c r="E3204" t="inlineStr">
+        <is>
+          <t>VII</t>
+        </is>
+      </c>
+      <c r="F3204" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
